--- a/Excel/StockQuotation (1).xlsx
+++ b/Excel/StockQuotation (1).xlsx
@@ -402,7 +402,7 @@
         <v/>
       </c>
       <c r="C1" t="str">
-        <v>01/02/23 15:05:58</v>
+        <v>03/02/23 12:58:01</v>
       </c>
     </row>
     <row r="4">
@@ -426,34 +426,34 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>1115.67</v>
+        <v>1122.23</v>
       </c>
       <c r="B7" t="str">
-        <v>5.98 (0.5388%)</v>
+        <v>3.74 (0.3343%)</v>
       </c>
       <c r="C7" t="str">
         <v>High</v>
       </c>
       <c r="D7">
-        <v>1116.14</v>
+        <v>1122.53</v>
       </c>
       <c r="E7" t="str">
         <v>Low</v>
       </c>
       <c r="F7">
-        <v>1110.55</v>
+        <v>1116.72</v>
       </c>
       <c r="G7" t="str">
         <v>Volume</v>
       </c>
       <c r="H7">
-        <v>546430760</v>
+        <v>490087396</v>
       </c>
       <c r="I7" t="str">
         <v>Value</v>
       </c>
       <c r="J7">
-        <v>2437734566.46</v>
+        <v>2220977033.24</v>
       </c>
     </row>
     <row r="9">
@@ -514,22 +514,22 @@
         <v>-</v>
       </c>
       <c r="C10">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>1.2820512820512822</v>
       </c>
       <c r="F10">
         <v>0.78</v>
       </c>
       <c r="G10">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H10">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -538,13 +538,13 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>15058316</v>
+        <v>3678888</v>
       </c>
       <c r="L10">
-        <v>11834.825929999999</v>
+        <v>2899.81239</v>
       </c>
       <c r="M10">
-        <v>638800</v>
+        <v>3582100</v>
       </c>
       <c r="N10">
         <v>0.78</v>
@@ -553,7 +553,7 @@
         <v>0.79</v>
       </c>
       <c r="P10">
-        <v>1626300</v>
+        <v>1211600</v>
       </c>
     </row>
     <row r="11">
@@ -567,43 +567,43 @@
         <v>3.68</v>
       </c>
       <c r="D11">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>1.6574585635359116</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="G11">
+        <v>3.72</v>
+      </c>
+      <c r="H11">
+        <v>3.68</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>1075196</v>
+      </c>
+      <c r="L11">
+        <v>3970.9574</v>
+      </c>
+      <c r="M11">
+        <v>276900</v>
+      </c>
+      <c r="N11">
+        <v>3.68</v>
+      </c>
+      <c r="O11">
         <v>3.7</v>
       </c>
-      <c r="H11">
-        <v>3.6</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>3341113</v>
-      </c>
-      <c r="L11">
-        <v>12187.60834</v>
-      </c>
-      <c r="M11">
-        <v>404000</v>
-      </c>
-      <c r="N11">
-        <v>3.66</v>
-      </c>
-      <c r="O11">
-        <v>3.68</v>
-      </c>
       <c r="P11">
-        <v>48700</v>
+        <v>289900</v>
       </c>
     </row>
     <row r="12">
@@ -614,22 +614,22 @@
         <v>-</v>
       </c>
       <c r="C12">
-        <v>33.25</v>
+        <v>32.25</v>
       </c>
       <c r="D12">
-        <v>0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="E12">
-        <v>0.7575757575757576</v>
+        <v>-1.5267175572519085</v>
       </c>
       <c r="F12">
-        <v>33</v>
+        <v>32.75</v>
       </c>
       <c r="G12">
-        <v>33.5</v>
+        <v>32.75</v>
       </c>
       <c r="H12">
-        <v>32.75</v>
+        <v>32</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -638,22 +638,22 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>900965</v>
+        <v>1366962</v>
       </c>
       <c r="L12">
-        <v>29859.18075</v>
+        <v>44180.37375</v>
       </c>
       <c r="M12">
-        <v>167500</v>
+        <v>147200</v>
       </c>
       <c r="N12">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O12">
-        <v>33.25</v>
+        <v>32.25</v>
       </c>
       <c r="P12">
-        <v>175900</v>
+        <v>66200</v>
       </c>
     </row>
     <row r="13">
@@ -664,13 +664,13 @@
         <v>-</v>
       </c>
       <c r="C13">
-        <v>6.7</v>
+        <v>6.65</v>
       </c>
       <c r="D13">
         <v>0.05</v>
       </c>
       <c r="E13">
-        <v>0.7518796992481203</v>
+        <v>0.7575757575757576</v>
       </c>
       <c r="F13">
         <v>6.65</v>
@@ -679,7 +679,7 @@
         <v>6.7</v>
       </c>
       <c r="H13">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -688,22 +688,22 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>297110</v>
+        <v>57744</v>
       </c>
       <c r="L13">
-        <v>1974.5675</v>
+        <v>384.3511</v>
       </c>
       <c r="M13">
-        <v>135400</v>
+        <v>56700</v>
       </c>
       <c r="N13">
+        <v>6.6</v>
+      </c>
+      <c r="O13">
         <v>6.65</v>
       </c>
-      <c r="O13">
-        <v>6.7</v>
-      </c>
       <c r="P13">
-        <v>142400</v>
+        <v>30400</v>
       </c>
     </row>
     <row r="14">
@@ -714,23 +714,23 @@
         <v>-</v>
       </c>
       <c r="C14">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="D14">
         <v>0.02</v>
       </c>
       <c r="E14">
-        <v>0.7194244604316546</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="F14">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="G14">
+        <v>2.86</v>
+      </c>
+      <c r="H14">
         <v>2.82</v>
       </c>
-      <c r="H14">
-        <v>2.78</v>
-      </c>
       <c r="I14">
         <v>0</v>
       </c>
@@ -738,22 +738,22 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>786865</v>
+        <v>350971</v>
       </c>
       <c r="L14">
-        <v>2205.18514</v>
+        <v>995.6371</v>
       </c>
       <c r="M14">
-        <v>354800</v>
+        <v>162500</v>
       </c>
       <c r="N14">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="O14">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="P14">
-        <v>84700</v>
+        <v>64900</v>
       </c>
     </row>
     <row r="15">
@@ -764,46 +764,46 @@
         <v>-</v>
       </c>
       <c r="C15">
+        <v>6.8</v>
+      </c>
+      <c r="D15">
+        <v>0.15</v>
+      </c>
+      <c r="E15">
+        <v>2.255639097744361</v>
+      </c>
+      <c r="F15">
         <v>6.7</v>
       </c>
-      <c r="D15">
-        <v>-0.05</v>
-      </c>
-      <c r="E15">
-        <v>-0.7407407407407407</v>
-      </c>
-      <c r="F15">
+      <c r="G15">
+        <v>6.85</v>
+      </c>
+      <c r="H15">
+        <v>6.65</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>3994938</v>
+      </c>
+      <c r="L15">
+        <v>26984.162399999997</v>
+      </c>
+      <c r="M15">
+        <v>30300</v>
+      </c>
+      <c r="N15">
         <v>6.75</v>
       </c>
-      <c r="G15">
+      <c r="O15">
         <v>6.8</v>
       </c>
-      <c r="H15">
-        <v>6.7</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>1242712</v>
-      </c>
-      <c r="L15">
-        <v>8366.616</v>
-      </c>
-      <c r="M15">
-        <v>84000</v>
-      </c>
-      <c r="N15">
-        <v>6.7</v>
-      </c>
-      <c r="O15">
-        <v>6.75</v>
-      </c>
       <c r="P15">
-        <v>708900</v>
+        <v>851100</v>
       </c>
     </row>
     <row r="16">
@@ -814,46 +814,46 @@
         <v>-</v>
       </c>
       <c r="C16">
+        <v>12.9</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
         <v>12.8</v>
       </c>
-      <c r="D16">
-        <v>-0.1</v>
-      </c>
-      <c r="E16">
-        <v>-0.7751937984496124</v>
-      </c>
-      <c r="F16">
+      <c r="G16">
+        <v>13</v>
+      </c>
+      <c r="H16">
+        <v>12.8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>83924</v>
+      </c>
+      <c r="L16">
+        <v>1082.9692</v>
+      </c>
+      <c r="M16">
+        <v>46400</v>
+      </c>
+      <c r="N16">
         <v>12.9</v>
-      </c>
-      <c r="G16">
-        <v>13.1</v>
-      </c>
-      <c r="H16">
-        <v>12.7</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>400480</v>
-      </c>
-      <c r="L16">
-        <v>5161.644</v>
-      </c>
-      <c r="M16">
-        <v>74800</v>
-      </c>
-      <c r="N16">
-        <v>12.8</v>
       </c>
       <c r="O16">
         <v>13</v>
       </c>
       <c r="P16">
-        <v>23200</v>
+        <v>64300</v>
       </c>
     </row>
     <row r="17">
@@ -864,22 +864,22 @@
         <v>-</v>
       </c>
       <c r="C17">
-        <v>3.88</v>
+        <v>4.08</v>
       </c>
       <c r="D17">
-        <v>0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="E17">
-        <v>2.1052631578947367</v>
+        <v>-0.4878048780487805</v>
       </c>
       <c r="F17">
-        <v>3.8</v>
+        <v>4.08</v>
       </c>
       <c r="G17">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="H17">
-        <v>3.78</v>
+        <v>4.02</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -888,22 +888,22 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>2935068</v>
+        <v>4076564</v>
       </c>
       <c r="L17">
-        <v>11312.446039999999</v>
+        <v>16551.82398</v>
       </c>
       <c r="M17">
-        <v>225400</v>
+        <v>276800</v>
       </c>
       <c r="N17">
-        <v>3.88</v>
+        <v>4.06</v>
       </c>
       <c r="O17">
-        <v>3.9</v>
+        <v>4.08</v>
       </c>
       <c r="P17">
-        <v>161800</v>
+        <v>279600</v>
       </c>
     </row>
     <row r="18">
@@ -914,23 +914,23 @@
         <v>-</v>
       </c>
       <c r="C18">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>-0.6944444444444444</v>
       </c>
       <c r="F18">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="G18">
+        <v>1.45</v>
+      </c>
+      <c r="H18">
         <v>1.43</v>
       </c>
-      <c r="H18">
-        <v>1.41</v>
-      </c>
       <c r="I18">
         <v>0</v>
       </c>
@@ -938,22 +938,22 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>3900983</v>
+        <v>1723855</v>
       </c>
       <c r="L18">
-        <v>5539.24765</v>
+        <v>2472.2457000000004</v>
       </c>
       <c r="M18">
-        <v>265000</v>
+        <v>594700</v>
       </c>
       <c r="N18">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="O18">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P18">
-        <v>444400</v>
+        <v>288900</v>
       </c>
     </row>
     <row r="19">
@@ -967,19 +967,19 @@
         <v>4.76</v>
       </c>
       <c r="D19">
-        <v>-0.12</v>
+        <v>-0.06</v>
       </c>
       <c r="E19">
-        <v>-2.459016393442623</v>
+        <v>-1.2448132780082988</v>
       </c>
       <c r="F19">
-        <v>4.84</v>
+        <v>4.86</v>
       </c>
       <c r="G19">
-        <v>4.84</v>
+        <v>4.86</v>
       </c>
       <c r="H19">
-        <v>4.74</v>
+        <v>4.76</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -988,22 +988,22 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>35600</v>
+        <v>6300</v>
       </c>
       <c r="L19">
-        <v>169.378</v>
+        <v>29.998</v>
       </c>
       <c r="M19">
-        <v>17000</v>
+        <v>5700</v>
       </c>
       <c r="N19">
         <v>4.76</v>
       </c>
       <c r="O19">
-        <v>4.82</v>
+        <v>4.8</v>
       </c>
       <c r="P19">
-        <v>4500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="20">
@@ -1017,16 +1017,16 @@
         <v>5</v>
       </c>
       <c r="D20">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>0.40160642570281124</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <v>5</v>
       </c>
       <c r="G20">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="H20">
         <v>4.98</v>
@@ -1038,22 +1038,22 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>155862</v>
+        <v>76900</v>
       </c>
       <c r="L20">
-        <v>779.305</v>
+        <v>384.41</v>
       </c>
       <c r="M20">
-        <v>97200</v>
+        <v>170000</v>
       </c>
       <c r="N20">
         <v>4.98</v>
       </c>
       <c r="O20">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="P20">
-        <v>175400</v>
+        <v>103800</v>
       </c>
     </row>
     <row r="21">
@@ -1064,19 +1064,19 @@
         <v>-</v>
       </c>
       <c r="C21">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>-1.4705882352941178</v>
       </c>
       <c r="F21">
         <v>0.68</v>
       </c>
       <c r="G21">
-        <v>0.69</v>
+        <v>0.68</v>
       </c>
       <c r="H21">
         <v>0.67</v>
@@ -1088,13 +1088,13 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>7055416</v>
+        <v>853235</v>
       </c>
       <c r="L21">
-        <v>4795.81906</v>
+        <v>573.3058000000001</v>
       </c>
       <c r="M21">
-        <v>24123000</v>
+        <v>19075700</v>
       </c>
       <c r="N21">
         <v>0.67</v>
@@ -1103,7 +1103,7 @@
         <v>0.68</v>
       </c>
       <c r="P21">
-        <v>5630800</v>
+        <v>5638000</v>
       </c>
     </row>
     <row r="22">
@@ -1114,22 +1114,22 @@
         <v>-</v>
       </c>
       <c r="C22">
-        <v>15.4</v>
+        <v>14.8</v>
       </c>
       <c r="D22">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>-3.75</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>15.9</v>
+        <v>14.7</v>
       </c>
       <c r="G22">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H22">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1138,22 +1138,22 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>5725503</v>
+        <v>914439</v>
       </c>
       <c r="L22">
-        <v>87699.7481</v>
+        <v>13538.7161</v>
       </c>
       <c r="M22">
-        <v>61900</v>
+        <v>115200</v>
       </c>
       <c r="N22">
-        <v>15.4</v>
+        <v>14.8</v>
       </c>
       <c r="O22">
-        <v>15.5</v>
+        <v>14.9</v>
       </c>
       <c r="P22">
-        <v>103900</v>
+        <v>85200</v>
       </c>
     </row>
     <row r="23">
@@ -1164,46 +1164,46 @@
         <v>-</v>
       </c>
       <c r="C23">
+        <v>13.7</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>13.7</v>
+      </c>
+      <c r="G23">
+        <v>13.8</v>
+      </c>
+      <c r="H23">
         <v>13.6</v>
       </c>
-      <c r="D23">
-        <v>0.1</v>
-      </c>
-      <c r="E23">
-        <v>0.7407407407407407</v>
-      </c>
-      <c r="F23">
-        <v>13.5</v>
-      </c>
-      <c r="G23">
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>246028</v>
+      </c>
+      <c r="L23">
+        <v>3372.5074</v>
+      </c>
+      <c r="M23">
+        <v>81400</v>
+      </c>
+      <c r="N23">
         <v>13.7</v>
       </c>
-      <c r="H23">
-        <v>13.4</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>817565</v>
-      </c>
-      <c r="L23">
-        <v>11064.475199999999</v>
-      </c>
-      <c r="M23">
-        <v>88500</v>
-      </c>
-      <c r="N23">
-        <v>13.6</v>
-      </c>
       <c r="O23">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="P23">
-        <v>106600</v>
+        <v>129000</v>
       </c>
     </row>
     <row r="24">
@@ -1214,23 +1214,23 @@
         <v>-</v>
       </c>
       <c r="C24">
+        <v>3.14</v>
+      </c>
+      <c r="D24">
+        <v>-0.02</v>
+      </c>
+      <c r="E24">
+        <v>-0.6329113924050633</v>
+      </c>
+      <c r="F24">
         <v>3.16</v>
       </c>
-      <c r="D24">
-        <v>0.08</v>
-      </c>
-      <c r="E24">
-        <v>2.5974025974025974</v>
-      </c>
-      <c r="F24">
+      <c r="G24">
+        <v>3.18</v>
+      </c>
+      <c r="H24">
         <v>3.1</v>
       </c>
-      <c r="G24">
-        <v>3.16</v>
-      </c>
-      <c r="H24">
-        <v>3.08</v>
-      </c>
       <c r="I24">
         <v>0</v>
       </c>
@@ -1238,22 +1238,22 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>14206518</v>
+        <v>2390375</v>
       </c>
       <c r="L24">
-        <v>44551.94612</v>
+        <v>7494.31042</v>
       </c>
       <c r="M24">
-        <v>579600</v>
+        <v>369100</v>
       </c>
       <c r="N24">
+        <v>3.12</v>
+      </c>
+      <c r="O24">
         <v>3.14</v>
       </c>
-      <c r="O24">
-        <v>3.16</v>
-      </c>
       <c r="P24">
-        <v>1886700</v>
+        <v>414100</v>
       </c>
     </row>
     <row r="25">
@@ -1264,22 +1264,22 @@
         <v>-</v>
       </c>
       <c r="C25">
-        <v>8.05</v>
+        <v>8.6</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>2.9940119760479043</v>
       </c>
       <c r="F25">
-        <v>8.1</v>
+        <v>8.65</v>
       </c>
       <c r="G25">
-        <v>8.1</v>
+        <v>8.75</v>
       </c>
       <c r="H25">
-        <v>8</v>
+        <v>8.55</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1288,22 +1288,22 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>1343488</v>
+        <v>8392365</v>
       </c>
       <c r="L25">
-        <v>10781.624</v>
+        <v>72569.17629999999</v>
       </c>
       <c r="M25">
-        <v>49300</v>
+        <v>323100</v>
       </c>
       <c r="N25">
-        <v>8.05</v>
+        <v>8.55</v>
       </c>
       <c r="O25">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="P25">
-        <v>196300</v>
+        <v>35500</v>
       </c>
     </row>
     <row r="26">
@@ -1317,19 +1317,19 @@
         <v>7</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>-0.7092198581560284</v>
       </c>
       <c r="F26">
-        <v>6.95</v>
+        <v>7.1</v>
       </c>
       <c r="G26">
-        <v>7.05</v>
+        <v>7.15</v>
       </c>
       <c r="H26">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1338,13 +1338,13 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>1724448</v>
+        <v>1101944</v>
       </c>
       <c r="L26">
-        <v>11963.0502</v>
+        <v>7777.92685</v>
       </c>
       <c r="M26">
-        <v>111000</v>
+        <v>207000</v>
       </c>
       <c r="N26">
         <v>6.95</v>
@@ -1353,7 +1353,7 @@
         <v>7</v>
       </c>
       <c r="P26">
-        <v>9900</v>
+        <v>89100</v>
       </c>
     </row>
     <row r="27">
@@ -1364,13 +1364,13 @@
         <v>-</v>
       </c>
       <c r="C27">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="D27">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>0.6993006993006993</v>
+        <v>0</v>
       </c>
       <c r="F27">
         <v>1.43</v>
@@ -1388,13 +1388,13 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>8253411</v>
+        <v>4514300</v>
       </c>
       <c r="L27">
-        <v>11806.454740000001</v>
+        <v>6456.164</v>
       </c>
       <c r="M27">
-        <v>620900</v>
+        <v>231400</v>
       </c>
       <c r="N27">
         <v>1.43</v>
@@ -1403,7 +1403,7 @@
         <v>1.44</v>
       </c>
       <c r="P27">
-        <v>1812000</v>
+        <v>1088100</v>
       </c>
     </row>
     <row r="28">
@@ -1414,23 +1414,23 @@
         <v>-</v>
       </c>
       <c r="C28">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="D28">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>-0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="G28">
+        <v>14.1</v>
+      </c>
+      <c r="H28">
         <v>14</v>
       </c>
-      <c r="H28">
-        <v>13.8</v>
-      </c>
       <c r="I28">
         <v>0</v>
       </c>
@@ -1438,22 +1438,22 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>123201</v>
+        <v>174015</v>
       </c>
       <c r="L28">
-        <v>1704.6038</v>
+        <v>2441.75</v>
       </c>
       <c r="M28">
-        <v>9800</v>
+        <v>12500</v>
       </c>
       <c r="N28">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="O28">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="P28">
-        <v>38900</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="29">
@@ -1464,16 +1464,16 @@
         <v>-</v>
       </c>
       <c r="C29">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>0.9900990099009901</v>
       </c>
       <c r="F29">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="G29">
         <v>10.2</v>
@@ -1488,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>169832</v>
+        <v>56400</v>
       </c>
       <c r="L29">
-        <v>1716.4762</v>
+        <v>570.92</v>
       </c>
       <c r="M29">
-        <v>50100</v>
+        <v>216900</v>
       </c>
       <c r="N29">
         <v>10.1</v>
@@ -1503,7 +1503,7 @@
         <v>10.2</v>
       </c>
       <c r="P29">
-        <v>398600</v>
+        <v>340400</v>
       </c>
     </row>
     <row r="30">
@@ -1514,22 +1514,22 @@
         <v>-</v>
       </c>
       <c r="C30">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="D30">
         <v>0.1</v>
       </c>
       <c r="E30">
-        <v>0.8849557522123894</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="F30">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="G30">
         <v>11.4</v>
       </c>
       <c r="H30">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -1538,13 +1538,13 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>1203665</v>
+        <v>862709</v>
       </c>
       <c r="L30">
-        <v>13604.317</v>
+        <v>9721.9009</v>
       </c>
       <c r="M30">
-        <v>230500</v>
+        <v>96600</v>
       </c>
       <c r="N30">
         <v>11.3</v>
@@ -1553,7 +1553,7 @@
         <v>11.4</v>
       </c>
       <c r="P30">
-        <v>628400</v>
+        <v>683300</v>
       </c>
     </row>
     <row r="31">
@@ -1564,22 +1564,22 @@
         <v>-</v>
       </c>
       <c r="C31">
-        <v>8.25</v>
+        <v>8.15</v>
       </c>
       <c r="D31">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E31">
-        <v>0.6097560975609756</v>
+        <v>-0.6097560975609756</v>
       </c>
       <c r="F31">
-        <v>8.3</v>
+        <v>8.2</v>
       </c>
       <c r="G31">
-        <v>8.4</v>
+        <v>8.2</v>
       </c>
       <c r="H31">
-        <v>8.25</v>
+        <v>8.05</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -1588,22 +1588,22 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>4882497</v>
+        <v>1701392</v>
       </c>
       <c r="L31">
-        <v>40605.382450000005</v>
+        <v>13832.67525</v>
       </c>
       <c r="M31">
-        <v>20100</v>
+        <v>272100</v>
       </c>
       <c r="N31">
-        <v>8.25</v>
+        <v>8.1</v>
       </c>
       <c r="O31">
-        <v>8.3</v>
+        <v>8.15</v>
       </c>
       <c r="P31">
-        <v>108400</v>
+        <v>136200</v>
       </c>
     </row>
     <row r="32">
@@ -1614,22 +1614,22 @@
         <v>-</v>
       </c>
       <c r="C32">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="D32">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E32">
-        <v>2.8846153846153846</v>
+        <v>0.9615384615384616</v>
       </c>
       <c r="F32">
         <v>1.04</v>
       </c>
       <c r="G32">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H32">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -1638,22 +1638,22 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>67967054</v>
+        <v>32546511</v>
       </c>
       <c r="L32">
-        <v>71188.11206</v>
+        <v>33871.83902000001</v>
       </c>
       <c r="M32">
-        <v>3204000</v>
+        <v>718400</v>
       </c>
       <c r="N32">
+        <v>1.05</v>
+      </c>
+      <c r="O32">
         <v>1.06</v>
       </c>
-      <c r="O32">
-        <v>1.07</v>
-      </c>
       <c r="P32">
-        <v>3820600</v>
+        <v>3674800</v>
       </c>
     </row>
     <row r="33">
@@ -1664,22 +1664,22 @@
         <v>-</v>
       </c>
       <c r="C33">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>1.5873015873015872</v>
       </c>
       <c r="F33">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="G33">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="H33">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -1688,22 +1688,22 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>1631531</v>
+        <v>12013137</v>
       </c>
       <c r="L33">
-        <v>3879.4257799999996</v>
+        <v>30631.03258</v>
       </c>
       <c r="M33">
-        <v>479200</v>
+        <v>257700</v>
       </c>
       <c r="N33">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="O33">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="P33">
-        <v>514800</v>
+        <v>759300</v>
       </c>
     </row>
     <row r="34">
@@ -1729,7 +1729,7 @@
         <v>0.46</v>
       </c>
       <c r="H34">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -1738,13 +1738,13 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>1873301</v>
+        <v>646500</v>
       </c>
       <c r="L34">
-        <v>844.57445</v>
+        <v>292.958</v>
       </c>
       <c r="M34">
-        <v>892300</v>
+        <v>4721400</v>
       </c>
       <c r="N34">
         <v>0.45</v>
@@ -1753,7 +1753,7 @@
         <v>0.46</v>
       </c>
       <c r="P34">
-        <v>3062800</v>
+        <v>8248200</v>
       </c>
     </row>
     <row r="35">
@@ -1764,22 +1764,22 @@
         <v>-</v>
       </c>
       <c r="C35">
-        <v>9.8</v>
+        <v>10.1</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>-0.9803921568627451</v>
       </c>
       <c r="F35">
-        <v>9.85</v>
+        <v>10.1</v>
       </c>
       <c r="G35">
-        <v>9.9</v>
+        <v>10.2</v>
       </c>
       <c r="H35">
-        <v>9.7</v>
+        <v>9.95</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -1788,22 +1788,22 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>2841436</v>
+        <v>2051395</v>
       </c>
       <c r="L35">
-        <v>27845.3551</v>
+        <v>20587.095699999998</v>
       </c>
       <c r="M35">
-        <v>245500</v>
+        <v>478500</v>
       </c>
       <c r="N35">
-        <v>9.75</v>
+        <v>10</v>
       </c>
       <c r="O35">
-        <v>9.8</v>
+        <v>10.1</v>
       </c>
       <c r="P35">
-        <v>58500</v>
+        <v>258200</v>
       </c>
     </row>
     <row r="36">
@@ -1814,22 +1814,22 @@
         <v>-</v>
       </c>
       <c r="C36">
-        <v>17.4</v>
+        <v>17.1</v>
       </c>
       <c r="D36">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E36">
-        <v>1.1627906976744187</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="F36">
+        <v>17</v>
+      </c>
+      <c r="G36">
         <v>17.2</v>
       </c>
-      <c r="G36">
-        <v>17.7</v>
-      </c>
       <c r="H36">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -1838,22 +1838,22 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>338320</v>
+        <v>47604</v>
       </c>
       <c r="L36">
-        <v>5928.5965</v>
+        <v>810.3581999999999</v>
       </c>
       <c r="M36">
-        <v>12300</v>
+        <v>26000</v>
       </c>
       <c r="N36">
-        <v>17.3</v>
+        <v>17</v>
       </c>
       <c r="O36">
-        <v>17.4</v>
+        <v>17.1</v>
       </c>
       <c r="P36">
-        <v>4000</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="37">
@@ -1864,22 +1864,22 @@
         <v>-</v>
       </c>
       <c r="C37">
-        <v>5.05</v>
+        <v>4.78</v>
       </c>
       <c r="D37">
-        <v>0.07</v>
+        <v>-0.04</v>
       </c>
       <c r="E37">
-        <v>1.4056224899598393</v>
+        <v>-0.8298755186721992</v>
       </c>
       <c r="F37">
-        <v>4.98</v>
+        <v>4.82</v>
       </c>
       <c r="G37">
-        <v>5.1</v>
+        <v>4.88</v>
       </c>
       <c r="H37">
-        <v>4.98</v>
+        <v>4.78</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -1888,22 +1888,22 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>716387</v>
+        <v>1610644</v>
       </c>
       <c r="L37">
-        <v>3594.4296</v>
+        <v>7746.83252</v>
       </c>
       <c r="M37">
-        <v>52700</v>
+        <v>372800</v>
       </c>
       <c r="N37">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="O37">
-        <v>5.05</v>
+        <v>4.78</v>
       </c>
       <c r="P37">
-        <v>177300</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="38">
@@ -1914,7 +1914,7 @@
         <v>-</v>
       </c>
       <c r="C38">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -1926,7 +1926,7 @@
         <v>13.2</v>
       </c>
       <c r="G38">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="H38">
         <v>13</v>
@@ -1938,22 +1938,22 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>1691505</v>
+        <v>444546</v>
       </c>
       <c r="L38">
-        <v>22338.7955</v>
+        <v>5831.7126</v>
       </c>
       <c r="M38">
-        <v>338000</v>
+        <v>168400</v>
       </c>
       <c r="N38">
+        <v>13</v>
+      </c>
+      <c r="O38">
         <v>13.1</v>
       </c>
-      <c r="O38">
-        <v>13.2</v>
-      </c>
       <c r="P38">
-        <v>189600</v>
+        <v>234600</v>
       </c>
     </row>
     <row r="39">
@@ -1964,19 +1964,19 @@
         <v>-</v>
       </c>
       <c r="C39">
+        <v>8.35</v>
+      </c>
+      <c r="D39">
+        <v>0.05</v>
+      </c>
+      <c r="E39">
+        <v>0.6024096385542169</v>
+      </c>
+      <c r="F39">
         <v>8.3</v>
       </c>
-      <c r="D39">
-        <v>-0.1</v>
-      </c>
-      <c r="E39">
-        <v>-1.1904761904761905</v>
-      </c>
-      <c r="F39">
-        <v>8.4</v>
-      </c>
       <c r="G39">
-        <v>8.4</v>
+        <v>8.35</v>
       </c>
       <c r="H39">
         <v>8.3</v>
@@ -1988,22 +1988,22 @@
         <v>0</v>
       </c>
       <c r="K39">
-        <v>246866</v>
+        <v>5287</v>
       </c>
       <c r="L39">
-        <v>2067.7608</v>
+        <v>44.0471</v>
       </c>
       <c r="M39">
-        <v>58300</v>
+        <v>15500</v>
       </c>
       <c r="N39">
         <v>8.3</v>
       </c>
       <c r="O39">
-        <v>8.4</v>
+        <v>8.35</v>
       </c>
       <c r="P39">
-        <v>96100</v>
+        <v>46600</v>
       </c>
     </row>
     <row r="40">
@@ -2026,34 +2026,34 @@
         <v>5.35</v>
       </c>
       <c r="G40">
+        <v>5.4</v>
+      </c>
+      <c r="H40">
+        <v>5.3</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>807364</v>
+      </c>
+      <c r="L40">
+        <v>4314.47025</v>
+      </c>
+      <c r="M40">
+        <v>9700</v>
+      </c>
+      <c r="N40">
         <v>5.35</v>
-      </c>
-      <c r="H40">
-        <v>5.25</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40">
-        <v>704721</v>
-      </c>
-      <c r="L40">
-        <v>3738.6962000000003</v>
-      </c>
-      <c r="M40">
-        <v>377100</v>
-      </c>
-      <c r="N40">
-        <v>5.3</v>
       </c>
       <c r="O40">
         <v>5.4</v>
       </c>
       <c r="P40">
-        <v>201200</v>
+        <v>152700</v>
       </c>
     </row>
     <row r="41">
@@ -2064,19 +2064,19 @@
         <v>-</v>
       </c>
       <c r="C41">
+        <v>8.85</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>8.9</v>
+      </c>
+      <c r="G41">
         <v>8.95</v>
-      </c>
-      <c r="D41">
-        <v>-0.05</v>
-      </c>
-      <c r="E41">
-        <v>-0.5555555555555556</v>
-      </c>
-      <c r="F41">
-        <v>9.05</v>
-      </c>
-      <c r="G41">
-        <v>9.05</v>
       </c>
       <c r="H41">
         <v>8.85</v>
@@ -2088,22 +2088,22 @@
         <v>0</v>
       </c>
       <c r="K41">
-        <v>1380760</v>
+        <v>821658</v>
       </c>
       <c r="L41">
-        <v>12336.323349999999</v>
+        <v>7289.69335</v>
       </c>
       <c r="M41">
-        <v>305300</v>
+        <v>276100</v>
       </c>
       <c r="N41">
+        <v>8.85</v>
+      </c>
+      <c r="O41">
         <v>8.9</v>
       </c>
-      <c r="O41">
-        <v>8.95</v>
-      </c>
       <c r="P41">
-        <v>182700</v>
+        <v>342800</v>
       </c>
     </row>
     <row r="42">
@@ -2114,22 +2114,22 @@
         <v>-</v>
       </c>
       <c r="C42">
-        <v>4.24</v>
+        <v>4.22</v>
       </c>
       <c r="D42">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="E42">
-        <v>0.47393364928909953</v>
+        <v>-0.4716981132075472</v>
       </c>
       <c r="F42">
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="G42">
         <v>4.26</v>
       </c>
       <c r="H42">
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2138,13 +2138,13 @@
         <v>0</v>
       </c>
       <c r="K42">
-        <v>250500</v>
+        <v>95120</v>
       </c>
       <c r="L42">
-        <v>1061.744</v>
+        <v>401.77678000000003</v>
       </c>
       <c r="M42">
-        <v>73700</v>
+        <v>18900</v>
       </c>
       <c r="N42">
         <v>4.22</v>
@@ -2153,7 +2153,7 @@
         <v>4.24</v>
       </c>
       <c r="P42">
-        <v>3400</v>
+        <v>82600</v>
       </c>
     </row>
     <row r="43">
@@ -2164,46 +2164,46 @@
         <v>-</v>
       </c>
       <c r="C43">
+        <v>4.42</v>
+      </c>
+      <c r="D43">
+        <v>0.02</v>
+      </c>
+      <c r="E43">
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="F43">
+        <v>4.4</v>
+      </c>
+      <c r="G43">
         <v>4.46</v>
       </c>
-      <c r="D43">
-        <v>-0.02</v>
-      </c>
-      <c r="E43">
-        <v>-0.44642857142857145</v>
-      </c>
-      <c r="F43">
-        <v>4.46</v>
-      </c>
-      <c r="G43">
-        <v>4.5</v>
-      </c>
       <c r="H43">
+        <v>4.32</v>
+      </c>
+      <c r="I43">
+        <v>9000000</v>
+      </c>
+      <c r="J43">
+        <v>37800</v>
+      </c>
+      <c r="K43">
+        <v>20712202</v>
+      </c>
+      <c r="L43">
+        <v>89338.69873999999</v>
+      </c>
+      <c r="M43">
+        <v>230800</v>
+      </c>
+      <c r="N43">
+        <v>4.4</v>
+      </c>
+      <c r="O43">
         <v>4.42</v>
       </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>7105803</v>
-      </c>
-      <c r="L43">
-        <v>31641.09252</v>
-      </c>
-      <c r="M43">
-        <v>36900</v>
-      </c>
-      <c r="N43">
-        <v>4.46</v>
-      </c>
-      <c r="O43">
-        <v>4.48</v>
-      </c>
       <c r="P43">
-        <v>152200</v>
+        <v>328600</v>
       </c>
     </row>
     <row r="44">
@@ -2214,22 +2214,22 @@
         <v>-</v>
       </c>
       <c r="C44">
+        <v>0.36</v>
+      </c>
+      <c r="D44">
+        <v>0.01</v>
+      </c>
+      <c r="E44">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="F44">
         <v>0.35</v>
-      </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
-      <c r="E44">
-        <v>0</v>
-      </c>
-      <c r="F44">
-        <v>0.36</v>
       </c>
       <c r="G44">
         <v>0.36</v>
       </c>
       <c r="H44">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0</v>
       </c>
       <c r="K44">
-        <v>542522</v>
+        <v>4392710</v>
       </c>
       <c r="L44">
-        <v>190.60892</v>
+        <v>1536.9375</v>
       </c>
       <c r="M44">
-        <v>2406000</v>
+        <v>1949200</v>
       </c>
       <c r="N44">
         <v>0.35</v>
@@ -2253,7 +2253,7 @@
         <v>0.36</v>
       </c>
       <c r="P44">
-        <v>12448600</v>
+        <v>12862500</v>
       </c>
     </row>
     <row r="45">
@@ -2264,22 +2264,22 @@
         <v>-</v>
       </c>
       <c r="C45">
-        <v>3.08</v>
+        <v>3.26</v>
       </c>
       <c r="D45">
-        <v>0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="E45">
-        <v>2.6666666666666665</v>
+        <v>-0.6097560975609756</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>3.32</v>
       </c>
       <c r="G45">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="H45">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2288,22 +2288,22 @@
         <v>0</v>
       </c>
       <c r="K45">
-        <v>10933789</v>
+        <v>60027542</v>
       </c>
       <c r="L45">
-        <v>33493.79954</v>
+        <v>197621.44712</v>
       </c>
       <c r="M45">
-        <v>210100</v>
+        <v>1009700</v>
       </c>
       <c r="N45">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="O45">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="P45">
-        <v>1921400</v>
+        <v>710400</v>
       </c>
     </row>
     <row r="46">
@@ -2314,22 +2314,22 @@
         <v>-</v>
       </c>
       <c r="C46">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>3.816793893129771</v>
       </c>
       <c r="F46">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
       <c r="G46">
-        <v>6.65</v>
+        <v>6.85</v>
       </c>
       <c r="H46">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2338,22 +2338,22 @@
         <v>0</v>
       </c>
       <c r="K46">
-        <v>56201</v>
+        <v>1220734</v>
       </c>
       <c r="L46">
-        <v>370.95155</v>
+        <v>8238.93685</v>
       </c>
       <c r="M46">
-        <v>107600</v>
+        <v>83700</v>
       </c>
       <c r="N46">
-        <v>6.55</v>
+        <v>6.75</v>
       </c>
       <c r="O46">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="P46">
-        <v>14000</v>
+        <v>64900</v>
       </c>
     </row>
     <row r="47">
@@ -2364,22 +2364,22 @@
         <v>-</v>
       </c>
       <c r="C47">
+        <v>30.75</v>
+      </c>
+      <c r="D47">
+        <v>0.25</v>
+      </c>
+      <c r="E47">
+        <v>0.819672131147541</v>
+      </c>
+      <c r="F47">
         <v>30.5</v>
-      </c>
-      <c r="D47">
-        <v>0.5</v>
-      </c>
-      <c r="E47">
-        <v>1.6666666666666667</v>
-      </c>
-      <c r="F47">
-        <v>30.25</v>
       </c>
       <c r="G47">
         <v>30.75</v>
       </c>
       <c r="H47">
-        <v>30.25</v>
+        <v>30.5</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2388,22 +2388,22 @@
         <v>0</v>
       </c>
       <c r="K47">
-        <v>128842</v>
+        <v>45207</v>
       </c>
       <c r="L47">
-        <v>3922.28825</v>
+        <v>1387.0495</v>
       </c>
       <c r="M47">
-        <v>92000</v>
+        <v>39500</v>
       </c>
       <c r="N47">
-        <v>30.25</v>
+        <v>30.5</v>
       </c>
       <c r="O47">
         <v>30.75</v>
       </c>
       <c r="P47">
-        <v>41300</v>
+        <v>42100</v>
       </c>
     </row>
     <row r="48">
@@ -2417,19 +2417,19 @@
         <v>12.6</v>
       </c>
       <c r="D48">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="E48">
-        <v>-1.5625</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="G48">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="H48">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2438,13 +2438,13 @@
         <v>0</v>
       </c>
       <c r="K48">
-        <v>1764871</v>
+        <v>676635</v>
       </c>
       <c r="L48">
-        <v>22199.389600000002</v>
+        <v>8532.4411</v>
       </c>
       <c r="M48">
-        <v>265300</v>
+        <v>90600</v>
       </c>
       <c r="N48">
         <v>12.6</v>
@@ -2453,7 +2453,7 @@
         <v>12.7</v>
       </c>
       <c r="P48">
-        <v>148600</v>
+        <v>186800</v>
       </c>
     </row>
     <row r="49">
@@ -2464,46 +2464,46 @@
         <v>-</v>
       </c>
       <c r="C49">
+        <v>12.5</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>12.4</v>
+      </c>
+      <c r="G49">
+        <v>12.5</v>
+      </c>
+      <c r="H49">
         <v>12.3</v>
       </c>
-      <c r="D49">
-        <v>0.2</v>
-      </c>
-      <c r="E49">
-        <v>1.6528925619834711</v>
-      </c>
-      <c r="F49">
-        <v>12.1</v>
-      </c>
-      <c r="G49">
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>2221074</v>
+      </c>
+      <c r="L49">
+        <v>27533.5165</v>
+      </c>
+      <c r="M49">
+        <v>140300</v>
+      </c>
+      <c r="N49">
         <v>12.4</v>
       </c>
-      <c r="H49">
-        <v>11.8</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>7645032</v>
-      </c>
-      <c r="L49">
-        <v>92706.7248</v>
-      </c>
-      <c r="M49">
-        <v>814300</v>
-      </c>
-      <c r="N49">
-        <v>12.3</v>
-      </c>
       <c r="O49">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="P49">
-        <v>2153200</v>
+        <v>413200</v>
       </c>
     </row>
     <row r="50">
@@ -2514,7 +2514,7 @@
         <v>-</v>
       </c>
       <c r="C50">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2526,10 +2526,10 @@
         <v>14.7</v>
       </c>
       <c r="G50">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="H50">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2538,22 +2538,22 @@
         <v>0</v>
       </c>
       <c r="K50">
-        <v>2415932</v>
+        <v>508393</v>
       </c>
       <c r="L50">
-        <v>35726.874899999995</v>
+        <v>7516.0815</v>
       </c>
       <c r="M50">
-        <v>173100</v>
+        <v>188800</v>
       </c>
       <c r="N50">
+        <v>14.7</v>
+      </c>
+      <c r="O50">
         <v>14.8</v>
       </c>
-      <c r="O50">
-        <v>14.9</v>
-      </c>
       <c r="P50">
-        <v>49000</v>
+        <v>123500</v>
       </c>
     </row>
     <row r="51">
@@ -2564,22 +2564,22 @@
         <v>-</v>
       </c>
       <c r="C51">
-        <v>7.2</v>
+        <v>7.35</v>
       </c>
       <c r="D51">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E51">
-        <v>0.6993006993006993</v>
+        <v>0</v>
       </c>
       <c r="F51">
-        <v>7.15</v>
+        <v>7.4</v>
       </c>
       <c r="G51">
-        <v>7.25</v>
+        <v>7.4</v>
       </c>
       <c r="H51">
-        <v>7.15</v>
+        <v>7.3</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2588,22 +2588,22 @@
         <v>0</v>
       </c>
       <c r="K51">
-        <v>446705</v>
+        <v>409222</v>
       </c>
       <c r="L51">
-        <v>3216.1165</v>
+        <v>3012.86275</v>
       </c>
       <c r="M51">
-        <v>166000</v>
+        <v>258900</v>
       </c>
       <c r="N51">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="O51">
-        <v>7.25</v>
+        <v>7.35</v>
       </c>
       <c r="P51">
-        <v>379200</v>
+        <v>97300</v>
       </c>
     </row>
     <row r="52">
@@ -2614,22 +2614,22 @@
         <v>-</v>
       </c>
       <c r="C52">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>2.6595744680851063</v>
       </c>
       <c r="F52">
         <v>18.8</v>
       </c>
       <c r="G52">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="H52">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2638,22 +2638,22 @@
         <v>0</v>
       </c>
       <c r="K52">
-        <v>767420</v>
+        <v>1017701</v>
       </c>
       <c r="L52">
-        <v>14349.256</v>
+        <v>19383.4492</v>
       </c>
       <c r="M52">
-        <v>18100</v>
+        <v>21800</v>
       </c>
       <c r="N52">
-        <v>18.8</v>
+        <v>19.2</v>
       </c>
       <c r="O52">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="P52">
-        <v>10500</v>
+        <v>64400</v>
       </c>
     </row>
     <row r="53">
@@ -2664,23 +2664,23 @@
         <v>-</v>
       </c>
       <c r="C53">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="D53">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="E53">
-        <v>1.9607843137254901</v>
+        <v>0</v>
       </c>
       <c r="F53">
+        <v>2.06</v>
+      </c>
+      <c r="G53">
+        <v>2.06</v>
+      </c>
+      <c r="H53">
         <v>2.04</v>
       </c>
-      <c r="G53">
-        <v>2.08</v>
-      </c>
-      <c r="H53">
-        <v>2.02</v>
-      </c>
       <c r="I53">
         <v>0</v>
       </c>
@@ -2688,22 +2688,22 @@
         <v>0</v>
       </c>
       <c r="K53">
-        <v>5476211</v>
+        <v>1216320</v>
       </c>
       <c r="L53">
-        <v>11240.46252</v>
+        <v>2493.1447000000003</v>
       </c>
       <c r="M53">
-        <v>611500</v>
+        <v>2143600</v>
       </c>
       <c r="N53">
+        <v>2.04</v>
+      </c>
+      <c r="O53">
         <v>2.06</v>
       </c>
-      <c r="O53">
-        <v>2.08</v>
-      </c>
       <c r="P53">
-        <v>1465500</v>
+        <v>1432900</v>
       </c>
     </row>
     <row r="54">
@@ -2714,46 +2714,46 @@
         <v>-</v>
       </c>
       <c r="C54">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>-0.5291005291005291</v>
       </c>
       <c r="F54">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="G54">
+        <v>3.82</v>
+      </c>
+      <c r="H54">
+        <v>3.76</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>2472647</v>
+      </c>
+      <c r="L54">
+        <v>9354.12644</v>
+      </c>
+      <c r="M54">
+        <v>914200</v>
+      </c>
+      <c r="N54">
         <v>3.74</v>
       </c>
-      <c r="H54">
-        <v>3.68</v>
-      </c>
-      <c r="I54">
-        <v>0</v>
-      </c>
-      <c r="J54">
-        <v>0</v>
-      </c>
-      <c r="K54">
-        <v>1657151</v>
-      </c>
-      <c r="L54">
-        <v>6140.924400000001</v>
-      </c>
-      <c r="M54">
-        <v>383700</v>
-      </c>
-      <c r="N54">
-        <v>3.7</v>
-      </c>
       <c r="O54">
-        <v>3.72</v>
+        <v>3.78</v>
       </c>
       <c r="P54">
-        <v>83800</v>
+        <v>158900</v>
       </c>
     </row>
     <row r="55">
@@ -2764,46 +2764,46 @@
         <v>-</v>
       </c>
       <c r="C55">
+        <v>3.96</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>3.98</v>
+      </c>
+      <c r="G55">
+        <v>3.98</v>
+      </c>
+      <c r="H55">
         <v>3.94</v>
       </c>
-      <c r="D55">
-        <v>0.06</v>
-      </c>
-      <c r="E55">
-        <v>1.5463917525773196</v>
-      </c>
-      <c r="F55">
-        <v>3.9</v>
-      </c>
-      <c r="G55">
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>67702</v>
+      </c>
+      <c r="L55">
+        <v>268.17591999999996</v>
+      </c>
+      <c r="M55">
+        <v>46000</v>
+      </c>
+      <c r="N55">
+        <v>3.94</v>
+      </c>
+      <c r="O55">
         <v>3.96</v>
       </c>
-      <c r="H55">
-        <v>3.88</v>
-      </c>
-      <c r="I55">
-        <v>0</v>
-      </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55">
-        <v>252545</v>
-      </c>
-      <c r="L55">
-        <v>989.2018</v>
-      </c>
-      <c r="M55">
-        <v>32200</v>
-      </c>
-      <c r="N55">
-        <v>3.92</v>
-      </c>
-      <c r="O55">
-        <v>3.94</v>
-      </c>
       <c r="P55">
-        <v>37500</v>
+        <v>190300</v>
       </c>
     </row>
     <row r="56">
@@ -2814,19 +2814,19 @@
         <v>-</v>
       </c>
       <c r="C56">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="D56">
         <v>0.05</v>
       </c>
       <c r="E56">
-        <v>0.746268656716418</v>
+        <v>0.7407407407407407</v>
       </c>
       <c r="F56">
         <v>6.75</v>
       </c>
       <c r="G56">
-        <v>6.8</v>
+        <v>6.85</v>
       </c>
       <c r="H56">
         <v>6.7</v>
@@ -2838,22 +2838,22 @@
         <v>0</v>
       </c>
       <c r="K56">
-        <v>164000</v>
+        <v>475400</v>
       </c>
       <c r="L56">
-        <v>1100.295</v>
+        <v>3225.67</v>
       </c>
       <c r="M56">
-        <v>19300</v>
+        <v>12200</v>
       </c>
       <c r="N56">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="O56">
-        <v>6.75</v>
+        <v>6.85</v>
       </c>
       <c r="P56">
-        <v>44600</v>
+        <v>39800</v>
       </c>
     </row>
     <row r="57">
@@ -2867,19 +2867,19 @@
         <v>8.7</v>
       </c>
       <c r="D57">
-        <v>-0.05</v>
+        <v>0.15</v>
       </c>
       <c r="E57">
-        <v>-0.5714285714285714</v>
+        <v>1.7543859649122806</v>
       </c>
       <c r="F57">
+        <v>8.6</v>
+      </c>
+      <c r="G57">
         <v>8.75</v>
       </c>
-      <c r="G57">
-        <v>8.85</v>
-      </c>
       <c r="H57">
-        <v>8.65</v>
+        <v>8.45</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2888,13 +2888,13 @@
         <v>0</v>
       </c>
       <c r="K57">
-        <v>1492581</v>
+        <v>3358900</v>
       </c>
       <c r="L57">
-        <v>13021.230800000001</v>
+        <v>28991.01</v>
       </c>
       <c r="M57">
-        <v>236700</v>
+        <v>199600</v>
       </c>
       <c r="N57">
         <v>8.7</v>
@@ -2903,7 +2903,7 @@
         <v>8.75</v>
       </c>
       <c r="P57">
-        <v>119300</v>
+        <v>407700</v>
       </c>
     </row>
     <row r="58">
@@ -2914,23 +2914,23 @@
         <v>-</v>
       </c>
       <c r="C58">
-        <v>5.25</v>
+        <v>5.15</v>
       </c>
       <c r="D58">
-        <v>0.2</v>
+        <v>-0.05</v>
       </c>
       <c r="E58">
-        <v>3.9603960396039604</v>
+        <v>-0.9615384615384616</v>
       </c>
       <c r="F58">
+        <v>5.2</v>
+      </c>
+      <c r="G58">
+        <v>5.2</v>
+      </c>
+      <c r="H58">
         <v>5.1</v>
       </c>
-      <c r="G58">
-        <v>5.25</v>
-      </c>
-      <c r="H58">
-        <v>5.05</v>
-      </c>
       <c r="I58">
         <v>0</v>
       </c>
@@ -2938,22 +2938,22 @@
         <v>0</v>
       </c>
       <c r="K58">
-        <v>19404100</v>
+        <v>7076827</v>
       </c>
       <c r="L58">
-        <v>100503.61545</v>
+        <v>36295.35845</v>
       </c>
       <c r="M58">
-        <v>1191800</v>
+        <v>2056700</v>
       </c>
       <c r="N58">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O58">
-        <v>5.25</v>
+        <v>5.15</v>
       </c>
       <c r="P58">
-        <v>2114500</v>
+        <v>675900</v>
       </c>
     </row>
     <row r="59">
@@ -2964,23 +2964,23 @@
         <v>-</v>
       </c>
       <c r="C59">
-        <v>9.05</v>
+        <v>9.2</v>
       </c>
       <c r="D59">
-        <v>-0.05</v>
+        <v>0.15</v>
       </c>
       <c r="E59">
-        <v>-0.5494505494505495</v>
+        <v>1.6574585635359116</v>
       </c>
       <c r="F59">
         <v>9.1</v>
       </c>
       <c r="G59">
+        <v>9.25</v>
+      </c>
+      <c r="H59">
         <v>9.1</v>
       </c>
-      <c r="H59">
-        <v>8.95</v>
-      </c>
       <c r="I59">
         <v>0</v>
       </c>
@@ -2988,22 +2988,22 @@
         <v>0</v>
       </c>
       <c r="K59">
-        <v>1684729</v>
+        <v>2885014</v>
       </c>
       <c r="L59">
-        <v>15256.25865</v>
+        <v>26530.363350000003</v>
       </c>
       <c r="M59">
-        <v>126600</v>
+        <v>485600</v>
       </c>
       <c r="N59">
-        <v>9.05</v>
+        <v>9.15</v>
       </c>
       <c r="O59">
-        <v>9.1</v>
+        <v>9.2</v>
       </c>
       <c r="P59">
-        <v>305600</v>
+        <v>129800</v>
       </c>
     </row>
     <row r="60">
@@ -3014,16 +3014,16 @@
         <v>-</v>
       </c>
       <c r="C60">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="D60">
-        <v>0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="E60">
-        <v>2.2099447513812156</v>
+        <v>-0.5434782608695652</v>
       </c>
       <c r="F60">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="G60">
         <v>3.72</v>
@@ -3038,22 +3038,22 @@
         <v>0</v>
       </c>
       <c r="K60">
-        <v>12986497</v>
+        <v>2406000</v>
       </c>
       <c r="L60">
-        <v>48007.01798</v>
+        <v>8891.812</v>
       </c>
       <c r="M60">
-        <v>1000800</v>
+        <v>475500</v>
       </c>
       <c r="N60">
+        <v>3.66</v>
+      </c>
+      <c r="O60">
         <v>3.68</v>
       </c>
-      <c r="O60">
-        <v>3.7</v>
-      </c>
       <c r="P60">
-        <v>861500</v>
+        <v>175600</v>
       </c>
     </row>
     <row r="61">
@@ -3064,22 +3064,22 @@
         <v>-</v>
       </c>
       <c r="C61">
-        <v>9.4</v>
+        <v>9.45</v>
       </c>
       <c r="D61">
         <v>0.05</v>
       </c>
       <c r="E61">
-        <v>0.5347593582887701</v>
+        <v>0.5319148936170213</v>
       </c>
       <c r="F61">
-        <v>9.35</v>
+        <v>9.4</v>
       </c>
       <c r="G61">
         <v>9.45</v>
       </c>
       <c r="H61">
-        <v>9.35</v>
+        <v>9.4</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -3088,13 +3088,13 @@
         <v>0</v>
       </c>
       <c r="K61">
-        <v>269177</v>
+        <v>78297</v>
       </c>
       <c r="L61">
-        <v>2529.66515</v>
+        <v>736.1718000000001</v>
       </c>
       <c r="M61">
-        <v>11500</v>
+        <v>249800</v>
       </c>
       <c r="N61">
         <v>9.4</v>
@@ -3103,7 +3103,7 @@
         <v>9.45</v>
       </c>
       <c r="P61">
-        <v>147700</v>
+        <v>100300</v>
       </c>
     </row>
     <row r="62">
@@ -3117,43 +3117,43 @@
         <v>15.7</v>
       </c>
       <c r="D62">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E62">
-        <v>0.6410256410256411</v>
+        <v>0</v>
       </c>
       <c r="F62">
-        <v>15.3</v>
+        <v>15.8</v>
       </c>
       <c r="G62">
+        <v>15.8</v>
+      </c>
+      <c r="H62">
+        <v>15.6</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>385183</v>
+      </c>
+      <c r="L62">
+        <v>6045.120599999999</v>
+      </c>
+      <c r="M62">
+        <v>103700</v>
+      </c>
+      <c r="N62">
         <v>15.7</v>
       </c>
-      <c r="H62">
-        <v>15.3</v>
-      </c>
-      <c r="I62">
-        <v>0</v>
-      </c>
-      <c r="J62">
-        <v>0</v>
-      </c>
-      <c r="K62">
-        <v>1166414</v>
-      </c>
-      <c r="L62">
-        <v>18057.9841</v>
-      </c>
-      <c r="M62">
-        <v>116400</v>
-      </c>
-      <c r="N62">
-        <v>15.6</v>
-      </c>
       <c r="O62">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="P62">
-        <v>135500</v>
+        <v>107100</v>
       </c>
     </row>
     <row r="63">
@@ -3167,13 +3167,13 @@
         <v>2.18</v>
       </c>
       <c r="D63">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="E63">
-        <v>-0.9090909090909091</v>
+        <v>0.9259259259259259</v>
       </c>
       <c r="F63">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G63">
         <v>2.2</v>
@@ -3188,13 +3188,13 @@
         <v>0</v>
       </c>
       <c r="K63">
-        <v>142101</v>
+        <v>243030</v>
       </c>
       <c r="L63">
-        <v>308.78222</v>
+        <v>526.9934000000001</v>
       </c>
       <c r="M63">
-        <v>220200</v>
+        <v>35400</v>
       </c>
       <c r="N63">
         <v>2.16</v>
@@ -3203,7 +3203,7 @@
         <v>2.18</v>
       </c>
       <c r="P63">
-        <v>55900</v>
+        <v>83300</v>
       </c>
     </row>
     <row r="64">
@@ -3214,13 +3214,13 @@
         <v>-</v>
       </c>
       <c r="C64">
-        <v>5.65</v>
+        <v>5.7</v>
       </c>
       <c r="D64">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E64">
-        <v>0.8928571428571429</v>
+        <v>0</v>
       </c>
       <c r="F64">
         <v>5.65</v>
@@ -3238,13 +3238,13 @@
         <v>0</v>
       </c>
       <c r="K64">
-        <v>271905</v>
+        <v>174379</v>
       </c>
       <c r="L64">
-        <v>1549.16325</v>
+        <v>993.8914</v>
       </c>
       <c r="M64">
-        <v>141000</v>
+        <v>178500</v>
       </c>
       <c r="N64">
         <v>5.65</v>
@@ -3253,7 +3253,7 @@
         <v>5.7</v>
       </c>
       <c r="P64">
-        <v>47500</v>
+        <v>116900</v>
       </c>
     </row>
     <row r="65">
@@ -3264,46 +3264,46 @@
         <v>-</v>
       </c>
       <c r="C65">
+        <v>4.64</v>
+      </c>
+      <c r="D65">
+        <v>-0.02</v>
+      </c>
+      <c r="E65">
+        <v>-0.4291845493562232</v>
+      </c>
+      <c r="F65">
+        <v>4.64</v>
+      </c>
+      <c r="G65">
+        <v>4.66</v>
+      </c>
+      <c r="H65">
         <v>4.62</v>
       </c>
-      <c r="D65">
-        <v>0.02</v>
-      </c>
-      <c r="E65">
-        <v>0.43478260869565216</v>
-      </c>
-      <c r="F65">
-        <v>4.6</v>
-      </c>
-      <c r="G65">
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>642381</v>
+      </c>
+      <c r="L65">
+        <v>2979.4011600000003</v>
+      </c>
+      <c r="M65">
+        <v>251100</v>
+      </c>
+      <c r="N65">
+        <v>4.62</v>
+      </c>
+      <c r="O65">
         <v>4.64</v>
       </c>
-      <c r="H65">
-        <v>4.6</v>
-      </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <v>0</v>
-      </c>
-      <c r="K65">
-        <v>555177</v>
-      </c>
-      <c r="L65">
-        <v>2562.77352</v>
-      </c>
-      <c r="M65">
-        <v>230800</v>
-      </c>
-      <c r="N65">
-        <v>4.6</v>
-      </c>
-      <c r="O65">
-        <v>4.62</v>
-      </c>
       <c r="P65">
-        <v>31800</v>
+        <v>31100</v>
       </c>
     </row>
     <row r="66">
@@ -3314,46 +3314,46 @@
         <v>-</v>
       </c>
       <c r="C66">
+        <v>5.15</v>
+      </c>
+      <c r="D66">
+        <v>-0.1</v>
+      </c>
+      <c r="E66">
+        <v>-1.9047619047619047</v>
+      </c>
+      <c r="F66">
         <v>5.2</v>
       </c>
-      <c r="D66">
-        <v>-0.05</v>
-      </c>
-      <c r="E66">
-        <v>-0.9523809523809523</v>
-      </c>
-      <c r="F66">
-        <v>5.25</v>
-      </c>
       <c r="G66">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H66">
+        <v>5.15</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>17631</v>
+      </c>
+      <c r="L66">
+        <v>90.94775</v>
+      </c>
+      <c r="M66">
+        <v>70800</v>
+      </c>
+      <c r="N66">
+        <v>5.15</v>
+      </c>
+      <c r="O66">
         <v>5.2</v>
       </c>
-      <c r="I66">
-        <v>0</v>
-      </c>
-      <c r="J66">
-        <v>0</v>
-      </c>
-      <c r="K66">
-        <v>194701</v>
-      </c>
-      <c r="L66">
-        <v>1014.8853</v>
-      </c>
-      <c r="M66">
-        <v>18200</v>
-      </c>
-      <c r="N66">
-        <v>5.2</v>
-      </c>
-      <c r="O66">
-        <v>5.25</v>
-      </c>
       <c r="P66">
-        <v>24100</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="67">
@@ -3364,23 +3364,23 @@
         <v>-</v>
       </c>
       <c r="C67">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="D67">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E67">
-        <v>1.7857142857142858</v>
+        <v>0</v>
       </c>
       <c r="F67">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="G67">
+        <v>0.59</v>
+      </c>
+      <c r="H67">
         <v>0.58</v>
       </c>
-      <c r="H67">
-        <v>0.56</v>
-      </c>
       <c r="I67">
         <v>0</v>
       </c>
@@ -3388,22 +3388,22 @@
         <v>0</v>
       </c>
       <c r="K67">
-        <v>13859803</v>
+        <v>6411211</v>
       </c>
       <c r="L67">
-        <v>7915.6337300000005</v>
+        <v>3775.61029</v>
       </c>
       <c r="M67">
-        <v>2169500</v>
+        <v>4823400</v>
       </c>
       <c r="N67">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="O67">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="P67">
-        <v>6385400</v>
+        <v>2961400</v>
       </c>
     </row>
     <row r="68">
@@ -3414,46 +3414,46 @@
         <v>-</v>
       </c>
       <c r="C68">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="D68">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E68">
-        <v>1.5957446808510638</v>
+        <v>0</v>
       </c>
       <c r="F68">
-        <v>19</v>
+        <v>18.7</v>
       </c>
       <c r="G68">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="H68">
+        <v>18.5</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>756276</v>
+      </c>
+      <c r="L68">
+        <v>14094.438300000002</v>
+      </c>
+      <c r="M68">
+        <v>93000</v>
+      </c>
+      <c r="N68">
         <v>18.7</v>
       </c>
-      <c r="I68">
-        <v>0</v>
-      </c>
-      <c r="J68">
-        <v>0</v>
-      </c>
-      <c r="K68">
-        <v>2943063</v>
-      </c>
-      <c r="L68">
-        <v>55556.0737</v>
-      </c>
-      <c r="M68">
-        <v>232800</v>
-      </c>
-      <c r="N68">
-        <v>19</v>
-      </c>
       <c r="O68">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="P68">
-        <v>235400</v>
+        <v>101500</v>
       </c>
     </row>
     <row r="69">
@@ -3464,22 +3464,22 @@
         <v>-</v>
       </c>
       <c r="C69">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>1.7543859649122806</v>
       </c>
       <c r="F69">
-        <v>11.8</v>
+        <v>11.3</v>
       </c>
       <c r="G69">
-        <v>12</v>
+        <v>11.7</v>
       </c>
       <c r="H69">
-        <v>11.7</v>
+        <v>11.3</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -3488,22 +3488,22 @@
         <v>0</v>
       </c>
       <c r="K69">
-        <v>1146948</v>
+        <v>1277509</v>
       </c>
       <c r="L69">
-        <v>13532.151199999998</v>
+        <v>14687.7444</v>
       </c>
       <c r="M69">
-        <v>157700</v>
+        <v>500</v>
       </c>
       <c r="N69">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="O69">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
       <c r="P69">
-        <v>104500</v>
+        <v>47600</v>
       </c>
     </row>
     <row r="70">
@@ -3514,19 +3514,19 @@
         <v>-</v>
       </c>
       <c r="C70">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="D70">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="E70">
-        <v>-0.5025125628140703</v>
+        <v>0.5025125628140703</v>
       </c>
       <c r="F70">
         <v>10</v>
       </c>
       <c r="G70">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="H70">
         <v>9.9</v>
@@ -3538,22 +3538,22 @@
         <v>0</v>
       </c>
       <c r="K70">
-        <v>564201</v>
+        <v>153907</v>
       </c>
       <c r="L70">
-        <v>5618.875</v>
+        <v>1532.35</v>
       </c>
       <c r="M70">
-        <v>203700</v>
+        <v>90800</v>
       </c>
       <c r="N70">
-        <v>9.9</v>
+        <v>9.95</v>
       </c>
       <c r="O70">
-        <v>9.95</v>
+        <v>10</v>
       </c>
       <c r="P70">
-        <v>46600</v>
+        <v>210700</v>
       </c>
     </row>
     <row r="71">
@@ -3564,46 +3564,46 @@
         <v>-</v>
       </c>
       <c r="C71">
+        <v>8.2</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>8.2</v>
+      </c>
+      <c r="G71">
+        <v>8.25</v>
+      </c>
+      <c r="H71">
         <v>8.15</v>
       </c>
-      <c r="D71">
-        <v>0</v>
-      </c>
-      <c r="E71">
-        <v>0</v>
-      </c>
-      <c r="F71">
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>49514</v>
+      </c>
+      <c r="L71">
+        <v>405.1487</v>
+      </c>
+      <c r="M71">
+        <v>42800</v>
+      </c>
+      <c r="N71">
         <v>8.15</v>
       </c>
-      <c r="G71">
+      <c r="O71">
         <v>8.2</v>
       </c>
-      <c r="H71">
-        <v>8.1</v>
-      </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="J71">
-        <v>0</v>
-      </c>
-      <c r="K71">
-        <v>57410</v>
-      </c>
-      <c r="L71">
-        <v>466.527</v>
-      </c>
-      <c r="M71">
-        <v>42300</v>
-      </c>
-      <c r="N71">
-        <v>8.1</v>
-      </c>
-      <c r="O71">
-        <v>8.15</v>
-      </c>
       <c r="P71">
-        <v>84100</v>
+        <v>33700</v>
       </c>
     </row>
     <row r="72">
@@ -3614,22 +3614,22 @@
         <v>-</v>
       </c>
       <c r="C72">
-        <v>4.46</v>
+        <v>4.56</v>
       </c>
       <c r="D72">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E72">
-        <v>0.9049773755656109</v>
+        <v>0.44052863436123346</v>
       </c>
       <c r="F72">
-        <v>4.42</v>
+        <v>4.58</v>
       </c>
       <c r="G72">
-        <v>4.48</v>
+        <v>4.58</v>
       </c>
       <c r="H72">
-        <v>4.42</v>
+        <v>4.5</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -3638,22 +3638,22 @@
         <v>0</v>
       </c>
       <c r="K72">
-        <v>410100</v>
+        <v>606003</v>
       </c>
       <c r="L72">
-        <v>1823.886</v>
+        <v>2757.60366</v>
       </c>
       <c r="M72">
-        <v>33600</v>
+        <v>4600</v>
       </c>
       <c r="N72">
-        <v>4.44</v>
+        <v>4.56</v>
       </c>
       <c r="O72">
-        <v>4.46</v>
+        <v>4.58</v>
       </c>
       <c r="P72">
-        <v>60700</v>
+        <v>21100</v>
       </c>
     </row>
     <row r="73">
@@ -3664,22 +3664,22 @@
         <v>-</v>
       </c>
       <c r="C73">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="D73">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="E73">
-        <v>3.896103896103896</v>
+        <v>-3.658536585365854</v>
       </c>
       <c r="F73">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="G73">
         <v>0.82</v>
       </c>
       <c r="H73">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -3688,22 +3688,22 @@
         <v>0</v>
       </c>
       <c r="K73">
-        <v>24713863</v>
+        <v>21401281</v>
       </c>
       <c r="L73">
-        <v>19657.716190000003</v>
+        <v>17026.981239999997</v>
       </c>
       <c r="M73">
-        <v>1396700</v>
+        <v>1938400</v>
       </c>
       <c r="N73">
+        <v>0.78</v>
+      </c>
+      <c r="O73">
         <v>0.8</v>
       </c>
-      <c r="O73">
-        <v>0.81</v>
-      </c>
       <c r="P73">
-        <v>1011900</v>
+        <v>1664200</v>
       </c>
     </row>
     <row r="74">
@@ -3714,7 +3714,7 @@
         <v>-</v>
       </c>
       <c r="C74">
-        <v>9.65</v>
+        <v>9.6</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -3738,10 +3738,10 @@
         <v>0</v>
       </c>
       <c r="K74">
-        <v>23300</v>
+        <v>11200</v>
       </c>
       <c r="L74">
-        <v>224.445</v>
+        <v>107.575</v>
       </c>
       <c r="M74">
         <v>2200</v>
@@ -3753,7 +3753,7 @@
         <v>9.65</v>
       </c>
       <c r="P74">
-        <v>14100</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="75">
@@ -3764,22 +3764,22 @@
         <v>-</v>
       </c>
       <c r="C75">
-        <v>4.52</v>
+        <v>4.76</v>
       </c>
       <c r="D75">
-        <v>0.36</v>
+        <v>0.06</v>
       </c>
       <c r="E75">
-        <v>8.653846153846153</v>
+        <v>1.2765957446808511</v>
       </c>
       <c r="F75">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="G75">
-        <v>4.54</v>
+        <v>4.78</v>
       </c>
       <c r="H75">
-        <v>4.16</v>
+        <v>4.64</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -3788,22 +3788,22 @@
         <v>0</v>
       </c>
       <c r="K75">
-        <v>59339575</v>
+        <v>13046361</v>
       </c>
       <c r="L75">
-        <v>260161.72984</v>
+        <v>61530.39298</v>
       </c>
       <c r="M75">
-        <v>542900</v>
+        <v>445300</v>
       </c>
       <c r="N75">
-        <v>4.5</v>
+        <v>4.76</v>
       </c>
       <c r="O75">
-        <v>4.52</v>
+        <v>4.78</v>
       </c>
       <c r="P75">
-        <v>385600</v>
+        <v>534500</v>
       </c>
     </row>
     <row r="76">
@@ -3826,10 +3826,10 @@
         <v>6.4</v>
       </c>
       <c r="G76">
-        <v>6.45</v>
+        <v>6.4</v>
       </c>
       <c r="H76">
-        <v>6.35</v>
+        <v>6.3</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="K76">
-        <v>5325556</v>
+        <v>4133384</v>
       </c>
       <c r="L76">
-        <v>33973.184700000005</v>
+        <v>26300.593699999998</v>
       </c>
       <c r="M76">
-        <v>1329300</v>
+        <v>1034300</v>
       </c>
       <c r="N76">
         <v>6.35</v>
@@ -3853,7 +3853,7 @@
         <v>6.4</v>
       </c>
       <c r="P76">
-        <v>826900</v>
+        <v>723800</v>
       </c>
     </row>
     <row r="77">
@@ -3864,22 +3864,22 @@
         <v>-</v>
       </c>
       <c r="C77">
+        <v>5.7</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
         <v>5.65</v>
       </c>
-      <c r="D77">
-        <v>-0.1</v>
-      </c>
-      <c r="E77">
-        <v>-1.7391304347826086</v>
-      </c>
-      <c r="F77">
-        <v>5.75</v>
-      </c>
       <c r="G77">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="H77">
-        <v>5.6</v>
+        <v>5.65</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -3888,22 +3888,22 @@
         <v>0</v>
       </c>
       <c r="K77">
-        <v>2983045</v>
+        <v>624747</v>
       </c>
       <c r="L77">
-        <v>16843.8995</v>
+        <v>3543.2245</v>
       </c>
       <c r="M77">
-        <v>1030700</v>
+        <v>286400</v>
       </c>
       <c r="N77">
-        <v>5.6</v>
+        <v>5.65</v>
       </c>
       <c r="O77">
-        <v>5.65</v>
+        <v>5.7</v>
       </c>
       <c r="P77">
-        <v>64900</v>
+        <v>229700</v>
       </c>
     </row>
     <row r="78">
@@ -3914,19 +3914,19 @@
         <v>-</v>
       </c>
       <c r="C78">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>-2.459016393442623</v>
       </c>
       <c r="F78">
-        <v>6</v>
+        <v>6.15</v>
       </c>
       <c r="G78">
-        <v>6.05</v>
+        <v>6.15</v>
       </c>
       <c r="H78">
         <v>5.95</v>
@@ -3938,13 +3938,13 @@
         <v>0</v>
       </c>
       <c r="K78">
-        <v>699905</v>
+        <v>1959825</v>
       </c>
       <c r="L78">
-        <v>4198.2055</v>
+        <v>11793.761</v>
       </c>
       <c r="M78">
-        <v>535600</v>
+        <v>537200</v>
       </c>
       <c r="N78">
         <v>5.95</v>
@@ -3953,7 +3953,7 @@
         <v>6</v>
       </c>
       <c r="P78">
-        <v>149800</v>
+        <v>118100</v>
       </c>
     </row>
     <row r="79">
@@ -3964,22 +3964,22 @@
         <v>-</v>
       </c>
       <c r="C79">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>3.896103896103896</v>
       </c>
       <c r="F79">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="G79">
-        <v>23.2</v>
+        <v>24</v>
       </c>
       <c r="H79">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -3988,22 +3988,22 @@
         <v>0</v>
       </c>
       <c r="K79">
-        <v>392606</v>
+        <v>1725770</v>
       </c>
       <c r="L79">
-        <v>9030.670699999999</v>
+        <v>40751.6852</v>
       </c>
       <c r="M79">
-        <v>68200</v>
+        <v>29000</v>
       </c>
       <c r="N79">
-        <v>22.8</v>
+        <v>23.9</v>
       </c>
       <c r="O79">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="P79">
-        <v>22100</v>
+        <v>197300</v>
       </c>
     </row>
     <row r="80">
@@ -4014,22 +4014,22 @@
         <v>-</v>
       </c>
       <c r="C80">
-        <v>42.5</v>
+        <v>42</v>
       </c>
       <c r="D80">
-        <v>-0.75</v>
+        <v>-0.5</v>
       </c>
       <c r="E80">
-        <v>-1.7341040462427746</v>
+        <v>-1.1764705882352942</v>
       </c>
       <c r="F80">
-        <v>43.25</v>
+        <v>42.25</v>
       </c>
       <c r="G80">
-        <v>43.25</v>
+        <v>42.25</v>
       </c>
       <c r="H80">
-        <v>42.25</v>
+        <v>41.75</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -4038,22 +4038,22 @@
         <v>0</v>
       </c>
       <c r="K80">
-        <v>28801</v>
+        <v>24400</v>
       </c>
       <c r="L80">
-        <v>1224.268</v>
+        <v>1023.725</v>
       </c>
       <c r="M80">
-        <v>5500</v>
+        <v>4700</v>
       </c>
       <c r="N80">
-        <v>42.5</v>
+        <v>41.75</v>
       </c>
       <c r="O80">
-        <v>42.75</v>
+        <v>42</v>
       </c>
       <c r="P80">
-        <v>6000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="81">
@@ -4064,22 +4064,22 @@
         <v>-</v>
       </c>
       <c r="C81">
+        <v>1.12</v>
+      </c>
+      <c r="D81">
+        <v>0.02</v>
+      </c>
+      <c r="E81">
+        <v>1.8181818181818181</v>
+      </c>
+      <c r="F81">
         <v>1.11</v>
       </c>
-      <c r="D81">
-        <v>-0.02</v>
-      </c>
-      <c r="E81">
-        <v>-1.7699115044247788</v>
-      </c>
-      <c r="F81">
-        <v>1.13</v>
-      </c>
       <c r="G81">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="H81">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -4088,13 +4088,13 @@
         <v>0</v>
       </c>
       <c r="K81">
-        <v>11782200</v>
+        <v>6268405</v>
       </c>
       <c r="L81">
-        <v>13207.004</v>
+        <v>6965.0455999999995</v>
       </c>
       <c r="M81">
-        <v>5646300</v>
+        <v>6890900</v>
       </c>
       <c r="N81">
         <v>1.11</v>
@@ -4103,7 +4103,7 @@
         <v>1.12</v>
       </c>
       <c r="P81">
-        <v>1637500</v>
+        <v>1154100</v>
       </c>
     </row>
     <row r="82">
@@ -4123,14 +4123,14 @@
         <v>0</v>
       </c>
       <c r="F82">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G82">
+        <v>2</v>
+      </c>
+      <c r="H82">
         <v>1.99</v>
       </c>
-      <c r="H82">
-        <v>1.98</v>
-      </c>
       <c r="I82">
         <v>0</v>
       </c>
@@ -4138,13 +4138,13 @@
         <v>0</v>
       </c>
       <c r="K82">
-        <v>180400</v>
+        <v>229111</v>
       </c>
       <c r="L82">
-        <v>357.94</v>
+        <v>456.00089</v>
       </c>
       <c r="M82">
-        <v>13000</v>
+        <v>159300</v>
       </c>
       <c r="N82">
         <v>1.98</v>
@@ -4153,7 +4153,7 @@
         <v>1.99</v>
       </c>
       <c r="P82">
-        <v>447200</v>
+        <v>28600</v>
       </c>
     </row>
     <row r="83">
@@ -4164,23 +4164,23 @@
         <v>-</v>
       </c>
       <c r="C83">
-        <v>3.44</v>
+        <v>3.58</v>
       </c>
       <c r="D83">
-        <v>0.02</v>
+        <v>0.12</v>
       </c>
       <c r="E83">
-        <v>0.5847953216374269</v>
+        <v>3.468208092485549</v>
       </c>
       <c r="F83">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="G83">
+        <v>3.6</v>
+      </c>
+      <c r="H83">
         <v>3.46</v>
       </c>
-      <c r="H83">
-        <v>3.44</v>
-      </c>
       <c r="I83">
         <v>0</v>
       </c>
@@ -4188,22 +4188,22 @@
         <v>0</v>
       </c>
       <c r="K83">
-        <v>234504</v>
+        <v>5314524</v>
       </c>
       <c r="L83">
-        <v>807.46182</v>
+        <v>18871.75614</v>
       </c>
       <c r="M83">
-        <v>67000</v>
+        <v>167300</v>
       </c>
       <c r="N83">
-        <v>3.44</v>
+        <v>3.56</v>
       </c>
       <c r="O83">
-        <v>3.46</v>
+        <v>3.58</v>
       </c>
       <c r="P83">
-        <v>122700</v>
+        <v>115800</v>
       </c>
     </row>
     <row r="84">
@@ -4214,19 +4214,19 @@
         <v>-</v>
       </c>
       <c r="C84">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="D84">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E84">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="F84">
         <v>0.4</v>
       </c>
       <c r="G84">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="H84">
         <v>0.4</v>
@@ -4238,22 +4238,22 @@
         <v>0</v>
       </c>
       <c r="K84">
-        <v>1488049</v>
+        <v>70870555</v>
       </c>
       <c r="L84">
-        <v>608.86526</v>
+        <v>29967.50557</v>
       </c>
       <c r="M84">
-        <v>14476500</v>
+        <v>35927500</v>
       </c>
       <c r="N84">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="O84">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="P84">
-        <v>21799400</v>
+        <v>2708400</v>
       </c>
     </row>
     <row r="85">
@@ -4267,19 +4267,19 @@
         <v>3.8</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>-0.5235602094240838</v>
       </c>
       <c r="F85">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="G85">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="H85">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -4288,13 +4288,13 @@
         <v>0</v>
       </c>
       <c r="K85">
-        <v>1069206</v>
+        <v>695401</v>
       </c>
       <c r="L85">
-        <v>4041.70924</v>
+        <v>2636.5717999999997</v>
       </c>
       <c r="M85">
-        <v>8900</v>
+        <v>30900</v>
       </c>
       <c r="N85">
         <v>3.78</v>
@@ -4303,7 +4303,7 @@
         <v>3.8</v>
       </c>
       <c r="P85">
-        <v>117400</v>
+        <v>39400</v>
       </c>
     </row>
     <row r="86">
@@ -4314,22 +4314,22 @@
         <v>-</v>
       </c>
       <c r="C86">
-        <v>9.15</v>
+        <v>9.25</v>
       </c>
       <c r="D86">
-        <v>-0.3</v>
+        <v>0.05</v>
       </c>
       <c r="E86">
-        <v>-3.1746031746031744</v>
+        <v>0.5434782608695652</v>
       </c>
       <c r="F86">
-        <v>9.45</v>
+        <v>9.25</v>
       </c>
       <c r="G86">
-        <v>9.5</v>
+        <v>9.3</v>
       </c>
       <c r="H86">
-        <v>9.1</v>
+        <v>9.2</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -4338,22 +4338,22 @@
         <v>0</v>
       </c>
       <c r="K86">
-        <v>4786935</v>
+        <v>1075296</v>
       </c>
       <c r="L86">
-        <v>44291.577549999995</v>
+        <v>9945.932949999999</v>
       </c>
       <c r="M86">
-        <v>182600</v>
+        <v>1332100</v>
       </c>
       <c r="N86">
-        <v>9.15</v>
+        <v>9.2</v>
       </c>
       <c r="O86">
-        <v>9.2</v>
+        <v>9.25</v>
       </c>
       <c r="P86">
-        <v>177100</v>
+        <v>119800</v>
       </c>
     </row>
     <row r="87">
@@ -4364,22 +4364,22 @@
         <v>-</v>
       </c>
       <c r="C87">
-        <v>9.75</v>
+        <v>9.6</v>
       </c>
       <c r="D87">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="E87">
-        <v>0.5154639175257731</v>
+        <v>-1.0309278350515463</v>
       </c>
       <c r="F87">
-        <v>9.75</v>
+        <v>9.7</v>
       </c>
       <c r="G87">
-        <v>9.75</v>
+        <v>9.7</v>
       </c>
       <c r="H87">
-        <v>9.7</v>
+        <v>9.6</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -4388,22 +4388,22 @@
         <v>0</v>
       </c>
       <c r="K87">
-        <v>88412</v>
+        <v>17605</v>
       </c>
       <c r="L87">
-        <v>860.3165</v>
+        <v>169.8885</v>
       </c>
       <c r="M87">
-        <v>9100</v>
+        <v>58700</v>
       </c>
       <c r="N87">
-        <v>9.7</v>
+        <v>9.6</v>
       </c>
       <c r="O87">
-        <v>9.75</v>
+        <v>9.65</v>
       </c>
       <c r="P87">
-        <v>25700</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="88">
@@ -4414,19 +4414,19 @@
         <v>-</v>
       </c>
       <c r="C88">
-        <v>20.4</v>
+        <v>20</v>
       </c>
       <c r="D88">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="E88">
-        <v>2</v>
+        <v>-0.4975124378109453</v>
       </c>
       <c r="F88">
         <v>19.9</v>
       </c>
       <c r="G88">
-        <v>20.5</v>
+        <v>20.1</v>
       </c>
       <c r="H88">
         <v>19.8</v>
@@ -4438,22 +4438,22 @@
         <v>0</v>
       </c>
       <c r="K88">
-        <v>1746974</v>
+        <v>362861</v>
       </c>
       <c r="L88">
-        <v>35296.6979</v>
+        <v>7246.95</v>
       </c>
       <c r="M88">
-        <v>118600</v>
+        <v>98700</v>
       </c>
       <c r="N88">
-        <v>20.3</v>
+        <v>19.9</v>
       </c>
       <c r="O88">
-        <v>20.4</v>
+        <v>20</v>
       </c>
       <c r="P88">
-        <v>36100</v>
+        <v>11900</v>
       </c>
     </row>
     <row r="89">
@@ -4464,22 +4464,22 @@
         <v>-</v>
       </c>
       <c r="C89">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="D89">
         <v>0.02</v>
       </c>
       <c r="E89">
-        <v>1.3157894736842106</v>
+        <v>1.2903225806451613</v>
       </c>
       <c r="F89">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="G89">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="H89">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -4488,22 +4488,22 @@
         <v>0</v>
       </c>
       <c r="K89">
-        <v>14824705</v>
+        <v>3439450</v>
       </c>
       <c r="L89">
-        <v>23630.8785</v>
+        <v>5459.583</v>
       </c>
       <c r="M89">
-        <v>1200</v>
+        <v>290200</v>
       </c>
       <c r="N89">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="O89">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="P89">
-        <v>208100</v>
+        <v>84300</v>
       </c>
     </row>
     <row r="90">
@@ -4514,22 +4514,22 @@
         <v>-</v>
       </c>
       <c r="C90">
+        <v>7.85</v>
+      </c>
+      <c r="D90">
+        <v>0.05</v>
+      </c>
+      <c r="E90">
+        <v>0.6410256410256411</v>
+      </c>
+      <c r="F90">
+        <v>7.85</v>
+      </c>
+      <c r="G90">
         <v>7.9</v>
       </c>
-      <c r="D90">
-        <v>0.15</v>
-      </c>
-      <c r="E90">
-        <v>1.935483870967742</v>
-      </c>
-      <c r="F90">
-        <v>7.7</v>
-      </c>
-      <c r="G90">
-        <v>7.95</v>
-      </c>
       <c r="H90">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -4538,22 +4538,22 @@
         <v>0</v>
       </c>
       <c r="K90">
-        <v>6889683</v>
+        <v>1972647</v>
       </c>
       <c r="L90">
-        <v>53788.1972</v>
+        <v>15431.817949999999</v>
       </c>
       <c r="M90">
-        <v>206600</v>
+        <v>539400</v>
       </c>
       <c r="N90">
+        <v>7.8</v>
+      </c>
+      <c r="O90">
         <v>7.85</v>
       </c>
-      <c r="O90">
-        <v>7.9</v>
-      </c>
       <c r="P90">
-        <v>406400</v>
+        <v>178800</v>
       </c>
     </row>
     <row r="91">
@@ -4564,46 +4564,46 @@
         <v>-</v>
       </c>
       <c r="C91">
-        <v>4.34</v>
+        <v>4.4</v>
       </c>
       <c r="D91">
-        <v>-0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E91">
-        <v>-0.91324200913242</v>
+        <v>0.45662100456621</v>
       </c>
       <c r="F91">
+        <v>4.42</v>
+      </c>
+      <c r="G91">
+        <v>4.44</v>
+      </c>
+      <c r="H91">
         <v>4.38</v>
       </c>
-      <c r="G91">
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>85150</v>
+      </c>
+      <c r="L91">
+        <v>374.869</v>
+      </c>
+      <c r="M91">
+        <v>7300</v>
+      </c>
+      <c r="N91">
         <v>4.4</v>
       </c>
-      <c r="H91">
-        <v>4.32</v>
-      </c>
-      <c r="I91">
-        <v>0</v>
-      </c>
-      <c r="J91">
-        <v>0</v>
-      </c>
-      <c r="K91">
-        <v>340806</v>
-      </c>
-      <c r="L91">
-        <v>1483.4401599999999</v>
-      </c>
-      <c r="M91">
-        <v>55300</v>
-      </c>
-      <c r="N91">
-        <v>4.34</v>
-      </c>
       <c r="O91">
-        <v>4.36</v>
+        <v>4.42</v>
       </c>
       <c r="P91">
-        <v>66600</v>
+        <v>17500</v>
       </c>
     </row>
     <row r="92">
@@ -4617,20 +4617,20 @@
         <v>1.22</v>
       </c>
       <c r="D92">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="E92">
-        <v>0.8264462809917356</v>
+        <v>-0.8130081300813008</v>
       </c>
       <c r="F92">
+        <v>1.23</v>
+      </c>
+      <c r="G92">
+        <v>1.23</v>
+      </c>
+      <c r="H92">
         <v>1.22</v>
       </c>
-      <c r="G92">
-        <v>1.24</v>
-      </c>
-      <c r="H92">
-        <v>1.21</v>
-      </c>
       <c r="I92">
         <v>0</v>
       </c>
@@ -4638,13 +4638,13 @@
         <v>0</v>
       </c>
       <c r="K92">
-        <v>18257954</v>
+        <v>5585437</v>
       </c>
       <c r="L92">
-        <v>22381.15319</v>
+        <v>6833.5833</v>
       </c>
       <c r="M92">
-        <v>1389300</v>
+        <v>1159900</v>
       </c>
       <c r="N92">
         <v>1.22</v>
@@ -4653,7 +4653,7 @@
         <v>1.23</v>
       </c>
       <c r="P92">
-        <v>2334700</v>
+        <v>1361500</v>
       </c>
     </row>
     <row r="93">
@@ -4664,46 +4664,46 @@
         <v>-</v>
       </c>
       <c r="C93">
+        <v>30.75</v>
+      </c>
+      <c r="D93">
+        <v>0.25</v>
+      </c>
+      <c r="E93">
+        <v>0.819672131147541</v>
+      </c>
+      <c r="F93">
+        <v>30.75</v>
+      </c>
+      <c r="G93">
+        <v>30.75</v>
+      </c>
+      <c r="H93">
         <v>30.5</v>
       </c>
-      <c r="D93">
-        <v>0</v>
-      </c>
-      <c r="E93">
-        <v>0</v>
-      </c>
-      <c r="F93">
-        <v>30.25</v>
-      </c>
-      <c r="G93">
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>48513</v>
+      </c>
+      <c r="L93">
+        <v>1483.43725</v>
+      </c>
+      <c r="M93">
+        <v>68500</v>
+      </c>
+      <c r="N93">
         <v>30.5</v>
       </c>
-      <c r="H93">
-        <v>30</v>
-      </c>
-      <c r="I93">
-        <v>0</v>
-      </c>
-      <c r="J93">
-        <v>0</v>
-      </c>
-      <c r="K93">
-        <v>117332</v>
-      </c>
-      <c r="L93">
-        <v>3552.12125</v>
-      </c>
-      <c r="M93">
-        <v>107500</v>
-      </c>
-      <c r="N93">
-        <v>30.25</v>
-      </c>
       <c r="O93">
-        <v>30.5</v>
+        <v>30.75</v>
       </c>
       <c r="P93">
-        <v>60500</v>
+        <v>49000</v>
       </c>
     </row>
     <row r="94">
@@ -4723,7 +4723,7 @@
         <v>1.36986301369863</v>
       </c>
       <c r="F94">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="G94">
         <v>0.74</v>
@@ -4738,13 +4738,13 @@
         <v>0</v>
       </c>
       <c r="K94">
-        <v>513101</v>
+        <v>4190200</v>
       </c>
       <c r="L94">
-        <v>375.31475</v>
+        <v>3058.959</v>
       </c>
       <c r="M94">
-        <v>1622100</v>
+        <v>224800</v>
       </c>
       <c r="N94">
         <v>0.73</v>
@@ -4753,7 +4753,7 @@
         <v>0.74</v>
       </c>
       <c r="P94">
-        <v>1487500</v>
+        <v>998900</v>
       </c>
     </row>
     <row r="95">
@@ -4764,22 +4764,22 @@
         <v>-</v>
       </c>
       <c r="C95">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="D95">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="E95">
-        <v>-0.8130081300813008</v>
+        <v>0.7751937984496124</v>
       </c>
       <c r="F95">
-        <v>6.25</v>
+        <v>6.45</v>
       </c>
       <c r="G95">
-        <v>6.25</v>
+        <v>6.6</v>
       </c>
       <c r="H95">
-        <v>6.1</v>
+        <v>6.45</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -4788,22 +4788,22 @@
         <v>0</v>
       </c>
       <c r="K95">
-        <v>376007</v>
+        <v>3012817</v>
       </c>
       <c r="L95">
-        <v>2302.70415</v>
+        <v>19612.27495</v>
       </c>
       <c r="M95">
-        <v>208300</v>
+        <v>449100</v>
       </c>
       <c r="N95">
-        <v>6.1</v>
+        <v>6.45</v>
       </c>
       <c r="O95">
-        <v>6.15</v>
+        <v>6.5</v>
       </c>
       <c r="P95">
-        <v>219200</v>
+        <v>25500</v>
       </c>
     </row>
     <row r="96">
@@ -4814,16 +4814,16 @@
         <v>-</v>
       </c>
       <c r="C96">
+        <v>6.35</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
         <v>6.4</v>
-      </c>
-      <c r="D96">
-        <v>0.1</v>
-      </c>
-      <c r="E96">
-        <v>1.5873015873015872</v>
-      </c>
-      <c r="F96">
-        <v>6.35</v>
       </c>
       <c r="G96">
         <v>6.4</v>
@@ -4838,13 +4838,13 @@
         <v>0</v>
       </c>
       <c r="K96">
-        <v>311300</v>
+        <v>111526</v>
       </c>
       <c r="L96">
-        <v>1977.85</v>
+        <v>708.2414</v>
       </c>
       <c r="M96">
-        <v>83100</v>
+        <v>3000</v>
       </c>
       <c r="N96">
         <v>6.35</v>
@@ -4853,7 +4853,7 @@
         <v>6.4</v>
       </c>
       <c r="P96">
-        <v>210700</v>
+        <v>156400</v>
       </c>
     </row>
     <row r="97">
@@ -4864,22 +4864,22 @@
         <v>-</v>
       </c>
       <c r="C97">
-        <v>16.6</v>
+        <v>17.3</v>
       </c>
       <c r="D97">
-        <v>-0.1</v>
+        <v>0.5</v>
       </c>
       <c r="E97">
-        <v>-0.5988023952095808</v>
+        <v>2.9761904761904763</v>
       </c>
       <c r="F97">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="G97">
-        <v>16.8</v>
+        <v>17.3</v>
       </c>
       <c r="H97">
-        <v>16.4</v>
+        <v>17</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -4888,22 +4888,22 @@
         <v>0</v>
       </c>
       <c r="K97">
-        <v>3886420</v>
+        <v>10289980</v>
       </c>
       <c r="L97">
-        <v>64587.191399999996</v>
+        <v>176632.6249</v>
       </c>
       <c r="M97">
-        <v>209300</v>
+        <v>82900</v>
       </c>
       <c r="N97">
-        <v>16.5</v>
+        <v>17.3</v>
       </c>
       <c r="O97">
-        <v>16.6</v>
+        <v>17.4</v>
       </c>
       <c r="P97">
-        <v>110300</v>
+        <v>1169500</v>
       </c>
     </row>
     <row r="98">
@@ -4914,23 +4914,23 @@
         <v>-</v>
       </c>
       <c r="C98">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="D98">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="E98">
-        <v>2.0202020202020203</v>
+        <v>0</v>
       </c>
       <c r="F98">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="G98">
+        <v>2.1</v>
+      </c>
+      <c r="H98">
         <v>2.04</v>
       </c>
-      <c r="H98">
-        <v>1.96</v>
-      </c>
       <c r="I98">
         <v>0</v>
       </c>
@@ -4938,22 +4938,22 @@
         <v>0</v>
       </c>
       <c r="K98">
-        <v>14825005</v>
+        <v>23570693</v>
       </c>
       <c r="L98">
-        <v>29488.94</v>
+        <v>48552.15958</v>
       </c>
       <c r="M98">
-        <v>412400</v>
+        <v>1000</v>
       </c>
       <c r="N98">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="O98">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="P98">
-        <v>1469700</v>
+        <v>1344400</v>
       </c>
     </row>
     <row r="99">
@@ -4964,19 +4964,19 @@
         <v>-</v>
       </c>
       <c r="C99">
+        <v>5.2</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>5.2</v>
+      </c>
+      <c r="G99">
         <v>5.25</v>
-      </c>
-      <c r="D99">
-        <v>0.05</v>
-      </c>
-      <c r="E99">
-        <v>0.9615384615384616</v>
-      </c>
-      <c r="F99">
-        <v>5.25</v>
-      </c>
-      <c r="G99">
-        <v>5.3</v>
       </c>
       <c r="H99">
         <v>5.2</v>
@@ -4988,13 +4988,13 @@
         <v>0</v>
       </c>
       <c r="K99">
-        <v>94500</v>
+        <v>160000</v>
       </c>
       <c r="L99">
-        <v>492.445</v>
+        <v>832.1</v>
       </c>
       <c r="M99">
-        <v>77900</v>
+        <v>27200</v>
       </c>
       <c r="N99">
         <v>5.2</v>
@@ -5003,7 +5003,7 @@
         <v>5.25</v>
       </c>
       <c r="P99">
-        <v>100</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="100">
@@ -5014,46 +5014,46 @@
         <v>-</v>
       </c>
       <c r="C100">
+        <v>26.25</v>
+      </c>
+      <c r="D100">
+        <v>0.25</v>
+      </c>
+      <c r="E100">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="F100">
+        <v>26.25</v>
+      </c>
+      <c r="G100">
+        <v>26.25</v>
+      </c>
+      <c r="H100">
+        <v>25.75</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>576701</v>
+      </c>
+      <c r="L100">
+        <v>14949.726</v>
+      </c>
+      <c r="M100">
+        <v>45500</v>
+      </c>
+      <c r="N100">
         <v>26</v>
       </c>
-      <c r="D100">
-        <v>0.75</v>
-      </c>
-      <c r="E100">
-        <v>2.9702970297029703</v>
-      </c>
-      <c r="F100">
-        <v>25.25</v>
-      </c>
-      <c r="G100">
-        <v>26</v>
-      </c>
-      <c r="H100">
-        <v>25.25</v>
-      </c>
-      <c r="I100">
-        <v>0</v>
-      </c>
-      <c r="J100">
-        <v>0</v>
-      </c>
-      <c r="K100">
-        <v>1013668</v>
-      </c>
-      <c r="L100">
-        <v>26058.52975</v>
-      </c>
-      <c r="M100">
-        <v>123200</v>
-      </c>
-      <c r="N100">
-        <v>25.75</v>
-      </c>
       <c r="O100">
-        <v>26</v>
+        <v>26.25</v>
       </c>
       <c r="P100">
-        <v>468500</v>
+        <v>91200</v>
       </c>
     </row>
     <row r="101">
@@ -5064,22 +5064,22 @@
         <v>-</v>
       </c>
       <c r="C101">
-        <v>6.35</v>
+        <v>7.1</v>
       </c>
       <c r="D101">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="E101">
-        <v>4.098360655737705</v>
+        <v>1.4285714285714286</v>
       </c>
       <c r="F101">
-        <v>6.15</v>
+        <v>6.95</v>
       </c>
       <c r="G101">
-        <v>6.35</v>
+        <v>7.15</v>
       </c>
       <c r="H101">
-        <v>6.15</v>
+        <v>6.95</v>
       </c>
       <c r="I101">
         <v>0</v>
@@ -5088,22 +5088,22 @@
         <v>0</v>
       </c>
       <c r="K101">
-        <v>1639776</v>
+        <v>3897052</v>
       </c>
       <c r="L101">
-        <v>10231.798449999998</v>
+        <v>27407.597850000002</v>
       </c>
       <c r="M101">
-        <v>185200</v>
+        <v>31700</v>
       </c>
       <c r="N101">
-        <v>6.3</v>
+        <v>7.1</v>
       </c>
       <c r="O101">
-        <v>6.35</v>
+        <v>7.15</v>
       </c>
       <c r="P101">
-        <v>118200</v>
+        <v>223700</v>
       </c>
     </row>
     <row r="102">
@@ -5114,22 +5114,22 @@
         <v>-</v>
       </c>
       <c r="C102">
-        <v>5.45</v>
+        <v>5.7</v>
       </c>
       <c r="D102">
-        <v>-0.15</v>
+        <v>0.05</v>
       </c>
       <c r="E102">
-        <v>-2.6785714285714284</v>
+        <v>0.8849557522123894</v>
       </c>
       <c r="F102">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="G102">
-        <v>5.55</v>
+        <v>6</v>
       </c>
       <c r="H102">
-        <v>5.4</v>
+        <v>5.65</v>
       </c>
       <c r="I102">
         <v>0</v>
@@ -5138,22 +5138,22 @@
         <v>0</v>
       </c>
       <c r="K102">
-        <v>2852000</v>
+        <v>16569929</v>
       </c>
       <c r="L102">
-        <v>15562.385</v>
+        <v>96573.90879999999</v>
       </c>
       <c r="M102">
-        <v>951400</v>
+        <v>692300</v>
       </c>
       <c r="N102">
-        <v>5.4</v>
+        <v>5.65</v>
       </c>
       <c r="O102">
-        <v>5.45</v>
+        <v>5.7</v>
       </c>
       <c r="P102">
-        <v>38600</v>
+        <v>145200</v>
       </c>
     </row>
     <row r="103">
@@ -5164,22 +5164,22 @@
         <v>-</v>
       </c>
       <c r="C103">
-        <v>46.75</v>
+        <v>47</v>
       </c>
       <c r="D103">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="E103">
-        <v>-0.5319148936170213</v>
+        <v>0</v>
       </c>
       <c r="F103">
+        <v>47</v>
+      </c>
+      <c r="G103">
         <v>47.25</v>
       </c>
-      <c r="G103">
-        <v>47.5</v>
-      </c>
       <c r="H103">
-        <v>46.75</v>
+        <v>46.5</v>
       </c>
       <c r="I103">
         <v>0</v>
@@ -5188,13 +5188,13 @@
         <v>0</v>
       </c>
       <c r="K103">
-        <v>336339</v>
+        <v>175409</v>
       </c>
       <c r="L103">
-        <v>15827.709</v>
+        <v>8221.47525</v>
       </c>
       <c r="M103">
-        <v>116600</v>
+        <v>37000</v>
       </c>
       <c r="N103">
         <v>46.75</v>
@@ -5203,7 +5203,7 @@
         <v>47</v>
       </c>
       <c r="P103">
-        <v>45000</v>
+        <v>17600</v>
       </c>
     </row>
     <row r="104">
@@ -5229,31 +5229,31 @@
         <v>21.5</v>
       </c>
       <c r="H104">
+        <v>21.2</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>380833</v>
+      </c>
+      <c r="L104">
+        <v>8121.3893</v>
+      </c>
+      <c r="M104">
+        <v>37800</v>
+      </c>
+      <c r="N104">
         <v>21.3</v>
       </c>
-      <c r="I104">
-        <v>0</v>
-      </c>
-      <c r="J104">
-        <v>0</v>
-      </c>
-      <c r="K104">
-        <v>596423</v>
-      </c>
-      <c r="L104">
-        <v>12768.0945</v>
-      </c>
-      <c r="M104">
-        <v>45400</v>
-      </c>
-      <c r="N104">
+      <c r="O104">
         <v>21.4</v>
       </c>
-      <c r="O104">
-        <v>21.5</v>
-      </c>
       <c r="P104">
-        <v>257600</v>
+        <v>23800</v>
       </c>
     </row>
     <row r="105">
@@ -5264,46 +5264,46 @@
         <v>-</v>
       </c>
       <c r="C105">
-        <v>4.76</v>
+        <v>4.7</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>0.42735042735042733</v>
       </c>
       <c r="F105">
-        <v>4.74</v>
+        <v>4.72</v>
       </c>
       <c r="G105">
-        <v>4.76</v>
+        <v>4.72</v>
       </c>
       <c r="H105">
+        <v>4.62</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>4342886</v>
+      </c>
+      <c r="L105">
+        <v>20281.8805</v>
+      </c>
+      <c r="M105">
+        <v>206600</v>
+      </c>
+      <c r="N105">
         <v>4.68</v>
       </c>
-      <c r="I105">
-        <v>0</v>
-      </c>
-      <c r="J105">
-        <v>0</v>
-      </c>
-      <c r="K105">
-        <v>8404919</v>
-      </c>
-      <c r="L105">
-        <v>39601.45078</v>
-      </c>
-      <c r="M105">
-        <v>399400</v>
-      </c>
-      <c r="N105">
-        <v>4.74</v>
-      </c>
       <c r="O105">
-        <v>4.76</v>
+        <v>4.7</v>
       </c>
       <c r="P105">
-        <v>391500</v>
+        <v>353900</v>
       </c>
     </row>
     <row r="106">
@@ -5314,19 +5314,19 @@
         <v>-</v>
       </c>
       <c r="C106">
+        <v>5.9</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106">
         <v>5.85</v>
       </c>
-      <c r="D106">
-        <v>-0.1</v>
-      </c>
-      <c r="E106">
-        <v>-1.680672268907563</v>
-      </c>
-      <c r="F106">
-        <v>6</v>
-      </c>
       <c r="G106">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H106">
         <v>5.85</v>
@@ -5338,22 +5338,22 @@
         <v>0</v>
       </c>
       <c r="K106">
-        <v>78877</v>
+        <v>16401</v>
       </c>
       <c r="L106">
-        <v>464.77465</v>
+        <v>96.7559</v>
       </c>
       <c r="M106">
-        <v>15400</v>
+        <v>9900</v>
       </c>
       <c r="N106">
-        <v>5.85</v>
+        <v>5.9</v>
       </c>
       <c r="O106">
-        <v>5.9</v>
+        <v>5.95</v>
       </c>
       <c r="P106">
-        <v>9300</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="107">
@@ -5364,22 +5364,22 @@
         <v>-</v>
       </c>
       <c r="C107">
-        <v>3.94</v>
+        <v>4.04</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>0.4975124378109453</v>
       </c>
       <c r="F107">
-        <v>3.94</v>
+        <v>4.04</v>
       </c>
       <c r="G107">
-        <v>3.96</v>
+        <v>4.06</v>
       </c>
       <c r="H107">
-        <v>3.94</v>
+        <v>4.02</v>
       </c>
       <c r="I107">
         <v>0</v>
@@ -5388,22 +5388,22 @@
         <v>0</v>
       </c>
       <c r="K107">
-        <v>2025431</v>
+        <v>1383374</v>
       </c>
       <c r="L107">
-        <v>8006.312980000001</v>
+        <v>5591.31502</v>
       </c>
       <c r="M107">
-        <v>394100</v>
+        <v>222700</v>
       </c>
       <c r="N107">
-        <v>3.94</v>
+        <v>4.02</v>
       </c>
       <c r="O107">
-        <v>3.96</v>
+        <v>4.04</v>
       </c>
       <c r="P107">
-        <v>587400</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="108">
@@ -5414,46 +5414,46 @@
         <v>-</v>
       </c>
       <c r="C108">
-        <v>4.38</v>
+        <v>4.44</v>
       </c>
       <c r="D108">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E108">
-        <v>-0.45454545454545453</v>
+        <v>0</v>
       </c>
       <c r="F108">
-        <v>4.4</v>
+        <v>4.44</v>
       </c>
       <c r="G108">
+        <v>4.48</v>
+      </c>
+      <c r="H108">
+        <v>4.42</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108">
+        <v>4074800</v>
+      </c>
+      <c r="L108">
+        <v>18138.34</v>
+      </c>
+      <c r="M108">
+        <v>352000</v>
+      </c>
+      <c r="N108">
         <v>4.44</v>
       </c>
-      <c r="H108">
-        <v>4.36</v>
-      </c>
-      <c r="I108">
-        <v>0</v>
-      </c>
-      <c r="J108">
-        <v>0</v>
-      </c>
-      <c r="K108">
-        <v>6020387</v>
-      </c>
-      <c r="L108">
-        <v>26455.173300000002</v>
-      </c>
-      <c r="M108">
-        <v>144900</v>
-      </c>
-      <c r="N108">
-        <v>4.38</v>
-      </c>
       <c r="O108">
-        <v>4.4</v>
+        <v>4.46</v>
       </c>
       <c r="P108">
-        <v>218700</v>
+        <v>113500</v>
       </c>
     </row>
     <row r="109">
@@ -5464,22 +5464,22 @@
         <v>-</v>
       </c>
       <c r="C109">
-        <v>27</v>
+        <v>27.25</v>
       </c>
       <c r="D109">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E109">
-        <v>0.9345794392523364</v>
+        <v>0</v>
       </c>
       <c r="F109">
-        <v>26.75</v>
+        <v>27.25</v>
       </c>
       <c r="G109">
         <v>27.25</v>
       </c>
       <c r="H109">
-        <v>26.75</v>
+        <v>27</v>
       </c>
       <c r="I109">
         <v>0</v>
@@ -5488,22 +5488,22 @@
         <v>0</v>
       </c>
       <c r="K109">
-        <v>201018</v>
+        <v>68701</v>
       </c>
       <c r="L109">
-        <v>5405.161</v>
+        <v>1858.07725</v>
       </c>
       <c r="M109">
-        <v>48800</v>
+        <v>27400</v>
       </c>
       <c r="N109">
-        <v>26.75</v>
+        <v>27</v>
       </c>
       <c r="O109">
-        <v>27</v>
+        <v>27.25</v>
       </c>
       <c r="P109">
-        <v>25800</v>
+        <v>37400</v>
       </c>
     </row>
     <row r="110">
@@ -5514,23 +5514,23 @@
         <v>-</v>
       </c>
       <c r="C110">
+        <v>1.7</v>
+      </c>
+      <c r="D110">
+        <v>-0.02</v>
+      </c>
+      <c r="E110">
+        <v>-1.1627906976744187</v>
+      </c>
+      <c r="F110">
         <v>1.72</v>
       </c>
-      <c r="D110">
-        <v>0.05</v>
-      </c>
-      <c r="E110">
-        <v>2.9940119760479043</v>
-      </c>
-      <c r="F110">
+      <c r="G110">
+        <v>1.73</v>
+      </c>
+      <c r="H110">
         <v>1.69</v>
       </c>
-      <c r="G110">
-        <v>1.72</v>
-      </c>
-      <c r="H110">
-        <v>1.68</v>
-      </c>
       <c r="I110">
         <v>0</v>
       </c>
@@ -5538,22 +5538,22 @@
         <v>0</v>
       </c>
       <c r="K110">
-        <v>8426820</v>
+        <v>7771417</v>
       </c>
       <c r="L110">
-        <v>14368.52222</v>
+        <v>13244.86273</v>
       </c>
       <c r="M110">
-        <v>280100</v>
+        <v>204300</v>
       </c>
       <c r="N110">
+        <v>1.7</v>
+      </c>
+      <c r="O110">
         <v>1.71</v>
       </c>
-      <c r="O110">
-        <v>1.72</v>
-      </c>
       <c r="P110">
-        <v>321800</v>
+        <v>143200</v>
       </c>
     </row>
     <row r="111">
@@ -5567,43 +5567,43 @@
         <v>5.3</v>
       </c>
       <c r="D111">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E111">
-        <v>0.9523809523809523</v>
+        <v>0</v>
       </c>
       <c r="F111">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="G111">
         <v>5.35</v>
       </c>
       <c r="H111">
+        <v>5.2</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>106528</v>
+      </c>
+      <c r="L111">
+        <v>559.3073</v>
+      </c>
+      <c r="M111">
+        <v>32100</v>
+      </c>
+      <c r="N111">
         <v>5.25</v>
       </c>
-      <c r="I111">
-        <v>0</v>
-      </c>
-      <c r="J111">
-        <v>0</v>
-      </c>
-      <c r="K111">
-        <v>134102</v>
-      </c>
-      <c r="L111">
-        <v>714.1054</v>
-      </c>
-      <c r="M111">
-        <v>40700</v>
-      </c>
-      <c r="N111">
+      <c r="O111">
         <v>5.3</v>
       </c>
-      <c r="O111">
-        <v>5.35</v>
-      </c>
       <c r="P111">
-        <v>54000</v>
+        <v>43300</v>
       </c>
     </row>
     <row r="112">
@@ -5614,22 +5614,22 @@
         <v>-</v>
       </c>
       <c r="C112">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>0.9174311926605505</v>
       </c>
       <c r="F112">
-        <v>21</v>
+        <v>21.5</v>
       </c>
       <c r="G112">
-        <v>21.1</v>
+        <v>22.2</v>
       </c>
       <c r="H112">
-        <v>20.7</v>
+        <v>18.4</v>
       </c>
       <c r="I112">
         <v>0</v>
@@ -5638,22 +5638,22 @@
         <v>0</v>
       </c>
       <c r="K112">
-        <v>1661489</v>
+        <v>13984692</v>
       </c>
       <c r="L112">
-        <v>34719.7191</v>
+        <v>291339.16760000004</v>
       </c>
       <c r="M112">
-        <v>40300</v>
+        <v>34000</v>
       </c>
       <c r="N112">
-        <v>20.9</v>
+        <v>21.9</v>
       </c>
       <c r="O112">
-        <v>21.1</v>
+        <v>22</v>
       </c>
       <c r="P112">
-        <v>209100</v>
+        <v>7600</v>
       </c>
     </row>
     <row r="113">
@@ -5664,16 +5664,16 @@
         <v>-</v>
       </c>
       <c r="C113">
+        <v>13.3</v>
+      </c>
+      <c r="D113">
+        <v>-0.1</v>
+      </c>
+      <c r="E113">
+        <v>-0.746268656716418</v>
+      </c>
+      <c r="F113">
         <v>13.4</v>
-      </c>
-      <c r="D113">
-        <v>0.2</v>
-      </c>
-      <c r="E113">
-        <v>1.5151515151515151</v>
-      </c>
-      <c r="F113">
-        <v>13.3</v>
       </c>
       <c r="G113">
         <v>13.4</v>
@@ -5688,13 +5688,13 @@
         <v>0</v>
       </c>
       <c r="K113">
-        <v>184452</v>
+        <v>121035</v>
       </c>
       <c r="L113">
-        <v>2453.7268</v>
+        <v>1610.2784</v>
       </c>
       <c r="M113">
-        <v>21100</v>
+        <v>52100</v>
       </c>
       <c r="N113">
         <v>13.3</v>
@@ -5703,7 +5703,7 @@
         <v>13.4</v>
       </c>
       <c r="P113">
-        <v>93900</v>
+        <v>86600</v>
       </c>
     </row>
     <row r="114">
@@ -5714,22 +5714,22 @@
         <v>-</v>
       </c>
       <c r="C114">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="D114">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E114">
-        <v>3.8461538461538463</v>
+        <v>1.8181818181818181</v>
       </c>
       <c r="F114">
-        <v>5.35</v>
+        <v>5.5</v>
       </c>
       <c r="G114">
-        <v>5.45</v>
+        <v>5.7</v>
       </c>
       <c r="H114">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I114">
         <v>0</v>
@@ -5738,22 +5738,22 @@
         <v>0</v>
       </c>
       <c r="K114">
-        <v>9341584</v>
+        <v>6152041</v>
       </c>
       <c r="L114">
-        <v>50377.874149999996</v>
+        <v>34403.487700000005</v>
       </c>
       <c r="M114">
-        <v>546700</v>
+        <v>96700</v>
       </c>
       <c r="N114">
-        <v>5.35</v>
+        <v>5.6</v>
       </c>
       <c r="O114">
-        <v>5.4</v>
+        <v>5.65</v>
       </c>
       <c r="P114">
-        <v>144000</v>
+        <v>439200</v>
       </c>
     </row>
     <row r="115">
@@ -5764,46 +5764,46 @@
         <v>-</v>
       </c>
       <c r="C115">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="D115">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="E115">
-        <v>0.6993006993006993</v>
+        <v>-0.684931506849315</v>
       </c>
       <c r="F115">
         <v>14.4</v>
       </c>
       <c r="G115">
+        <v>14.6</v>
+      </c>
+      <c r="H115">
+        <v>14.4</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <v>88451</v>
+      </c>
+      <c r="L115">
+        <v>1281.78</v>
+      </c>
+      <c r="M115">
+        <v>8800</v>
+      </c>
+      <c r="N115">
         <v>14.5</v>
       </c>
-      <c r="H115">
-        <v>14.3</v>
-      </c>
-      <c r="I115">
-        <v>0</v>
-      </c>
-      <c r="J115">
-        <v>0</v>
-      </c>
-      <c r="K115">
-        <v>327233</v>
-      </c>
-      <c r="L115">
-        <v>4708.9682999999995</v>
-      </c>
-      <c r="M115">
-        <v>481900</v>
-      </c>
-      <c r="N115">
-        <v>14.3</v>
-      </c>
       <c r="O115">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="P115">
-        <v>13700</v>
+        <v>232500</v>
       </c>
     </row>
     <row r="116">
@@ -5814,22 +5814,22 @@
         <v>-</v>
       </c>
       <c r="C116">
-        <v>9.5</v>
+        <v>9.55</v>
       </c>
       <c r="D116">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="E116">
-        <v>-1.0416666666666667</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="F116">
-        <v>9.6</v>
+        <v>9.55</v>
       </c>
       <c r="G116">
-        <v>9.6</v>
+        <v>9.55</v>
       </c>
       <c r="H116">
-        <v>9.45</v>
+        <v>9.55</v>
       </c>
       <c r="I116">
         <v>0</v>
@@ -5838,22 +5838,22 @@
         <v>0</v>
       </c>
       <c r="K116">
-        <v>301408</v>
+        <v>9655</v>
       </c>
       <c r="L116">
-        <v>2867.2173</v>
+        <v>92.19625</v>
       </c>
       <c r="M116">
-        <v>2400</v>
+        <v>21600</v>
       </c>
       <c r="N116">
         <v>9.5</v>
       </c>
       <c r="O116">
-        <v>9.55</v>
+        <v>9.6</v>
       </c>
       <c r="P116">
-        <v>17000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="117">
@@ -5864,7 +5864,7 @@
         <v>-</v>
       </c>
       <c r="C117">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -5876,34 +5876,34 @@
         <v>14.6</v>
       </c>
       <c r="G117">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="H117">
+        <v>14.5</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>55434</v>
+      </c>
+      <c r="L117">
+        <v>808.4295999999999</v>
+      </c>
+      <c r="M117">
+        <v>203300</v>
+      </c>
+      <c r="N117">
+        <v>14.5</v>
+      </c>
+      <c r="O117">
         <v>14.6</v>
       </c>
-      <c r="I117">
-        <v>0</v>
-      </c>
-      <c r="J117">
-        <v>0</v>
-      </c>
-      <c r="K117">
-        <v>447794</v>
-      </c>
-      <c r="L117">
-        <v>6544.0118</v>
-      </c>
-      <c r="M117">
-        <v>13900</v>
-      </c>
-      <c r="N117">
-        <v>14.6</v>
-      </c>
-      <c r="O117">
-        <v>14.7</v>
-      </c>
       <c r="P117">
-        <v>48800</v>
+        <v>73100</v>
       </c>
     </row>
     <row r="118">
@@ -5914,46 +5914,46 @@
         <v>-</v>
       </c>
       <c r="C118">
+        <v>9.8</v>
+      </c>
+      <c r="D118">
+        <v>0.05</v>
+      </c>
+      <c r="E118">
+        <v>0.5128205128205128</v>
+      </c>
+      <c r="F118">
+        <v>9.8</v>
+      </c>
+      <c r="G118">
+        <v>9.85</v>
+      </c>
+      <c r="H118">
+        <v>9.7</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>80650</v>
+      </c>
+      <c r="L118">
+        <v>787.4644000000001</v>
+      </c>
+      <c r="M118">
+        <v>4100</v>
+      </c>
+      <c r="N118">
         <v>9.75</v>
       </c>
-      <c r="D118">
-        <v>0.1</v>
-      </c>
-      <c r="E118">
-        <v>1.0362694300518134</v>
-      </c>
-      <c r="F118">
-        <v>9.7</v>
-      </c>
-      <c r="G118">
-        <v>9.75</v>
-      </c>
-      <c r="H118">
-        <v>9.5</v>
-      </c>
-      <c r="I118">
-        <v>0</v>
-      </c>
-      <c r="J118">
-        <v>0</v>
-      </c>
-      <c r="K118">
-        <v>197600</v>
-      </c>
-      <c r="L118">
-        <v>1905.45</v>
-      </c>
-      <c r="M118">
-        <v>3000</v>
-      </c>
-      <c r="N118">
-        <v>9.7</v>
-      </c>
       <c r="O118">
-        <v>9.75</v>
+        <v>9.8</v>
       </c>
       <c r="P118">
-        <v>45900</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="119">
@@ -5964,7 +5964,7 @@
         <v>-</v>
       </c>
       <c r="C119">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -5973,7 +5973,7 @@
         <v>0</v>
       </c>
       <c r="F119">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="G119">
         <v>10.1</v>
@@ -5988,13 +5988,13 @@
         <v>0</v>
       </c>
       <c r="K119">
-        <v>1341409</v>
+        <v>441648</v>
       </c>
       <c r="L119">
-        <v>13472.601</v>
+        <v>4417.4496</v>
       </c>
       <c r="M119">
-        <v>717400</v>
+        <v>45100</v>
       </c>
       <c r="N119">
         <v>10</v>
@@ -6003,7 +6003,7 @@
         <v>10.1</v>
       </c>
       <c r="P119">
-        <v>618700</v>
+        <v>324500</v>
       </c>
     </row>
     <row r="120">
@@ -6014,19 +6014,19 @@
         <v>-</v>
       </c>
       <c r="C120">
-        <v>188.5</v>
+        <v>188</v>
       </c>
       <c r="D120">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="E120">
-        <v>0.5333333333333333</v>
+        <v>-0.26525198938992045</v>
       </c>
       <c r="F120">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G120">
-        <v>188.5</v>
+        <v>189</v>
       </c>
       <c r="H120">
         <v>187.5</v>
@@ -6038,13 +6038,13 @@
         <v>0</v>
       </c>
       <c r="K120">
-        <v>10007</v>
+        <v>3687</v>
       </c>
       <c r="L120">
-        <v>1882.5695</v>
+        <v>693.267</v>
       </c>
       <c r="M120">
-        <v>8300</v>
+        <v>400</v>
       </c>
       <c r="N120">
         <v>188</v>
@@ -6053,7 +6053,7 @@
         <v>188.5</v>
       </c>
       <c r="P120">
-        <v>1500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="121">
@@ -6067,19 +6067,19 @@
         <v>5.55</v>
       </c>
       <c r="D121">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="E121">
-        <v>6.730769230769231</v>
+        <v>0</v>
       </c>
       <c r="F121">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="G121">
-        <v>5.65</v>
+        <v>5.6</v>
       </c>
       <c r="H121">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I121">
         <v>0</v>
@@ -6088,22 +6088,22 @@
         <v>0</v>
       </c>
       <c r="K121">
-        <v>16831035</v>
+        <v>2139650</v>
       </c>
       <c r="L121">
-        <v>91524.1082</v>
+        <v>11737.397550000002</v>
       </c>
       <c r="M121">
-        <v>381000</v>
+        <v>149700</v>
       </c>
       <c r="N121">
+        <v>5.5</v>
+      </c>
+      <c r="O121">
         <v>5.55</v>
       </c>
-      <c r="O121">
-        <v>5.6</v>
-      </c>
       <c r="P121">
-        <v>912700</v>
+        <v>136100</v>
       </c>
     </row>
     <row r="122">
@@ -6114,23 +6114,23 @@
         <v>-</v>
       </c>
       <c r="C122">
+        <v>4.7</v>
+      </c>
+      <c r="D122">
+        <v>-0.02</v>
+      </c>
+      <c r="E122">
+        <v>-0.423728813559322</v>
+      </c>
+      <c r="F122">
+        <v>4.74</v>
+      </c>
+      <c r="G122">
+        <v>4.74</v>
+      </c>
+      <c r="H122">
         <v>4.68</v>
       </c>
-      <c r="D122">
-        <v>0.02</v>
-      </c>
-      <c r="E122">
-        <v>0.4291845493562232</v>
-      </c>
-      <c r="F122">
-        <v>4.7</v>
-      </c>
-      <c r="G122">
-        <v>4.7</v>
-      </c>
-      <c r="H122">
-        <v>4.66</v>
-      </c>
       <c r="I122">
         <v>0</v>
       </c>
@@ -6138,13 +6138,13 @@
         <v>0</v>
       </c>
       <c r="K122">
-        <v>266300</v>
+        <v>200000</v>
       </c>
       <c r="L122">
-        <v>1247.39</v>
+        <v>940.926</v>
       </c>
       <c r="M122">
-        <v>129900</v>
+        <v>55700</v>
       </c>
       <c r="N122">
         <v>4.68</v>
@@ -6153,7 +6153,7 @@
         <v>4.7</v>
       </c>
       <c r="P122">
-        <v>13300</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="123">
@@ -6164,46 +6164,46 @@
         <v>-</v>
       </c>
       <c r="C123">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="D123">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="E123">
-        <v>2.6315789473684212</v>
+        <v>0.5235602094240838</v>
       </c>
       <c r="F123">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="G123">
-        <v>3.92</v>
+        <v>3.84</v>
       </c>
       <c r="H123">
+        <v>3.8</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>2224262</v>
+      </c>
+      <c r="L123">
+        <v>8465.24408</v>
+      </c>
+      <c r="M123">
+        <v>242900</v>
+      </c>
+      <c r="N123">
         <v>3.82</v>
       </c>
-      <c r="I123">
-        <v>0</v>
-      </c>
-      <c r="J123">
-        <v>0</v>
-      </c>
-      <c r="K123">
-        <v>7019497</v>
-      </c>
-      <c r="L123">
-        <v>27182.30348</v>
-      </c>
-      <c r="M123">
-        <v>429000</v>
-      </c>
-      <c r="N123">
-        <v>3.88</v>
-      </c>
       <c r="O123">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="P123">
-        <v>406000</v>
+        <v>138200</v>
       </c>
     </row>
     <row r="124">
@@ -6214,22 +6214,22 @@
         <v>-</v>
       </c>
       <c r="C124">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="D124">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E124">
-        <v>2.484472049689441</v>
+        <v>1.2121212121212122</v>
       </c>
       <c r="F124">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="G124">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="H124">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="I124">
         <v>0</v>
@@ -6238,22 +6238,22 @@
         <v>0</v>
       </c>
       <c r="K124">
-        <v>545114</v>
+        <v>917273</v>
       </c>
       <c r="L124">
-        <v>8931.2103</v>
+        <v>15234.4586</v>
       </c>
       <c r="M124">
-        <v>109800</v>
+        <v>81100</v>
       </c>
       <c r="N124">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="O124">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="P124">
-        <v>123500</v>
+        <v>128600</v>
       </c>
     </row>
     <row r="125">
@@ -6267,19 +6267,19 @@
         <v>12</v>
       </c>
       <c r="D125">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E125">
-        <v>3.4482758620689653</v>
+        <v>1.694915254237288</v>
       </c>
       <c r="F125">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="G125">
         <v>12</v>
       </c>
       <c r="H125">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="I125">
         <v>0</v>
@@ -6288,13 +6288,13 @@
         <v>0</v>
       </c>
       <c r="K125">
-        <v>945706</v>
+        <v>342610</v>
       </c>
       <c r="L125">
-        <v>11193.981699999998</v>
+        <v>4085.668</v>
       </c>
       <c r="M125">
-        <v>118200</v>
+        <v>248800</v>
       </c>
       <c r="N125">
         <v>11.9</v>
@@ -6303,7 +6303,7 @@
         <v>12</v>
       </c>
       <c r="P125">
-        <v>121900</v>
+        <v>121200</v>
       </c>
     </row>
     <row r="126">
@@ -6323,37 +6323,37 @@
         <v>-0.9174311926605505</v>
       </c>
       <c r="F126">
+        <v>11</v>
+      </c>
+      <c r="G126">
+        <v>11</v>
+      </c>
+      <c r="H126">
+        <v>10.6</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>18205</v>
+      </c>
+      <c r="L126">
+        <v>196.735</v>
+      </c>
+      <c r="M126">
+        <v>200</v>
+      </c>
+      <c r="N126">
+        <v>10.8</v>
+      </c>
+      <c r="O126">
         <v>10.9</v>
       </c>
-      <c r="G126">
-        <v>10.9</v>
-      </c>
-      <c r="H126">
-        <v>10.7</v>
-      </c>
-      <c r="I126">
-        <v>0</v>
-      </c>
-      <c r="J126">
-        <v>0</v>
-      </c>
-      <c r="K126">
-        <v>8900</v>
-      </c>
-      <c r="L126">
-        <v>95.28</v>
-      </c>
-      <c r="M126">
-        <v>13200</v>
-      </c>
-      <c r="N126">
-        <v>10.7</v>
-      </c>
-      <c r="O126">
-        <v>10.8</v>
-      </c>
       <c r="P126">
-        <v>300</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="127">
@@ -6367,43 +6367,43 @@
         <v>16.2</v>
       </c>
       <c r="D127">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="E127">
-        <v>-0.6134969325153374</v>
+        <v>0.6211180124223602</v>
       </c>
       <c r="F127">
+        <v>16.2</v>
+      </c>
+      <c r="G127">
         <v>16.3</v>
       </c>
-      <c r="G127">
-        <v>16.4</v>
-      </c>
       <c r="H127">
+        <v>16</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>2458468</v>
+      </c>
+      <c r="L127">
+        <v>39842.401600000005</v>
+      </c>
+      <c r="M127">
+        <v>339400</v>
+      </c>
+      <c r="N127">
+        <v>16.1</v>
+      </c>
+      <c r="O127">
         <v>16.2</v>
       </c>
-      <c r="I127">
-        <v>0</v>
-      </c>
-      <c r="J127">
-        <v>0</v>
-      </c>
-      <c r="K127">
-        <v>1879628</v>
-      </c>
-      <c r="L127">
-        <v>30561.8573</v>
-      </c>
-      <c r="M127">
-        <v>179800</v>
-      </c>
-      <c r="N127">
-        <v>16.2</v>
-      </c>
-      <c r="O127">
-        <v>16.3</v>
-      </c>
       <c r="P127">
-        <v>146400</v>
+        <v>115300</v>
       </c>
     </row>
     <row r="128">
@@ -6414,7 +6414,7 @@
         <v>-</v>
       </c>
       <c r="C128">
-        <v>38.5</v>
+        <v>39</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -6423,37 +6423,37 @@
         <v>0</v>
       </c>
       <c r="F128">
+        <v>39.25</v>
+      </c>
+      <c r="G128">
+        <v>39.25</v>
+      </c>
+      <c r="H128">
+        <v>39</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <v>5651</v>
+      </c>
+      <c r="L128">
+        <v>220.414</v>
+      </c>
+      <c r="M128">
+        <v>7400</v>
+      </c>
+      <c r="N128">
         <v>38.75</v>
       </c>
-      <c r="G128">
-        <v>38.75</v>
-      </c>
-      <c r="H128">
-        <v>38.5</v>
-      </c>
-      <c r="I128">
-        <v>0</v>
-      </c>
-      <c r="J128">
-        <v>0</v>
-      </c>
-      <c r="K128">
-        <v>10712</v>
-      </c>
-      <c r="L128">
-        <v>412.44</v>
-      </c>
-      <c r="M128">
-        <v>15200</v>
-      </c>
-      <c r="N128">
-        <v>38.25</v>
-      </c>
       <c r="O128">
-        <v>38.5</v>
+        <v>39</v>
       </c>
       <c r="P128">
-        <v>1700</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="129">
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="K129">
-        <v>1013800</v>
+        <v>2757600</v>
       </c>
       <c r="L129">
-        <v>1045.882</v>
+        <v>2848.487</v>
       </c>
       <c r="M129">
-        <v>4400</v>
+        <v>297500</v>
       </c>
       <c r="N129">
         <v>1.03</v>
@@ -6503,7 +6503,7 @@
         <v>1.04</v>
       </c>
       <c r="P129">
-        <v>272000</v>
+        <v>367100</v>
       </c>
     </row>
     <row r="130">
@@ -6514,22 +6514,22 @@
         <v>-</v>
       </c>
       <c r="C130">
+        <v>9.2</v>
+      </c>
+      <c r="D130">
+        <v>0.05</v>
+      </c>
+      <c r="E130">
+        <v>0.546448087431694</v>
+      </c>
+      <c r="F130">
+        <v>9.15</v>
+      </c>
+      <c r="G130">
         <v>9.25</v>
       </c>
-      <c r="D130">
-        <v>0.15</v>
-      </c>
-      <c r="E130">
-        <v>1.6483516483516483</v>
-      </c>
-      <c r="F130">
-        <v>9.05</v>
-      </c>
-      <c r="G130">
-        <v>9.3</v>
-      </c>
       <c r="H130">
-        <v>9.05</v>
+        <v>9.15</v>
       </c>
       <c r="I130">
         <v>0</v>
@@ -6538,22 +6538,22 @@
         <v>0</v>
       </c>
       <c r="K130">
-        <v>1224489</v>
+        <v>76701</v>
       </c>
       <c r="L130">
-        <v>11276.13335</v>
+        <v>705.5343</v>
       </c>
       <c r="M130">
-        <v>15800</v>
+        <v>50100</v>
       </c>
       <c r="N130">
+        <v>9.15</v>
+      </c>
+      <c r="O130">
         <v>9.2</v>
       </c>
-      <c r="O130">
-        <v>9.25</v>
-      </c>
       <c r="P130">
-        <v>38600</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="131">
@@ -6564,46 +6564,46 @@
         <v>-</v>
       </c>
       <c r="C131">
+        <v>8.6</v>
+      </c>
+      <c r="D131">
+        <v>0</v>
+      </c>
+      <c r="E131">
+        <v>0</v>
+      </c>
+      <c r="F131">
+        <v>8.6</v>
+      </c>
+      <c r="G131">
+        <v>8.65</v>
+      </c>
+      <c r="H131">
         <v>8.55</v>
       </c>
-      <c r="D131">
-        <v>0</v>
-      </c>
-      <c r="E131">
-        <v>0</v>
-      </c>
-      <c r="F131">
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>118839</v>
+      </c>
+      <c r="L131">
+        <v>1022.78445</v>
+      </c>
+      <c r="M131">
+        <v>162300</v>
+      </c>
+      <c r="N131">
         <v>8.55</v>
       </c>
-      <c r="G131">
-        <v>8.55</v>
-      </c>
-      <c r="H131">
-        <v>8.45</v>
-      </c>
-      <c r="I131">
-        <v>0</v>
-      </c>
-      <c r="J131">
-        <v>0</v>
-      </c>
-      <c r="K131">
-        <v>428900</v>
-      </c>
-      <c r="L131">
-        <v>3644.165</v>
-      </c>
-      <c r="M131">
-        <v>11000</v>
-      </c>
-      <c r="N131">
-        <v>8.5</v>
-      </c>
       <c r="O131">
-        <v>8.55</v>
+        <v>8.65</v>
       </c>
       <c r="P131">
-        <v>43900</v>
+        <v>30700</v>
       </c>
     </row>
     <row r="132">
@@ -6614,22 +6614,22 @@
         <v>-</v>
       </c>
       <c r="C132">
-        <v>23.1</v>
+        <v>21.6</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="E132">
-        <v>0</v>
+        <v>-2.262443438914027</v>
       </c>
       <c r="F132">
-        <v>23.1</v>
+        <v>22.1</v>
       </c>
       <c r="G132">
-        <v>23.2</v>
+        <v>22.2</v>
       </c>
       <c r="H132">
-        <v>23</v>
+        <v>21.2</v>
       </c>
       <c r="I132">
         <v>0</v>
@@ -6638,22 +6638,22 @@
         <v>0</v>
       </c>
       <c r="K132">
-        <v>172700</v>
+        <v>1227714</v>
       </c>
       <c r="L132">
-        <v>3989.58</v>
+        <v>26581.2238</v>
       </c>
       <c r="M132">
-        <v>15100</v>
+        <v>7700</v>
       </c>
       <c r="N132">
-        <v>23.1</v>
+        <v>21.5</v>
       </c>
       <c r="O132">
-        <v>23.2</v>
+        <v>21.6</v>
       </c>
       <c r="P132">
-        <v>131700</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="133">
@@ -6664,22 +6664,22 @@
         <v>-</v>
       </c>
       <c r="C133">
+        <v>11.4</v>
+      </c>
+      <c r="D133">
+        <v>0.1</v>
+      </c>
+      <c r="E133">
+        <v>0.8849557522123894</v>
+      </c>
+      <c r="F133">
+        <v>11.3</v>
+      </c>
+      <c r="G133">
         <v>11.5</v>
       </c>
-      <c r="D133">
-        <v>-0.1</v>
-      </c>
-      <c r="E133">
-        <v>-0.8620689655172413</v>
-      </c>
-      <c r="F133">
-        <v>11.6</v>
-      </c>
-      <c r="G133">
-        <v>11.8</v>
-      </c>
       <c r="H133">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="I133">
         <v>0</v>
@@ -6688,22 +6688,22 @@
         <v>0</v>
       </c>
       <c r="K133">
-        <v>1985773</v>
+        <v>3665534</v>
       </c>
       <c r="L133">
-        <v>23135.683100000002</v>
+        <v>41548.7886</v>
       </c>
       <c r="M133">
-        <v>260400</v>
+        <v>742200</v>
       </c>
       <c r="N133">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="O133">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="P133">
-        <v>365700</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="134">
@@ -6714,23 +6714,23 @@
         <v>-</v>
       </c>
       <c r="C134">
+        <v>13.6</v>
+      </c>
+      <c r="D134">
+        <v>-0.1</v>
+      </c>
+      <c r="E134">
+        <v>-0.7299270072992701</v>
+      </c>
+      <c r="F134">
         <v>13.7</v>
       </c>
-      <c r="D134">
-        <v>0.2</v>
-      </c>
-      <c r="E134">
-        <v>1.4814814814814814</v>
-      </c>
-      <c r="F134">
+      <c r="G134">
+        <v>13.8</v>
+      </c>
+      <c r="H134">
         <v>13.5</v>
       </c>
-      <c r="G134">
-        <v>13.9</v>
-      </c>
-      <c r="H134">
-        <v>13.4</v>
-      </c>
       <c r="I134">
         <v>0</v>
       </c>
@@ -6738,22 +6738,22 @@
         <v>0</v>
       </c>
       <c r="K134">
-        <v>6836708</v>
+        <v>1197110</v>
       </c>
       <c r="L134">
-        <v>94139.24979999999</v>
+        <v>16235.2397</v>
       </c>
       <c r="M134">
-        <v>337400</v>
+        <v>322400</v>
       </c>
       <c r="N134">
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="O134">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="P134">
-        <v>221400</v>
+        <v>347200</v>
       </c>
     </row>
     <row r="135">
@@ -6764,7 +6764,7 @@
         <v>-</v>
       </c>
       <c r="C135">
-        <v>8.2</v>
+        <v>8.15</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -6776,34 +6776,34 @@
         <v>8.2</v>
       </c>
       <c r="G135">
-        <v>8.3</v>
+        <v>8.2</v>
       </c>
       <c r="H135">
+        <v>8.1</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>122799</v>
+      </c>
+      <c r="L135">
+        <v>1001.0569</v>
+      </c>
+      <c r="M135">
+        <v>7300</v>
+      </c>
+      <c r="N135">
         <v>8.15</v>
       </c>
-      <c r="I135">
-        <v>0</v>
-      </c>
-      <c r="J135">
-        <v>0</v>
-      </c>
-      <c r="K135">
-        <v>137338</v>
-      </c>
-      <c r="L135">
-        <v>1125.5578500000001</v>
-      </c>
-      <c r="M135">
-        <v>44300</v>
-      </c>
-      <c r="N135">
+      <c r="O135">
         <v>8.2</v>
       </c>
-      <c r="O135">
-        <v>8.25</v>
-      </c>
       <c r="P135">
-        <v>62900</v>
+        <v>74200</v>
       </c>
     </row>
     <row r="136">
@@ -6814,22 +6814,22 @@
         <v>-</v>
       </c>
       <c r="C136">
-        <v>9.2</v>
+        <v>9</v>
       </c>
       <c r="D136">
-        <v>0.15</v>
+        <v>-0.15</v>
       </c>
       <c r="E136">
-        <v>1.6574585635359116</v>
+        <v>-1.639344262295082</v>
       </c>
       <c r="F136">
-        <v>9.2</v>
+        <v>9.15</v>
       </c>
       <c r="G136">
-        <v>9.25</v>
+        <v>9.15</v>
       </c>
       <c r="H136">
-        <v>9.15</v>
+        <v>9</v>
       </c>
       <c r="I136">
         <v>0</v>
@@ -6838,22 +6838,22 @@
         <v>0</v>
       </c>
       <c r="K136">
-        <v>454800</v>
+        <v>220027</v>
       </c>
       <c r="L136">
-        <v>4184.14</v>
+        <v>1988.36925</v>
       </c>
       <c r="M136">
-        <v>30900</v>
+        <v>18600</v>
       </c>
       <c r="N136">
-        <v>9.15</v>
+        <v>8.95</v>
       </c>
       <c r="O136">
-        <v>9.2</v>
+        <v>9.05</v>
       </c>
       <c r="P136">
-        <v>26100</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="137">
@@ -6864,16 +6864,16 @@
         <v>-</v>
       </c>
       <c r="C137">
+        <v>2.52</v>
+      </c>
+      <c r="D137">
+        <v>-0.02</v>
+      </c>
+      <c r="E137">
+        <v>-0.7874015748031497</v>
+      </c>
+      <c r="F137">
         <v>2.54</v>
-      </c>
-      <c r="D137">
-        <v>0</v>
-      </c>
-      <c r="E137">
-        <v>0</v>
-      </c>
-      <c r="F137">
-        <v>2.56</v>
       </c>
       <c r="G137">
         <v>2.56</v>
@@ -6888,22 +6888,22 @@
         <v>0</v>
       </c>
       <c r="K137">
-        <v>1197550</v>
+        <v>1019900</v>
       </c>
       <c r="L137">
-        <v>3042.213</v>
+        <v>2590.578</v>
       </c>
       <c r="M137">
-        <v>720000</v>
+        <v>609700</v>
       </c>
       <c r="N137">
+        <v>2.52</v>
+      </c>
+      <c r="O137">
         <v>2.54</v>
       </c>
-      <c r="O137">
-        <v>2.56</v>
-      </c>
       <c r="P137">
-        <v>1180100</v>
+        <v>79300</v>
       </c>
     </row>
     <row r="138">
@@ -6914,22 +6914,22 @@
         <v>-</v>
       </c>
       <c r="C138">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E138">
-        <v>0</v>
+        <v>-0.8264462809917356</v>
       </c>
       <c r="F138">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="G138">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="H138">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="I138">
         <v>0</v>
@@ -6938,22 +6938,22 @@
         <v>0</v>
       </c>
       <c r="K138">
-        <v>1405201</v>
+        <v>1779100</v>
       </c>
       <c r="L138">
-        <v>1635.14517</v>
+        <v>2153.838</v>
       </c>
       <c r="M138">
-        <v>307400</v>
+        <v>779800</v>
       </c>
       <c r="N138">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="O138">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="P138">
-        <v>373800</v>
+        <v>339700</v>
       </c>
     </row>
     <row r="139">
@@ -6964,46 +6964,46 @@
         <v>-</v>
       </c>
       <c r="C139">
-        <v>8.25</v>
+        <v>8.1</v>
       </c>
       <c r="D139">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="E139">
-        <v>1.2269938650306749</v>
+        <v>0.6211180124223602</v>
       </c>
       <c r="F139">
-        <v>8.2</v>
+        <v>8.1</v>
       </c>
       <c r="G139">
-        <v>8.25</v>
+        <v>8.15</v>
       </c>
       <c r="H139">
+        <v>8.05</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>1728396</v>
+      </c>
+      <c r="L139">
+        <v>14003.966849999999</v>
+      </c>
+      <c r="M139">
+        <v>458900</v>
+      </c>
+      <c r="N139">
         <v>8.1</v>
       </c>
-      <c r="I139">
-        <v>0</v>
-      </c>
-      <c r="J139">
-        <v>0</v>
-      </c>
-      <c r="K139">
-        <v>3469133</v>
-      </c>
-      <c r="L139">
-        <v>28309.263600000002</v>
-      </c>
-      <c r="M139">
-        <v>386800</v>
-      </c>
-      <c r="N139">
-        <v>8.2</v>
-      </c>
       <c r="O139">
-        <v>8.25</v>
+        <v>8.15</v>
       </c>
       <c r="P139">
-        <v>602500</v>
+        <v>449900</v>
       </c>
     </row>
     <row r="140">
@@ -7014,23 +7014,23 @@
         <v>-</v>
       </c>
       <c r="C140">
-        <v>12.6</v>
+        <v>12.9</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E140">
-        <v>0</v>
+        <v>0.78125</v>
       </c>
       <c r="F140">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="G140">
+        <v>12.9</v>
+      </c>
+      <c r="H140">
         <v>12.7</v>
       </c>
-      <c r="H140">
-        <v>12.5</v>
-      </c>
       <c r="I140">
         <v>0</v>
       </c>
@@ -7038,22 +7038,22 @@
         <v>0</v>
       </c>
       <c r="K140">
-        <v>89359</v>
+        <v>84224</v>
       </c>
       <c r="L140">
-        <v>1130.7265</v>
+        <v>1081.092</v>
       </c>
       <c r="M140">
-        <v>16200</v>
+        <v>2500</v>
       </c>
       <c r="N140">
-        <v>12.6</v>
+        <v>12.9</v>
       </c>
       <c r="O140">
-        <v>12.7</v>
+        <v>13</v>
       </c>
       <c r="P140">
-        <v>36900</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="141">
@@ -7064,46 +7064,46 @@
         <v>-</v>
       </c>
       <c r="C141">
-        <v>5.4</v>
+        <v>5.35</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E141">
-        <v>0</v>
+        <v>0.9433962264150944</v>
       </c>
       <c r="F141">
+        <v>5.3</v>
+      </c>
+      <c r="G141">
         <v>5.35</v>
       </c>
-      <c r="G141">
-        <v>5.4</v>
-      </c>
       <c r="H141">
+        <v>5.3</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>72200</v>
+      </c>
+      <c r="L141">
+        <v>382.67</v>
+      </c>
+      <c r="M141">
+        <v>38800</v>
+      </c>
+      <c r="N141">
+        <v>5.3</v>
+      </c>
+      <c r="O141">
         <v>5.35</v>
       </c>
-      <c r="I141">
-        <v>0</v>
-      </c>
-      <c r="J141">
-        <v>0</v>
-      </c>
-      <c r="K141">
-        <v>124802</v>
-      </c>
-      <c r="L141">
-        <v>669.1508</v>
-      </c>
-      <c r="M141">
-        <v>305300</v>
-      </c>
-      <c r="N141">
-        <v>5.35</v>
-      </c>
-      <c r="O141">
-        <v>5.4</v>
-      </c>
       <c r="P141">
-        <v>152300</v>
+        <v>83200</v>
       </c>
     </row>
     <row r="142">
@@ -7117,10 +7117,10 @@
         <v>4.74</v>
       </c>
       <c r="D142">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E142">
-        <v>0.423728813559322</v>
+        <v>0</v>
       </c>
       <c r="F142">
         <v>4.76</v>
@@ -7138,22 +7138,22 @@
         <v>0</v>
       </c>
       <c r="K142">
-        <v>29900</v>
+        <v>29500</v>
       </c>
       <c r="L142">
-        <v>141.276</v>
+        <v>139.68</v>
       </c>
       <c r="M142">
-        <v>2900</v>
+        <v>5100</v>
       </c>
       <c r="N142">
-        <v>4.72</v>
+        <v>4.74</v>
       </c>
       <c r="O142">
-        <v>4.74</v>
+        <v>4.76</v>
       </c>
       <c r="P142">
-        <v>38900</v>
+        <v>33900</v>
       </c>
     </row>
     <row r="143">
@@ -7164,13 +7164,13 @@
         <v>-</v>
       </c>
       <c r="C143">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="D143">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="E143">
-        <v>-0.6622516556291391</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F143">
         <v>1.51</v>
@@ -7188,13 +7188,13 @@
         <v>0</v>
       </c>
       <c r="K143">
-        <v>2270672</v>
+        <v>1648301</v>
       </c>
       <c r="L143">
-        <v>3409.46574</v>
+        <v>2474.31152</v>
       </c>
       <c r="M143">
-        <v>144200</v>
+        <v>411200</v>
       </c>
       <c r="N143">
         <v>1.5</v>
@@ -7203,7 +7203,7 @@
         <v>1.51</v>
       </c>
       <c r="P143">
-        <v>601500</v>
+        <v>262000</v>
       </c>
     </row>
     <row r="144">
@@ -7214,22 +7214,22 @@
         <v>-</v>
       </c>
       <c r="C144">
+        <v>15.6</v>
+      </c>
+      <c r="D144">
+        <v>0.1</v>
+      </c>
+      <c r="E144">
+        <v>0.6451612903225806</v>
+      </c>
+      <c r="F144">
+        <v>15.5</v>
+      </c>
+      <c r="G144">
         <v>15.8</v>
       </c>
-      <c r="D144">
-        <v>0</v>
-      </c>
-      <c r="E144">
-        <v>0</v>
-      </c>
-      <c r="F144">
-        <v>15.9</v>
-      </c>
-      <c r="G144">
-        <v>15.9</v>
-      </c>
       <c r="H144">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="I144">
         <v>0</v>
@@ -7238,22 +7238,22 @@
         <v>0</v>
       </c>
       <c r="K144">
-        <v>512148</v>
+        <v>625731</v>
       </c>
       <c r="L144">
-        <v>8093.406</v>
+        <v>9743.0036</v>
       </c>
       <c r="M144">
-        <v>322900</v>
+        <v>35600</v>
       </c>
       <c r="N144">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="O144">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="P144">
-        <v>186800</v>
+        <v>204100</v>
       </c>
     </row>
     <row r="145">
@@ -7264,46 +7264,46 @@
         <v>-</v>
       </c>
       <c r="C145">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="D145">
         <v>0.02</v>
       </c>
       <c r="E145">
-        <v>0.5882352941176471</v>
+        <v>0.591715976331361</v>
       </c>
       <c r="F145">
+        <v>3.4</v>
+      </c>
+      <c r="G145">
+        <v>3.46</v>
+      </c>
+      <c r="H145">
+        <v>3.36</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+      <c r="J145">
+        <v>0</v>
+      </c>
+      <c r="K145">
+        <v>2601300</v>
+      </c>
+      <c r="L145">
+        <v>8870.898</v>
+      </c>
+      <c r="M145">
+        <v>291700</v>
+      </c>
+      <c r="N145">
+        <v>3.4</v>
+      </c>
+      <c r="O145">
         <v>3.42</v>
       </c>
-      <c r="G145">
-        <v>3.54</v>
-      </c>
-      <c r="H145">
-        <v>3.4</v>
-      </c>
-      <c r="I145">
-        <v>0</v>
-      </c>
-      <c r="J145">
-        <v>0</v>
-      </c>
-      <c r="K145">
-        <v>13817730</v>
-      </c>
-      <c r="L145">
-        <v>48052.502799999995</v>
-      </c>
-      <c r="M145">
-        <v>40000</v>
-      </c>
-      <c r="N145">
-        <v>3.42</v>
-      </c>
-      <c r="O145">
-        <v>3.44</v>
-      </c>
       <c r="P145">
-        <v>124200</v>
+        <v>154700</v>
       </c>
     </row>
     <row r="146">
@@ -7317,20 +7317,20 @@
         <v>7.8</v>
       </c>
       <c r="D146">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E146">
-        <v>0.6451612903225806</v>
+        <v>-0.6369426751592356</v>
       </c>
       <c r="F146">
-        <v>7.75</v>
+        <v>7.85</v>
       </c>
       <c r="G146">
+        <v>7.85</v>
+      </c>
+      <c r="H146">
         <v>7.8</v>
       </c>
-      <c r="H146">
-        <v>7.75</v>
-      </c>
       <c r="I146">
         <v>0</v>
       </c>
@@ -7338,22 +7338,22 @@
         <v>0</v>
       </c>
       <c r="K146">
-        <v>421824</v>
+        <v>35501</v>
       </c>
       <c r="L146">
-        <v>3272.6622</v>
+        <v>277.44784999999996</v>
       </c>
       <c r="M146">
-        <v>150100</v>
+        <v>124200</v>
       </c>
       <c r="N146">
-        <v>7.75</v>
+        <v>7.8</v>
       </c>
       <c r="O146">
-        <v>7.8</v>
+        <v>7.85</v>
       </c>
       <c r="P146">
-        <v>115400</v>
+        <v>139800</v>
       </c>
     </row>
     <row r="147">
@@ -7367,43 +7367,43 @@
         <v>8.7</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E147">
-        <v>0</v>
+        <v>1.1627906976744187</v>
       </c>
       <c r="F147">
-        <v>8.8</v>
+        <v>8.6</v>
       </c>
       <c r="G147">
-        <v>8.8</v>
+        <v>8.7</v>
       </c>
       <c r="H147">
+        <v>8.6</v>
+      </c>
+      <c r="I147">
+        <v>0</v>
+      </c>
+      <c r="J147">
+        <v>0</v>
+      </c>
+      <c r="K147">
+        <v>296352</v>
+      </c>
+      <c r="L147">
+        <v>2566.5049</v>
+      </c>
+      <c r="M147">
+        <v>26800</v>
+      </c>
+      <c r="N147">
+        <v>8.65</v>
+      </c>
+      <c r="O147">
         <v>8.7</v>
       </c>
-      <c r="I147">
-        <v>0</v>
-      </c>
-      <c r="J147">
-        <v>0</v>
-      </c>
-      <c r="K147">
-        <v>341902</v>
-      </c>
-      <c r="L147">
-        <v>2989.4602</v>
-      </c>
-      <c r="M147">
-        <v>30000</v>
-      </c>
-      <c r="N147">
-        <v>8.7</v>
-      </c>
-      <c r="O147">
-        <v>8.75</v>
-      </c>
       <c r="P147">
-        <v>31000</v>
+        <v>503900</v>
       </c>
     </row>
     <row r="148">
@@ -7414,46 +7414,46 @@
         <v>-</v>
       </c>
       <c r="C148">
+        <v>5.55</v>
+      </c>
+      <c r="D148">
+        <v>0</v>
+      </c>
+      <c r="E148">
+        <v>0</v>
+      </c>
+      <c r="F148">
+        <v>5.5</v>
+      </c>
+      <c r="G148">
         <v>5.6</v>
       </c>
-      <c r="D148">
-        <v>0</v>
-      </c>
-      <c r="E148">
-        <v>0</v>
-      </c>
-      <c r="F148">
-        <v>5.6</v>
-      </c>
-      <c r="G148">
-        <v>5.65</v>
-      </c>
       <c r="H148">
+        <v>5.5</v>
+      </c>
+      <c r="I148">
+        <v>0</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+      <c r="K148">
+        <v>356500</v>
+      </c>
+      <c r="L148">
+        <v>1968.645</v>
+      </c>
+      <c r="M148">
+        <v>226000</v>
+      </c>
+      <c r="N148">
+        <v>5.5</v>
+      </c>
+      <c r="O148">
         <v>5.55</v>
       </c>
-      <c r="I148">
-        <v>0</v>
-      </c>
-      <c r="J148">
-        <v>0</v>
-      </c>
-      <c r="K148">
-        <v>265100</v>
-      </c>
-      <c r="L148">
-        <v>1477.825</v>
-      </c>
-      <c r="M148">
-        <v>19800</v>
-      </c>
-      <c r="N148">
-        <v>5.55</v>
-      </c>
-      <c r="O148">
-        <v>5.6</v>
-      </c>
       <c r="P148">
-        <v>32000</v>
+        <v>38200</v>
       </c>
     </row>
     <row r="149">
@@ -7464,23 +7464,23 @@
         <v>-</v>
       </c>
       <c r="C149">
+        <v>4.12</v>
+      </c>
+      <c r="D149">
+        <v>0.04</v>
+      </c>
+      <c r="E149">
+        <v>0.9803921568627451</v>
+      </c>
+      <c r="F149">
+        <v>4.1</v>
+      </c>
+      <c r="G149">
+        <v>4.14</v>
+      </c>
+      <c r="H149">
         <v>4.06</v>
       </c>
-      <c r="D149">
-        <v>0.02</v>
-      </c>
-      <c r="E149">
-        <v>0.49504950495049505</v>
-      </c>
-      <c r="F149">
-        <v>4.02</v>
-      </c>
-      <c r="G149">
-        <v>4.08</v>
-      </c>
-      <c r="H149">
-        <v>4.02</v>
-      </c>
       <c r="I149">
         <v>0</v>
       </c>
@@ -7488,22 +7488,22 @@
         <v>0</v>
       </c>
       <c r="K149">
-        <v>1034669</v>
+        <v>3154627</v>
       </c>
       <c r="L149">
-        <v>4193.62842</v>
+        <v>12942.35524</v>
       </c>
       <c r="M149">
-        <v>57400</v>
+        <v>257400</v>
       </c>
       <c r="N149">
-        <v>4.06</v>
+        <v>4.1</v>
       </c>
       <c r="O149">
-        <v>4.08</v>
+        <v>4.12</v>
       </c>
       <c r="P149">
-        <v>382700</v>
+        <v>83500</v>
       </c>
     </row>
     <row r="150">
@@ -7514,46 +7514,46 @@
         <v>-</v>
       </c>
       <c r="C150">
+        <v>11.9</v>
+      </c>
+      <c r="D150">
+        <v>0.2</v>
+      </c>
+      <c r="E150">
+        <v>1.7094017094017093</v>
+      </c>
+      <c r="F150">
+        <v>11.7</v>
+      </c>
+      <c r="G150">
         <v>12</v>
       </c>
-      <c r="D150">
-        <v>0.1</v>
-      </c>
-      <c r="E150">
-        <v>0.8403361344537815</v>
-      </c>
-      <c r="F150">
-        <v>12.1</v>
-      </c>
-      <c r="G150">
-        <v>12.1</v>
-      </c>
       <c r="H150">
+        <v>11.7</v>
+      </c>
+      <c r="I150">
+        <v>0</v>
+      </c>
+      <c r="J150">
+        <v>0</v>
+      </c>
+      <c r="K150">
+        <v>2575189</v>
+      </c>
+      <c r="L150">
+        <v>30484.8</v>
+      </c>
+      <c r="M150">
+        <v>44400</v>
+      </c>
+      <c r="N150">
         <v>11.9</v>
       </c>
-      <c r="I150">
-        <v>0</v>
-      </c>
-      <c r="J150">
-        <v>0</v>
-      </c>
-      <c r="K150">
-        <v>1912446</v>
-      </c>
-      <c r="L150">
-        <v>22977.213399999997</v>
-      </c>
-      <c r="M150">
-        <v>434300</v>
-      </c>
-      <c r="N150">
+      <c r="O150">
         <v>12</v>
       </c>
-      <c r="O150">
-        <v>12.1</v>
-      </c>
       <c r="P150">
-        <v>667900</v>
+        <v>833400</v>
       </c>
     </row>
     <row r="151">
@@ -7564,7 +7564,7 @@
         <v>-</v>
       </c>
       <c r="C151">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -7573,14 +7573,14 @@
         <v>0</v>
       </c>
       <c r="F151">
-        <v>18.1</v>
+        <v>18.4</v>
       </c>
       <c r="G151">
+        <v>18.4</v>
+      </c>
+      <c r="H151">
         <v>18.3</v>
       </c>
-      <c r="H151">
-        <v>18.1</v>
-      </c>
       <c r="I151">
         <v>0</v>
       </c>
@@ -7588,22 +7588,22 @@
         <v>0</v>
       </c>
       <c r="K151">
-        <v>48305</v>
+        <v>191110</v>
       </c>
       <c r="L151">
-        <v>877.272</v>
+        <v>3503.364</v>
       </c>
       <c r="M151">
-        <v>314300</v>
+        <v>14300</v>
       </c>
       <c r="N151">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="O151">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="P151">
-        <v>14900</v>
+        <v>138300</v>
       </c>
     </row>
     <row r="152">
@@ -7623,7 +7623,7 @@
         <v>0</v>
       </c>
       <c r="F152">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="G152">
         <v>1.46</v>
@@ -7638,13 +7638,13 @@
         <v>0</v>
       </c>
       <c r="K152">
-        <v>6733999</v>
+        <v>4811698</v>
       </c>
       <c r="L152">
-        <v>9764.073359999999</v>
+        <v>6985.97938</v>
       </c>
       <c r="M152">
-        <v>1196500</v>
+        <v>2533300</v>
       </c>
       <c r="N152">
         <v>1.44</v>
@@ -7653,7 +7653,7 @@
         <v>1.45</v>
       </c>
       <c r="P152">
-        <v>1432200</v>
+        <v>227900</v>
       </c>
     </row>
     <row r="153">
@@ -7664,22 +7664,22 @@
         <v>-</v>
       </c>
       <c r="C153">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="D153">
         <v>0.1</v>
       </c>
       <c r="E153">
-        <v>0.5586592178770949</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="F153">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="G153">
         <v>18.1</v>
       </c>
       <c r="H153">
-        <v>17.9</v>
+        <v>17.7</v>
       </c>
       <c r="I153">
         <v>0</v>
@@ -7688,22 +7688,22 @@
         <v>0</v>
       </c>
       <c r="K153">
-        <v>298710</v>
+        <v>82100</v>
       </c>
       <c r="L153">
-        <v>5364.499</v>
+        <v>1473.36</v>
       </c>
       <c r="M153">
-        <v>12800</v>
+        <v>10200</v>
       </c>
       <c r="N153">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="O153">
         <v>18.1</v>
       </c>
       <c r="P153">
-        <v>43600</v>
+        <v>23000</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StockQuotation (1).xlsx
+++ b/Excel/StockQuotation (1).xlsx
@@ -402,7 +402,7 @@
         <v/>
       </c>
       <c r="C1" t="str">
-        <v>03/02/23 12:58:01</v>
+        <v>07/02/23 23:29:28</v>
       </c>
     </row>
     <row r="4">
@@ -426,34 +426,34 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>1122.23</v>
+        <v>1126.3</v>
       </c>
       <c r="B7" t="str">
-        <v>3.74 (0.3343%)</v>
+        <v>0.92 (0.0817%)</v>
       </c>
       <c r="C7" t="str">
         <v>High</v>
       </c>
       <c r="D7">
-        <v>1122.53</v>
+        <v>1130.58</v>
       </c>
       <c r="E7" t="str">
         <v>Low</v>
       </c>
       <c r="F7">
-        <v>1116.72</v>
+        <v>1122.42</v>
       </c>
       <c r="G7" t="str">
         <v>Volume</v>
       </c>
       <c r="H7">
-        <v>490087396</v>
+        <v>1243021590</v>
       </c>
       <c r="I7" t="str">
         <v>Value</v>
       </c>
       <c r="J7">
-        <v>2220977033.24</v>
+        <v>4132739558.89</v>
       </c>
     </row>
     <row r="9">
@@ -514,22 +514,22 @@
         <v>-</v>
       </c>
       <c r="C10">
-        <v>0.79</v>
+        <v>0.88</v>
       </c>
       <c r="D10">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>1.2820512820512822</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="G10">
-        <v>0.79</v>
+        <v>0.92</v>
       </c>
       <c r="H10">
-        <v>0.78</v>
+        <v>0.86</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -538,22 +538,22 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>3678888</v>
+        <v>300735083</v>
       </c>
       <c r="L10">
-        <v>2899.81239</v>
+        <v>269440.61246</v>
       </c>
       <c r="M10">
-        <v>3582100</v>
+        <v>2307300</v>
       </c>
       <c r="N10">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="O10">
-        <v>0.79</v>
+        <v>0.88</v>
       </c>
       <c r="P10">
-        <v>1211600</v>
+        <v>1230700</v>
       </c>
     </row>
     <row r="11">
@@ -564,22 +564,22 @@
         <v>-</v>
       </c>
       <c r="C11">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>-0.5376344086021505</v>
       </c>
       <c r="F11">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="G11">
         <v>3.72</v>
       </c>
       <c r="H11">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -588,22 +588,22 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>1075196</v>
+        <v>1095242</v>
       </c>
       <c r="L11">
-        <v>3970.9574</v>
+        <v>4058.4807</v>
       </c>
       <c r="M11">
-        <v>276900</v>
+        <v>48700</v>
       </c>
       <c r="N11">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="O11">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="P11">
-        <v>289900</v>
+        <v>132600</v>
       </c>
     </row>
     <row r="12">
@@ -614,46 +614,46 @@
         <v>-</v>
       </c>
       <c r="C12">
-        <v>32.25</v>
+        <v>32.75</v>
       </c>
       <c r="D12">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="E12">
-        <v>-1.5267175572519085</v>
+        <v>-0.7575757575757576</v>
       </c>
       <c r="F12">
+        <v>33</v>
+      </c>
+      <c r="G12">
+        <v>33.25</v>
+      </c>
+      <c r="H12">
+        <v>32.5</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>1688685</v>
+      </c>
+      <c r="L12">
+        <v>55467.10525</v>
+      </c>
+      <c r="M12">
+        <v>5000</v>
+      </c>
+      <c r="N12">
         <v>32.75</v>
       </c>
-      <c r="G12">
-        <v>32.75</v>
-      </c>
-      <c r="H12">
-        <v>32</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>1366962</v>
-      </c>
-      <c r="L12">
-        <v>44180.37375</v>
-      </c>
-      <c r="M12">
-        <v>147200</v>
-      </c>
-      <c r="N12">
-        <v>32</v>
-      </c>
       <c r="O12">
-        <v>32.25</v>
+        <v>33</v>
       </c>
       <c r="P12">
-        <v>66200</v>
+        <v>328000</v>
       </c>
     </row>
     <row r="13">
@@ -664,13 +664,13 @@
         <v>-</v>
       </c>
       <c r="C13">
-        <v>6.65</v>
+        <v>6.6</v>
       </c>
       <c r="D13">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E13">
-        <v>0.7575757575757576</v>
+        <v>-0.7518796992481203</v>
       </c>
       <c r="F13">
         <v>6.65</v>
@@ -679,7 +679,7 @@
         <v>6.7</v>
       </c>
       <c r="H13">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -688,13 +688,13 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>57744</v>
+        <v>307537</v>
       </c>
       <c r="L13">
-        <v>384.3511</v>
+        <v>2034.8716000000002</v>
       </c>
       <c r="M13">
-        <v>56700</v>
+        <v>54800</v>
       </c>
       <c r="N13">
         <v>6.6</v>
@@ -703,7 +703,7 @@
         <v>6.65</v>
       </c>
       <c r="P13">
-        <v>30400</v>
+        <v>45900</v>
       </c>
     </row>
     <row r="14">
@@ -714,22 +714,22 @@
         <v>-</v>
       </c>
       <c r="C14">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="D14">
-        <v>0.02</v>
+        <v>0.14</v>
       </c>
       <c r="E14">
-        <v>0.7142857142857143</v>
+        <v>4.895104895104895</v>
       </c>
       <c r="F14">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="G14">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -738,22 +738,22 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>350971</v>
+        <v>5198687</v>
       </c>
       <c r="L14">
-        <v>995.6371</v>
+        <v>15360.20196</v>
       </c>
       <c r="M14">
-        <v>162500</v>
+        <v>74700</v>
       </c>
       <c r="N14">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="O14">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="P14">
-        <v>64900</v>
+        <v>380400</v>
       </c>
     </row>
     <row r="15">
@@ -764,46 +764,46 @@
         <v>-</v>
       </c>
       <c r="C15">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="D15">
-        <v>0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="E15">
-        <v>2.255639097744361</v>
+        <v>-1.492537313432836</v>
       </c>
       <c r="F15">
         <v>6.7</v>
       </c>
       <c r="G15">
-        <v>6.85</v>
+        <v>6.7</v>
       </c>
       <c r="H15">
+        <v>6.6</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>1178324</v>
+      </c>
+      <c r="L15">
+        <v>7806.0696</v>
+      </c>
+      <c r="M15">
+        <v>594500</v>
+      </c>
+      <c r="N15">
+        <v>6.6</v>
+      </c>
+      <c r="O15">
         <v>6.65</v>
       </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>3994938</v>
-      </c>
-      <c r="L15">
-        <v>26984.162399999997</v>
-      </c>
-      <c r="M15">
-        <v>30300</v>
-      </c>
-      <c r="N15">
-        <v>6.75</v>
-      </c>
-      <c r="O15">
-        <v>6.8</v>
-      </c>
       <c r="P15">
-        <v>851100</v>
+        <v>337700</v>
       </c>
     </row>
     <row r="16">
@@ -817,16 +817,16 @@
         <v>12.9</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>-0.7692307692307693</v>
       </c>
       <c r="F16">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="G16">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="H16">
         <v>12.8</v>
@@ -838,22 +838,22 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>83924</v>
+        <v>296417</v>
       </c>
       <c r="L16">
-        <v>1082.9692</v>
+        <v>3835.5916</v>
       </c>
       <c r="M16">
-        <v>46400</v>
+        <v>86000</v>
       </c>
       <c r="N16">
+        <v>12.8</v>
+      </c>
+      <c r="O16">
         <v>12.9</v>
       </c>
-      <c r="O16">
-        <v>13</v>
-      </c>
       <c r="P16">
-        <v>64300</v>
+        <v>27100</v>
       </c>
     </row>
     <row r="17">
@@ -864,46 +864,46 @@
         <v>-</v>
       </c>
       <c r="C17">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="D17">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="E17">
-        <v>-0.4878048780487805</v>
+        <v>-0.9900990099009901</v>
       </c>
       <c r="F17">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
       <c r="G17">
-        <v>4.1</v>
+        <v>4.06</v>
       </c>
       <c r="H17">
+        <v>3.98</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>2506280</v>
+      </c>
+      <c r="L17">
+        <v>10023.6756</v>
+      </c>
+      <c r="M17">
+        <v>322600</v>
+      </c>
+      <c r="N17">
+        <v>4</v>
+      </c>
+      <c r="O17">
         <v>4.02</v>
       </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>4076564</v>
-      </c>
-      <c r="L17">
-        <v>16551.82398</v>
-      </c>
-      <c r="M17">
-        <v>276800</v>
-      </c>
-      <c r="N17">
-        <v>4.06</v>
-      </c>
-      <c r="O17">
-        <v>4.08</v>
-      </c>
       <c r="P17">
-        <v>279600</v>
+        <v>71000</v>
       </c>
     </row>
     <row r="18">
@@ -914,22 +914,22 @@
         <v>-</v>
       </c>
       <c r="C18">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="D18">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="E18">
-        <v>-0.6944444444444444</v>
+        <v>0.7092198581560284</v>
       </c>
       <c r="F18">
+        <v>1.41</v>
+      </c>
+      <c r="G18">
         <v>1.44</v>
       </c>
-      <c r="G18">
-        <v>1.45</v>
-      </c>
       <c r="H18">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -938,22 +938,22 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>1723855</v>
+        <v>9665714</v>
       </c>
       <c r="L18">
-        <v>2472.2457000000004</v>
+        <v>13756.94175</v>
       </c>
       <c r="M18">
-        <v>594700</v>
+        <v>2032300</v>
       </c>
       <c r="N18">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="O18">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="P18">
-        <v>288900</v>
+        <v>89400</v>
       </c>
     </row>
     <row r="19">
@@ -967,43 +967,43 @@
         <v>4.76</v>
       </c>
       <c r="D19">
-        <v>-0.06</v>
+        <v>0.04</v>
       </c>
       <c r="E19">
-        <v>-1.2448132780082988</v>
+        <v>0.847457627118644</v>
       </c>
       <c r="F19">
-        <v>4.86</v>
+        <v>4.76</v>
       </c>
       <c r="G19">
-        <v>4.86</v>
+        <v>4.78</v>
       </c>
       <c r="H19">
+        <v>4.72</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>119600</v>
+      </c>
+      <c r="L19">
+        <v>569.22</v>
+      </c>
+      <c r="M19">
+        <v>6600</v>
+      </c>
+      <c r="N19">
+        <v>4.74</v>
+      </c>
+      <c r="O19">
         <v>4.76</v>
       </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>6300</v>
-      </c>
-      <c r="L19">
-        <v>29.998</v>
-      </c>
-      <c r="M19">
-        <v>5700</v>
-      </c>
-      <c r="N19">
-        <v>4.76</v>
-      </c>
-      <c r="O19">
-        <v>4.8</v>
-      </c>
       <c r="P19">
-        <v>1000</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="20">
@@ -1026,7 +1026,7 @@
         <v>5</v>
       </c>
       <c r="G20">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="H20">
         <v>4.98</v>
@@ -1038,13 +1038,13 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>76900</v>
+        <v>79200</v>
       </c>
       <c r="L20">
-        <v>384.41</v>
+        <v>395.991</v>
       </c>
       <c r="M20">
-        <v>170000</v>
+        <v>201800</v>
       </c>
       <c r="N20">
         <v>4.98</v>
@@ -1053,7 +1053,7 @@
         <v>5</v>
       </c>
       <c r="P20">
-        <v>103800</v>
+        <v>66300</v>
       </c>
     </row>
     <row r="21">
@@ -1076,10 +1076,10 @@
         <v>0.68</v>
       </c>
       <c r="G21">
-        <v>0.68</v>
+        <v>0.69</v>
       </c>
       <c r="H21">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1088,13 +1088,13 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>853235</v>
+        <v>39274616</v>
       </c>
       <c r="L21">
-        <v>573.3058000000001</v>
+        <v>26405.03672</v>
       </c>
       <c r="M21">
-        <v>19075700</v>
+        <v>948400</v>
       </c>
       <c r="N21">
         <v>0.67</v>
@@ -1103,7 +1103,7 @@
         <v>0.68</v>
       </c>
       <c r="P21">
-        <v>5638000</v>
+        <v>13531900</v>
       </c>
     </row>
     <row r="22">
@@ -1114,46 +1114,46 @@
         <v>-</v>
       </c>
       <c r="C22">
+        <v>14.6</v>
+      </c>
+      <c r="D22">
+        <v>-0.1</v>
+      </c>
+      <c r="E22">
+        <v>-0.6802721088435374</v>
+      </c>
+      <c r="F22">
         <v>14.8</v>
       </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
+      <c r="G22">
+        <v>14.8</v>
+      </c>
+      <c r="H22">
+        <v>14.6</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>998658</v>
+      </c>
+      <c r="L22">
+        <v>14649.8635</v>
+      </c>
+      <c r="M22">
+        <v>62800</v>
+      </c>
+      <c r="N22">
+        <v>14.6</v>
+      </c>
+      <c r="O22">
         <v>14.7</v>
       </c>
-      <c r="G22">
-        <v>15</v>
-      </c>
-      <c r="H22">
-        <v>14.7</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>914439</v>
-      </c>
-      <c r="L22">
-        <v>13538.7161</v>
-      </c>
-      <c r="M22">
-        <v>115200</v>
-      </c>
-      <c r="N22">
-        <v>14.8</v>
-      </c>
-      <c r="O22">
-        <v>14.9</v>
-      </c>
       <c r="P22">
-        <v>85200</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="23">
@@ -1164,23 +1164,23 @@
         <v>-</v>
       </c>
       <c r="C23">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>0.7246376811594203</v>
       </c>
       <c r="F23">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="G23">
+        <v>14</v>
+      </c>
+      <c r="H23">
         <v>13.8</v>
       </c>
-      <c r="H23">
-        <v>13.6</v>
-      </c>
       <c r="I23">
         <v>0</v>
       </c>
@@ -1188,22 +1188,22 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>246028</v>
+        <v>740963</v>
       </c>
       <c r="L23">
-        <v>3372.5074</v>
+        <v>10289.0565</v>
       </c>
       <c r="M23">
-        <v>81400</v>
+        <v>281600</v>
       </c>
       <c r="N23">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="O23">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="P23">
-        <v>129000</v>
+        <v>133600</v>
       </c>
     </row>
     <row r="24">
@@ -1214,22 +1214,22 @@
         <v>-</v>
       </c>
       <c r="C24">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="D24">
         <v>-0.02</v>
       </c>
       <c r="E24">
-        <v>-0.6329113924050633</v>
+        <v>-0.6369426751592356</v>
       </c>
       <c r="F24">
+        <v>3.14</v>
+      </c>
+      <c r="G24">
         <v>3.16</v>
       </c>
-      <c r="G24">
-        <v>3.18</v>
-      </c>
       <c r="H24">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1238,13 +1238,13 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>2390375</v>
+        <v>1291978</v>
       </c>
       <c r="L24">
-        <v>7494.31042</v>
+        <v>4053.55446</v>
       </c>
       <c r="M24">
-        <v>369100</v>
+        <v>428800</v>
       </c>
       <c r="N24">
         <v>3.12</v>
@@ -1253,7 +1253,7 @@
         <v>3.14</v>
       </c>
       <c r="P24">
-        <v>414100</v>
+        <v>452300</v>
       </c>
     </row>
     <row r="25">
@@ -1264,46 +1264,46 @@
         <v>-</v>
       </c>
       <c r="C25">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="D25">
-        <v>0.25</v>
+        <v>-0.15</v>
       </c>
       <c r="E25">
-        <v>2.9940119760479043</v>
+        <v>-1.7341040462427746</v>
       </c>
       <c r="F25">
         <v>8.65</v>
       </c>
       <c r="G25">
-        <v>8.75</v>
+        <v>8.65</v>
       </c>
       <c r="H25">
+        <v>8.5</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>925083</v>
+      </c>
+      <c r="L25">
+        <v>7915.8463</v>
+      </c>
+      <c r="M25">
+        <v>199800</v>
+      </c>
+      <c r="N25">
+        <v>8.5</v>
+      </c>
+      <c r="O25">
         <v>8.55</v>
       </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>8392365</v>
-      </c>
-      <c r="L25">
-        <v>72569.17629999999</v>
-      </c>
-      <c r="M25">
-        <v>323100</v>
-      </c>
-      <c r="N25">
-        <v>8.55</v>
-      </c>
-      <c r="O25">
-        <v>8.6</v>
-      </c>
       <c r="P25">
-        <v>35500</v>
+        <v>31500</v>
       </c>
     </row>
     <row r="26">
@@ -1314,22 +1314,22 @@
         <v>-</v>
       </c>
       <c r="C26">
+        <v>6.85</v>
+      </c>
+      <c r="D26">
+        <v>-0.1</v>
+      </c>
+      <c r="E26">
+        <v>-1.4388489208633093</v>
+      </c>
+      <c r="F26">
         <v>7</v>
       </c>
-      <c r="D26">
-        <v>-0.05</v>
-      </c>
-      <c r="E26">
-        <v>-0.7092198581560284</v>
-      </c>
-      <c r="F26">
-        <v>7.1</v>
-      </c>
       <c r="G26">
-        <v>7.15</v>
+        <v>7.05</v>
       </c>
       <c r="H26">
-        <v>7</v>
+        <v>6.85</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1338,22 +1338,22 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>1101944</v>
+        <v>1202031</v>
       </c>
       <c r="L26">
-        <v>7777.92685</v>
+        <v>8313.443650000001</v>
       </c>
       <c r="M26">
-        <v>207000</v>
+        <v>161100</v>
       </c>
       <c r="N26">
-        <v>6.95</v>
+        <v>6.85</v>
       </c>
       <c r="O26">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="P26">
-        <v>89100</v>
+        <v>38600</v>
       </c>
     </row>
     <row r="27">
@@ -1364,23 +1364,23 @@
         <v>-</v>
       </c>
       <c r="C27">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>8.904109589041095</v>
       </c>
       <c r="F27">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="G27">
+        <v>1.61</v>
+      </c>
+      <c r="H27">
         <v>1.44</v>
       </c>
-      <c r="H27">
-        <v>1.42</v>
-      </c>
       <c r="I27">
         <v>0</v>
       </c>
@@ -1388,22 +1388,22 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>4514300</v>
+        <v>261554760</v>
       </c>
       <c r="L27">
-        <v>6456.164</v>
+        <v>406670.12568</v>
       </c>
       <c r="M27">
-        <v>231400</v>
+        <v>2080900</v>
       </c>
       <c r="N27">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="O27">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="P27">
-        <v>1088100</v>
+        <v>5383300</v>
       </c>
     </row>
     <row r="28">
@@ -1414,22 +1414,22 @@
         <v>-</v>
       </c>
       <c r="C28">
-        <v>14</v>
+        <v>14.8</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>4.964539007092198</v>
       </c>
       <c r="F28">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="G28">
-        <v>14.1</v>
+        <v>14.8</v>
       </c>
       <c r="H28">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1438,22 +1438,22 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>174015</v>
+        <v>2109111</v>
       </c>
       <c r="L28">
-        <v>2441.75</v>
+        <v>30301.7474</v>
       </c>
       <c r="M28">
-        <v>12500</v>
+        <v>17000</v>
       </c>
       <c r="N28">
-        <v>14</v>
+        <v>14.6</v>
       </c>
       <c r="O28">
-        <v>14.1</v>
+        <v>14.8</v>
       </c>
       <c r="P28">
-        <v>21000</v>
+        <v>66400</v>
       </c>
     </row>
     <row r="29">
@@ -1464,23 +1464,23 @@
         <v>-</v>
       </c>
       <c r="C29">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="D29">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>0.9900990099009901</v>
+        <v>0</v>
       </c>
       <c r="F29">
         <v>10.2</v>
       </c>
       <c r="G29">
+        <v>10.4</v>
+      </c>
+      <c r="H29">
         <v>10.2</v>
       </c>
-      <c r="H29">
-        <v>10.1</v>
-      </c>
       <c r="I29">
         <v>0</v>
       </c>
@@ -1488,22 +1488,22 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>56400</v>
+        <v>321738</v>
       </c>
       <c r="L29">
-        <v>570.92</v>
+        <v>3312.4498</v>
       </c>
       <c r="M29">
-        <v>216900</v>
+        <v>918600</v>
       </c>
       <c r="N29">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="O29">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="P29">
-        <v>340400</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="30">
@@ -1517,43 +1517,43 @@
         <v>11.3</v>
       </c>
       <c r="D30">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E30">
-        <v>0.8928571428571429</v>
+        <v>2.727272727272727</v>
       </c>
       <c r="F30">
+        <v>11.1</v>
+      </c>
+      <c r="G30">
+        <v>11.3</v>
+      </c>
+      <c r="H30">
+        <v>11</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>5251881</v>
+      </c>
+      <c r="L30">
+        <v>58557.3028</v>
+      </c>
+      <c r="M30">
+        <v>141800</v>
+      </c>
+      <c r="N30">
         <v>11.2</v>
       </c>
-      <c r="G30">
-        <v>11.4</v>
-      </c>
-      <c r="H30">
-        <v>11.1</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>862709</v>
-      </c>
-      <c r="L30">
-        <v>9721.9009</v>
-      </c>
-      <c r="M30">
-        <v>96600</v>
-      </c>
-      <c r="N30">
+      <c r="O30">
         <v>11.3</v>
       </c>
-      <c r="O30">
-        <v>11.4</v>
-      </c>
       <c r="P30">
-        <v>683300</v>
+        <v>540600</v>
       </c>
     </row>
     <row r="31">
@@ -1567,19 +1567,19 @@
         <v>8.15</v>
       </c>
       <c r="D31">
-        <v>-0.05</v>
+        <v>0.1</v>
       </c>
       <c r="E31">
-        <v>-0.6097560975609756</v>
+        <v>1.2422360248447204</v>
       </c>
       <c r="F31">
-        <v>8.2</v>
+        <v>8.05</v>
       </c>
       <c r="G31">
-        <v>8.2</v>
+        <v>8.15</v>
       </c>
       <c r="H31">
-        <v>8.05</v>
+        <v>7.9</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>1701392</v>
+        <v>3605840</v>
       </c>
       <c r="L31">
-        <v>13832.67525</v>
+        <v>28918.8061</v>
       </c>
       <c r="M31">
-        <v>272100</v>
+        <v>76800</v>
       </c>
       <c r="N31">
         <v>8.1</v>
@@ -1603,7 +1603,7 @@
         <v>8.15</v>
       </c>
       <c r="P31">
-        <v>136200</v>
+        <v>154700</v>
       </c>
     </row>
     <row r="32">
@@ -1617,13 +1617,13 @@
         <v>1.05</v>
       </c>
       <c r="D32">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>0.9615384615384616</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G32">
         <v>1.06</v>
@@ -1638,22 +1638,22 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>32546511</v>
+        <v>39242016</v>
       </c>
       <c r="L32">
-        <v>33871.83902000001</v>
+        <v>40738.33656</v>
       </c>
       <c r="M32">
-        <v>718400</v>
+        <v>1212300</v>
       </c>
       <c r="N32">
+        <v>1.04</v>
+      </c>
+      <c r="O32">
         <v>1.05</v>
       </c>
-      <c r="O32">
-        <v>1.06</v>
-      </c>
       <c r="P32">
-        <v>3674800</v>
+        <v>1460900</v>
       </c>
     </row>
     <row r="33">
@@ -1664,19 +1664,19 @@
         <v>-</v>
       </c>
       <c r="C33">
+        <v>2.5</v>
+      </c>
+      <c r="D33">
+        <v>0.02</v>
+      </c>
+      <c r="E33">
+        <v>0.8064516129032258</v>
+      </c>
+      <c r="F33">
+        <v>2.5</v>
+      </c>
+      <c r="G33">
         <v>2.56</v>
-      </c>
-      <c r="D33">
-        <v>0.04</v>
-      </c>
-      <c r="E33">
-        <v>1.5873015873015872</v>
-      </c>
-      <c r="F33">
-        <v>2.54</v>
-      </c>
-      <c r="G33">
-        <v>2.58</v>
       </c>
       <c r="H33">
         <v>2.5</v>
@@ -1688,22 +1688,22 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>12013137</v>
+        <v>3835765</v>
       </c>
       <c r="L33">
-        <v>30631.03258</v>
+        <v>9672.5494</v>
       </c>
       <c r="M33">
-        <v>257700</v>
+        <v>146400</v>
       </c>
       <c r="N33">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="O33">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="P33">
-        <v>759300</v>
+        <v>256800</v>
       </c>
     </row>
     <row r="34">
@@ -1717,20 +1717,20 @@
         <v>0.46</v>
       </c>
       <c r="D34">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E34">
-        <v>2.2222222222222223</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="G34">
+        <v>0.47</v>
+      </c>
+      <c r="H34">
         <v>0.46</v>
       </c>
-      <c r="H34">
-        <v>0.45</v>
-      </c>
       <c r="I34">
         <v>0</v>
       </c>
@@ -1738,22 +1738,22 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>646500</v>
+        <v>12995101</v>
       </c>
       <c r="L34">
-        <v>292.958</v>
+        <v>5991.07247</v>
       </c>
       <c r="M34">
-        <v>4721400</v>
+        <v>1776000</v>
       </c>
       <c r="N34">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="O34">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="P34">
-        <v>8248200</v>
+        <v>13108700</v>
       </c>
     </row>
     <row r="35">
@@ -1764,46 +1764,46 @@
         <v>-</v>
       </c>
       <c r="C35">
+        <v>10.2</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>10.2</v>
+      </c>
+      <c r="G35">
+        <v>10.3</v>
+      </c>
+      <c r="H35">
         <v>10.1</v>
       </c>
-      <c r="D35">
-        <v>-0.1</v>
-      </c>
-      <c r="E35">
-        <v>-0.9803921568627451</v>
-      </c>
-      <c r="F35">
-        <v>10.1</v>
-      </c>
-      <c r="G35">
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>3612521</v>
+      </c>
+      <c r="L35">
+        <v>36867.08605</v>
+      </c>
+      <c r="M35">
+        <v>34900</v>
+      </c>
+      <c r="N35">
         <v>10.2</v>
       </c>
-      <c r="H35">
-        <v>9.95</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>2051395</v>
-      </c>
-      <c r="L35">
-        <v>20587.095699999998</v>
-      </c>
-      <c r="M35">
-        <v>478500</v>
-      </c>
-      <c r="N35">
-        <v>10</v>
-      </c>
       <c r="O35">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="P35">
-        <v>258200</v>
+        <v>787600</v>
       </c>
     </row>
     <row r="36">
@@ -1814,23 +1814,23 @@
         <v>-</v>
       </c>
       <c r="C36">
-        <v>17.1</v>
+        <v>18.4</v>
       </c>
       <c r="D36">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="E36">
-        <v>0.5882352941176471</v>
+        <v>6.976744186046512</v>
       </c>
       <c r="F36">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="G36">
+        <v>18.4</v>
+      </c>
+      <c r="H36">
         <v>17.2</v>
       </c>
-      <c r="H36">
-        <v>17</v>
-      </c>
       <c r="I36">
         <v>0</v>
       </c>
@@ -1838,22 +1838,22 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>47604</v>
+        <v>2574408</v>
       </c>
       <c r="L36">
-        <v>810.3581999999999</v>
+        <v>46135.951</v>
       </c>
       <c r="M36">
-        <v>26000</v>
+        <v>6000</v>
       </c>
       <c r="N36">
-        <v>17</v>
+        <v>18.3</v>
       </c>
       <c r="O36">
-        <v>17.1</v>
+        <v>18.4</v>
       </c>
       <c r="P36">
-        <v>4600</v>
+        <v>59900</v>
       </c>
     </row>
     <row r="37">
@@ -1864,22 +1864,22 @@
         <v>-</v>
       </c>
       <c r="C37">
-        <v>4.78</v>
+        <v>4.7</v>
       </c>
       <c r="D37">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="E37">
-        <v>-0.8298755186721992</v>
+        <v>-0.423728813559322</v>
       </c>
       <c r="F37">
-        <v>4.82</v>
+        <v>4.7</v>
       </c>
       <c r="G37">
-        <v>4.88</v>
+        <v>4.76</v>
       </c>
       <c r="H37">
-        <v>4.78</v>
+        <v>4.7</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -1888,22 +1888,22 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>1610644</v>
+        <v>485800</v>
       </c>
       <c r="L37">
-        <v>7746.83252</v>
+        <v>2295.21</v>
       </c>
       <c r="M37">
-        <v>372800</v>
+        <v>40600</v>
       </c>
       <c r="N37">
-        <v>4.76</v>
+        <v>4.7</v>
       </c>
       <c r="O37">
-        <v>4.78</v>
+        <v>4.72</v>
       </c>
       <c r="P37">
-        <v>18000</v>
+        <v>58100</v>
       </c>
     </row>
     <row r="38">
@@ -1914,46 +1914,46 @@
         <v>-</v>
       </c>
       <c r="C38">
+        <v>13</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>13</v>
+      </c>
+      <c r="G38">
         <v>13.1</v>
       </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38">
-        <v>13.2</v>
-      </c>
-      <c r="G38">
-        <v>13.2</v>
-      </c>
       <c r="H38">
+        <v>12.8</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>1248511</v>
+      </c>
+      <c r="L38">
+        <v>16126.752</v>
+      </c>
+      <c r="M38">
+        <v>60000</v>
+      </c>
+      <c r="N38">
+        <v>12.9</v>
+      </c>
+      <c r="O38">
         <v>13</v>
       </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>444546</v>
-      </c>
-      <c r="L38">
-        <v>5831.7126</v>
-      </c>
-      <c r="M38">
-        <v>168400</v>
-      </c>
-      <c r="N38">
-        <v>13</v>
-      </c>
-      <c r="O38">
-        <v>13.1</v>
-      </c>
       <c r="P38">
-        <v>234600</v>
+        <v>6900</v>
       </c>
     </row>
     <row r="39">
@@ -1964,46 +1964,46 @@
         <v>-</v>
       </c>
       <c r="C39">
-        <v>8.35</v>
+        <v>8.25</v>
       </c>
       <c r="D39">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E39">
-        <v>0.6024096385542169</v>
+        <v>-0.6024096385542169</v>
       </c>
       <c r="F39">
+        <v>8.25</v>
+      </c>
+      <c r="G39">
         <v>8.3</v>
       </c>
-      <c r="G39">
-        <v>8.35</v>
-      </c>
       <c r="H39">
+        <v>8.25</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>137355</v>
+      </c>
+      <c r="L39">
+        <v>1134.4045</v>
+      </c>
+      <c r="M39">
+        <v>11800</v>
+      </c>
+      <c r="N39">
+        <v>8.25</v>
+      </c>
+      <c r="O39">
         <v>8.3</v>
       </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39">
-        <v>5287</v>
-      </c>
-      <c r="L39">
-        <v>44.0471</v>
-      </c>
-      <c r="M39">
-        <v>15500</v>
-      </c>
-      <c r="N39">
-        <v>8.3</v>
-      </c>
-      <c r="O39">
-        <v>8.35</v>
-      </c>
       <c r="P39">
-        <v>46600</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="40">
@@ -2014,46 +2014,46 @@
         <v>-</v>
       </c>
       <c r="C40">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>1.8691588785046729</v>
       </c>
       <c r="F40">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="G40">
+        <v>5.5</v>
+      </c>
+      <c r="H40">
+        <v>5.25</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>1512018</v>
+      </c>
+      <c r="L40">
+        <v>8110.20285</v>
+      </c>
+      <c r="M40">
+        <v>48300</v>
+      </c>
+      <c r="N40">
         <v>5.4</v>
       </c>
-      <c r="H40">
-        <v>5.3</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40">
-        <v>807364</v>
-      </c>
-      <c r="L40">
-        <v>4314.47025</v>
-      </c>
-      <c r="M40">
-        <v>9700</v>
-      </c>
-      <c r="N40">
-        <v>5.35</v>
-      </c>
       <c r="O40">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="P40">
-        <v>152700</v>
+        <v>79900</v>
       </c>
     </row>
     <row r="41">
@@ -2064,19 +2064,19 @@
         <v>-</v>
       </c>
       <c r="C41">
-        <v>8.85</v>
+        <v>9</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>1.1235955056179776</v>
       </c>
       <c r="F41">
         <v>8.9</v>
       </c>
       <c r="G41">
-        <v>8.95</v>
+        <v>9</v>
       </c>
       <c r="H41">
         <v>8.85</v>
@@ -2088,22 +2088,22 @@
         <v>0</v>
       </c>
       <c r="K41">
-        <v>821658</v>
+        <v>2881447</v>
       </c>
       <c r="L41">
-        <v>7289.69335</v>
+        <v>25641.38905</v>
       </c>
       <c r="M41">
-        <v>276100</v>
+        <v>1000</v>
       </c>
       <c r="N41">
-        <v>8.85</v>
+        <v>8.95</v>
       </c>
       <c r="O41">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="P41">
-        <v>342800</v>
+        <v>202400</v>
       </c>
     </row>
     <row r="42">
@@ -2117,43 +2117,43 @@
         <v>4.22</v>
       </c>
       <c r="D42">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <v>-0.4716981132075472</v>
+        <v>0</v>
       </c>
       <c r="F42">
+        <v>4.24</v>
+      </c>
+      <c r="G42">
+        <v>4.24</v>
+      </c>
+      <c r="H42">
+        <v>4.2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>114128</v>
+      </c>
+      <c r="L42">
+        <v>481.57872</v>
+      </c>
+      <c r="M42">
+        <v>149800</v>
+      </c>
+      <c r="N42">
+        <v>4.2</v>
+      </c>
+      <c r="O42">
         <v>4.22</v>
       </c>
-      <c r="G42">
-        <v>4.26</v>
-      </c>
-      <c r="H42">
-        <v>4.22</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42">
-        <v>95120</v>
-      </c>
-      <c r="L42">
-        <v>401.77678000000003</v>
-      </c>
-      <c r="M42">
-        <v>18900</v>
-      </c>
-      <c r="N42">
-        <v>4.22</v>
-      </c>
-      <c r="O42">
-        <v>4.24</v>
-      </c>
       <c r="P42">
-        <v>82600</v>
+        <v>29800</v>
       </c>
     </row>
     <row r="43">
@@ -2164,46 +2164,46 @@
         <v>-</v>
       </c>
       <c r="C43">
-        <v>4.42</v>
+        <v>4.6</v>
       </c>
       <c r="D43">
-        <v>0.02</v>
+        <v>0.16</v>
       </c>
       <c r="E43">
-        <v>0.45454545454545453</v>
+        <v>3.6036036036036037</v>
       </c>
       <c r="F43">
-        <v>4.4</v>
+        <v>4.46</v>
       </c>
       <c r="G43">
+        <v>4.62</v>
+      </c>
+      <c r="H43">
         <v>4.46</v>
       </c>
-      <c r="H43">
-        <v>4.32</v>
-      </c>
       <c r="I43">
-        <v>9000000</v>
+        <v>0</v>
       </c>
       <c r="J43">
-        <v>37800</v>
+        <v>0</v>
       </c>
       <c r="K43">
-        <v>20712202</v>
+        <v>27268940</v>
       </c>
       <c r="L43">
-        <v>89338.69873999999</v>
+        <v>123563.55742</v>
       </c>
       <c r="M43">
-        <v>230800</v>
+        <v>67000</v>
       </c>
       <c r="N43">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O43">
-        <v>4.42</v>
+        <v>4.62</v>
       </c>
       <c r="P43">
-        <v>328600</v>
+        <v>256800</v>
       </c>
     </row>
     <row r="44">
@@ -2214,13 +2214,13 @@
         <v>-</v>
       </c>
       <c r="C44">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="D44">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>2.857142857142857</v>
+        <v>0</v>
       </c>
       <c r="F44">
         <v>0.35</v>
@@ -2229,7 +2229,7 @@
         <v>0.36</v>
       </c>
       <c r="H44">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0</v>
       </c>
       <c r="K44">
-        <v>4392710</v>
+        <v>4481900</v>
       </c>
       <c r="L44">
-        <v>1536.9375</v>
+        <v>1569.266</v>
       </c>
       <c r="M44">
-        <v>1949200</v>
+        <v>3719600</v>
       </c>
       <c r="N44">
         <v>0.35</v>
@@ -2253,7 +2253,7 @@
         <v>0.36</v>
       </c>
       <c r="P44">
-        <v>12862500</v>
+        <v>11496100</v>
       </c>
     </row>
     <row r="45">
@@ -2264,22 +2264,22 @@
         <v>-</v>
       </c>
       <c r="C45">
+        <v>3.14</v>
+      </c>
+      <c r="D45">
+        <v>-0.12</v>
+      </c>
+      <c r="E45">
+        <v>-3.6809815950920246</v>
+      </c>
+      <c r="F45">
         <v>3.26</v>
       </c>
-      <c r="D45">
-        <v>-0.02</v>
-      </c>
-      <c r="E45">
-        <v>-0.6097560975609756</v>
-      </c>
-      <c r="F45">
-        <v>3.32</v>
-      </c>
       <c r="G45">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="H45">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2288,22 +2288,22 @@
         <v>0</v>
       </c>
       <c r="K45">
-        <v>60027542</v>
+        <v>15835661</v>
       </c>
       <c r="L45">
-        <v>197621.44712</v>
+        <v>50270.7672</v>
       </c>
       <c r="M45">
-        <v>1009700</v>
+        <v>571300</v>
       </c>
       <c r="N45">
-        <v>3.24</v>
+        <v>3.14</v>
       </c>
       <c r="O45">
-        <v>3.26</v>
+        <v>3.16</v>
       </c>
       <c r="P45">
-        <v>710400</v>
+        <v>457200</v>
       </c>
     </row>
     <row r="46">
@@ -2314,22 +2314,22 @@
         <v>-</v>
       </c>
       <c r="C46">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="D46">
-        <v>0.25</v>
+        <v>-0.1</v>
       </c>
       <c r="E46">
-        <v>3.816793893129771</v>
+        <v>-1.4705882352941178</v>
       </c>
       <c r="F46">
-        <v>6.55</v>
+        <v>6.75</v>
       </c>
       <c r="G46">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
       <c r="H46">
-        <v>6.55</v>
+        <v>6.65</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2338,22 +2338,22 @@
         <v>0</v>
       </c>
       <c r="K46">
-        <v>1220734</v>
+        <v>366701</v>
       </c>
       <c r="L46">
-        <v>8238.93685</v>
+        <v>2461.03175</v>
       </c>
       <c r="M46">
-        <v>83700</v>
+        <v>42700</v>
       </c>
       <c r="N46">
-        <v>6.75</v>
+        <v>6.65</v>
       </c>
       <c r="O46">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="P46">
-        <v>64900</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="47">
@@ -2364,22 +2364,22 @@
         <v>-</v>
       </c>
       <c r="C47">
-        <v>30.75</v>
+        <v>31.5</v>
       </c>
       <c r="D47">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E47">
-        <v>0.819672131147541</v>
+        <v>1.6129032258064515</v>
       </c>
       <c r="F47">
-        <v>30.5</v>
+        <v>31.5</v>
       </c>
       <c r="G47">
-        <v>30.75</v>
+        <v>32.25</v>
       </c>
       <c r="H47">
-        <v>30.5</v>
+        <v>31.5</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2388,22 +2388,22 @@
         <v>0</v>
       </c>
       <c r="K47">
-        <v>45207</v>
+        <v>521964</v>
       </c>
       <c r="L47">
-        <v>1387.0495</v>
+        <v>16558.09075</v>
       </c>
       <c r="M47">
-        <v>39500</v>
+        <v>17800</v>
       </c>
       <c r="N47">
-        <v>30.5</v>
+        <v>31.25</v>
       </c>
       <c r="O47">
-        <v>30.75</v>
+        <v>31.5</v>
       </c>
       <c r="P47">
-        <v>42100</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="48">
@@ -2417,43 +2417,43 @@
         <v>12.6</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>1.6129032258064515</v>
       </c>
       <c r="F48">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="G48">
         <v>12.7</v>
       </c>
       <c r="H48">
+        <v>12.3</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>5246533</v>
+      </c>
+      <c r="L48">
+        <v>65452.071200000006</v>
+      </c>
+      <c r="M48">
+        <v>8000</v>
+      </c>
+      <c r="N48">
+        <v>12.5</v>
+      </c>
+      <c r="O48">
         <v>12.6</v>
       </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>676635</v>
-      </c>
-      <c r="L48">
-        <v>8532.4411</v>
-      </c>
-      <c r="M48">
-        <v>90600</v>
-      </c>
-      <c r="N48">
-        <v>12.6</v>
-      </c>
-      <c r="O48">
-        <v>12.7</v>
-      </c>
       <c r="P48">
-        <v>186800</v>
+        <v>7600</v>
       </c>
     </row>
     <row r="49">
@@ -2464,23 +2464,23 @@
         <v>-</v>
       </c>
       <c r="C49">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="F49">
+        <v>12.6</v>
+      </c>
+      <c r="G49">
+        <v>12.7</v>
+      </c>
+      <c r="H49">
         <v>12.4</v>
       </c>
-      <c r="G49">
-        <v>12.5</v>
-      </c>
-      <c r="H49">
-        <v>12.3</v>
-      </c>
       <c r="I49">
         <v>0</v>
       </c>
@@ -2488,13 +2488,13 @@
         <v>0</v>
       </c>
       <c r="K49">
-        <v>2221074</v>
+        <v>3613668</v>
       </c>
       <c r="L49">
-        <v>27533.5165</v>
+        <v>45327.817299999995</v>
       </c>
       <c r="M49">
-        <v>140300</v>
+        <v>656600</v>
       </c>
       <c r="N49">
         <v>12.4</v>
@@ -2503,7 +2503,7 @@
         <v>12.5</v>
       </c>
       <c r="P49">
-        <v>413200</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="50">
@@ -2514,7 +2514,7 @@
         <v>-</v>
       </c>
       <c r="C50">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2523,14 +2523,14 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>14.7</v>
+        <v>15</v>
       </c>
       <c r="G50">
+        <v>15.2</v>
+      </c>
+      <c r="H50">
         <v>14.8</v>
       </c>
-      <c r="H50">
-        <v>14.7</v>
-      </c>
       <c r="I50">
         <v>0</v>
       </c>
@@ -2538,22 +2538,22 @@
         <v>0</v>
       </c>
       <c r="K50">
-        <v>508393</v>
+        <v>2849592</v>
       </c>
       <c r="L50">
-        <v>7516.0815</v>
+        <v>42696.6472</v>
       </c>
       <c r="M50">
-        <v>188800</v>
+        <v>142800</v>
       </c>
       <c r="N50">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="O50">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="P50">
-        <v>123500</v>
+        <v>114900</v>
       </c>
     </row>
     <row r="51">
@@ -2564,7 +2564,7 @@
         <v>-</v>
       </c>
       <c r="C51">
-        <v>7.35</v>
+        <v>7.8</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2573,13 +2573,13 @@
         <v>0</v>
       </c>
       <c r="F51">
-        <v>7.4</v>
+        <v>7.85</v>
       </c>
       <c r="G51">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="H51">
-        <v>7.3</v>
+        <v>7.75</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2588,22 +2588,22 @@
         <v>0</v>
       </c>
       <c r="K51">
-        <v>409222</v>
+        <v>3641118</v>
       </c>
       <c r="L51">
-        <v>3012.86275</v>
+        <v>28484.72065</v>
       </c>
       <c r="M51">
-        <v>258900</v>
+        <v>180600</v>
       </c>
       <c r="N51">
-        <v>7.3</v>
+        <v>7.75</v>
       </c>
       <c r="O51">
-        <v>7.35</v>
+        <v>7.8</v>
       </c>
       <c r="P51">
-        <v>97300</v>
+        <v>79700</v>
       </c>
     </row>
     <row r="52">
@@ -2614,22 +2614,22 @@
         <v>-</v>
       </c>
       <c r="C52">
-        <v>19.3</v>
+        <v>19.6</v>
       </c>
       <c r="D52">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E52">
-        <v>2.6595744680851063</v>
+        <v>0</v>
       </c>
       <c r="F52">
-        <v>18.8</v>
+        <v>19.7</v>
       </c>
       <c r="G52">
-        <v>19.3</v>
+        <v>19.8</v>
       </c>
       <c r="H52">
-        <v>18.7</v>
+        <v>19.1</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2638,22 +2638,22 @@
         <v>0</v>
       </c>
       <c r="K52">
-        <v>1017701</v>
+        <v>1496504</v>
       </c>
       <c r="L52">
-        <v>19383.4492</v>
+        <v>28983.378</v>
       </c>
       <c r="M52">
-        <v>21800</v>
+        <v>116800</v>
       </c>
       <c r="N52">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="O52">
-        <v>19.3</v>
+        <v>19.6</v>
       </c>
       <c r="P52">
-        <v>64400</v>
+        <v>75800</v>
       </c>
     </row>
     <row r="53">
@@ -2664,22 +2664,22 @@
         <v>-</v>
       </c>
       <c r="C53">
+        <v>2</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>2</v>
+      </c>
+      <c r="G53">
         <v>2.04</v>
       </c>
-      <c r="D53">
-        <v>0</v>
-      </c>
-      <c r="E53">
-        <v>0</v>
-      </c>
-      <c r="F53">
-        <v>2.06</v>
-      </c>
-      <c r="G53">
-        <v>2.06</v>
-      </c>
       <c r="H53">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2688,22 +2688,22 @@
         <v>0</v>
       </c>
       <c r="K53">
-        <v>1216320</v>
+        <v>7755719</v>
       </c>
       <c r="L53">
-        <v>2493.1447000000003</v>
+        <v>15553.398</v>
       </c>
       <c r="M53">
-        <v>2143600</v>
+        <v>251000</v>
       </c>
       <c r="N53">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="O53">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="P53">
-        <v>1432900</v>
+        <v>643800</v>
       </c>
     </row>
     <row r="54">
@@ -2714,22 +2714,22 @@
         <v>-</v>
       </c>
       <c r="C54">
-        <v>3.76</v>
+        <v>4.12</v>
       </c>
       <c r="D54">
         <v>-0.02</v>
       </c>
       <c r="E54">
-        <v>-0.5291005291005291</v>
+        <v>-0.4830917874396135</v>
       </c>
       <c r="F54">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="G54">
-        <v>3.82</v>
+        <v>4.22</v>
       </c>
       <c r="H54">
-        <v>3.76</v>
+        <v>4.06</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2738,22 +2738,22 @@
         <v>0</v>
       </c>
       <c r="K54">
-        <v>2472647</v>
+        <v>26726143</v>
       </c>
       <c r="L54">
-        <v>9354.12644</v>
+        <v>110904.4647</v>
       </c>
       <c r="M54">
-        <v>914200</v>
+        <v>186900</v>
       </c>
       <c r="N54">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="O54">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="P54">
-        <v>158900</v>
+        <v>146000</v>
       </c>
     </row>
     <row r="55">
@@ -2764,46 +2764,46 @@
         <v>-</v>
       </c>
       <c r="C55">
+        <v>4</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>4</v>
+      </c>
+      <c r="G55">
+        <v>4.02</v>
+      </c>
+      <c r="H55">
         <v>3.96</v>
       </c>
-      <c r="D55">
-        <v>0</v>
-      </c>
-      <c r="E55">
-        <v>0</v>
-      </c>
-      <c r="F55">
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>1331609</v>
+      </c>
+      <c r="L55">
+        <v>5305.451639999999</v>
+      </c>
+      <c r="M55">
+        <v>10000</v>
+      </c>
+      <c r="N55">
         <v>3.98</v>
       </c>
-      <c r="G55">
-        <v>3.98</v>
-      </c>
-      <c r="H55">
-        <v>3.94</v>
-      </c>
-      <c r="I55">
-        <v>0</v>
-      </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55">
-        <v>67702</v>
-      </c>
-      <c r="L55">
-        <v>268.17591999999996</v>
-      </c>
-      <c r="M55">
-        <v>46000</v>
-      </c>
-      <c r="N55">
-        <v>3.94</v>
-      </c>
       <c r="O55">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="P55">
-        <v>190300</v>
+        <v>404500</v>
       </c>
     </row>
     <row r="56">
@@ -2814,46 +2814,46 @@
         <v>-</v>
       </c>
       <c r="C56">
+        <v>6.85</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>6.9</v>
+      </c>
+      <c r="G56">
+        <v>6.9</v>
+      </c>
+      <c r="H56">
         <v>6.8</v>
       </c>
-      <c r="D56">
-        <v>0.05</v>
-      </c>
-      <c r="E56">
-        <v>0.7407407407407407</v>
-      </c>
-      <c r="F56">
-        <v>6.75</v>
-      </c>
-      <c r="G56">
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>332910</v>
+      </c>
+      <c r="L56">
+        <v>2285.784</v>
+      </c>
+      <c r="M56">
+        <v>1800</v>
+      </c>
+      <c r="N56">
         <v>6.85</v>
       </c>
-      <c r="H56">
-        <v>6.7</v>
-      </c>
-      <c r="I56">
-        <v>0</v>
-      </c>
-      <c r="J56">
-        <v>0</v>
-      </c>
-      <c r="K56">
-        <v>475400</v>
-      </c>
-      <c r="L56">
-        <v>3225.67</v>
-      </c>
-      <c r="M56">
-        <v>12200</v>
-      </c>
-      <c r="N56">
-        <v>6.8</v>
-      </c>
       <c r="O56">
-        <v>6.85</v>
+        <v>6.9</v>
       </c>
       <c r="P56">
-        <v>39800</v>
+        <v>36100</v>
       </c>
     </row>
     <row r="57">
@@ -2864,22 +2864,22 @@
         <v>-</v>
       </c>
       <c r="C57">
+        <v>8.35</v>
+      </c>
+      <c r="D57">
+        <v>-0.3</v>
+      </c>
+      <c r="E57">
+        <v>-3.468208092485549</v>
+      </c>
+      <c r="F57">
         <v>8.7</v>
       </c>
-      <c r="D57">
-        <v>0.15</v>
-      </c>
-      <c r="E57">
-        <v>1.7543859649122806</v>
-      </c>
-      <c r="F57">
-        <v>8.6</v>
-      </c>
       <c r="G57">
-        <v>8.75</v>
+        <v>8.7</v>
       </c>
       <c r="H57">
-        <v>8.45</v>
+        <v>8.25</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2888,22 +2888,22 @@
         <v>0</v>
       </c>
       <c r="K57">
-        <v>3358900</v>
+        <v>10133431</v>
       </c>
       <c r="L57">
-        <v>28991.01</v>
+        <v>85210.2562</v>
       </c>
       <c r="M57">
-        <v>199600</v>
+        <v>24700</v>
       </c>
       <c r="N57">
-        <v>8.7</v>
+        <v>8.35</v>
       </c>
       <c r="O57">
-        <v>8.75</v>
+        <v>8.4</v>
       </c>
       <c r="P57">
-        <v>407700</v>
+        <v>281200</v>
       </c>
     </row>
     <row r="58">
@@ -2917,13 +2917,13 @@
         <v>5.15</v>
       </c>
       <c r="D58">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="E58">
-        <v>-0.9615384615384616</v>
+        <v>0</v>
       </c>
       <c r="F58">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="G58">
         <v>5.2</v>
@@ -2938,22 +2938,22 @@
         <v>0</v>
       </c>
       <c r="K58">
-        <v>7076827</v>
+        <v>3031912</v>
       </c>
       <c r="L58">
-        <v>36295.35845</v>
+        <v>15617.105</v>
       </c>
       <c r="M58">
-        <v>2056700</v>
+        <v>815300</v>
       </c>
       <c r="N58">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="O58">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="P58">
-        <v>675900</v>
+        <v>1060900</v>
       </c>
     </row>
     <row r="59">
@@ -2964,22 +2964,22 @@
         <v>-</v>
       </c>
       <c r="C59">
-        <v>9.2</v>
+        <v>9.65</v>
       </c>
       <c r="D59">
-        <v>0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="E59">
-        <v>1.6574585635359116</v>
+        <v>-0.5154639175257731</v>
       </c>
       <c r="F59">
-        <v>9.1</v>
+        <v>9.85</v>
       </c>
       <c r="G59">
-        <v>9.25</v>
+        <v>9.85</v>
       </c>
       <c r="H59">
-        <v>9.1</v>
+        <v>9.6</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2988,22 +2988,22 @@
         <v>0</v>
       </c>
       <c r="K59">
-        <v>2885014</v>
+        <v>8777623</v>
       </c>
       <c r="L59">
-        <v>26530.363350000003</v>
+        <v>85499.26920000001</v>
       </c>
       <c r="M59">
-        <v>485600</v>
+        <v>93700</v>
       </c>
       <c r="N59">
-        <v>9.15</v>
+        <v>9.65</v>
       </c>
       <c r="O59">
-        <v>9.2</v>
+        <v>9.7</v>
       </c>
       <c r="P59">
-        <v>129800</v>
+        <v>151400</v>
       </c>
     </row>
     <row r="60">
@@ -3017,19 +3017,19 @@
         <v>3.66</v>
       </c>
       <c r="D60">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E60">
-        <v>-0.5434782608695652</v>
+        <v>0</v>
       </c>
       <c r="F60">
-        <v>3.72</v>
+        <v>3.66</v>
       </c>
       <c r="G60">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="H60">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -3038,13 +3038,13 @@
         <v>0</v>
       </c>
       <c r="K60">
-        <v>2406000</v>
+        <v>4525592</v>
       </c>
       <c r="L60">
-        <v>8891.812</v>
+        <v>16602.01504</v>
       </c>
       <c r="M60">
-        <v>475500</v>
+        <v>711200</v>
       </c>
       <c r="N60">
         <v>3.66</v>
@@ -3053,7 +3053,7 @@
         <v>3.68</v>
       </c>
       <c r="P60">
-        <v>175600</v>
+        <v>86300</v>
       </c>
     </row>
     <row r="61">
@@ -3064,46 +3064,46 @@
         <v>-</v>
       </c>
       <c r="C61">
+        <v>9.5</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>9.5</v>
+      </c>
+      <c r="G61">
+        <v>9.5</v>
+      </c>
+      <c r="H61">
         <v>9.45</v>
       </c>
-      <c r="D61">
-        <v>0.05</v>
-      </c>
-      <c r="E61">
-        <v>0.5319148936170213</v>
-      </c>
-      <c r="F61">
-        <v>9.4</v>
-      </c>
-      <c r="G61">
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>157023</v>
+      </c>
+      <c r="L61">
+        <v>1484.63425</v>
+      </c>
+      <c r="M61">
+        <v>300</v>
+      </c>
+      <c r="N61">
         <v>9.45</v>
       </c>
-      <c r="H61">
-        <v>9.4</v>
-      </c>
-      <c r="I61">
-        <v>0</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
-      </c>
-      <c r="K61">
-        <v>78297</v>
-      </c>
-      <c r="L61">
-        <v>736.1718000000001</v>
-      </c>
-      <c r="M61">
-        <v>249800</v>
-      </c>
-      <c r="N61">
-        <v>9.4</v>
-      </c>
       <c r="O61">
-        <v>9.45</v>
+        <v>9.5</v>
       </c>
       <c r="P61">
-        <v>100300</v>
+        <v>133500</v>
       </c>
     </row>
     <row r="62">
@@ -3114,23 +3114,23 @@
         <v>-</v>
       </c>
       <c r="C62">
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>0.6329113924050633</v>
       </c>
       <c r="F62">
         <v>15.8</v>
       </c>
       <c r="G62">
+        <v>16.1</v>
+      </c>
+      <c r="H62">
         <v>15.8</v>
       </c>
-      <c r="H62">
-        <v>15.6</v>
-      </c>
       <c r="I62">
         <v>0</v>
       </c>
@@ -3138,22 +3138,22 @@
         <v>0</v>
       </c>
       <c r="K62">
-        <v>385183</v>
+        <v>1423636</v>
       </c>
       <c r="L62">
-        <v>6045.120599999999</v>
+        <v>22665.0539</v>
       </c>
       <c r="M62">
-        <v>103700</v>
+        <v>62600</v>
       </c>
       <c r="N62">
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="O62">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="P62">
-        <v>107100</v>
+        <v>104600</v>
       </c>
     </row>
     <row r="63">
@@ -3164,19 +3164,19 @@
         <v>-</v>
       </c>
       <c r="C63">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="D63">
         <v>0.02</v>
       </c>
       <c r="E63">
-        <v>0.9259259259259259</v>
+        <v>0.9345794392523364</v>
       </c>
       <c r="F63">
         <v>2.16</v>
       </c>
       <c r="G63">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H63">
         <v>2.16</v>
@@ -3188,13 +3188,13 @@
         <v>0</v>
       </c>
       <c r="K63">
-        <v>243030</v>
+        <v>122409</v>
       </c>
       <c r="L63">
-        <v>526.9934000000001</v>
+        <v>265.69162</v>
       </c>
       <c r="M63">
-        <v>35400</v>
+        <v>30800</v>
       </c>
       <c r="N63">
         <v>2.16</v>
@@ -3203,7 +3203,7 @@
         <v>2.18</v>
       </c>
       <c r="P63">
-        <v>83300</v>
+        <v>215100</v>
       </c>
     </row>
     <row r="64">
@@ -3223,10 +3223,10 @@
         <v>0</v>
       </c>
       <c r="F64">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="G64">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="H64">
         <v>5.65</v>
@@ -3238,13 +3238,13 @@
         <v>0</v>
       </c>
       <c r="K64">
-        <v>174379</v>
+        <v>191700</v>
       </c>
       <c r="L64">
-        <v>993.8914</v>
+        <v>1088.485</v>
       </c>
       <c r="M64">
-        <v>178500</v>
+        <v>45400</v>
       </c>
       <c r="N64">
         <v>5.65</v>
@@ -3253,7 +3253,7 @@
         <v>5.7</v>
       </c>
       <c r="P64">
-        <v>116900</v>
+        <v>400</v>
       </c>
     </row>
     <row r="65">
@@ -3267,19 +3267,19 @@
         <v>4.64</v>
       </c>
       <c r="D65">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="E65">
-        <v>-0.4291845493562232</v>
+        <v>0.8695652173913043</v>
       </c>
       <c r="F65">
+        <v>4.6</v>
+      </c>
+      <c r="G65">
         <v>4.64</v>
       </c>
-      <c r="G65">
-        <v>4.66</v>
-      </c>
       <c r="H65">
-        <v>4.62</v>
+        <v>4.58</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -3288,13 +3288,13 @@
         <v>0</v>
       </c>
       <c r="K65">
-        <v>642381</v>
+        <v>2602752</v>
       </c>
       <c r="L65">
-        <v>2979.4011600000003</v>
+        <v>12004.61808</v>
       </c>
       <c r="M65">
-        <v>251100</v>
+        <v>31200</v>
       </c>
       <c r="N65">
         <v>4.62</v>
@@ -3303,7 +3303,7 @@
         <v>4.64</v>
       </c>
       <c r="P65">
-        <v>31100</v>
+        <v>236500</v>
       </c>
     </row>
     <row r="66">
@@ -3317,13 +3317,13 @@
         <v>5.15</v>
       </c>
       <c r="D66">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E66">
-        <v>-1.9047619047619047</v>
+        <v>0</v>
       </c>
       <c r="F66">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="G66">
         <v>5.2</v>
@@ -3338,13 +3338,13 @@
         <v>0</v>
       </c>
       <c r="K66">
-        <v>17631</v>
+        <v>17700</v>
       </c>
       <c r="L66">
-        <v>90.94775</v>
+        <v>91.755</v>
       </c>
       <c r="M66">
-        <v>70800</v>
+        <v>88600</v>
       </c>
       <c r="N66">
         <v>5.15</v>
@@ -3353,7 +3353,7 @@
         <v>5.2</v>
       </c>
       <c r="P66">
-        <v>23600</v>
+        <v>600</v>
       </c>
     </row>
     <row r="67">
@@ -3364,23 +3364,23 @@
         <v>-</v>
       </c>
       <c r="C67">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>6.896551724137931</v>
       </c>
       <c r="F67">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="G67">
+        <v>0.62</v>
+      </c>
+      <c r="H67">
         <v>0.59</v>
       </c>
-      <c r="H67">
-        <v>0.58</v>
-      </c>
       <c r="I67">
         <v>0</v>
       </c>
@@ -3388,22 +3388,22 @@
         <v>0</v>
       </c>
       <c r="K67">
-        <v>6411211</v>
+        <v>59064093</v>
       </c>
       <c r="L67">
-        <v>3775.61029</v>
+        <v>35968.68908</v>
       </c>
       <c r="M67">
-        <v>4823400</v>
+        <v>93205100</v>
       </c>
       <c r="N67">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="O67">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="P67">
-        <v>2961400</v>
+        <v>9305700</v>
       </c>
     </row>
     <row r="68">
@@ -3414,13 +3414,13 @@
         <v>-</v>
       </c>
       <c r="C68">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>-1.0638297872340425</v>
       </c>
       <c r="F68">
         <v>18.7</v>
@@ -3429,7 +3429,7 @@
         <v>18.8</v>
       </c>
       <c r="H68">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -3438,22 +3438,22 @@
         <v>0</v>
       </c>
       <c r="K68">
-        <v>756276</v>
+        <v>1235687</v>
       </c>
       <c r="L68">
-        <v>14094.438300000002</v>
+        <v>23003.4544</v>
       </c>
       <c r="M68">
-        <v>93000</v>
+        <v>122700</v>
       </c>
       <c r="N68">
+        <v>18.6</v>
+      </c>
+      <c r="O68">
         <v>18.7</v>
       </c>
-      <c r="O68">
-        <v>18.8</v>
-      </c>
       <c r="P68">
-        <v>101500</v>
+        <v>20100</v>
       </c>
     </row>
     <row r="69">
@@ -3467,43 +3467,43 @@
         <v>11.6</v>
       </c>
       <c r="D69">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="E69">
-        <v>1.7543859649122806</v>
+        <v>-0.8547008547008547</v>
       </c>
       <c r="F69">
-        <v>11.3</v>
+        <v>11.7</v>
       </c>
       <c r="G69">
+        <v>11.8</v>
+      </c>
+      <c r="H69">
+        <v>11.6</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>913070</v>
+      </c>
+      <c r="L69">
+        <v>10710.544699999999</v>
+      </c>
+      <c r="M69">
+        <v>112700</v>
+      </c>
+      <c r="N69">
+        <v>11.6</v>
+      </c>
+      <c r="O69">
         <v>11.7</v>
       </c>
-      <c r="H69">
-        <v>11.3</v>
-      </c>
-      <c r="I69">
-        <v>0</v>
-      </c>
-      <c r="J69">
-        <v>0</v>
-      </c>
-      <c r="K69">
-        <v>1277509</v>
-      </c>
-      <c r="L69">
-        <v>14687.7444</v>
-      </c>
-      <c r="M69">
-        <v>500</v>
-      </c>
-      <c r="N69">
-        <v>11.5</v>
-      </c>
-      <c r="O69">
-        <v>11.6</v>
-      </c>
       <c r="P69">
-        <v>47600</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="70">
@@ -3514,16 +3514,16 @@
         <v>-</v>
       </c>
       <c r="C70">
-        <v>10</v>
+        <v>9.95</v>
       </c>
       <c r="D70">
         <v>0.05</v>
       </c>
       <c r="E70">
-        <v>0.5025125628140703</v>
+        <v>0.5050505050505051</v>
       </c>
       <c r="F70">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="G70">
         <v>10</v>
@@ -3538,22 +3538,22 @@
         <v>0</v>
       </c>
       <c r="K70">
-        <v>153907</v>
+        <v>406865</v>
       </c>
       <c r="L70">
-        <v>1532.35</v>
+        <v>4040.2102999999997</v>
       </c>
       <c r="M70">
-        <v>90800</v>
+        <v>128500</v>
       </c>
       <c r="N70">
+        <v>9.9</v>
+      </c>
+      <c r="O70">
         <v>9.95</v>
       </c>
-      <c r="O70">
-        <v>10</v>
-      </c>
       <c r="P70">
-        <v>210700</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="71">
@@ -3564,46 +3564,46 @@
         <v>-</v>
       </c>
       <c r="C71">
-        <v>8.2</v>
+        <v>8.1</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>-0.6134969325153374</v>
       </c>
       <c r="F71">
         <v>8.2</v>
       </c>
       <c r="G71">
-        <v>8.25</v>
+        <v>8.2</v>
       </c>
       <c r="H71">
+        <v>8</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>349601</v>
+      </c>
+      <c r="L71">
+        <v>2830.04815</v>
+      </c>
+      <c r="M71">
+        <v>15600</v>
+      </c>
+      <c r="N71">
+        <v>8.1</v>
+      </c>
+      <c r="O71">
         <v>8.15</v>
       </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="J71">
-        <v>0</v>
-      </c>
-      <c r="K71">
-        <v>49514</v>
-      </c>
-      <c r="L71">
-        <v>405.1487</v>
-      </c>
-      <c r="M71">
-        <v>42800</v>
-      </c>
-      <c r="N71">
-        <v>8.15</v>
-      </c>
-      <c r="O71">
-        <v>8.2</v>
-      </c>
       <c r="P71">
-        <v>33700</v>
+        <v>17800</v>
       </c>
     </row>
     <row r="72">
@@ -3614,19 +3614,19 @@
         <v>-</v>
       </c>
       <c r="C72">
-        <v>4.56</v>
+        <v>4.52</v>
       </c>
       <c r="D72">
-        <v>0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="E72">
-        <v>0.44052863436123346</v>
+        <v>-1.3100436681222707</v>
       </c>
       <c r="F72">
-        <v>4.58</v>
+        <v>4.64</v>
       </c>
       <c r="G72">
-        <v>4.58</v>
+        <v>4.64</v>
       </c>
       <c r="H72">
         <v>4.5</v>
@@ -3638,22 +3638,22 @@
         <v>0</v>
       </c>
       <c r="K72">
-        <v>606003</v>
+        <v>934982</v>
       </c>
       <c r="L72">
-        <v>2757.60366</v>
+        <v>4270.11116</v>
       </c>
       <c r="M72">
-        <v>4600</v>
+        <v>19100</v>
       </c>
       <c r="N72">
-        <v>4.56</v>
+        <v>4.52</v>
       </c>
       <c r="O72">
-        <v>4.58</v>
+        <v>4.54</v>
       </c>
       <c r="P72">
-        <v>21100</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="73">
@@ -3664,19 +3664,19 @@
         <v>-</v>
       </c>
       <c r="C73">
+        <v>0.78</v>
+      </c>
+      <c r="D73">
+        <v>-0.01</v>
+      </c>
+      <c r="E73">
+        <v>-1.2658227848101267</v>
+      </c>
+      <c r="F73">
+        <v>0.78</v>
+      </c>
+      <c r="G73">
         <v>0.79</v>
-      </c>
-      <c r="D73">
-        <v>-0.03</v>
-      </c>
-      <c r="E73">
-        <v>-3.658536585365854</v>
-      </c>
-      <c r="F73">
-        <v>0.82</v>
-      </c>
-      <c r="G73">
-        <v>0.82</v>
       </c>
       <c r="H73">
         <v>0.78</v>
@@ -3688,22 +3688,22 @@
         <v>0</v>
       </c>
       <c r="K73">
-        <v>21401281</v>
+        <v>4998544</v>
       </c>
       <c r="L73">
-        <v>17026.981239999997</v>
+        <v>3910.43846</v>
       </c>
       <c r="M73">
-        <v>1938400</v>
+        <v>5160000</v>
       </c>
       <c r="N73">
         <v>0.78</v>
       </c>
       <c r="O73">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="P73">
-        <v>1664200</v>
+        <v>625100</v>
       </c>
     </row>
     <row r="74">
@@ -3717,16 +3717,16 @@
         <v>9.6</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>-1.0309278350515463</v>
       </c>
       <c r="F74">
-        <v>9.65</v>
+        <v>9.7</v>
       </c>
       <c r="G74">
-        <v>9.65</v>
+        <v>9.7</v>
       </c>
       <c r="H74">
         <v>9.6</v>
@@ -3738,13 +3738,13 @@
         <v>0</v>
       </c>
       <c r="K74">
-        <v>11200</v>
+        <v>70010</v>
       </c>
       <c r="L74">
-        <v>107.575</v>
+        <v>673.90645</v>
       </c>
       <c r="M74">
-        <v>2200</v>
+        <v>36300</v>
       </c>
       <c r="N74">
         <v>9.6</v>
@@ -3753,7 +3753,7 @@
         <v>9.65</v>
       </c>
       <c r="P74">
-        <v>4100</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="75">
@@ -3764,23 +3764,23 @@
         <v>-</v>
       </c>
       <c r="C75">
-        <v>4.76</v>
+        <v>4.84</v>
       </c>
       <c r="D75">
-        <v>0.06</v>
+        <v>-0.16</v>
       </c>
       <c r="E75">
-        <v>1.2765957446808511</v>
+        <v>-3.2</v>
       </c>
       <c r="F75">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="G75">
+        <v>5.05</v>
+      </c>
+      <c r="H75">
         <v>4.78</v>
       </c>
-      <c r="H75">
-        <v>4.64</v>
-      </c>
       <c r="I75">
         <v>0</v>
       </c>
@@ -3788,22 +3788,22 @@
         <v>0</v>
       </c>
       <c r="K75">
-        <v>13046361</v>
+        <v>36472971</v>
       </c>
       <c r="L75">
-        <v>61530.39298</v>
+        <v>178669.22118</v>
       </c>
       <c r="M75">
-        <v>445300</v>
+        <v>64800</v>
       </c>
       <c r="N75">
-        <v>4.76</v>
+        <v>4.84</v>
       </c>
       <c r="O75">
-        <v>4.78</v>
+        <v>4.86</v>
       </c>
       <c r="P75">
-        <v>534500</v>
+        <v>414500</v>
       </c>
     </row>
     <row r="76">
@@ -3814,46 +3814,46 @@
         <v>-</v>
       </c>
       <c r="C76">
+        <v>6.45</v>
+      </c>
+      <c r="D76">
+        <v>-0.05</v>
+      </c>
+      <c r="E76">
+        <v>-0.7692307692307693</v>
+      </c>
+      <c r="F76">
+        <v>6.5</v>
+      </c>
+      <c r="G76">
+        <v>6.5</v>
+      </c>
+      <c r="H76">
         <v>6.4</v>
       </c>
-      <c r="D76">
-        <v>0</v>
-      </c>
-      <c r="E76">
-        <v>0</v>
-      </c>
-      <c r="F76">
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>5084039</v>
+      </c>
+      <c r="L76">
+        <v>32840.1161</v>
+      </c>
+      <c r="M76">
+        <v>1176800</v>
+      </c>
+      <c r="N76">
         <v>6.4</v>
       </c>
-      <c r="G76">
-        <v>6.4</v>
-      </c>
-      <c r="H76">
-        <v>6.3</v>
-      </c>
-      <c r="I76">
-        <v>0</v>
-      </c>
-      <c r="J76">
-        <v>0</v>
-      </c>
-      <c r="K76">
-        <v>4133384</v>
-      </c>
-      <c r="L76">
-        <v>26300.593699999998</v>
-      </c>
-      <c r="M76">
-        <v>1034300</v>
-      </c>
-      <c r="N76">
-        <v>6.35</v>
-      </c>
       <c r="O76">
-        <v>6.4</v>
+        <v>6.45</v>
       </c>
       <c r="P76">
-        <v>723800</v>
+        <v>136400</v>
       </c>
     </row>
     <row r="77">
@@ -3864,19 +3864,19 @@
         <v>-</v>
       </c>
       <c r="C77">
-        <v>5.7</v>
+        <v>5.65</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>-0.8771929824561403</v>
       </c>
       <c r="F77">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="G77">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="H77">
         <v>5.65</v>
@@ -3888,13 +3888,13 @@
         <v>0</v>
       </c>
       <c r="K77">
-        <v>624747</v>
+        <v>4374247</v>
       </c>
       <c r="L77">
-        <v>3543.2245</v>
+        <v>24894.49825</v>
       </c>
       <c r="M77">
-        <v>286400</v>
+        <v>322000</v>
       </c>
       <c r="N77">
         <v>5.65</v>
@@ -3903,7 +3903,7 @@
         <v>5.7</v>
       </c>
       <c r="P77">
-        <v>229700</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="78">
@@ -3914,19 +3914,19 @@
         <v>-</v>
       </c>
       <c r="C78">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="D78">
-        <v>-0.15</v>
+        <v>0</v>
       </c>
       <c r="E78">
-        <v>-2.459016393442623</v>
+        <v>0</v>
       </c>
       <c r="F78">
-        <v>6.15</v>
+        <v>6.05</v>
       </c>
       <c r="G78">
-        <v>6.15</v>
+        <v>6.05</v>
       </c>
       <c r="H78">
         <v>5.95</v>
@@ -3938,22 +3938,22 @@
         <v>0</v>
       </c>
       <c r="K78">
-        <v>1959825</v>
+        <v>1057658</v>
       </c>
       <c r="L78">
-        <v>11793.761</v>
+        <v>6319.468</v>
       </c>
       <c r="M78">
-        <v>537200</v>
+        <v>25100</v>
       </c>
       <c r="N78">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="O78">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="P78">
-        <v>118100</v>
+        <v>430700</v>
       </c>
     </row>
     <row r="79">
@@ -3964,22 +3964,22 @@
         <v>-</v>
       </c>
       <c r="C79">
-        <v>24</v>
+        <v>24.9</v>
       </c>
       <c r="D79">
-        <v>0.9</v>
+        <v>-0.1</v>
       </c>
       <c r="E79">
-        <v>3.896103896103896</v>
+        <v>-0.4</v>
       </c>
       <c r="F79">
-        <v>23.2</v>
+        <v>25.5</v>
       </c>
       <c r="G79">
-        <v>24</v>
+        <v>25.5</v>
       </c>
       <c r="H79">
-        <v>23.1</v>
+        <v>24.5</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -3988,22 +3988,22 @@
         <v>0</v>
       </c>
       <c r="K79">
-        <v>1725770</v>
+        <v>1428350</v>
       </c>
       <c r="L79">
-        <v>40751.6852</v>
+        <v>35539.2028</v>
       </c>
       <c r="M79">
-        <v>29000</v>
+        <v>22500</v>
       </c>
       <c r="N79">
-        <v>23.9</v>
+        <v>24.9</v>
       </c>
       <c r="O79">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P79">
-        <v>197300</v>
+        <v>334100</v>
       </c>
     </row>
     <row r="80">
@@ -4014,46 +4014,46 @@
         <v>-</v>
       </c>
       <c r="C80">
-        <v>42</v>
+        <v>41.5</v>
       </c>
       <c r="D80">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="E80">
-        <v>-1.1764705882352942</v>
+        <v>-0.5988023952095808</v>
       </c>
       <c r="F80">
-        <v>42.25</v>
+        <v>41.75</v>
       </c>
       <c r="G80">
-        <v>42.25</v>
+        <v>41.75</v>
       </c>
       <c r="H80">
+        <v>41.5</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>8805</v>
+      </c>
+      <c r="L80">
+        <v>365.83425</v>
+      </c>
+      <c r="M80">
+        <v>400</v>
+      </c>
+      <c r="N80">
+        <v>41.5</v>
+      </c>
+      <c r="O80">
         <v>41.75</v>
       </c>
-      <c r="I80">
-        <v>0</v>
-      </c>
-      <c r="J80">
-        <v>0</v>
-      </c>
-      <c r="K80">
-        <v>24400</v>
-      </c>
-      <c r="L80">
-        <v>1023.725</v>
-      </c>
-      <c r="M80">
-        <v>4700</v>
-      </c>
-      <c r="N80">
-        <v>41.75</v>
-      </c>
-      <c r="O80">
-        <v>42</v>
-      </c>
       <c r="P80">
-        <v>2200</v>
+        <v>20400</v>
       </c>
     </row>
     <row r="81">
@@ -4064,19 +4064,19 @@
         <v>-</v>
       </c>
       <c r="C81">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="D81">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E81">
-        <v>1.8181818181818181</v>
+        <v>0</v>
       </c>
       <c r="F81">
         <v>1.11</v>
       </c>
       <c r="G81">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="H81">
         <v>1.1</v>
@@ -4088,22 +4088,22 @@
         <v>0</v>
       </c>
       <c r="K81">
-        <v>6268405</v>
+        <v>4040952</v>
       </c>
       <c r="L81">
-        <v>6965.0455999999995</v>
+        <v>4453.17992</v>
       </c>
       <c r="M81">
-        <v>6890900</v>
+        <v>1842600</v>
       </c>
       <c r="N81">
+        <v>1.1</v>
+      </c>
+      <c r="O81">
         <v>1.11</v>
       </c>
-      <c r="O81">
-        <v>1.12</v>
-      </c>
       <c r="P81">
-        <v>1154100</v>
+        <v>845200</v>
       </c>
     </row>
     <row r="82">
@@ -4114,22 +4114,22 @@
         <v>-</v>
       </c>
       <c r="C82">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>0.9803921568627451</v>
       </c>
       <c r="F82">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="G82">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="H82">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -4138,22 +4138,22 @@
         <v>0</v>
       </c>
       <c r="K82">
-        <v>229111</v>
+        <v>456601</v>
       </c>
       <c r="L82">
-        <v>456.00089</v>
+        <v>932.6700400000001</v>
       </c>
       <c r="M82">
-        <v>159300</v>
+        <v>34200</v>
       </c>
       <c r="N82">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="O82">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="P82">
-        <v>28600</v>
+        <v>166100</v>
       </c>
     </row>
     <row r="83">
@@ -4164,22 +4164,22 @@
         <v>-</v>
       </c>
       <c r="C83">
+        <v>3.56</v>
+      </c>
+      <c r="D83">
+        <v>0.04</v>
+      </c>
+      <c r="E83">
+        <v>1.1363636363636365</v>
+      </c>
+      <c r="F83">
+        <v>3.56</v>
+      </c>
+      <c r="G83">
         <v>3.58</v>
       </c>
-      <c r="D83">
-        <v>0.12</v>
-      </c>
-      <c r="E83">
-        <v>3.468208092485549</v>
-      </c>
-      <c r="F83">
-        <v>3.46</v>
-      </c>
-      <c r="G83">
-        <v>3.6</v>
-      </c>
       <c r="H83">
-        <v>3.46</v>
+        <v>3.52</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -4188,22 +4188,22 @@
         <v>0</v>
       </c>
       <c r="K83">
-        <v>5314524</v>
+        <v>1176916</v>
       </c>
       <c r="L83">
-        <v>18871.75614</v>
+        <v>4173.16084</v>
       </c>
       <c r="M83">
-        <v>167300</v>
+        <v>93000</v>
       </c>
       <c r="N83">
+        <v>3.54</v>
+      </c>
+      <c r="O83">
         <v>3.56</v>
       </c>
-      <c r="O83">
-        <v>3.58</v>
-      </c>
       <c r="P83">
-        <v>115800</v>
+        <v>156500</v>
       </c>
     </row>
     <row r="84">
@@ -4214,22 +4214,22 @@
         <v>-</v>
       </c>
       <c r="C84">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="D84">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E84">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F84">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="G84">
         <v>0.44</v>
       </c>
       <c r="H84">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -4238,13 +4238,13 @@
         <v>0</v>
       </c>
       <c r="K84">
-        <v>70870555</v>
+        <v>9194383</v>
       </c>
       <c r="L84">
-        <v>29967.50557</v>
+        <v>3950.43152</v>
       </c>
       <c r="M84">
-        <v>35927500</v>
+        <v>29158200</v>
       </c>
       <c r="N84">
         <v>0.42</v>
@@ -4253,7 +4253,7 @@
         <v>0.43</v>
       </c>
       <c r="P84">
-        <v>2708400</v>
+        <v>12507400</v>
       </c>
     </row>
     <row r="85">
@@ -4264,19 +4264,19 @@
         <v>-</v>
       </c>
       <c r="C85">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="D85">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E85">
-        <v>-0.5235602094240838</v>
+        <v>0</v>
       </c>
       <c r="F85">
-        <v>3.76</v>
+        <v>3.82</v>
       </c>
       <c r="G85">
-        <v>3.82</v>
+        <v>3.92</v>
       </c>
       <c r="H85">
         <v>3.76</v>
@@ -4288,22 +4288,22 @@
         <v>0</v>
       </c>
       <c r="K85">
-        <v>695401</v>
+        <v>5181880</v>
       </c>
       <c r="L85">
-        <v>2636.5717999999997</v>
+        <v>19896.3425</v>
       </c>
       <c r="M85">
-        <v>30900</v>
+        <v>215600</v>
       </c>
       <c r="N85">
+        <v>3.76</v>
+      </c>
+      <c r="O85">
         <v>3.78</v>
       </c>
-      <c r="O85">
-        <v>3.8</v>
-      </c>
       <c r="P85">
-        <v>39400</v>
+        <v>116800</v>
       </c>
     </row>
     <row r="86">
@@ -4314,46 +4314,46 @@
         <v>-</v>
       </c>
       <c r="C86">
+        <v>9.3</v>
+      </c>
+      <c r="D86">
+        <v>-0.15</v>
+      </c>
+      <c r="E86">
+        <v>-1.5873015873015872</v>
+      </c>
+      <c r="F86">
+        <v>9.55</v>
+      </c>
+      <c r="G86">
+        <v>9.6</v>
+      </c>
+      <c r="H86">
+        <v>9.3</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>6649299</v>
+      </c>
+      <c r="L86">
+        <v>62934.129049999996</v>
+      </c>
+      <c r="M86">
+        <v>458300</v>
+      </c>
+      <c r="N86">
         <v>9.25</v>
       </c>
-      <c r="D86">
-        <v>0.05</v>
-      </c>
-      <c r="E86">
-        <v>0.5434782608695652</v>
-      </c>
-      <c r="F86">
-        <v>9.25</v>
-      </c>
-      <c r="G86">
+      <c r="O86">
         <v>9.3</v>
       </c>
-      <c r="H86">
-        <v>9.2</v>
-      </c>
-      <c r="I86">
-        <v>0</v>
-      </c>
-      <c r="J86">
-        <v>0</v>
-      </c>
-      <c r="K86">
-        <v>1075296</v>
-      </c>
-      <c r="L86">
-        <v>9945.932949999999</v>
-      </c>
-      <c r="M86">
-        <v>1332100</v>
-      </c>
-      <c r="N86">
-        <v>9.2</v>
-      </c>
-      <c r="O86">
-        <v>9.25</v>
-      </c>
       <c r="P86">
-        <v>119800</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="87">
@@ -4364,22 +4364,22 @@
         <v>-</v>
       </c>
       <c r="C87">
-        <v>9.6</v>
+        <v>9.65</v>
       </c>
       <c r="D87">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="E87">
-        <v>-1.0309278350515463</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="F87">
-        <v>9.7</v>
+        <v>9.55</v>
       </c>
       <c r="G87">
         <v>9.7</v>
       </c>
       <c r="H87">
-        <v>9.6</v>
+        <v>9.55</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -4388,13 +4388,13 @@
         <v>0</v>
       </c>
       <c r="K87">
-        <v>17605</v>
+        <v>24233</v>
       </c>
       <c r="L87">
-        <v>169.8885</v>
+        <v>232.7922</v>
       </c>
       <c r="M87">
-        <v>58700</v>
+        <v>20600</v>
       </c>
       <c r="N87">
         <v>9.6</v>
@@ -4403,7 +4403,7 @@
         <v>9.65</v>
       </c>
       <c r="P87">
-        <v>3300</v>
+        <v>11700</v>
       </c>
     </row>
     <row r="88">
@@ -4417,19 +4417,19 @@
         <v>20</v>
       </c>
       <c r="D88">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="E88">
-        <v>-0.4975124378109453</v>
+        <v>0.5025125628140703</v>
       </c>
       <c r="F88">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="G88">
         <v>20.1</v>
       </c>
       <c r="H88">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -4438,22 +4438,22 @@
         <v>0</v>
       </c>
       <c r="K88">
-        <v>362861</v>
+        <v>1248209</v>
       </c>
       <c r="L88">
-        <v>7246.95</v>
+        <v>24861.0687</v>
       </c>
       <c r="M88">
-        <v>98700</v>
+        <v>73000</v>
       </c>
       <c r="N88">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="O88">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="P88">
-        <v>11900</v>
+        <v>126800</v>
       </c>
     </row>
     <row r="89">
@@ -4464,22 +4464,22 @@
         <v>-</v>
       </c>
       <c r="C89">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="D89">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="E89">
-        <v>1.2903225806451613</v>
+        <v>-1.2987012987012987</v>
       </c>
       <c r="F89">
         <v>1.55</v>
       </c>
       <c r="G89">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="H89">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -4488,22 +4488,22 @@
         <v>0</v>
       </c>
       <c r="K89">
-        <v>3439450</v>
+        <v>3849850</v>
       </c>
       <c r="L89">
-        <v>5459.583</v>
+        <v>5894.6715</v>
       </c>
       <c r="M89">
-        <v>290200</v>
+        <v>107300</v>
       </c>
       <c r="N89">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="O89">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="P89">
-        <v>84300</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="90">
@@ -4514,23 +4514,23 @@
         <v>-</v>
       </c>
       <c r="C90">
+        <v>8</v>
+      </c>
+      <c r="D90">
+        <v>0.1</v>
+      </c>
+      <c r="E90">
+        <v>1.2658227848101267</v>
+      </c>
+      <c r="F90">
+        <v>7.9</v>
+      </c>
+      <c r="G90">
+        <v>8</v>
+      </c>
+      <c r="H90">
         <v>7.85</v>
       </c>
-      <c r="D90">
-        <v>0.05</v>
-      </c>
-      <c r="E90">
-        <v>0.6410256410256411</v>
-      </c>
-      <c r="F90">
-        <v>7.85</v>
-      </c>
-      <c r="G90">
-        <v>7.9</v>
-      </c>
-      <c r="H90">
-        <v>7.8</v>
-      </c>
       <c r="I90">
         <v>0</v>
       </c>
@@ -4538,22 +4538,22 @@
         <v>0</v>
       </c>
       <c r="K90">
-        <v>1972647</v>
+        <v>10279852</v>
       </c>
       <c r="L90">
-        <v>15431.817949999999</v>
+        <v>81970.08775</v>
       </c>
       <c r="M90">
-        <v>539400</v>
+        <v>437700</v>
       </c>
       <c r="N90">
-        <v>7.8</v>
+        <v>7.95</v>
       </c>
       <c r="O90">
-        <v>7.85</v>
+        <v>8</v>
       </c>
       <c r="P90">
-        <v>178800</v>
+        <v>132200</v>
       </c>
     </row>
     <row r="91">
@@ -4564,22 +4564,22 @@
         <v>-</v>
       </c>
       <c r="C91">
-        <v>4.4</v>
+        <v>4.42</v>
       </c>
       <c r="D91">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E91">
-        <v>0.45662100456621</v>
+        <v>0</v>
       </c>
       <c r="F91">
-        <v>4.42</v>
+        <v>4.44</v>
       </c>
       <c r="G91">
-        <v>4.44</v>
+        <v>4.46</v>
       </c>
       <c r="H91">
-        <v>4.38</v>
+        <v>4.36</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -4588,22 +4588,22 @@
         <v>0</v>
       </c>
       <c r="K91">
-        <v>85150</v>
+        <v>334018</v>
       </c>
       <c r="L91">
-        <v>374.869</v>
+        <v>1460.69144</v>
       </c>
       <c r="M91">
-        <v>7300</v>
+        <v>28000</v>
       </c>
       <c r="N91">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="O91">
         <v>4.42</v>
       </c>
       <c r="P91">
-        <v>17500</v>
+        <v>53700</v>
       </c>
     </row>
     <row r="92">
@@ -4614,22 +4614,22 @@
         <v>-</v>
       </c>
       <c r="C92">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="D92">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E92">
-        <v>-0.8130081300813008</v>
+        <v>1.7391304347826086</v>
       </c>
       <c r="F92">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="G92">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="H92">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -4638,22 +4638,22 @@
         <v>0</v>
       </c>
       <c r="K92">
-        <v>5585437</v>
+        <v>48974553</v>
       </c>
       <c r="L92">
-        <v>6833.5833</v>
+        <v>57509.14428</v>
       </c>
       <c r="M92">
-        <v>1159900</v>
+        <v>1048100</v>
       </c>
       <c r="N92">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="O92">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="P92">
-        <v>1361500</v>
+        <v>2874100</v>
       </c>
     </row>
     <row r="93">
@@ -4664,22 +4664,22 @@
         <v>-</v>
       </c>
       <c r="C93">
-        <v>30.75</v>
+        <v>31.25</v>
       </c>
       <c r="D93">
-        <v>0.25</v>
+        <v>-0.25</v>
       </c>
       <c r="E93">
-        <v>0.819672131147541</v>
+        <v>-0.7936507936507936</v>
       </c>
       <c r="F93">
-        <v>30.75</v>
+        <v>31.5</v>
       </c>
       <c r="G93">
-        <v>30.75</v>
+        <v>31.5</v>
       </c>
       <c r="H93">
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -4688,22 +4688,22 @@
         <v>0</v>
       </c>
       <c r="K93">
-        <v>48513</v>
+        <v>367902</v>
       </c>
       <c r="L93">
-        <v>1483.43725</v>
+        <v>11501.73625</v>
       </c>
       <c r="M93">
-        <v>68500</v>
+        <v>127300</v>
       </c>
       <c r="N93">
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="O93">
-        <v>30.75</v>
+        <v>31.5</v>
       </c>
       <c r="P93">
-        <v>49000</v>
+        <v>56600</v>
       </c>
     </row>
     <row r="94">
@@ -4717,20 +4717,20 @@
         <v>0.74</v>
       </c>
       <c r="D94">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E94">
-        <v>1.36986301369863</v>
+        <v>0</v>
       </c>
       <c r="F94">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="G94">
+        <v>0.75</v>
+      </c>
+      <c r="H94">
         <v>0.74</v>
       </c>
-      <c r="H94">
-        <v>0.73</v>
-      </c>
       <c r="I94">
         <v>0</v>
       </c>
@@ -4738,22 +4738,22 @@
         <v>0</v>
       </c>
       <c r="K94">
-        <v>4190200</v>
+        <v>3190610</v>
       </c>
       <c r="L94">
-        <v>3058.959</v>
+        <v>2389.1915</v>
       </c>
       <c r="M94">
-        <v>224800</v>
+        <v>884300</v>
       </c>
       <c r="N94">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="O94">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="P94">
-        <v>998900</v>
+        <v>187100</v>
       </c>
     </row>
     <row r="95">
@@ -4764,22 +4764,22 @@
         <v>-</v>
       </c>
       <c r="C95">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="D95">
-        <v>0.05</v>
+        <v>-0.15</v>
       </c>
       <c r="E95">
-        <v>0.7751937984496124</v>
+        <v>-2.3622047244094486</v>
       </c>
       <c r="F95">
-        <v>6.45</v>
+        <v>6.4</v>
       </c>
       <c r="G95">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H95">
-        <v>6.45</v>
+        <v>6.15</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -4788,22 +4788,22 @@
         <v>0</v>
       </c>
       <c r="K95">
-        <v>3012817</v>
+        <v>2363196</v>
       </c>
       <c r="L95">
-        <v>19612.27495</v>
+        <v>14709.372150000001</v>
       </c>
       <c r="M95">
-        <v>449100</v>
+        <v>76000</v>
       </c>
       <c r="N95">
-        <v>6.45</v>
+        <v>6.2</v>
       </c>
       <c r="O95">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="P95">
-        <v>25500</v>
+        <v>83700</v>
       </c>
     </row>
     <row r="96">
@@ -4814,19 +4814,19 @@
         <v>-</v>
       </c>
       <c r="C96">
+        <v>6.3</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
         <v>6.35</v>
       </c>
-      <c r="D96">
-        <v>0</v>
-      </c>
-      <c r="E96">
-        <v>0</v>
-      </c>
-      <c r="F96">
-        <v>6.4</v>
-      </c>
       <c r="G96">
-        <v>6.4</v>
+        <v>6.45</v>
       </c>
       <c r="H96">
         <v>6.3</v>
@@ -4838,22 +4838,22 @@
         <v>0</v>
       </c>
       <c r="K96">
-        <v>111526</v>
+        <v>1451650</v>
       </c>
       <c r="L96">
-        <v>708.2414</v>
+        <v>9237.882800000001</v>
       </c>
       <c r="M96">
-        <v>3000</v>
+        <v>51500</v>
       </c>
       <c r="N96">
+        <v>6.3</v>
+      </c>
+      <c r="O96">
         <v>6.35</v>
       </c>
-      <c r="O96">
-        <v>6.4</v>
-      </c>
       <c r="P96">
-        <v>156400</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="97">
@@ -4867,19 +4867,19 @@
         <v>17.3</v>
       </c>
       <c r="D97">
-        <v>0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="E97">
-        <v>2.9761904761904763</v>
+        <v>-1.1428571428571428</v>
       </c>
       <c r="F97">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="G97">
-        <v>17.3</v>
+        <v>17.6</v>
       </c>
       <c r="H97">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -4888,13 +4888,13 @@
         <v>0</v>
       </c>
       <c r="K97">
-        <v>10289980</v>
+        <v>4053447</v>
       </c>
       <c r="L97">
-        <v>176632.6249</v>
+        <v>70573.511</v>
       </c>
       <c r="M97">
-        <v>82900</v>
+        <v>339300</v>
       </c>
       <c r="N97">
         <v>17.3</v>
@@ -4903,7 +4903,7 @@
         <v>17.4</v>
       </c>
       <c r="P97">
-        <v>1169500</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="98">
@@ -4914,46 +4914,46 @@
         <v>-</v>
       </c>
       <c r="C98">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F98">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="G98">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="H98">
+        <v>2</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>7185045</v>
+      </c>
+      <c r="L98">
+        <v>14467.114300000001</v>
+      </c>
+      <c r="M98">
+        <v>903500</v>
+      </c>
+      <c r="N98">
+        <v>2</v>
+      </c>
+      <c r="O98">
         <v>2.04</v>
       </c>
-      <c r="I98">
-        <v>0</v>
-      </c>
-      <c r="J98">
-        <v>0</v>
-      </c>
-      <c r="K98">
-        <v>23570693</v>
-      </c>
-      <c r="L98">
-        <v>48552.15958</v>
-      </c>
-      <c r="M98">
-        <v>1000</v>
-      </c>
-      <c r="N98">
-        <v>2.06</v>
-      </c>
-      <c r="O98">
-        <v>2.08</v>
-      </c>
       <c r="P98">
-        <v>1344400</v>
+        <v>531000</v>
       </c>
     </row>
     <row r="99">
@@ -4964,23 +4964,23 @@
         <v>-</v>
       </c>
       <c r="C99">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E99">
-        <v>0</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="F99">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="G99">
+        <v>5.3</v>
+      </c>
+      <c r="H99">
         <v>5.25</v>
       </c>
-      <c r="H99">
-        <v>5.2</v>
-      </c>
       <c r="I99">
         <v>0</v>
       </c>
@@ -4988,22 +4988,22 @@
         <v>0</v>
       </c>
       <c r="K99">
-        <v>160000</v>
+        <v>44790</v>
       </c>
       <c r="L99">
-        <v>832.1</v>
+        <v>236.87255</v>
       </c>
       <c r="M99">
-        <v>27200</v>
+        <v>63000</v>
       </c>
       <c r="N99">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="O99">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="P99">
-        <v>26000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="100">
@@ -5014,46 +5014,46 @@
         <v>-</v>
       </c>
       <c r="C100">
-        <v>26.25</v>
+        <v>25.75</v>
       </c>
       <c r="D100">
-        <v>0.25</v>
+        <v>-0.25</v>
       </c>
       <c r="E100">
-        <v>0.9615384615384616</v>
+        <v>-0.9615384615384616</v>
       </c>
       <c r="F100">
-        <v>26.25</v>
+        <v>26</v>
       </c>
       <c r="G100">
         <v>26.25</v>
       </c>
       <c r="H100">
+        <v>25.5</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>681003</v>
+      </c>
+      <c r="L100">
+        <v>17658.303</v>
+      </c>
+      <c r="M100">
+        <v>43900</v>
+      </c>
+      <c r="N100">
         <v>25.75</v>
       </c>
-      <c r="I100">
-        <v>0</v>
-      </c>
-      <c r="J100">
-        <v>0</v>
-      </c>
-      <c r="K100">
-        <v>576701</v>
-      </c>
-      <c r="L100">
-        <v>14949.726</v>
-      </c>
-      <c r="M100">
-        <v>45500</v>
-      </c>
-      <c r="N100">
+      <c r="O100">
         <v>26</v>
       </c>
-      <c r="O100">
-        <v>26.25</v>
-      </c>
       <c r="P100">
-        <v>91200</v>
+        <v>35500</v>
       </c>
     </row>
     <row r="101">
@@ -5064,46 +5064,46 @@
         <v>-</v>
       </c>
       <c r="C101">
+        <v>7.05</v>
+      </c>
+      <c r="D101">
+        <v>-0.2</v>
+      </c>
+      <c r="E101">
+        <v>-2.7586206896551726</v>
+      </c>
+      <c r="F101">
+        <v>7.3</v>
+      </c>
+      <c r="G101">
+        <v>7.3</v>
+      </c>
+      <c r="H101">
+        <v>7</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>2719032</v>
+      </c>
+      <c r="L101">
+        <v>19312.0583</v>
+      </c>
+      <c r="M101">
+        <v>160900</v>
+      </c>
+      <c r="N101">
+        <v>7.05</v>
+      </c>
+      <c r="O101">
         <v>7.1</v>
       </c>
-      <c r="D101">
-        <v>0.1</v>
-      </c>
-      <c r="E101">
-        <v>1.4285714285714286</v>
-      </c>
-      <c r="F101">
-        <v>6.95</v>
-      </c>
-      <c r="G101">
-        <v>7.15</v>
-      </c>
-      <c r="H101">
-        <v>6.95</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0</v>
-      </c>
-      <c r="K101">
-        <v>3897052</v>
-      </c>
-      <c r="L101">
-        <v>27407.597850000002</v>
-      </c>
-      <c r="M101">
-        <v>31700</v>
-      </c>
-      <c r="N101">
-        <v>7.1</v>
-      </c>
-      <c r="O101">
-        <v>7.15</v>
-      </c>
       <c r="P101">
-        <v>223700</v>
+        <v>91000</v>
       </c>
     </row>
     <row r="102">
@@ -5114,22 +5114,22 @@
         <v>-</v>
       </c>
       <c r="C102">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="D102">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="E102">
-        <v>0.8849557522123894</v>
+        <v>-1.7543859649122806</v>
       </c>
       <c r="F102">
-        <v>5.7</v>
+        <v>5.85</v>
       </c>
       <c r="G102">
-        <v>6</v>
+        <v>5.85</v>
       </c>
       <c r="H102">
-        <v>5.65</v>
+        <v>5.6</v>
       </c>
       <c r="I102">
         <v>0</v>
@@ -5138,22 +5138,22 @@
         <v>0</v>
       </c>
       <c r="K102">
-        <v>16569929</v>
+        <v>9903903</v>
       </c>
       <c r="L102">
-        <v>96573.90879999999</v>
+        <v>56251.202</v>
       </c>
       <c r="M102">
-        <v>692300</v>
+        <v>643900</v>
       </c>
       <c r="N102">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="O102">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="P102">
-        <v>145200</v>
+        <v>1186400</v>
       </c>
     </row>
     <row r="103">
@@ -5164,22 +5164,22 @@
         <v>-</v>
       </c>
       <c r="C103">
-        <v>47</v>
+        <v>52.5</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>6.0606060606060606</v>
       </c>
       <c r="F103">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G103">
-        <v>47.25</v>
+        <v>52.5</v>
       </c>
       <c r="H103">
-        <v>46.5</v>
+        <v>50</v>
       </c>
       <c r="I103">
         <v>0</v>
@@ -5188,22 +5188,22 @@
         <v>0</v>
       </c>
       <c r="K103">
-        <v>175409</v>
+        <v>2552941</v>
       </c>
       <c r="L103">
-        <v>8221.47525</v>
+        <v>131784.8835</v>
       </c>
       <c r="M103">
-        <v>37000</v>
+        <v>33900</v>
       </c>
       <c r="N103">
-        <v>46.75</v>
+        <v>51.75</v>
       </c>
       <c r="O103">
-        <v>47</v>
+        <v>52.5</v>
       </c>
       <c r="P103">
-        <v>17600</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="104">
@@ -5214,46 +5214,46 @@
         <v>-</v>
       </c>
       <c r="C104">
+        <v>21.5</v>
+      </c>
+      <c r="D104">
+        <v>-0.1</v>
+      </c>
+      <c r="E104">
+        <v>-0.46296296296296297</v>
+      </c>
+      <c r="F104">
+        <v>21.6</v>
+      </c>
+      <c r="G104">
+        <v>21.7</v>
+      </c>
+      <c r="H104">
+        <v>21.3</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>438245</v>
+      </c>
+      <c r="L104">
+        <v>9425.7183</v>
+      </c>
+      <c r="M104">
+        <v>129000</v>
+      </c>
+      <c r="N104">
         <v>21.4</v>
       </c>
-      <c r="D104">
-        <v>0</v>
-      </c>
-      <c r="E104">
-        <v>0</v>
-      </c>
-      <c r="F104">
+      <c r="O104">
         <v>21.5</v>
       </c>
-      <c r="G104">
-        <v>21.5</v>
-      </c>
-      <c r="H104">
-        <v>21.2</v>
-      </c>
-      <c r="I104">
-        <v>0</v>
-      </c>
-      <c r="J104">
-        <v>0</v>
-      </c>
-      <c r="K104">
-        <v>380833</v>
-      </c>
-      <c r="L104">
-        <v>8121.3893</v>
-      </c>
-      <c r="M104">
-        <v>37800</v>
-      </c>
-      <c r="N104">
-        <v>21.3</v>
-      </c>
-      <c r="O104">
-        <v>21.4</v>
-      </c>
       <c r="P104">
-        <v>23800</v>
+        <v>400</v>
       </c>
     </row>
     <row r="105">
@@ -5264,19 +5264,19 @@
         <v>-</v>
       </c>
       <c r="C105">
+        <v>4.64</v>
+      </c>
+      <c r="D105">
+        <v>0.04</v>
+      </c>
+      <c r="E105">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="F105">
+        <v>4.62</v>
+      </c>
+      <c r="G105">
         <v>4.7</v>
-      </c>
-      <c r="D105">
-        <v>0.02</v>
-      </c>
-      <c r="E105">
-        <v>0.42735042735042733</v>
-      </c>
-      <c r="F105">
-        <v>4.72</v>
-      </c>
-      <c r="G105">
-        <v>4.72</v>
       </c>
       <c r="H105">
         <v>4.62</v>
@@ -5288,22 +5288,22 @@
         <v>0</v>
       </c>
       <c r="K105">
-        <v>4342886</v>
+        <v>6508767</v>
       </c>
       <c r="L105">
-        <v>20281.8805</v>
+        <v>30310.22646</v>
       </c>
       <c r="M105">
-        <v>206600</v>
+        <v>228200</v>
       </c>
       <c r="N105">
-        <v>4.68</v>
+        <v>4.64</v>
       </c>
       <c r="O105">
-        <v>4.7</v>
+        <v>4.66</v>
       </c>
       <c r="P105">
-        <v>353900</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="106">
@@ -5314,13 +5314,13 @@
         <v>-</v>
       </c>
       <c r="C106">
-        <v>5.9</v>
+        <v>5.85</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>0.8620689655172413</v>
       </c>
       <c r="F106">
         <v>5.85</v>
@@ -5329,31 +5329,31 @@
         <v>5.9</v>
       </c>
       <c r="H106">
+        <v>5.8</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>104600</v>
+      </c>
+      <c r="L106">
+        <v>610.435</v>
+      </c>
+      <c r="M106">
+        <v>1300</v>
+      </c>
+      <c r="N106">
         <v>5.85</v>
       </c>
-      <c r="I106">
-        <v>0</v>
-      </c>
-      <c r="J106">
-        <v>0</v>
-      </c>
-      <c r="K106">
-        <v>16401</v>
-      </c>
-      <c r="L106">
-        <v>96.7559</v>
-      </c>
-      <c r="M106">
-        <v>9900</v>
-      </c>
-      <c r="N106">
+      <c r="O106">
         <v>5.9</v>
       </c>
-      <c r="O106">
-        <v>5.95</v>
-      </c>
       <c r="P106">
-        <v>10600</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="107">
@@ -5364,46 +5364,46 @@
         <v>-</v>
       </c>
       <c r="C107">
+        <v>4</v>
+      </c>
+      <c r="D107">
+        <v>-0.04</v>
+      </c>
+      <c r="E107">
+        <v>-0.9900990099009901</v>
+      </c>
+      <c r="F107">
+        <v>4.02</v>
+      </c>
+      <c r="G107">
         <v>4.04</v>
       </c>
-      <c r="D107">
-        <v>0.02</v>
-      </c>
-      <c r="E107">
-        <v>0.4975124378109453</v>
-      </c>
-      <c r="F107">
-        <v>4.04</v>
-      </c>
-      <c r="G107">
-        <v>4.06</v>
-      </c>
       <c r="H107">
+        <v>4</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>499009</v>
+      </c>
+      <c r="L107">
+        <v>2002.30424</v>
+      </c>
+      <c r="M107">
+        <v>592700</v>
+      </c>
+      <c r="N107">
+        <v>4</v>
+      </c>
+      <c r="O107">
         <v>4.02</v>
       </c>
-      <c r="I107">
-        <v>0</v>
-      </c>
-      <c r="J107">
-        <v>0</v>
-      </c>
-      <c r="K107">
-        <v>1383374</v>
-      </c>
-      <c r="L107">
-        <v>5591.31502</v>
-      </c>
-      <c r="M107">
-        <v>222700</v>
-      </c>
-      <c r="N107">
-        <v>4.02</v>
-      </c>
-      <c r="O107">
-        <v>4.04</v>
-      </c>
       <c r="P107">
-        <v>165000</v>
+        <v>37300</v>
       </c>
     </row>
     <row r="108">
@@ -5417,43 +5417,43 @@
         <v>4.44</v>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>-1.3333333333333333</v>
       </c>
       <c r="F108">
+        <v>4.48</v>
+      </c>
+      <c r="G108">
+        <v>4.5</v>
+      </c>
+      <c r="H108">
+        <v>4.4</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108">
+        <v>8944234</v>
+      </c>
+      <c r="L108">
+        <v>39711.11982</v>
+      </c>
+      <c r="M108">
+        <v>315100</v>
+      </c>
+      <c r="N108">
+        <v>4.42</v>
+      </c>
+      <c r="O108">
         <v>4.44</v>
       </c>
-      <c r="G108">
-        <v>4.48</v>
-      </c>
-      <c r="H108">
-        <v>4.42</v>
-      </c>
-      <c r="I108">
-        <v>0</v>
-      </c>
-      <c r="J108">
-        <v>0</v>
-      </c>
-      <c r="K108">
-        <v>4074800</v>
-      </c>
-      <c r="L108">
-        <v>18138.34</v>
-      </c>
-      <c r="M108">
-        <v>352000</v>
-      </c>
-      <c r="N108">
-        <v>4.44</v>
-      </c>
-      <c r="O108">
-        <v>4.46</v>
-      </c>
       <c r="P108">
-        <v>113500</v>
+        <v>207900</v>
       </c>
     </row>
     <row r="109">
@@ -5464,46 +5464,46 @@
         <v>-</v>
       </c>
       <c r="C109">
-        <v>27.25</v>
+        <v>27</v>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>0.9345794392523364</v>
       </c>
       <c r="F109">
-        <v>27.25</v>
+        <v>27</v>
       </c>
       <c r="G109">
-        <v>27.25</v>
+        <v>27</v>
       </c>
       <c r="H109">
+        <v>26.5</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <v>287202</v>
+      </c>
+      <c r="L109">
+        <v>7707.92875</v>
+      </c>
+      <c r="M109">
+        <v>48300</v>
+      </c>
+      <c r="N109">
+        <v>26.75</v>
+      </c>
+      <c r="O109">
         <v>27</v>
       </c>
-      <c r="I109">
-        <v>0</v>
-      </c>
-      <c r="J109">
-        <v>0</v>
-      </c>
-      <c r="K109">
-        <v>68701</v>
-      </c>
-      <c r="L109">
-        <v>1858.07725</v>
-      </c>
-      <c r="M109">
-        <v>27400</v>
-      </c>
-      <c r="N109">
-        <v>27</v>
-      </c>
-      <c r="O109">
-        <v>27.25</v>
-      </c>
       <c r="P109">
-        <v>37400</v>
+        <v>82600</v>
       </c>
     </row>
     <row r="110">
@@ -5514,46 +5514,46 @@
         <v>-</v>
       </c>
       <c r="C110">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="D110">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="E110">
-        <v>-1.1627906976744187</v>
+        <v>-1.7543859649122806</v>
       </c>
       <c r="F110">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="G110">
         <v>1.73</v>
       </c>
       <c r="H110">
+        <v>1.68</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>12142101</v>
+      </c>
+      <c r="L110">
+        <v>20718.8567</v>
+      </c>
+      <c r="M110">
+        <v>1982600</v>
+      </c>
+      <c r="N110">
+        <v>1.68</v>
+      </c>
+      <c r="O110">
         <v>1.69</v>
       </c>
-      <c r="I110">
-        <v>0</v>
-      </c>
-      <c r="J110">
-        <v>0</v>
-      </c>
-      <c r="K110">
-        <v>7771417</v>
-      </c>
-      <c r="L110">
-        <v>13244.86273</v>
-      </c>
-      <c r="M110">
-        <v>204300</v>
-      </c>
-      <c r="N110">
-        <v>1.7</v>
-      </c>
-      <c r="O110">
-        <v>1.71</v>
-      </c>
       <c r="P110">
-        <v>143200</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="111">
@@ -5564,22 +5564,22 @@
         <v>-</v>
       </c>
       <c r="C111">
+        <v>5.35</v>
+      </c>
+      <c r="D111">
+        <v>0.05</v>
+      </c>
+      <c r="E111">
+        <v>0.9433962264150944</v>
+      </c>
+      <c r="F111">
         <v>5.3</v>
-      </c>
-      <c r="D111">
-        <v>0</v>
-      </c>
-      <c r="E111">
-        <v>0</v>
-      </c>
-      <c r="F111">
-        <v>5.35</v>
       </c>
       <c r="G111">
         <v>5.35</v>
       </c>
       <c r="H111">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="I111">
         <v>0</v>
@@ -5588,22 +5588,22 @@
         <v>0</v>
       </c>
       <c r="K111">
-        <v>106528</v>
+        <v>149400</v>
       </c>
       <c r="L111">
-        <v>559.3073</v>
+        <v>794.34</v>
       </c>
       <c r="M111">
-        <v>32100</v>
+        <v>3000</v>
       </c>
       <c r="N111">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="O111">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="P111">
-        <v>43300</v>
+        <v>39300</v>
       </c>
     </row>
     <row r="112">
@@ -5614,22 +5614,22 @@
         <v>-</v>
       </c>
       <c r="C112">
-        <v>22</v>
+        <v>25.75</v>
       </c>
       <c r="D112">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E112">
-        <v>0.9174311926605505</v>
+        <v>1.9801980198019802</v>
       </c>
       <c r="F112">
-        <v>21.5</v>
+        <v>25.25</v>
       </c>
       <c r="G112">
-        <v>22.2</v>
+        <v>26</v>
       </c>
       <c r="H112">
-        <v>18.4</v>
+        <v>24.3</v>
       </c>
       <c r="I112">
         <v>0</v>
@@ -5638,22 +5638,22 @@
         <v>0</v>
       </c>
       <c r="K112">
-        <v>13984692</v>
+        <v>7651251</v>
       </c>
       <c r="L112">
-        <v>291339.16760000004</v>
+        <v>192262.764</v>
       </c>
       <c r="M112">
-        <v>34000</v>
+        <v>34800</v>
       </c>
       <c r="N112">
-        <v>21.9</v>
+        <v>25.5</v>
       </c>
       <c r="O112">
-        <v>22</v>
+        <v>25.75</v>
       </c>
       <c r="P112">
-        <v>7600</v>
+        <v>84100</v>
       </c>
     </row>
     <row r="113">
@@ -5667,43 +5667,43 @@
         <v>13.3</v>
       </c>
       <c r="D113">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="E113">
-        <v>-0.746268656716418</v>
+        <v>0.7575757575757576</v>
       </c>
       <c r="F113">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="G113">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="H113">
+        <v>13.1</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>479502</v>
+      </c>
+      <c r="L113">
+        <v>6331.3506</v>
+      </c>
+      <c r="M113">
+        <v>131700</v>
+      </c>
+      <c r="N113">
+        <v>13.2</v>
+      </c>
+      <c r="O113">
         <v>13.3</v>
       </c>
-      <c r="I113">
-        <v>0</v>
-      </c>
-      <c r="J113">
-        <v>0</v>
-      </c>
-      <c r="K113">
-        <v>121035</v>
-      </c>
-      <c r="L113">
-        <v>1610.2784</v>
-      </c>
-      <c r="M113">
-        <v>52100</v>
-      </c>
-      <c r="N113">
-        <v>13.3</v>
-      </c>
-      <c r="O113">
-        <v>13.4</v>
-      </c>
       <c r="P113">
-        <v>86600</v>
+        <v>112000</v>
       </c>
     </row>
     <row r="114">
@@ -5714,46 +5714,46 @@
         <v>-</v>
       </c>
       <c r="C114">
+        <v>5.7</v>
+      </c>
+      <c r="D114">
+        <v>0.15</v>
+      </c>
+      <c r="E114">
+        <v>2.7027027027027026</v>
+      </c>
+      <c r="F114">
         <v>5.6</v>
       </c>
-      <c r="D114">
-        <v>0.1</v>
-      </c>
-      <c r="E114">
-        <v>1.8181818181818181</v>
-      </c>
-      <c r="F114">
-        <v>5.5</v>
-      </c>
       <c r="G114">
+        <v>5.85</v>
+      </c>
+      <c r="H114">
+        <v>5.6</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>12325066</v>
+      </c>
+      <c r="L114">
+        <v>70888.591</v>
+      </c>
+      <c r="M114">
+        <v>330100</v>
+      </c>
+      <c r="N114">
         <v>5.7</v>
       </c>
-      <c r="H114">
-        <v>5.5</v>
-      </c>
-      <c r="I114">
-        <v>0</v>
-      </c>
-      <c r="J114">
-        <v>0</v>
-      </c>
-      <c r="K114">
-        <v>6152041</v>
-      </c>
-      <c r="L114">
-        <v>34403.487700000005</v>
-      </c>
-      <c r="M114">
-        <v>96700</v>
-      </c>
-      <c r="N114">
-        <v>5.6</v>
-      </c>
       <c r="O114">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="P114">
-        <v>439200</v>
+        <v>56900</v>
       </c>
     </row>
     <row r="115">
@@ -5764,37 +5764,37 @@
         <v>-</v>
       </c>
       <c r="C115">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="D115">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="E115">
-        <v>-0.684931506849315</v>
+        <v>0.6896551724137931</v>
       </c>
       <c r="F115">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="G115">
         <v>14.6</v>
       </c>
       <c r="H115">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="I115">
-        <v>0</v>
+        <v>95000</v>
       </c>
       <c r="J115">
-        <v>0</v>
+        <v>1385.1</v>
       </c>
       <c r="K115">
-        <v>88451</v>
+        <v>373800</v>
       </c>
       <c r="L115">
-        <v>1281.78</v>
+        <v>5449.58</v>
       </c>
       <c r="M115">
-        <v>8800</v>
+        <v>171300</v>
       </c>
       <c r="N115">
         <v>14.5</v>
@@ -5803,7 +5803,7 @@
         <v>14.6</v>
       </c>
       <c r="P115">
-        <v>232500</v>
+        <v>142700</v>
       </c>
     </row>
     <row r="116">
@@ -5814,19 +5814,19 @@
         <v>-</v>
       </c>
       <c r="C116">
-        <v>9.55</v>
+        <v>9.65</v>
       </c>
       <c r="D116">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="E116">
-        <v>0.5263157894736842</v>
+        <v>1.0471204188481675</v>
       </c>
       <c r="F116">
         <v>9.55</v>
       </c>
       <c r="G116">
-        <v>9.55</v>
+        <v>9.65</v>
       </c>
       <c r="H116">
         <v>9.55</v>
@@ -5838,22 +5838,22 @@
         <v>0</v>
       </c>
       <c r="K116">
-        <v>9655</v>
+        <v>35604</v>
       </c>
       <c r="L116">
-        <v>92.19625</v>
+        <v>341.77340000000004</v>
       </c>
       <c r="M116">
-        <v>21600</v>
+        <v>30100</v>
       </c>
       <c r="N116">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="O116">
-        <v>9.6</v>
+        <v>9.65</v>
       </c>
       <c r="P116">
-        <v>12200</v>
+        <v>35500</v>
       </c>
     </row>
     <row r="117">
@@ -5864,13 +5864,13 @@
         <v>-</v>
       </c>
       <c r="C117">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E117">
-        <v>0</v>
+        <v>-1.36986301369863</v>
       </c>
       <c r="F117">
         <v>14.6</v>
@@ -5879,31 +5879,31 @@
         <v>14.6</v>
       </c>
       <c r="H117">
+        <v>14.2</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>983344</v>
+      </c>
+      <c r="L117">
+        <v>14154.1464</v>
+      </c>
+      <c r="M117">
+        <v>44900</v>
+      </c>
+      <c r="N117">
+        <v>14.4</v>
+      </c>
+      <c r="O117">
         <v>14.5</v>
       </c>
-      <c r="I117">
-        <v>0</v>
-      </c>
-      <c r="J117">
-        <v>0</v>
-      </c>
-      <c r="K117">
-        <v>55434</v>
-      </c>
-      <c r="L117">
-        <v>808.4295999999999</v>
-      </c>
-      <c r="M117">
-        <v>203300</v>
-      </c>
-      <c r="N117">
-        <v>14.5</v>
-      </c>
-      <c r="O117">
-        <v>14.6</v>
-      </c>
       <c r="P117">
-        <v>73100</v>
+        <v>24600</v>
       </c>
     </row>
     <row r="118">
@@ -5914,46 +5914,46 @@
         <v>-</v>
       </c>
       <c r="C118">
+        <v>9.7</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118">
+        <v>9.7</v>
+      </c>
+      <c r="G118">
         <v>9.8</v>
       </c>
-      <c r="D118">
-        <v>0.05</v>
-      </c>
-      <c r="E118">
-        <v>0.5128205128205128</v>
-      </c>
-      <c r="F118">
-        <v>9.8</v>
-      </c>
-      <c r="G118">
-        <v>9.85</v>
-      </c>
       <c r="H118">
+        <v>9.65</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>74000</v>
+      </c>
+      <c r="L118">
+        <v>719.175</v>
+      </c>
+      <c r="M118">
+        <v>17600</v>
+      </c>
+      <c r="N118">
+        <v>9.65</v>
+      </c>
+      <c r="O118">
         <v>9.7</v>
       </c>
-      <c r="I118">
-        <v>0</v>
-      </c>
-      <c r="J118">
-        <v>0</v>
-      </c>
-      <c r="K118">
-        <v>80650</v>
-      </c>
-      <c r="L118">
-        <v>787.4644000000001</v>
-      </c>
-      <c r="M118">
-        <v>4100</v>
-      </c>
-      <c r="N118">
-        <v>9.75</v>
-      </c>
-      <c r="O118">
-        <v>9.8</v>
-      </c>
       <c r="P118">
-        <v>4700</v>
+        <v>400</v>
       </c>
     </row>
     <row r="119">
@@ -5964,46 +5964,46 @@
         <v>-</v>
       </c>
       <c r="C119">
+        <v>9.95</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119">
+        <v>9.95</v>
+      </c>
+      <c r="G119">
         <v>10</v>
       </c>
-      <c r="D119">
-        <v>0</v>
-      </c>
-      <c r="E119">
-        <v>0</v>
-      </c>
-      <c r="F119">
+      <c r="H119">
+        <v>9.9</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <v>1153621</v>
+      </c>
+      <c r="L119">
+        <v>11490.54515</v>
+      </c>
+      <c r="M119">
+        <v>117100</v>
+      </c>
+      <c r="N119">
+        <v>9.95</v>
+      </c>
+      <c r="O119">
         <v>10</v>
       </c>
-      <c r="G119">
-        <v>10.1</v>
-      </c>
-      <c r="H119">
-        <v>10</v>
-      </c>
-      <c r="I119">
-        <v>0</v>
-      </c>
-      <c r="J119">
-        <v>0</v>
-      </c>
-      <c r="K119">
-        <v>441648</v>
-      </c>
-      <c r="L119">
-        <v>4417.4496</v>
-      </c>
-      <c r="M119">
-        <v>45100</v>
-      </c>
-      <c r="N119">
-        <v>10</v>
-      </c>
-      <c r="O119">
-        <v>10.1</v>
-      </c>
       <c r="P119">
-        <v>324500</v>
+        <v>135900</v>
       </c>
     </row>
     <row r="120">
@@ -6014,22 +6014,22 @@
         <v>-</v>
       </c>
       <c r="C120">
+        <v>190</v>
+      </c>
+      <c r="D120">
+        <v>2</v>
+      </c>
+      <c r="E120">
+        <v>1.0638297872340425</v>
+      </c>
+      <c r="F120">
         <v>188</v>
       </c>
-      <c r="D120">
-        <v>-0.5</v>
-      </c>
-      <c r="E120">
-        <v>-0.26525198938992045</v>
-      </c>
-      <c r="F120">
-        <v>189</v>
-      </c>
       <c r="G120">
-        <v>189</v>
+        <v>190.5</v>
       </c>
       <c r="H120">
-        <v>187.5</v>
+        <v>188</v>
       </c>
       <c r="I120">
         <v>0</v>
@@ -6038,22 +6038,22 @@
         <v>0</v>
       </c>
       <c r="K120">
-        <v>3687</v>
+        <v>41029</v>
       </c>
       <c r="L120">
-        <v>693.267</v>
+        <v>7748.941</v>
       </c>
       <c r="M120">
-        <v>400</v>
+        <v>2200</v>
       </c>
       <c r="N120">
-        <v>188</v>
+        <v>189.5</v>
       </c>
       <c r="O120">
-        <v>188.5</v>
+        <v>190</v>
       </c>
       <c r="P120">
-        <v>200</v>
+        <v>700</v>
       </c>
     </row>
     <row r="121">
@@ -6064,22 +6064,22 @@
         <v>-</v>
       </c>
       <c r="C121">
-        <v>5.55</v>
+        <v>5.1</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>-0.35</v>
       </c>
       <c r="E121">
-        <v>0</v>
+        <v>-6.422018348623853</v>
       </c>
       <c r="F121">
         <v>5.5</v>
       </c>
       <c r="G121">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H121">
-        <v>5.4</v>
+        <v>5.05</v>
       </c>
       <c r="I121">
         <v>0</v>
@@ -6088,22 +6088,22 @@
         <v>0</v>
       </c>
       <c r="K121">
-        <v>2139650</v>
+        <v>13855772</v>
       </c>
       <c r="L121">
-        <v>11737.397550000002</v>
+        <v>72347.81885</v>
       </c>
       <c r="M121">
-        <v>149700</v>
+        <v>141000</v>
       </c>
       <c r="N121">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="O121">
-        <v>5.55</v>
+        <v>5.15</v>
       </c>
       <c r="P121">
-        <v>136100</v>
+        <v>197400</v>
       </c>
     </row>
     <row r="122">
@@ -6114,19 +6114,19 @@
         <v>-</v>
       </c>
       <c r="C122">
-        <v>4.7</v>
+        <v>4.68</v>
       </c>
       <c r="D122">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E122">
-        <v>-0.423728813559322</v>
+        <v>0</v>
       </c>
       <c r="F122">
-        <v>4.74</v>
+        <v>4.68</v>
       </c>
       <c r="G122">
-        <v>4.74</v>
+        <v>4.72</v>
       </c>
       <c r="H122">
         <v>4.68</v>
@@ -6138,13 +6138,13 @@
         <v>0</v>
       </c>
       <c r="K122">
-        <v>200000</v>
+        <v>236390</v>
       </c>
       <c r="L122">
-        <v>940.926</v>
+        <v>1111.30126</v>
       </c>
       <c r="M122">
-        <v>55700</v>
+        <v>83200</v>
       </c>
       <c r="N122">
         <v>4.68</v>
@@ -6153,7 +6153,7 @@
         <v>4.7</v>
       </c>
       <c r="P122">
-        <v>10500</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="123">
@@ -6164,46 +6164,46 @@
         <v>-</v>
       </c>
       <c r="C123">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="D123">
         <v>0.02</v>
       </c>
       <c r="E123">
-        <v>0.5235602094240838</v>
+        <v>0.5291005291005291</v>
       </c>
       <c r="F123">
+        <v>3.78</v>
+      </c>
+      <c r="G123">
         <v>3.82</v>
       </c>
-      <c r="G123">
-        <v>3.84</v>
-      </c>
       <c r="H123">
+        <v>3.78</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>3411133</v>
+      </c>
+      <c r="L123">
+        <v>12949.616039999999</v>
+      </c>
+      <c r="M123">
+        <v>600700</v>
+      </c>
+      <c r="N123">
+        <v>3.78</v>
+      </c>
+      <c r="O123">
         <v>3.8</v>
       </c>
-      <c r="I123">
-        <v>0</v>
-      </c>
-      <c r="J123">
-        <v>0</v>
-      </c>
-      <c r="K123">
-        <v>2224262</v>
-      </c>
-      <c r="L123">
-        <v>8465.24408</v>
-      </c>
-      <c r="M123">
-        <v>242900</v>
-      </c>
-      <c r="N123">
-        <v>3.82</v>
-      </c>
-      <c r="O123">
-        <v>3.84</v>
-      </c>
       <c r="P123">
-        <v>138200</v>
+        <v>34700</v>
       </c>
     </row>
     <row r="124">
@@ -6214,22 +6214,22 @@
         <v>-</v>
       </c>
       <c r="C124">
-        <v>16.7</v>
+        <v>17.1</v>
       </c>
       <c r="D124">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E124">
-        <v>1.2121212121212122</v>
+        <v>0</v>
       </c>
       <c r="F124">
-        <v>16.4</v>
+        <v>17.2</v>
       </c>
       <c r="G124">
-        <v>16.7</v>
+        <v>17.6</v>
       </c>
       <c r="H124">
-        <v>16.4</v>
+        <v>17</v>
       </c>
       <c r="I124">
         <v>0</v>
@@ -6238,22 +6238,22 @@
         <v>0</v>
       </c>
       <c r="K124">
-        <v>917273</v>
+        <v>6475566</v>
       </c>
       <c r="L124">
-        <v>15234.4586</v>
+        <v>112298.1049</v>
       </c>
       <c r="M124">
-        <v>81100</v>
+        <v>9600</v>
       </c>
       <c r="N124">
-        <v>16.6</v>
+        <v>17.1</v>
       </c>
       <c r="O124">
-        <v>16.7</v>
+        <v>17.2</v>
       </c>
       <c r="P124">
-        <v>128600</v>
+        <v>203200</v>
       </c>
     </row>
     <row r="125">
@@ -6264,22 +6264,22 @@
         <v>-</v>
       </c>
       <c r="C125">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="D125">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="E125">
-        <v>1.694915254237288</v>
+        <v>-0.819672131147541</v>
       </c>
       <c r="F125">
-        <v>11.8</v>
+        <v>12.1</v>
       </c>
       <c r="G125">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="H125">
-        <v>11.8</v>
+        <v>12.1</v>
       </c>
       <c r="I125">
         <v>0</v>
@@ -6288,22 +6288,22 @@
         <v>0</v>
       </c>
       <c r="K125">
-        <v>342610</v>
+        <v>2355890</v>
       </c>
       <c r="L125">
-        <v>4085.668</v>
+        <v>28786.486800000002</v>
       </c>
       <c r="M125">
-        <v>248800</v>
+        <v>139400</v>
       </c>
       <c r="N125">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="O125">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="P125">
-        <v>121200</v>
+        <v>93900</v>
       </c>
     </row>
     <row r="126">
@@ -6314,46 +6314,46 @@
         <v>-</v>
       </c>
       <c r="C126">
+        <v>10.6</v>
+      </c>
+      <c r="D126">
+        <v>0.1</v>
+      </c>
+      <c r="E126">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="F126">
+        <v>10.5</v>
+      </c>
+      <c r="G126">
         <v>10.8</v>
       </c>
-      <c r="D126">
-        <v>-0.1</v>
-      </c>
-      <c r="E126">
-        <v>-0.9174311926605505</v>
-      </c>
-      <c r="F126">
-        <v>11</v>
-      </c>
-      <c r="G126">
-        <v>11</v>
-      </c>
       <c r="H126">
+        <v>10.5</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>212100</v>
+      </c>
+      <c r="L126">
+        <v>2265.44</v>
+      </c>
+      <c r="M126">
+        <v>43700</v>
+      </c>
+      <c r="N126">
         <v>10.6</v>
       </c>
-      <c r="I126">
-        <v>0</v>
-      </c>
-      <c r="J126">
-        <v>0</v>
-      </c>
-      <c r="K126">
-        <v>18205</v>
-      </c>
-      <c r="L126">
-        <v>196.735</v>
-      </c>
-      <c r="M126">
-        <v>200</v>
-      </c>
-      <c r="N126">
+      <c r="O126">
         <v>10.8</v>
       </c>
-      <c r="O126">
-        <v>10.9</v>
-      </c>
       <c r="P126">
-        <v>2600</v>
+        <v>10900</v>
       </c>
     </row>
     <row r="127">
@@ -6364,22 +6364,22 @@
         <v>-</v>
       </c>
       <c r="C127">
+        <v>16.1</v>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+      <c r="E127">
+        <v>0</v>
+      </c>
+      <c r="F127">
+        <v>16.1</v>
+      </c>
+      <c r="G127">
         <v>16.2</v>
       </c>
-      <c r="D127">
-        <v>0.1</v>
-      </c>
-      <c r="E127">
-        <v>0.6211180124223602</v>
-      </c>
-      <c r="F127">
-        <v>16.2</v>
-      </c>
-      <c r="G127">
-        <v>16.3</v>
-      </c>
       <c r="H127">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="I127">
         <v>0</v>
@@ -6388,13 +6388,13 @@
         <v>0</v>
       </c>
       <c r="K127">
-        <v>2458468</v>
+        <v>5819119</v>
       </c>
       <c r="L127">
-        <v>39842.401600000005</v>
+        <v>93254.035</v>
       </c>
       <c r="M127">
-        <v>339400</v>
+        <v>71300</v>
       </c>
       <c r="N127">
         <v>16.1</v>
@@ -6403,7 +6403,7 @@
         <v>16.2</v>
       </c>
       <c r="P127">
-        <v>115300</v>
+        <v>308200</v>
       </c>
     </row>
     <row r="128">
@@ -6414,22 +6414,22 @@
         <v>-</v>
       </c>
       <c r="C128">
+        <v>38.75</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
+      <c r="F128">
+        <v>38.75</v>
+      </c>
+      <c r="G128">
         <v>39</v>
       </c>
-      <c r="D128">
-        <v>0</v>
-      </c>
-      <c r="E128">
-        <v>0</v>
-      </c>
-      <c r="F128">
-        <v>39.25</v>
-      </c>
-      <c r="G128">
-        <v>39.25</v>
-      </c>
       <c r="H128">
-        <v>39</v>
+        <v>38.75</v>
       </c>
       <c r="I128">
         <v>0</v>
@@ -6438,13 +6438,13 @@
         <v>0</v>
       </c>
       <c r="K128">
-        <v>5651</v>
+        <v>38115</v>
       </c>
       <c r="L128">
-        <v>220.414</v>
+        <v>1482.779</v>
       </c>
       <c r="M128">
-        <v>7400</v>
+        <v>1700</v>
       </c>
       <c r="N128">
         <v>38.75</v>
@@ -6453,7 +6453,7 @@
         <v>39</v>
       </c>
       <c r="P128">
-        <v>4000</v>
+        <v>12900</v>
       </c>
     </row>
     <row r="129">
@@ -6464,22 +6464,22 @@
         <v>-</v>
       </c>
       <c r="C129">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E129">
-        <v>0</v>
+        <v>-0.9174311926605505</v>
       </c>
       <c r="F129">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="G129">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="H129">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="I129">
         <v>0</v>
@@ -6488,22 +6488,22 @@
         <v>0</v>
       </c>
       <c r="K129">
-        <v>2757600</v>
+        <v>7667372</v>
       </c>
       <c r="L129">
-        <v>2848.487</v>
+        <v>8363.61527</v>
       </c>
       <c r="M129">
-        <v>297500</v>
+        <v>264500</v>
       </c>
       <c r="N129">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="O129">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="P129">
-        <v>367100</v>
+        <v>65500</v>
       </c>
     </row>
     <row r="130">
@@ -6514,22 +6514,22 @@
         <v>-</v>
       </c>
       <c r="C130">
-        <v>9.2</v>
+        <v>9.15</v>
       </c>
       <c r="D130">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E130">
-        <v>0.546448087431694</v>
+        <v>0</v>
       </c>
       <c r="F130">
-        <v>9.15</v>
+        <v>9.25</v>
       </c>
       <c r="G130">
         <v>9.25</v>
       </c>
       <c r="H130">
-        <v>9.15</v>
+        <v>9.1</v>
       </c>
       <c r="I130">
         <v>0</v>
@@ -6538,13 +6538,13 @@
         <v>0</v>
       </c>
       <c r="K130">
-        <v>76701</v>
+        <v>303310</v>
       </c>
       <c r="L130">
-        <v>705.5343</v>
+        <v>2783.03955</v>
       </c>
       <c r="M130">
-        <v>50100</v>
+        <v>40000</v>
       </c>
       <c r="N130">
         <v>9.15</v>
@@ -6553,7 +6553,7 @@
         <v>9.2</v>
       </c>
       <c r="P130">
-        <v>24400</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="131">
@@ -6564,22 +6564,22 @@
         <v>-</v>
       </c>
       <c r="C131">
-        <v>8.6</v>
+        <v>8.45</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="E131">
-        <v>0</v>
+        <v>-1.744186046511628</v>
       </c>
       <c r="F131">
         <v>8.6</v>
       </c>
       <c r="G131">
-        <v>8.65</v>
+        <v>8.6</v>
       </c>
       <c r="H131">
-        <v>8.55</v>
+        <v>8.4</v>
       </c>
       <c r="I131">
         <v>0</v>
@@ -6588,22 +6588,22 @@
         <v>0</v>
       </c>
       <c r="K131">
-        <v>118839</v>
+        <v>1346001</v>
       </c>
       <c r="L131">
-        <v>1022.78445</v>
+        <v>11400.1986</v>
       </c>
       <c r="M131">
-        <v>162300</v>
+        <v>1400</v>
       </c>
       <c r="N131">
-        <v>8.55</v>
+        <v>8.45</v>
       </c>
       <c r="O131">
-        <v>8.65</v>
+        <v>8.5</v>
       </c>
       <c r="P131">
-        <v>30700</v>
+        <v>51200</v>
       </c>
     </row>
     <row r="132">
@@ -6614,22 +6614,22 @@
         <v>-</v>
       </c>
       <c r="C132">
-        <v>21.6</v>
+        <v>22.7</v>
       </c>
       <c r="D132">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="E132">
-        <v>-2.262443438914027</v>
+        <v>2.2522522522522523</v>
       </c>
       <c r="F132">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="G132">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="H132">
-        <v>21.2</v>
+        <v>22</v>
       </c>
       <c r="I132">
         <v>0</v>
@@ -6638,22 +6638,22 @@
         <v>0</v>
       </c>
       <c r="K132">
-        <v>1227714</v>
+        <v>2985565</v>
       </c>
       <c r="L132">
-        <v>26581.2238</v>
+        <v>67133.51</v>
       </c>
       <c r="M132">
-        <v>7700</v>
+        <v>600</v>
       </c>
       <c r="N132">
-        <v>21.5</v>
+        <v>22.6</v>
       </c>
       <c r="O132">
-        <v>21.6</v>
+        <v>22.7</v>
       </c>
       <c r="P132">
-        <v>1500</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="133">
@@ -6664,46 +6664,46 @@
         <v>-</v>
       </c>
       <c r="C133">
+        <v>11.6</v>
+      </c>
+      <c r="D133">
+        <v>0.2</v>
+      </c>
+      <c r="E133">
+        <v>1.7543859649122806</v>
+      </c>
+      <c r="F133">
         <v>11.4</v>
       </c>
-      <c r="D133">
-        <v>0.1</v>
-      </c>
-      <c r="E133">
-        <v>0.8849557522123894</v>
-      </c>
-      <c r="F133">
+      <c r="G133">
+        <v>11.7</v>
+      </c>
+      <c r="H133">
         <v>11.3</v>
       </c>
-      <c r="G133">
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>6892972</v>
+      </c>
+      <c r="L133">
+        <v>79342.97859999999</v>
+      </c>
+      <c r="M133">
+        <v>792500</v>
+      </c>
+      <c r="N133">
         <v>11.5</v>
       </c>
-      <c r="H133">
-        <v>11.2</v>
-      </c>
-      <c r="I133">
-        <v>0</v>
-      </c>
-      <c r="J133">
-        <v>0</v>
-      </c>
-      <c r="K133">
-        <v>3665534</v>
-      </c>
-      <c r="L133">
-        <v>41548.7886</v>
-      </c>
-      <c r="M133">
-        <v>742200</v>
-      </c>
-      <c r="N133">
-        <v>11.3</v>
-      </c>
       <c r="O133">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="P133">
-        <v>6600</v>
+        <v>248100</v>
       </c>
     </row>
     <row r="134">
@@ -6714,46 +6714,46 @@
         <v>-</v>
       </c>
       <c r="C134">
+        <v>13.4</v>
+      </c>
+      <c r="D134">
+        <v>-0.2</v>
+      </c>
+      <c r="E134">
+        <v>-1.4705882352941178</v>
+      </c>
+      <c r="F134">
         <v>13.6</v>
       </c>
-      <c r="D134">
-        <v>-0.1</v>
-      </c>
-      <c r="E134">
-        <v>-0.7299270072992701</v>
-      </c>
-      <c r="F134">
-        <v>13.7</v>
-      </c>
       <c r="G134">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="H134">
+        <v>13.3</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>1934281</v>
+      </c>
+      <c r="L134">
+        <v>26024.160399999997</v>
+      </c>
+      <c r="M134">
+        <v>275600</v>
+      </c>
+      <c r="N134">
+        <v>13.4</v>
+      </c>
+      <c r="O134">
         <v>13.5</v>
       </c>
-      <c r="I134">
-        <v>0</v>
-      </c>
-      <c r="J134">
-        <v>0</v>
-      </c>
-      <c r="K134">
-        <v>1197110</v>
-      </c>
-      <c r="L134">
-        <v>16235.2397</v>
-      </c>
-      <c r="M134">
-        <v>322400</v>
-      </c>
-      <c r="N134">
-        <v>13.5</v>
-      </c>
-      <c r="O134">
-        <v>13.6</v>
-      </c>
       <c r="P134">
-        <v>347200</v>
+        <v>137500</v>
       </c>
     </row>
     <row r="135">
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="F135">
-        <v>8.2</v>
+        <v>8.25</v>
       </c>
       <c r="G135">
-        <v>8.2</v>
+        <v>8.25</v>
       </c>
       <c r="H135">
         <v>8.1</v>
@@ -6788,13 +6788,13 @@
         <v>0</v>
       </c>
       <c r="K135">
-        <v>122799</v>
+        <v>121777</v>
       </c>
       <c r="L135">
-        <v>1001.0569</v>
+        <v>995.21645</v>
       </c>
       <c r="M135">
-        <v>7300</v>
+        <v>12100</v>
       </c>
       <c r="N135">
         <v>8.15</v>
@@ -6803,7 +6803,7 @@
         <v>8.2</v>
       </c>
       <c r="P135">
-        <v>74200</v>
+        <v>28700</v>
       </c>
     </row>
     <row r="136">
@@ -6814,19 +6814,19 @@
         <v>-</v>
       </c>
       <c r="C136">
-        <v>9</v>
+        <v>9.05</v>
       </c>
       <c r="D136">
-        <v>-0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="E136">
-        <v>-1.639344262295082</v>
+        <v>-0.5494505494505495</v>
       </c>
       <c r="F136">
-        <v>9.15</v>
+        <v>9.05</v>
       </c>
       <c r="G136">
-        <v>9.15</v>
+        <v>9.1</v>
       </c>
       <c r="H136">
         <v>9</v>
@@ -6838,22 +6838,22 @@
         <v>0</v>
       </c>
       <c r="K136">
-        <v>220027</v>
+        <v>91100</v>
       </c>
       <c r="L136">
-        <v>1988.36925</v>
+        <v>824.39</v>
       </c>
       <c r="M136">
-        <v>18600</v>
+        <v>12100</v>
       </c>
       <c r="N136">
-        <v>8.95</v>
+        <v>9.05</v>
       </c>
       <c r="O136">
-        <v>9.05</v>
+        <v>9.1</v>
       </c>
       <c r="P136">
-        <v>5000</v>
+        <v>7400</v>
       </c>
     </row>
     <row r="137">
@@ -6864,13 +6864,13 @@
         <v>-</v>
       </c>
       <c r="C137">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="D137">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="E137">
-        <v>-0.7874015748031497</v>
+        <v>0.7874015748031497</v>
       </c>
       <c r="F137">
         <v>2.54</v>
@@ -6879,7 +6879,7 @@
         <v>2.56</v>
       </c>
       <c r="H137">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I137">
         <v>0</v>
@@ -6888,22 +6888,22 @@
         <v>0</v>
       </c>
       <c r="K137">
-        <v>1019900</v>
+        <v>1955738</v>
       </c>
       <c r="L137">
-        <v>2590.578</v>
+        <v>4972.2472800000005</v>
       </c>
       <c r="M137">
-        <v>609700</v>
+        <v>325900</v>
       </c>
       <c r="N137">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O137">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="P137">
-        <v>79300</v>
+        <v>974100</v>
       </c>
     </row>
     <row r="138">
@@ -6914,22 +6914,22 @@
         <v>-</v>
       </c>
       <c r="C138">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="D138">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="E138">
-        <v>-0.8264462809917356</v>
+        <v>0.8620689655172413</v>
       </c>
       <c r="F138">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="G138">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="H138">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="I138">
         <v>0</v>
@@ -6938,22 +6938,22 @@
         <v>0</v>
       </c>
       <c r="K138">
-        <v>1779100</v>
+        <v>2418600</v>
       </c>
       <c r="L138">
-        <v>2153.838</v>
+        <v>2811.27308</v>
       </c>
       <c r="M138">
-        <v>779800</v>
+        <v>213000</v>
       </c>
       <c r="N138">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="O138">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="P138">
-        <v>339700</v>
+        <v>183700</v>
       </c>
     </row>
     <row r="139">
@@ -6973,37 +6973,37 @@
         <v>0.6211180124223602</v>
       </c>
       <c r="F139">
-        <v>8.1</v>
+        <v>8.05</v>
       </c>
       <c r="G139">
         <v>8.15</v>
       </c>
       <c r="H139">
+        <v>8</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>3759691</v>
+      </c>
+      <c r="L139">
+        <v>30312.5005</v>
+      </c>
+      <c r="M139">
+        <v>178500</v>
+      </c>
+      <c r="N139">
         <v>8.05</v>
       </c>
-      <c r="I139">
-        <v>0</v>
-      </c>
-      <c r="J139">
-        <v>0</v>
-      </c>
-      <c r="K139">
-        <v>1728396</v>
-      </c>
-      <c r="L139">
-        <v>14003.966849999999</v>
-      </c>
-      <c r="M139">
-        <v>458900</v>
-      </c>
-      <c r="N139">
+      <c r="O139">
         <v>8.1</v>
       </c>
-      <c r="O139">
-        <v>8.15</v>
-      </c>
       <c r="P139">
-        <v>449900</v>
+        <v>88100</v>
       </c>
     </row>
     <row r="140">
@@ -7014,19 +7014,19 @@
         <v>-</v>
       </c>
       <c r="C140">
+        <v>12.7</v>
+      </c>
+      <c r="D140">
+        <v>-0.1</v>
+      </c>
+      <c r="E140">
+        <v>-0.78125</v>
+      </c>
+      <c r="F140">
         <v>12.9</v>
       </c>
-      <c r="D140">
-        <v>0.1</v>
-      </c>
-      <c r="E140">
-        <v>0.78125</v>
-      </c>
-      <c r="F140">
-        <v>12.7</v>
-      </c>
       <c r="G140">
-        <v>12.9</v>
+        <v>13.2</v>
       </c>
       <c r="H140">
         <v>12.7</v>
@@ -7038,22 +7038,22 @@
         <v>0</v>
       </c>
       <c r="K140">
-        <v>84224</v>
+        <v>374109</v>
       </c>
       <c r="L140">
-        <v>1081.092</v>
+        <v>4841.7169</v>
       </c>
       <c r="M140">
-        <v>2500</v>
+        <v>47200</v>
       </c>
       <c r="N140">
+        <v>12.7</v>
+      </c>
+      <c r="O140">
         <v>12.9</v>
       </c>
-      <c r="O140">
-        <v>13</v>
-      </c>
       <c r="P140">
-        <v>45200</v>
+        <v>19300</v>
       </c>
     </row>
     <row r="141">
@@ -7064,16 +7064,16 @@
         <v>-</v>
       </c>
       <c r="C141">
+        <v>5.3</v>
+      </c>
+      <c r="D141">
+        <v>-0.1</v>
+      </c>
+      <c r="E141">
+        <v>-1.8518518518518519</v>
+      </c>
+      <c r="F141">
         <v>5.35</v>
-      </c>
-      <c r="D141">
-        <v>0.05</v>
-      </c>
-      <c r="E141">
-        <v>0.9433962264150944</v>
-      </c>
-      <c r="F141">
-        <v>5.3</v>
       </c>
       <c r="G141">
         <v>5.35</v>
@@ -7088,13 +7088,13 @@
         <v>0</v>
       </c>
       <c r="K141">
-        <v>72200</v>
+        <v>475369</v>
       </c>
       <c r="L141">
-        <v>382.67</v>
+        <v>2521.35165</v>
       </c>
       <c r="M141">
-        <v>38800</v>
+        <v>11000</v>
       </c>
       <c r="N141">
         <v>5.3</v>
@@ -7103,7 +7103,7 @@
         <v>5.35</v>
       </c>
       <c r="P141">
-        <v>83200</v>
+        <v>62700</v>
       </c>
     </row>
     <row r="142">
@@ -7117,16 +7117,16 @@
         <v>4.74</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="E142">
-        <v>0</v>
+        <v>-0.42016806722689076</v>
       </c>
       <c r="F142">
         <v>4.76</v>
       </c>
       <c r="G142">
-        <v>4.76</v>
+        <v>4.78</v>
       </c>
       <c r="H142">
         <v>4.72</v>
@@ -7138,22 +7138,22 @@
         <v>0</v>
       </c>
       <c r="K142">
-        <v>29500</v>
+        <v>113009</v>
       </c>
       <c r="L142">
-        <v>139.68</v>
+        <v>536.1805</v>
       </c>
       <c r="M142">
-        <v>5100</v>
+        <v>44900</v>
       </c>
       <c r="N142">
+        <v>4.72</v>
+      </c>
+      <c r="O142">
         <v>4.74</v>
       </c>
-      <c r="O142">
-        <v>4.76</v>
-      </c>
       <c r="P142">
-        <v>33900</v>
+        <v>29200</v>
       </c>
     </row>
     <row r="143">
@@ -7164,19 +7164,19 @@
         <v>-</v>
       </c>
       <c r="C143">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="D143">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E143">
-        <v>0.6666666666666666</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="F143">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G143">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="H143">
         <v>1.5</v>
@@ -7188,22 +7188,22 @@
         <v>0</v>
       </c>
       <c r="K143">
-        <v>1648301</v>
+        <v>9092247</v>
       </c>
       <c r="L143">
-        <v>2474.31152</v>
+        <v>13766.77546</v>
       </c>
       <c r="M143">
-        <v>411200</v>
+        <v>56000</v>
       </c>
       <c r="N143">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="O143">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="P143">
-        <v>262000</v>
+        <v>1261600</v>
       </c>
     </row>
     <row r="144">
@@ -7223,10 +7223,10 @@
         <v>0.6451612903225806</v>
       </c>
       <c r="F144">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="G144">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="H144">
         <v>15.5</v>
@@ -7238,13 +7238,13 @@
         <v>0</v>
       </c>
       <c r="K144">
-        <v>625731</v>
+        <v>230347</v>
       </c>
       <c r="L144">
-        <v>9743.0036</v>
+        <v>3590.2223</v>
       </c>
       <c r="M144">
-        <v>35600</v>
+        <v>170800</v>
       </c>
       <c r="N144">
         <v>15.5</v>
@@ -7253,7 +7253,7 @@
         <v>15.6</v>
       </c>
       <c r="P144">
-        <v>204100</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="145">
@@ -7264,22 +7264,22 @@
         <v>-</v>
       </c>
       <c r="C145">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="D145">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="E145">
-        <v>0.591715976331361</v>
+        <v>-0.5952380952380952</v>
       </c>
       <c r="F145">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="G145">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="H145">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="I145">
         <v>0</v>
@@ -7288,22 +7288,22 @@
         <v>0</v>
       </c>
       <c r="K145">
-        <v>2601300</v>
+        <v>5129884</v>
       </c>
       <c r="L145">
-        <v>8870.898</v>
+        <v>17331.42158</v>
       </c>
       <c r="M145">
-        <v>291700</v>
+        <v>494300</v>
       </c>
       <c r="N145">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="O145">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="P145">
-        <v>154700</v>
+        <v>73100</v>
       </c>
     </row>
     <row r="146">
@@ -7317,19 +7317,19 @@
         <v>7.8</v>
       </c>
       <c r="D146">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="E146">
-        <v>-0.6369426751592356</v>
+        <v>0</v>
       </c>
       <c r="F146">
-        <v>7.85</v>
+        <v>7.8</v>
       </c>
       <c r="G146">
         <v>7.85</v>
       </c>
       <c r="H146">
-        <v>7.8</v>
+        <v>7.75</v>
       </c>
       <c r="I146">
         <v>0</v>
@@ -7338,13 +7338,13 @@
         <v>0</v>
       </c>
       <c r="K146">
-        <v>35501</v>
+        <v>267235</v>
       </c>
       <c r="L146">
-        <v>277.44784999999996</v>
+        <v>2089.61475</v>
       </c>
       <c r="M146">
-        <v>124200</v>
+        <v>101600</v>
       </c>
       <c r="N146">
         <v>7.8</v>
@@ -7353,7 +7353,7 @@
         <v>7.85</v>
       </c>
       <c r="P146">
-        <v>139800</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="147">
@@ -7364,46 +7364,46 @@
         <v>-</v>
       </c>
       <c r="C147">
-        <v>8.7</v>
+        <v>8.55</v>
       </c>
       <c r="D147">
-        <v>0.1</v>
+        <v>-0.25</v>
       </c>
       <c r="E147">
-        <v>1.1627906976744187</v>
+        <v>-2.840909090909091</v>
       </c>
       <c r="F147">
+        <v>8.85</v>
+      </c>
+      <c r="G147">
+        <v>8.85</v>
+      </c>
+      <c r="H147">
+        <v>8.45</v>
+      </c>
+      <c r="I147">
+        <v>0</v>
+      </c>
+      <c r="J147">
+        <v>0</v>
+      </c>
+      <c r="K147">
+        <v>2876859</v>
+      </c>
+      <c r="L147">
+        <v>24813.46125</v>
+      </c>
+      <c r="M147">
+        <v>10200</v>
+      </c>
+      <c r="N147">
+        <v>8.55</v>
+      </c>
+      <c r="O147">
         <v>8.6</v>
       </c>
-      <c r="G147">
-        <v>8.7</v>
-      </c>
-      <c r="H147">
-        <v>8.6</v>
-      </c>
-      <c r="I147">
-        <v>0</v>
-      </c>
-      <c r="J147">
-        <v>0</v>
-      </c>
-      <c r="K147">
-        <v>296352</v>
-      </c>
-      <c r="L147">
-        <v>2566.5049</v>
-      </c>
-      <c r="M147">
-        <v>26800</v>
-      </c>
-      <c r="N147">
-        <v>8.65</v>
-      </c>
-      <c r="O147">
-        <v>8.7</v>
-      </c>
       <c r="P147">
-        <v>503900</v>
+        <v>37800</v>
       </c>
     </row>
     <row r="148">
@@ -7417,19 +7417,19 @@
         <v>5.55</v>
       </c>
       <c r="D148">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E148">
-        <v>0</v>
+        <v>-0.8928571428571429</v>
       </c>
       <c r="F148">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="G148">
         <v>5.6</v>
       </c>
       <c r="H148">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="I148">
         <v>0</v>
@@ -7438,13 +7438,13 @@
         <v>0</v>
       </c>
       <c r="K148">
-        <v>356500</v>
+        <v>746211</v>
       </c>
       <c r="L148">
-        <v>1968.645</v>
+        <v>4115.07705</v>
       </c>
       <c r="M148">
-        <v>226000</v>
+        <v>700</v>
       </c>
       <c r="N148">
         <v>5.5</v>
@@ -7453,7 +7453,7 @@
         <v>5.55</v>
       </c>
       <c r="P148">
-        <v>38200</v>
+        <v>79200</v>
       </c>
     </row>
     <row r="149">
@@ -7467,19 +7467,19 @@
         <v>4.12</v>
       </c>
       <c r="D149">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="E149">
-        <v>0.9803921568627451</v>
+        <v>0</v>
       </c>
       <c r="F149">
-        <v>4.1</v>
+        <v>4.12</v>
       </c>
       <c r="G149">
         <v>4.14</v>
       </c>
       <c r="H149">
-        <v>4.06</v>
+        <v>4.08</v>
       </c>
       <c r="I149">
         <v>0</v>
@@ -7488,13 +7488,13 @@
         <v>0</v>
       </c>
       <c r="K149">
-        <v>3154627</v>
+        <v>1427266</v>
       </c>
       <c r="L149">
-        <v>12942.35524</v>
+        <v>5862.84376</v>
       </c>
       <c r="M149">
-        <v>257400</v>
+        <v>86100</v>
       </c>
       <c r="N149">
         <v>4.1</v>
@@ -7503,7 +7503,7 @@
         <v>4.12</v>
       </c>
       <c r="P149">
-        <v>83500</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="150">
@@ -7514,46 +7514,46 @@
         <v>-</v>
       </c>
       <c r="C150">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="D150">
-        <v>0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="E150">
-        <v>1.7094017094017093</v>
+        <v>-2.5</v>
       </c>
       <c r="F150">
+        <v>12</v>
+      </c>
+      <c r="G150">
+        <v>12.1</v>
+      </c>
+      <c r="H150">
+        <v>11.6</v>
+      </c>
+      <c r="I150">
+        <v>0</v>
+      </c>
+      <c r="J150">
+        <v>0</v>
+      </c>
+      <c r="K150">
+        <v>6565095</v>
+      </c>
+      <c r="L150">
+        <v>77325.6161</v>
+      </c>
+      <c r="M150">
+        <v>801500</v>
+      </c>
+      <c r="N150">
         <v>11.7</v>
       </c>
-      <c r="G150">
-        <v>12</v>
-      </c>
-      <c r="H150">
-        <v>11.7</v>
-      </c>
-      <c r="I150">
-        <v>0</v>
-      </c>
-      <c r="J150">
-        <v>0</v>
-      </c>
-      <c r="K150">
-        <v>2575189</v>
-      </c>
-      <c r="L150">
-        <v>30484.8</v>
-      </c>
-      <c r="M150">
-        <v>44400</v>
-      </c>
-      <c r="N150">
-        <v>11.9</v>
-      </c>
       <c r="O150">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="P150">
-        <v>833400</v>
+        <v>357100</v>
       </c>
     </row>
     <row r="151">
@@ -7564,7 +7564,7 @@
         <v>-</v>
       </c>
       <c r="C151">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -7573,13 +7573,13 @@
         <v>0</v>
       </c>
       <c r="F151">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="G151">
-        <v>18.4</v>
+        <v>18.8</v>
       </c>
       <c r="H151">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="I151">
         <v>0</v>
@@ -7588,22 +7588,22 @@
         <v>0</v>
       </c>
       <c r="K151">
-        <v>191110</v>
+        <v>584418</v>
       </c>
       <c r="L151">
-        <v>3503.364</v>
+        <v>10880.5927</v>
       </c>
       <c r="M151">
-        <v>14300</v>
+        <v>1000</v>
       </c>
       <c r="N151">
-        <v>18.3</v>
+        <v>18.6</v>
       </c>
       <c r="O151">
-        <v>18.4</v>
+        <v>18.7</v>
       </c>
       <c r="P151">
-        <v>138300</v>
+        <v>92100</v>
       </c>
     </row>
     <row r="152">
@@ -7614,7 +7614,7 @@
         <v>-</v>
       </c>
       <c r="C152">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="D152">
         <v>0</v>
@@ -7623,37 +7623,37 @@
         <v>0</v>
       </c>
       <c r="F152">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="G152">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="H152">
+        <v>1.42</v>
+      </c>
+      <c r="I152">
+        <v>0</v>
+      </c>
+      <c r="J152">
+        <v>0</v>
+      </c>
+      <c r="K152">
+        <v>16048321</v>
+      </c>
+      <c r="L152">
+        <v>22934.85749</v>
+      </c>
+      <c r="M152">
+        <v>41800</v>
+      </c>
+      <c r="N152">
+        <v>1.43</v>
+      </c>
+      <c r="O152">
         <v>1.44</v>
       </c>
-      <c r="I152">
-        <v>0</v>
-      </c>
-      <c r="J152">
-        <v>0</v>
-      </c>
-      <c r="K152">
-        <v>4811698</v>
-      </c>
-      <c r="L152">
-        <v>6985.97938</v>
-      </c>
-      <c r="M152">
-        <v>2533300</v>
-      </c>
-      <c r="N152">
-        <v>1.44</v>
-      </c>
-      <c r="O152">
-        <v>1.45</v>
-      </c>
       <c r="P152">
-        <v>227900</v>
+        <v>1763100</v>
       </c>
     </row>
     <row r="153">
@@ -7664,22 +7664,22 @@
         <v>-</v>
       </c>
       <c r="C153">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="D153">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="E153">
-        <v>0.5555555555555556</v>
+        <v>3.977272727272727</v>
       </c>
       <c r="F153">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="G153">
-        <v>18.1</v>
+        <v>18.4</v>
       </c>
       <c r="H153">
-        <v>17.7</v>
+        <v>17.5</v>
       </c>
       <c r="I153">
         <v>0</v>
@@ -7688,22 +7688,22 @@
         <v>0</v>
       </c>
       <c r="K153">
-        <v>82100</v>
+        <v>1457528</v>
       </c>
       <c r="L153">
-        <v>1473.36</v>
+        <v>26301.2235</v>
       </c>
       <c r="M153">
-        <v>10200</v>
+        <v>5300</v>
       </c>
       <c r="N153">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="O153">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="P153">
-        <v>23000</v>
+        <v>106500</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StockQuotation (1).xlsx
+++ b/Excel/StockQuotation (1).xlsx
@@ -402,7 +402,7 @@
         <v/>
       </c>
       <c r="C1" t="str">
-        <v>07/02/23 23:29:28</v>
+        <v>08/02/23 20:05:19</v>
       </c>
     </row>
     <row r="4">
@@ -426,34 +426,34 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>1126.3</v>
+        <v>1116.45</v>
       </c>
       <c r="B7" t="str">
-        <v>0.92 (0.0817%)</v>
+        <v>-9.85 (-0.8745%)</v>
       </c>
       <c r="C7" t="str">
         <v>High</v>
       </c>
       <c r="D7">
-        <v>1130.58</v>
+        <v>1129.41</v>
       </c>
       <c r="E7" t="str">
         <v>Low</v>
       </c>
       <c r="F7">
-        <v>1122.42</v>
+        <v>1115.9</v>
       </c>
       <c r="G7" t="str">
         <v>Volume</v>
       </c>
       <c r="H7">
-        <v>1243021590</v>
+        <v>1171224810</v>
       </c>
       <c r="I7" t="str">
         <v>Value</v>
       </c>
       <c r="J7">
-        <v>4132739558.89</v>
+        <v>4525005016.7</v>
       </c>
     </row>
     <row r="9">
@@ -514,22 +514,22 @@
         <v>-</v>
       </c>
       <c r="C10">
+        <v>0.84</v>
+      </c>
+      <c r="D10">
+        <v>-0.04</v>
+      </c>
+      <c r="E10">
+        <v>-4.545454545454546</v>
+      </c>
+      <c r="F10">
         <v>0.88</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0.9</v>
-      </c>
       <c r="G10">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="H10">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -538,22 +538,22 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>300735083</v>
+        <v>40779359</v>
       </c>
       <c r="L10">
-        <v>269440.61246</v>
+        <v>34760.449700000005</v>
       </c>
       <c r="M10">
-        <v>2307300</v>
+        <v>3131200</v>
       </c>
       <c r="N10">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="O10">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="P10">
-        <v>1230700</v>
+        <v>266600</v>
       </c>
     </row>
     <row r="11">
@@ -567,16 +567,16 @@
         <v>3.7</v>
       </c>
       <c r="D11">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>-0.5376344086021505</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>3.72</v>
       </c>
       <c r="G11">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="H11">
         <v>3.7</v>
@@ -588,13 +588,13 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>1095242</v>
+        <v>1425543</v>
       </c>
       <c r="L11">
-        <v>4058.4807</v>
+        <v>5297.13798</v>
       </c>
       <c r="M11">
-        <v>48700</v>
+        <v>365400</v>
       </c>
       <c r="N11">
         <v>3.7</v>
@@ -603,7 +603,7 @@
         <v>3.72</v>
       </c>
       <c r="P11">
-        <v>132600</v>
+        <v>161300</v>
       </c>
     </row>
     <row r="12">
@@ -614,22 +614,22 @@
         <v>-</v>
       </c>
       <c r="C12">
-        <v>32.75</v>
+        <v>31.75</v>
       </c>
       <c r="D12">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
       <c r="E12">
-        <v>-0.7575757575757576</v>
+        <v>-3.053435114503817</v>
       </c>
       <c r="F12">
         <v>33</v>
       </c>
       <c r="G12">
-        <v>33.25</v>
+        <v>33</v>
       </c>
       <c r="H12">
-        <v>32.5</v>
+        <v>31.5</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -638,22 +638,22 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>1688685</v>
+        <v>1449205</v>
       </c>
       <c r="L12">
-        <v>55467.10525</v>
+        <v>46651.59125</v>
       </c>
       <c r="M12">
-        <v>5000</v>
+        <v>135600</v>
       </c>
       <c r="N12">
-        <v>32.75</v>
+        <v>31.75</v>
       </c>
       <c r="O12">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P12">
-        <v>328000</v>
+        <v>35200</v>
       </c>
     </row>
     <row r="13">
@@ -664,22 +664,22 @@
         <v>-</v>
       </c>
       <c r="C13">
+        <v>6.8</v>
+      </c>
+      <c r="D13">
+        <v>0.2</v>
+      </c>
+      <c r="E13">
+        <v>3.0303030303030303</v>
+      </c>
+      <c r="F13">
         <v>6.6</v>
       </c>
-      <c r="D13">
-        <v>-0.05</v>
-      </c>
-      <c r="E13">
-        <v>-0.7518796992481203</v>
-      </c>
-      <c r="F13">
-        <v>6.65</v>
-      </c>
       <c r="G13">
-        <v>6.7</v>
+        <v>6.85</v>
       </c>
       <c r="H13">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -688,22 +688,22 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>307537</v>
+        <v>1642344</v>
       </c>
       <c r="L13">
-        <v>2034.8716000000002</v>
+        <v>11119.335550000002</v>
       </c>
       <c r="M13">
-        <v>54800</v>
+        <v>50400</v>
       </c>
       <c r="N13">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O13">
-        <v>6.65</v>
+        <v>6.85</v>
       </c>
       <c r="P13">
-        <v>45900</v>
+        <v>131400</v>
       </c>
     </row>
     <row r="14">
@@ -714,22 +714,22 @@
         <v>-</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="D14">
-        <v>0.14</v>
+        <v>0.02</v>
       </c>
       <c r="E14">
-        <v>4.895104895104895</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F14">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="H14">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -738,22 +738,22 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>5198687</v>
+        <v>18022789</v>
       </c>
       <c r="L14">
-        <v>15360.20196</v>
+        <v>54890.7284</v>
       </c>
       <c r="M14">
-        <v>74700</v>
+        <v>100900</v>
       </c>
       <c r="N14">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="O14">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="P14">
-        <v>380400</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="15">
@@ -764,22 +764,22 @@
         <v>-</v>
       </c>
       <c r="C15">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="D15">
         <v>-0.1</v>
       </c>
       <c r="E15">
-        <v>-1.492537313432836</v>
+        <v>-1.5151515151515151</v>
       </c>
       <c r="F15">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="G15">
-        <v>6.7</v>
+        <v>6.65</v>
       </c>
       <c r="H15">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -788,22 +788,22 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>1178324</v>
+        <v>2771756</v>
       </c>
       <c r="L15">
-        <v>7806.0696</v>
+        <v>18135.754390000002</v>
       </c>
       <c r="M15">
-        <v>594500</v>
+        <v>547000</v>
       </c>
       <c r="N15">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="O15">
-        <v>6.65</v>
+        <v>6.55</v>
       </c>
       <c r="P15">
-        <v>337700</v>
+        <v>110500</v>
       </c>
     </row>
     <row r="16">
@@ -814,46 +814,46 @@
         <v>-</v>
       </c>
       <c r="C16">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="D16">
         <v>-0.1</v>
       </c>
       <c r="E16">
-        <v>-0.7692307692307693</v>
+        <v>-0.7751937984496124</v>
       </c>
       <c r="F16">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="G16">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="H16">
+        <v>12.7</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>268667</v>
+      </c>
+      <c r="L16">
+        <v>3443.391</v>
+      </c>
+      <c r="M16">
+        <v>26100</v>
+      </c>
+      <c r="N16">
+        <v>12.7</v>
+      </c>
+      <c r="O16">
         <v>12.8</v>
       </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>296417</v>
-      </c>
-      <c r="L16">
-        <v>3835.5916</v>
-      </c>
-      <c r="M16">
-        <v>86000</v>
-      </c>
-      <c r="N16">
-        <v>12.8</v>
-      </c>
-      <c r="O16">
-        <v>12.9</v>
-      </c>
       <c r="P16">
-        <v>27100</v>
+        <v>25900</v>
       </c>
     </row>
     <row r="17">
@@ -864,22 +864,22 @@
         <v>-</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="D17">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="E17">
-        <v>-0.9900990099009901</v>
+        <v>-2.5</v>
       </c>
       <c r="F17">
         <v>4.04</v>
       </c>
       <c r="G17">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="H17">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -888,22 +888,22 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>2506280</v>
+        <v>2934748</v>
       </c>
       <c r="L17">
-        <v>10023.6756</v>
+        <v>11580.533300000001</v>
       </c>
       <c r="M17">
-        <v>322600</v>
+        <v>385700</v>
       </c>
       <c r="N17">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O17">
-        <v>4.02</v>
+        <v>3.94</v>
       </c>
       <c r="P17">
-        <v>71000</v>
+        <v>57500</v>
       </c>
     </row>
     <row r="18">
@@ -914,22 +914,22 @@
         <v>-</v>
       </c>
       <c r="C18">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="D18">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="E18">
-        <v>0.7092198581560284</v>
+        <v>-0.704225352112676</v>
       </c>
       <c r="F18">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="G18">
         <v>1.44</v>
       </c>
       <c r="H18">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>9665714</v>
+        <v>8443950</v>
       </c>
       <c r="L18">
-        <v>13756.94175</v>
+        <v>11920.6589</v>
       </c>
       <c r="M18">
-        <v>2032300</v>
+        <v>193100</v>
       </c>
       <c r="N18">
         <v>1.41</v>
@@ -953,7 +953,7 @@
         <v>1.42</v>
       </c>
       <c r="P18">
-        <v>89400</v>
+        <v>296800</v>
       </c>
     </row>
     <row r="19">
@@ -967,19 +967,19 @@
         <v>4.76</v>
       </c>
       <c r="D19">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>0.847457627118644</v>
+        <v>0</v>
       </c>
       <c r="F19">
         <v>4.76</v>
       </c>
       <c r="G19">
-        <v>4.78</v>
+        <v>4.76</v>
       </c>
       <c r="H19">
-        <v>4.72</v>
+        <v>4.64</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -988,13 +988,13 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>119600</v>
+        <v>411600</v>
       </c>
       <c r="L19">
-        <v>569.22</v>
+        <v>1931.2</v>
       </c>
       <c r="M19">
-        <v>6600</v>
+        <v>2400</v>
       </c>
       <c r="N19">
         <v>4.74</v>
@@ -1003,7 +1003,7 @@
         <v>4.76</v>
       </c>
       <c r="P19">
-        <v>4400</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="20">
@@ -1014,22 +1014,22 @@
         <v>-</v>
       </c>
       <c r="C20">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="F20">
         <v>5</v>
       </c>
       <c r="G20">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="H20">
-        <v>4.98</v>
+        <v>4.96</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1038,13 +1038,13 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>79200</v>
+        <v>306800</v>
       </c>
       <c r="L20">
-        <v>395.991</v>
+        <v>1528.69</v>
       </c>
       <c r="M20">
-        <v>201800</v>
+        <v>4200</v>
       </c>
       <c r="N20">
         <v>4.98</v>
@@ -1053,7 +1053,7 @@
         <v>5</v>
       </c>
       <c r="P20">
-        <v>66300</v>
+        <v>70400</v>
       </c>
     </row>
     <row r="21">
@@ -1067,16 +1067,16 @@
         <v>0.67</v>
       </c>
       <c r="D21">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>-1.4705882352941178</v>
+        <v>0</v>
       </c>
       <c r="F21">
+        <v>0.67</v>
+      </c>
+      <c r="G21">
         <v>0.68</v>
-      </c>
-      <c r="G21">
-        <v>0.69</v>
       </c>
       <c r="H21">
         <v>0.66</v>
@@ -1088,22 +1088,22 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>39274616</v>
+        <v>10201521</v>
       </c>
       <c r="L21">
-        <v>26405.03672</v>
+        <v>6821.066690000001</v>
       </c>
       <c r="M21">
-        <v>948400</v>
+        <v>4887100</v>
       </c>
       <c r="N21">
+        <v>0.66</v>
+      </c>
+      <c r="O21">
         <v>0.67</v>
       </c>
-      <c r="O21">
-        <v>0.68</v>
-      </c>
       <c r="P21">
-        <v>13531900</v>
+        <v>8442700</v>
       </c>
     </row>
     <row r="22">
@@ -1114,22 +1114,22 @@
         <v>-</v>
       </c>
       <c r="C22">
+        <v>14.4</v>
+      </c>
+      <c r="D22">
+        <v>-0.2</v>
+      </c>
+      <c r="E22">
+        <v>-1.36986301369863</v>
+      </c>
+      <c r="F22">
         <v>14.6</v>
       </c>
-      <c r="D22">
-        <v>-0.1</v>
-      </c>
-      <c r="E22">
-        <v>-0.6802721088435374</v>
-      </c>
-      <c r="F22">
-        <v>14.8</v>
-      </c>
       <c r="G22">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="H22">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1138,22 +1138,22 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>998658</v>
+        <v>874889</v>
       </c>
       <c r="L22">
-        <v>14649.8635</v>
+        <v>12715.695099999999</v>
       </c>
       <c r="M22">
-        <v>62800</v>
+        <v>98100</v>
       </c>
       <c r="N22">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="O22">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="P22">
-        <v>8700</v>
+        <v>50900</v>
       </c>
     </row>
     <row r="23">
@@ -1164,46 +1164,46 @@
         <v>-</v>
       </c>
       <c r="C23">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="D23">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E23">
-        <v>0.7246376811594203</v>
+        <v>-1.4388489208633093</v>
       </c>
       <c r="F23">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="G23">
         <v>14</v>
       </c>
       <c r="H23">
+        <v>13.7</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>644605</v>
+      </c>
+      <c r="L23">
+        <v>8900.9921</v>
+      </c>
+      <c r="M23">
+        <v>90900</v>
+      </c>
+      <c r="N23">
+        <v>13.7</v>
+      </c>
+      <c r="O23">
         <v>13.8</v>
       </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>740963</v>
-      </c>
-      <c r="L23">
-        <v>10289.0565</v>
-      </c>
-      <c r="M23">
-        <v>281600</v>
-      </c>
-      <c r="N23">
-        <v>13.8</v>
-      </c>
-      <c r="O23">
-        <v>13.9</v>
-      </c>
       <c r="P23">
-        <v>133600</v>
+        <v>43300</v>
       </c>
     </row>
     <row r="24">
@@ -1217,13 +1217,13 @@
         <v>3.12</v>
       </c>
       <c r="D24">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>-0.6369426751592356</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="G24">
         <v>3.16</v>
@@ -1238,13 +1238,13 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>1291978</v>
+        <v>2304332</v>
       </c>
       <c r="L24">
-        <v>4053.55446</v>
+        <v>7215.89818</v>
       </c>
       <c r="M24">
-        <v>428800</v>
+        <v>205400</v>
       </c>
       <c r="N24">
         <v>3.12</v>
@@ -1253,7 +1253,7 @@
         <v>3.14</v>
       </c>
       <c r="P24">
-        <v>452300</v>
+        <v>170800</v>
       </c>
     </row>
     <row r="25">
@@ -1267,16 +1267,16 @@
         <v>8.5</v>
       </c>
       <c r="D25">
-        <v>-0.15</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>-1.7341040462427746</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>8.65</v>
+        <v>8.5</v>
       </c>
       <c r="G25">
-        <v>8.65</v>
+        <v>8.7</v>
       </c>
       <c r="H25">
         <v>8.5</v>
@@ -1288,13 +1288,13 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>925083</v>
+        <v>2124032</v>
       </c>
       <c r="L25">
-        <v>7915.8463</v>
+        <v>18255.465</v>
       </c>
       <c r="M25">
-        <v>199800</v>
+        <v>153800</v>
       </c>
       <c r="N25">
         <v>8.5</v>
@@ -1303,7 +1303,7 @@
         <v>8.55</v>
       </c>
       <c r="P25">
-        <v>31500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="26">
@@ -1314,46 +1314,46 @@
         <v>-</v>
       </c>
       <c r="C26">
+        <v>6.8</v>
+      </c>
+      <c r="D26">
+        <v>-0.05</v>
+      </c>
+      <c r="E26">
+        <v>-0.7299270072992701</v>
+      </c>
+      <c r="F26">
         <v>6.85</v>
       </c>
-      <c r="D26">
-        <v>-0.1</v>
-      </c>
-      <c r="E26">
-        <v>-1.4388489208633093</v>
-      </c>
-      <c r="F26">
-        <v>7</v>
-      </c>
       <c r="G26">
-        <v>7.05</v>
+        <v>6.9</v>
       </c>
       <c r="H26">
+        <v>6.8</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>972539</v>
+      </c>
+      <c r="L26">
+        <v>6642.33215</v>
+      </c>
+      <c r="M26">
+        <v>95000</v>
+      </c>
+      <c r="N26">
+        <v>6.8</v>
+      </c>
+      <c r="O26">
         <v>6.85</v>
       </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>1202031</v>
-      </c>
-      <c r="L26">
-        <v>8313.443650000001</v>
-      </c>
-      <c r="M26">
-        <v>161100</v>
-      </c>
-      <c r="N26">
-        <v>6.85</v>
-      </c>
-      <c r="O26">
-        <v>6.9</v>
-      </c>
       <c r="P26">
-        <v>38600</v>
+        <v>16100</v>
       </c>
     </row>
     <row r="27">
@@ -1364,22 +1364,22 @@
         <v>-</v>
       </c>
       <c r="C27">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="D27">
-        <v>0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="E27">
-        <v>8.904109589041095</v>
+        <v>-3.7735849056603774</v>
       </c>
       <c r="F27">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="G27">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="H27">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1388,22 +1388,22 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>261554760</v>
+        <v>126751173</v>
       </c>
       <c r="L27">
-        <v>406670.12568</v>
+        <v>198411.97203</v>
       </c>
       <c r="M27">
-        <v>2080900</v>
+        <v>1041300</v>
       </c>
       <c r="N27">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="O27">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="P27">
-        <v>5383300</v>
+        <v>1064800</v>
       </c>
     </row>
     <row r="28">
@@ -1414,22 +1414,22 @@
         <v>-</v>
       </c>
       <c r="C28">
-        <v>14.8</v>
+        <v>15.7</v>
       </c>
       <c r="D28">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="E28">
-        <v>4.964539007092198</v>
+        <v>6.081081081081081</v>
       </c>
       <c r="F28">
-        <v>14.2</v>
+        <v>14.9</v>
       </c>
       <c r="G28">
-        <v>14.8</v>
+        <v>15.7</v>
       </c>
       <c r="H28">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1438,22 +1438,22 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>2109111</v>
+        <v>2811240</v>
       </c>
       <c r="L28">
-        <v>30301.7474</v>
+        <v>42677.7191</v>
       </c>
       <c r="M28">
-        <v>17000</v>
+        <v>12000</v>
       </c>
       <c r="N28">
-        <v>14.6</v>
+        <v>15.6</v>
       </c>
       <c r="O28">
-        <v>14.8</v>
+        <v>15.7</v>
       </c>
       <c r="P28">
-        <v>66400</v>
+        <v>157200</v>
       </c>
     </row>
     <row r="29">
@@ -1464,16 +1464,16 @@
         <v>-</v>
       </c>
       <c r="C29">
+        <v>10.2</v>
+      </c>
+      <c r="D29">
+        <v>-0.1</v>
+      </c>
+      <c r="E29">
+        <v>-0.970873786407767</v>
+      </c>
+      <c r="F29">
         <v>10.3</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <v>10.2</v>
       </c>
       <c r="G29">
         <v>10.4</v>
@@ -1488,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>321738</v>
+        <v>177824</v>
       </c>
       <c r="L29">
-        <v>3312.4498</v>
+        <v>1825.4173</v>
       </c>
       <c r="M29">
-        <v>918600</v>
+        <v>895700</v>
       </c>
       <c r="N29">
         <v>10.2</v>
@@ -1503,7 +1503,7 @@
         <v>10.3</v>
       </c>
       <c r="P29">
-        <v>62400</v>
+        <v>104200</v>
       </c>
     </row>
     <row r="30">
@@ -1517,43 +1517,43 @@
         <v>11.3</v>
       </c>
       <c r="D30">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>2.727272727272727</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="G30">
+        <v>11.6</v>
+      </c>
+      <c r="H30">
+        <v>11.2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>4353988</v>
+      </c>
+      <c r="L30">
+        <v>49576.9692</v>
+      </c>
+      <c r="M30">
+        <v>381400</v>
+      </c>
+      <c r="N30">
         <v>11.3</v>
       </c>
-      <c r="H30">
-        <v>11</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>5251881</v>
-      </c>
-      <c r="L30">
-        <v>58557.3028</v>
-      </c>
-      <c r="M30">
-        <v>141800</v>
-      </c>
-      <c r="N30">
-        <v>11.2</v>
-      </c>
       <c r="O30">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="P30">
-        <v>540600</v>
+        <v>250600</v>
       </c>
     </row>
     <row r="31">
@@ -1564,19 +1564,19 @@
         <v>-</v>
       </c>
       <c r="C31">
-        <v>8.15</v>
+        <v>7.95</v>
       </c>
       <c r="D31">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E31">
-        <v>1.2422360248447204</v>
+        <v>-2.4539877300613497</v>
       </c>
       <c r="F31">
-        <v>8.05</v>
+        <v>8.25</v>
       </c>
       <c r="G31">
-        <v>8.15</v>
+        <v>8.4</v>
       </c>
       <c r="H31">
         <v>7.9</v>
@@ -1588,22 +1588,22 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>3605840</v>
+        <v>6036925</v>
       </c>
       <c r="L31">
-        <v>28918.8061</v>
+        <v>49462.7229</v>
       </c>
       <c r="M31">
-        <v>76800</v>
+        <v>443500</v>
       </c>
       <c r="N31">
-        <v>8.1</v>
+        <v>7.95</v>
       </c>
       <c r="O31">
-        <v>8.15</v>
+        <v>8</v>
       </c>
       <c r="P31">
-        <v>154700</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="32">
@@ -1614,22 +1614,22 @@
         <v>-</v>
       </c>
       <c r="C32">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>-1.9047619047619047</v>
       </c>
       <c r="F32">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="G32">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H32">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -1638,22 +1638,22 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>39242016</v>
+        <v>121882109</v>
       </c>
       <c r="L32">
-        <v>40738.33656</v>
+        <v>127439.92078</v>
       </c>
       <c r="M32">
-        <v>1212300</v>
+        <v>3571000</v>
       </c>
       <c r="N32">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="O32">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="P32">
-        <v>1460900</v>
+        <v>1518300</v>
       </c>
     </row>
     <row r="33">
@@ -1664,22 +1664,22 @@
         <v>-</v>
       </c>
       <c r="C33">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="D33">
-        <v>0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="E33">
-        <v>0.8064516129032258</v>
+        <v>-2.4</v>
       </c>
       <c r="F33">
         <v>2.5</v>
       </c>
       <c r="G33">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="H33">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -1688,22 +1688,22 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>3835765</v>
+        <v>8983631</v>
       </c>
       <c r="L33">
-        <v>9672.5494</v>
+        <v>22037.04878</v>
       </c>
       <c r="M33">
-        <v>146400</v>
+        <v>283200</v>
       </c>
       <c r="N33">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="O33">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="P33">
-        <v>256800</v>
+        <v>83700</v>
       </c>
     </row>
     <row r="34">
@@ -1714,46 +1714,46 @@
         <v>-</v>
       </c>
       <c r="C34">
+        <v>0.45</v>
+      </c>
+      <c r="D34">
+        <v>-0.01</v>
+      </c>
+      <c r="E34">
+        <v>-2.1739130434782608</v>
+      </c>
+      <c r="F34">
         <v>0.46</v>
       </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34">
-        <v>0.47</v>
-      </c>
       <c r="G34">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="H34">
+        <v>0.45</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>71100091</v>
+      </c>
+      <c r="L34">
+        <v>33271.18186</v>
+      </c>
+      <c r="M34">
+        <v>14128000</v>
+      </c>
+      <c r="N34">
+        <v>0.45</v>
+      </c>
+      <c r="O34">
         <v>0.46</v>
       </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>12995101</v>
-      </c>
-      <c r="L34">
-        <v>5991.07247</v>
-      </c>
-      <c r="M34">
-        <v>1776000</v>
-      </c>
-      <c r="N34">
-        <v>0.46</v>
-      </c>
-      <c r="O34">
-        <v>0.47</v>
-      </c>
       <c r="P34">
-        <v>13108700</v>
+        <v>667500</v>
       </c>
     </row>
     <row r="35">
@@ -1764,22 +1764,22 @@
         <v>-</v>
       </c>
       <c r="C35">
-        <v>10.2</v>
+        <v>9.95</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>-2.450980392156863</v>
       </c>
       <c r="F35">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="G35">
         <v>10.3</v>
       </c>
       <c r="H35">
-        <v>10.1</v>
+        <v>9.9</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -1788,22 +1788,22 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>3612521</v>
+        <v>3431148</v>
       </c>
       <c r="L35">
-        <v>36867.08605</v>
+        <v>34433.8324</v>
       </c>
       <c r="M35">
-        <v>34900</v>
+        <v>7100</v>
       </c>
       <c r="N35">
-        <v>10.2</v>
+        <v>9.95</v>
       </c>
       <c r="O35">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="P35">
-        <v>787600</v>
+        <v>17600</v>
       </c>
     </row>
     <row r="36">
@@ -1814,22 +1814,22 @@
         <v>-</v>
       </c>
       <c r="C36">
+        <v>17.9</v>
+      </c>
+      <c r="D36">
+        <v>-0.5</v>
+      </c>
+      <c r="E36">
+        <v>-2.717391304347826</v>
+      </c>
+      <c r="F36">
         <v>18.4</v>
       </c>
-      <c r="D36">
-        <v>1.2</v>
-      </c>
-      <c r="E36">
-        <v>6.976744186046512</v>
-      </c>
-      <c r="F36">
-        <v>17.2</v>
-      </c>
       <c r="G36">
-        <v>18.4</v>
+        <v>18.9</v>
       </c>
       <c r="H36">
-        <v>17.2</v>
+        <v>17.8</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -1838,22 +1838,22 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>2574408</v>
+        <v>4571883</v>
       </c>
       <c r="L36">
-        <v>46135.951</v>
+        <v>84311.7101</v>
       </c>
       <c r="M36">
-        <v>6000</v>
+        <v>13500</v>
       </c>
       <c r="N36">
-        <v>18.3</v>
+        <v>17.9</v>
       </c>
       <c r="O36">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="P36">
-        <v>59900</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="37">
@@ -1864,22 +1864,22 @@
         <v>-</v>
       </c>
       <c r="C37">
-        <v>4.7</v>
+        <v>4.56</v>
       </c>
       <c r="D37">
-        <v>-0.02</v>
+        <v>-0.14</v>
       </c>
       <c r="E37">
-        <v>-0.423728813559322</v>
+        <v>-2.978723404255319</v>
       </c>
       <c r="F37">
-        <v>4.7</v>
+        <v>4.72</v>
       </c>
       <c r="G37">
-        <v>4.76</v>
+        <v>4.74</v>
       </c>
       <c r="H37">
-        <v>4.7</v>
+        <v>4.54</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -1888,22 +1888,22 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>485800</v>
+        <v>1233705</v>
       </c>
       <c r="L37">
-        <v>2295.21</v>
+        <v>5699.37238</v>
       </c>
       <c r="M37">
-        <v>40600</v>
+        <v>1900</v>
       </c>
       <c r="N37">
-        <v>4.7</v>
+        <v>4.56</v>
       </c>
       <c r="O37">
-        <v>4.72</v>
+        <v>4.58</v>
       </c>
       <c r="P37">
-        <v>58100</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="38">
@@ -1914,46 +1914,46 @@
         <v>-</v>
       </c>
       <c r="C38">
-        <v>13</v>
+        <v>12.7</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>-2.3076923076923075</v>
       </c>
       <c r="F38">
         <v>13</v>
       </c>
       <c r="G38">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="H38">
+        <v>12.7</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>926947</v>
+      </c>
+      <c r="L38">
+        <v>11869.731800000001</v>
+      </c>
+      <c r="M38">
+        <v>60300</v>
+      </c>
+      <c r="N38">
+        <v>12.7</v>
+      </c>
+      <c r="O38">
         <v>12.8</v>
       </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>1248511</v>
-      </c>
-      <c r="L38">
-        <v>16126.752</v>
-      </c>
-      <c r="M38">
-        <v>60000</v>
-      </c>
-      <c r="N38">
-        <v>12.9</v>
-      </c>
-      <c r="O38">
-        <v>13</v>
-      </c>
       <c r="P38">
-        <v>6900</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="39">
@@ -1964,13 +1964,13 @@
         <v>-</v>
       </c>
       <c r="C39">
-        <v>8.25</v>
+        <v>8.2</v>
       </c>
       <c r="D39">
         <v>-0.05</v>
       </c>
       <c r="E39">
-        <v>-0.6024096385542169</v>
+        <v>-0.6060606060606061</v>
       </c>
       <c r="F39">
         <v>8.25</v>
@@ -1979,31 +1979,31 @@
         <v>8.3</v>
       </c>
       <c r="H39">
+        <v>8.2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>62782</v>
+      </c>
+      <c r="L39">
+        <v>518.53745</v>
+      </c>
+      <c r="M39">
+        <v>45000</v>
+      </c>
+      <c r="N39">
+        <v>8.2</v>
+      </c>
+      <c r="O39">
         <v>8.25</v>
       </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39">
-        <v>137355</v>
-      </c>
-      <c r="L39">
-        <v>1134.4045</v>
-      </c>
-      <c r="M39">
-        <v>11800</v>
-      </c>
-      <c r="N39">
-        <v>8.25</v>
-      </c>
-      <c r="O39">
-        <v>8.3</v>
-      </c>
       <c r="P39">
-        <v>10000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="40">
@@ -2014,23 +2014,23 @@
         <v>-</v>
       </c>
       <c r="C40">
+        <v>5.35</v>
+      </c>
+      <c r="D40">
+        <v>-0.1</v>
+      </c>
+      <c r="E40">
+        <v>-1.834862385321101</v>
+      </c>
+      <c r="F40">
         <v>5.45</v>
       </c>
-      <c r="D40">
-        <v>0.1</v>
-      </c>
-      <c r="E40">
-        <v>1.8691588785046729</v>
-      </c>
-      <c r="F40">
+      <c r="G40">
+        <v>5.45</v>
+      </c>
+      <c r="H40">
         <v>5.3</v>
       </c>
-      <c r="G40">
-        <v>5.5</v>
-      </c>
-      <c r="H40">
-        <v>5.25</v>
-      </c>
       <c r="I40">
         <v>0</v>
       </c>
@@ -2038,22 +2038,22 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>1512018</v>
+        <v>1381715</v>
       </c>
       <c r="L40">
-        <v>8110.20285</v>
+        <v>7442.78855</v>
       </c>
       <c r="M40">
-        <v>48300</v>
+        <v>87600</v>
       </c>
       <c r="N40">
+        <v>5.35</v>
+      </c>
+      <c r="O40">
         <v>5.4</v>
       </c>
-      <c r="O40">
-        <v>5.45</v>
-      </c>
       <c r="P40">
-        <v>79900</v>
+        <v>359200</v>
       </c>
     </row>
     <row r="41">
@@ -2067,20 +2067,20 @@
         <v>9</v>
       </c>
       <c r="D41">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>1.1235955056179776</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>8.9</v>
+        <v>9.05</v>
       </c>
       <c r="G41">
+        <v>9.25</v>
+      </c>
+      <c r="H41">
         <v>9</v>
       </c>
-      <c r="H41">
-        <v>8.85</v>
-      </c>
       <c r="I41">
         <v>0</v>
       </c>
@@ -2088,22 +2088,22 @@
         <v>0</v>
       </c>
       <c r="K41">
-        <v>2881447</v>
+        <v>8427605</v>
       </c>
       <c r="L41">
-        <v>25641.38905</v>
+        <v>76800.0745</v>
       </c>
       <c r="M41">
-        <v>1000</v>
+        <v>265500</v>
       </c>
       <c r="N41">
-        <v>8.95</v>
+        <v>9</v>
       </c>
       <c r="O41">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="P41">
-        <v>202400</v>
+        <v>198800</v>
       </c>
     </row>
     <row r="42">
@@ -2114,46 +2114,46 @@
         <v>-</v>
       </c>
       <c r="C42">
-        <v>4.22</v>
+        <v>4.24</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>0.47393364928909953</v>
       </c>
       <c r="F42">
         <v>4.24</v>
       </c>
       <c r="G42">
+        <v>4.28</v>
+      </c>
+      <c r="H42">
+        <v>4.22</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>452117</v>
+      </c>
+      <c r="L42">
+        <v>1919.61028</v>
+      </c>
+      <c r="M42">
+        <v>87800</v>
+      </c>
+      <c r="N42">
+        <v>4.22</v>
+      </c>
+      <c r="O42">
         <v>4.24</v>
       </c>
-      <c r="H42">
-        <v>4.2</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42">
-        <v>114128</v>
-      </c>
-      <c r="L42">
-        <v>481.57872</v>
-      </c>
-      <c r="M42">
-        <v>149800</v>
-      </c>
-      <c r="N42">
-        <v>4.2</v>
-      </c>
-      <c r="O42">
-        <v>4.22</v>
-      </c>
       <c r="P42">
-        <v>29800</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="43">
@@ -2167,19 +2167,19 @@
         <v>4.6</v>
       </c>
       <c r="D43">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="E43">
-        <v>3.6036036036036037</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>4.46</v>
+        <v>4.6</v>
       </c>
       <c r="G43">
-        <v>4.62</v>
+        <v>4.74</v>
       </c>
       <c r="H43">
-        <v>4.46</v>
+        <v>4.54</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2188,22 +2188,22 @@
         <v>0</v>
       </c>
       <c r="K43">
-        <v>27268940</v>
+        <v>22945073</v>
       </c>
       <c r="L43">
-        <v>123563.55742</v>
+        <v>106227.2775</v>
       </c>
       <c r="M43">
-        <v>67000</v>
+        <v>183700</v>
       </c>
       <c r="N43">
+        <v>4.58</v>
+      </c>
+      <c r="O43">
         <v>4.6</v>
       </c>
-      <c r="O43">
-        <v>4.62</v>
-      </c>
       <c r="P43">
-        <v>256800</v>
+        <v>174500</v>
       </c>
     </row>
     <row r="44">
@@ -2214,19 +2214,19 @@
         <v>-</v>
       </c>
       <c r="C44">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="F44">
         <v>0.35</v>
       </c>
       <c r="G44">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="H44">
         <v>0.35</v>
@@ -2238,22 +2238,22 @@
         <v>0</v>
       </c>
       <c r="K44">
-        <v>4481900</v>
+        <v>35952832</v>
       </c>
       <c r="L44">
-        <v>1569.266</v>
+        <v>12957.53543</v>
       </c>
       <c r="M44">
-        <v>3719600</v>
+        <v>1174300</v>
       </c>
       <c r="N44">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="O44">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="P44">
-        <v>11496100</v>
+        <v>8746800</v>
       </c>
     </row>
     <row r="45">
@@ -2264,22 +2264,22 @@
         <v>-</v>
       </c>
       <c r="C45">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="D45">
-        <v>-0.12</v>
+        <v>-0.06</v>
       </c>
       <c r="E45">
-        <v>-3.6809815950920246</v>
+        <v>-1.910828025477707</v>
       </c>
       <c r="F45">
-        <v>3.26</v>
+        <v>3.16</v>
       </c>
       <c r="G45">
-        <v>3.26</v>
+        <v>3.18</v>
       </c>
       <c r="H45">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2288,22 +2288,22 @@
         <v>0</v>
       </c>
       <c r="K45">
-        <v>15835661</v>
+        <v>11667021</v>
       </c>
       <c r="L45">
-        <v>50270.7672</v>
+        <v>36258.75514</v>
       </c>
       <c r="M45">
-        <v>571300</v>
+        <v>195900</v>
       </c>
       <c r="N45">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="O45">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="P45">
-        <v>457200</v>
+        <v>137000</v>
       </c>
     </row>
     <row r="46">
@@ -2314,46 +2314,46 @@
         <v>-</v>
       </c>
       <c r="C46">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="D46">
         <v>-0.1</v>
       </c>
       <c r="E46">
-        <v>-1.4705882352941178</v>
+        <v>-1.492537313432836</v>
       </c>
       <c r="F46">
-        <v>6.75</v>
+        <v>6.65</v>
       </c>
       <c r="G46">
-        <v>6.75</v>
+        <v>6.7</v>
       </c>
       <c r="H46">
+        <v>6.6</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>235349</v>
+      </c>
+      <c r="L46">
+        <v>1568.5283</v>
+      </c>
+      <c r="M46">
+        <v>220300</v>
+      </c>
+      <c r="N46">
+        <v>6.6</v>
+      </c>
+      <c r="O46">
         <v>6.65</v>
       </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <v>366701</v>
-      </c>
-      <c r="L46">
-        <v>2461.03175</v>
-      </c>
-      <c r="M46">
-        <v>42700</v>
-      </c>
-      <c r="N46">
-        <v>6.65</v>
-      </c>
-      <c r="O46">
-        <v>6.7</v>
-      </c>
       <c r="P46">
-        <v>46100</v>
+        <v>16600</v>
       </c>
     </row>
     <row r="47">
@@ -2364,22 +2364,22 @@
         <v>-</v>
       </c>
       <c r="C47">
-        <v>31.5</v>
+        <v>31.25</v>
       </c>
       <c r="D47">
-        <v>0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="E47">
-        <v>1.6129032258064515</v>
+        <v>-0.7936507936507936</v>
       </c>
       <c r="F47">
-        <v>31.5</v>
+        <v>31.75</v>
       </c>
       <c r="G47">
-        <v>32.25</v>
+        <v>31.75</v>
       </c>
       <c r="H47">
-        <v>31.5</v>
+        <v>31</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2388,13 +2388,13 @@
         <v>0</v>
       </c>
       <c r="K47">
-        <v>521964</v>
+        <v>251640</v>
       </c>
       <c r="L47">
-        <v>16558.09075</v>
+        <v>7885.956</v>
       </c>
       <c r="M47">
-        <v>17800</v>
+        <v>9800</v>
       </c>
       <c r="N47">
         <v>31.25</v>
@@ -2403,7 +2403,7 @@
         <v>31.5</v>
       </c>
       <c r="P47">
-        <v>6700</v>
+        <v>53100</v>
       </c>
     </row>
     <row r="48">
@@ -2414,16 +2414,16 @@
         <v>-</v>
       </c>
       <c r="C48">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="D48">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E48">
-        <v>1.6129032258064515</v>
+        <v>-1.5873015873015872</v>
       </c>
       <c r="F48">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="G48">
         <v>12.7</v>
@@ -2438,22 +2438,22 @@
         <v>0</v>
       </c>
       <c r="K48">
-        <v>5246533</v>
+        <v>2256720</v>
       </c>
       <c r="L48">
-        <v>65452.071200000006</v>
+        <v>28129.2783</v>
       </c>
       <c r="M48">
-        <v>8000</v>
+        <v>68100</v>
       </c>
       <c r="N48">
+        <v>12.4</v>
+      </c>
+      <c r="O48">
         <v>12.5</v>
       </c>
-      <c r="O48">
-        <v>12.6</v>
-      </c>
       <c r="P48">
-        <v>7600</v>
+        <v>127200</v>
       </c>
     </row>
     <row r="49">
@@ -2464,22 +2464,22 @@
         <v>-</v>
       </c>
       <c r="C49">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="D49">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="E49">
-        <v>-0.8</v>
+        <v>-2.4193548387096775</v>
       </c>
       <c r="F49">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="G49">
-        <v>12.7</v>
+        <v>12.5</v>
       </c>
       <c r="H49">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2488,22 +2488,22 @@
         <v>0</v>
       </c>
       <c r="K49">
-        <v>3613668</v>
+        <v>4461052</v>
       </c>
       <c r="L49">
-        <v>45327.817299999995</v>
+        <v>54519.0479</v>
       </c>
       <c r="M49">
-        <v>656600</v>
+        <v>579500</v>
       </c>
       <c r="N49">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="O49">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="P49">
-        <v>15000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="50">
@@ -2514,22 +2514,22 @@
         <v>-</v>
       </c>
       <c r="C50">
+        <v>14.5</v>
+      </c>
+      <c r="D50">
+        <v>-0.4</v>
+      </c>
+      <c r="E50">
+        <v>-2.684563758389262</v>
+      </c>
+      <c r="F50">
+        <v>14.8</v>
+      </c>
+      <c r="G50">
         <v>14.9</v>
       </c>
-      <c r="D50">
-        <v>0</v>
-      </c>
-      <c r="E50">
-        <v>0</v>
-      </c>
-      <c r="F50">
-        <v>15</v>
-      </c>
-      <c r="G50">
-        <v>15.2</v>
-      </c>
       <c r="H50">
-        <v>14.8</v>
+        <v>14.5</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2538,22 +2538,22 @@
         <v>0</v>
       </c>
       <c r="K50">
-        <v>2849592</v>
+        <v>3075851</v>
       </c>
       <c r="L50">
-        <v>42696.6472</v>
+        <v>45153.07</v>
       </c>
       <c r="M50">
-        <v>142800</v>
+        <v>208400</v>
       </c>
       <c r="N50">
-        <v>14.9</v>
+        <v>14.5</v>
       </c>
       <c r="O50">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="P50">
-        <v>114900</v>
+        <v>19100</v>
       </c>
     </row>
     <row r="51">
@@ -2573,13 +2573,13 @@
         <v>0</v>
       </c>
       <c r="F51">
-        <v>7.85</v>
+        <v>7.8</v>
       </c>
       <c r="G51">
         <v>7.9</v>
       </c>
       <c r="H51">
-        <v>7.75</v>
+        <v>7.65</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2588,22 +2588,22 @@
         <v>0</v>
       </c>
       <c r="K51">
-        <v>3641118</v>
+        <v>2321143</v>
       </c>
       <c r="L51">
-        <v>28484.72065</v>
+        <v>18114.75605</v>
       </c>
       <c r="M51">
-        <v>180600</v>
+        <v>52400</v>
       </c>
       <c r="N51">
-        <v>7.75</v>
+        <v>7.8</v>
       </c>
       <c r="O51">
-        <v>7.8</v>
+        <v>7.85</v>
       </c>
       <c r="P51">
-        <v>79700</v>
+        <v>70900</v>
       </c>
     </row>
     <row r="52">
@@ -2614,13 +2614,13 @@
         <v>-</v>
       </c>
       <c r="C52">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>-1.0204081632653061</v>
       </c>
       <c r="F52">
         <v>19.7</v>
@@ -2629,7 +2629,7 @@
         <v>19.8</v>
       </c>
       <c r="H52">
-        <v>19.1</v>
+        <v>19.4</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2638,22 +2638,22 @@
         <v>0</v>
       </c>
       <c r="K52">
-        <v>1496504</v>
+        <v>940357</v>
       </c>
       <c r="L52">
-        <v>28983.378</v>
+        <v>18431.8929</v>
       </c>
       <c r="M52">
-        <v>116800</v>
+        <v>27000</v>
       </c>
       <c r="N52">
+        <v>19.4</v>
+      </c>
+      <c r="O52">
         <v>19.5</v>
       </c>
-      <c r="O52">
-        <v>19.6</v>
-      </c>
       <c r="P52">
-        <v>75800</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="53">
@@ -2664,46 +2664,46 @@
         <v>-</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="F53">
         <v>2</v>
       </c>
       <c r="G53">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H53">
+        <v>1.97</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>8796357</v>
+      </c>
+      <c r="L53">
+        <v>17502.47814</v>
+      </c>
+      <c r="M53">
+        <v>154100</v>
+      </c>
+      <c r="N53">
+        <v>1.99</v>
+      </c>
+      <c r="O53">
         <v>2</v>
       </c>
-      <c r="I53">
-        <v>0</v>
-      </c>
-      <c r="J53">
-        <v>0</v>
-      </c>
-      <c r="K53">
-        <v>7755719</v>
-      </c>
-      <c r="L53">
-        <v>15553.398</v>
-      </c>
-      <c r="M53">
-        <v>251000</v>
-      </c>
-      <c r="N53">
-        <v>2</v>
-      </c>
-      <c r="O53">
-        <v>2.02</v>
-      </c>
       <c r="P53">
-        <v>643800</v>
+        <v>613400</v>
       </c>
     </row>
     <row r="54">
@@ -2714,46 +2714,46 @@
         <v>-</v>
       </c>
       <c r="C54">
+        <v>4.08</v>
+      </c>
+      <c r="D54">
+        <v>-0.04</v>
+      </c>
+      <c r="E54">
+        <v>-0.970873786407767</v>
+      </c>
+      <c r="F54">
         <v>4.12</v>
       </c>
-      <c r="D54">
-        <v>-0.02</v>
-      </c>
-      <c r="E54">
-        <v>-0.4830917874396135</v>
-      </c>
-      <c r="F54">
-        <v>4.2</v>
-      </c>
       <c r="G54">
-        <v>4.22</v>
+        <v>4.12</v>
       </c>
       <c r="H54">
+        <v>4.04</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>5315361</v>
+      </c>
+      <c r="L54">
+        <v>21669.274920000003</v>
+      </c>
+      <c r="M54">
+        <v>35700</v>
+      </c>
+      <c r="N54">
         <v>4.06</v>
       </c>
-      <c r="I54">
-        <v>0</v>
-      </c>
-      <c r="J54">
-        <v>0</v>
-      </c>
-      <c r="K54">
-        <v>26726143</v>
-      </c>
-      <c r="L54">
-        <v>110904.4647</v>
-      </c>
-      <c r="M54">
-        <v>186900</v>
-      </c>
-      <c r="N54">
-        <v>4.1</v>
-      </c>
       <c r="O54">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="P54">
-        <v>146000</v>
+        <v>270100</v>
       </c>
     </row>
     <row r="55">
@@ -2764,19 +2764,19 @@
         <v>-</v>
       </c>
       <c r="C55">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F55">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="G55">
-        <v>4.02</v>
+        <v>4.16</v>
       </c>
       <c r="H55">
         <v>3.96</v>
@@ -2788,22 +2788,22 @@
         <v>0</v>
       </c>
       <c r="K55">
-        <v>1331609</v>
+        <v>7393999</v>
       </c>
       <c r="L55">
-        <v>5305.451639999999</v>
+        <v>30091.148719999997</v>
       </c>
       <c r="M55">
-        <v>10000</v>
+        <v>135100</v>
       </c>
       <c r="N55">
+        <v>3.96</v>
+      </c>
+      <c r="O55">
         <v>3.98</v>
       </c>
-      <c r="O55">
-        <v>4</v>
-      </c>
       <c r="P55">
-        <v>404500</v>
+        <v>102000</v>
       </c>
     </row>
     <row r="56">
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="F56">
-        <v>6.9</v>
+        <v>6.85</v>
       </c>
       <c r="G56">
         <v>6.9</v>
@@ -2838,13 +2838,13 @@
         <v>0</v>
       </c>
       <c r="K56">
-        <v>332910</v>
+        <v>303302</v>
       </c>
       <c r="L56">
-        <v>2285.784</v>
+        <v>2082.991</v>
       </c>
       <c r="M56">
-        <v>1800</v>
+        <v>9000</v>
       </c>
       <c r="N56">
         <v>6.85</v>
@@ -2853,7 +2853,7 @@
         <v>6.9</v>
       </c>
       <c r="P56">
-        <v>36100</v>
+        <v>93100</v>
       </c>
     </row>
     <row r="57">
@@ -2864,46 +2864,46 @@
         <v>-</v>
       </c>
       <c r="C57">
+        <v>8.2</v>
+      </c>
+      <c r="D57">
+        <v>-0.15</v>
+      </c>
+      <c r="E57">
+        <v>-1.7964071856287425</v>
+      </c>
+      <c r="F57">
         <v>8.35</v>
       </c>
-      <c r="D57">
-        <v>-0.3</v>
-      </c>
-      <c r="E57">
-        <v>-3.468208092485549</v>
-      </c>
-      <c r="F57">
-        <v>8.7</v>
-      </c>
       <c r="G57">
-        <v>8.7</v>
+        <v>8.45</v>
       </c>
       <c r="H57">
+        <v>8.15</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>6820410</v>
+      </c>
+      <c r="L57">
+        <v>56155.569200000005</v>
+      </c>
+      <c r="M57">
+        <v>202800</v>
+      </c>
+      <c r="N57">
+        <v>8.2</v>
+      </c>
+      <c r="O57">
         <v>8.25</v>
       </c>
-      <c r="I57">
-        <v>0</v>
-      </c>
-      <c r="J57">
-        <v>0</v>
-      </c>
-      <c r="K57">
-        <v>10133431</v>
-      </c>
-      <c r="L57">
-        <v>85210.2562</v>
-      </c>
-      <c r="M57">
-        <v>24700</v>
-      </c>
-      <c r="N57">
-        <v>8.35</v>
-      </c>
-      <c r="O57">
-        <v>8.4</v>
-      </c>
       <c r="P57">
-        <v>281200</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="58">
@@ -2929,7 +2929,7 @@
         <v>5.2</v>
       </c>
       <c r="H58">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -2938,13 +2938,13 @@
         <v>0</v>
       </c>
       <c r="K58">
-        <v>3031912</v>
+        <v>2560116</v>
       </c>
       <c r="L58">
-        <v>15617.105</v>
+        <v>13219.152300000002</v>
       </c>
       <c r="M58">
-        <v>815300</v>
+        <v>606300</v>
       </c>
       <c r="N58">
         <v>5.15</v>
@@ -2953,7 +2953,7 @@
         <v>5.2</v>
       </c>
       <c r="P58">
-        <v>1060900</v>
+        <v>1261000</v>
       </c>
     </row>
     <row r="59">
@@ -2967,43 +2967,43 @@
         <v>9.65</v>
       </c>
       <c r="D59">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="E59">
-        <v>-0.5154639175257731</v>
+        <v>0</v>
       </c>
       <c r="F59">
-        <v>9.85</v>
+        <v>9.7</v>
       </c>
       <c r="G59">
-        <v>9.85</v>
+        <v>9.8</v>
       </c>
       <c r="H59">
+        <v>9.3</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>4746935</v>
+      </c>
+      <c r="L59">
+        <v>45463.65945000001</v>
+      </c>
+      <c r="M59">
+        <v>406500</v>
+      </c>
+      <c r="N59">
         <v>9.6</v>
       </c>
-      <c r="I59">
-        <v>0</v>
-      </c>
-      <c r="J59">
-        <v>0</v>
-      </c>
-      <c r="K59">
-        <v>8777623</v>
-      </c>
-      <c r="L59">
-        <v>85499.26920000001</v>
-      </c>
-      <c r="M59">
-        <v>93700</v>
-      </c>
-      <c r="N59">
+      <c r="O59">
         <v>9.65</v>
       </c>
-      <c r="O59">
-        <v>9.7</v>
-      </c>
       <c r="P59">
-        <v>151400</v>
+        <v>20500</v>
       </c>
     </row>
     <row r="60">
@@ -3023,14 +3023,14 @@
         <v>0</v>
       </c>
       <c r="F60">
+        <v>3.72</v>
+      </c>
+      <c r="G60">
+        <v>3.72</v>
+      </c>
+      <c r="H60">
         <v>3.66</v>
       </c>
-      <c r="G60">
-        <v>3.7</v>
-      </c>
-      <c r="H60">
-        <v>3.64</v>
-      </c>
       <c r="I60">
         <v>0</v>
       </c>
@@ -3038,13 +3038,13 @@
         <v>0</v>
       </c>
       <c r="K60">
-        <v>4525592</v>
+        <v>7537526</v>
       </c>
       <c r="L60">
-        <v>16602.01504</v>
+        <v>27784.93184</v>
       </c>
       <c r="M60">
-        <v>711200</v>
+        <v>163200</v>
       </c>
       <c r="N60">
         <v>3.66</v>
@@ -3053,7 +3053,7 @@
         <v>3.68</v>
       </c>
       <c r="P60">
-        <v>86300</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="61">
@@ -3064,46 +3064,46 @@
         <v>-</v>
       </c>
       <c r="C61">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>-1.0526315789473684</v>
       </c>
       <c r="F61">
-        <v>9.5</v>
+        <v>9.45</v>
       </c>
       <c r="G61">
         <v>9.5</v>
       </c>
       <c r="H61">
+        <v>9.4</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>236124</v>
+      </c>
+      <c r="L61">
+        <v>2232.1576</v>
+      </c>
+      <c r="M61">
+        <v>236900</v>
+      </c>
+      <c r="N61">
+        <v>9.4</v>
+      </c>
+      <c r="O61">
         <v>9.45</v>
       </c>
-      <c r="I61">
-        <v>0</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
-      </c>
-      <c r="K61">
-        <v>157023</v>
-      </c>
-      <c r="L61">
-        <v>1484.63425</v>
-      </c>
-      <c r="M61">
-        <v>300</v>
-      </c>
-      <c r="N61">
-        <v>9.45</v>
-      </c>
-      <c r="O61">
-        <v>9.5</v>
-      </c>
       <c r="P61">
-        <v>133500</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="62">
@@ -3114,46 +3114,46 @@
         <v>-</v>
       </c>
       <c r="C62">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="D62">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E62">
-        <v>0.6329113924050633</v>
+        <v>-1.2578616352201257</v>
       </c>
       <c r="F62">
-        <v>15.8</v>
+        <v>16.1</v>
       </c>
       <c r="G62">
         <v>16.1</v>
       </c>
       <c r="H62">
+        <v>15.7</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>1289195</v>
+      </c>
+      <c r="L62">
+        <v>20475.682699999998</v>
+      </c>
+      <c r="M62">
+        <v>108800</v>
+      </c>
+      <c r="N62">
+        <v>15.7</v>
+      </c>
+      <c r="O62">
         <v>15.8</v>
       </c>
-      <c r="I62">
-        <v>0</v>
-      </c>
-      <c r="J62">
-        <v>0</v>
-      </c>
-      <c r="K62">
-        <v>1423636</v>
-      </c>
-      <c r="L62">
-        <v>22665.0539</v>
-      </c>
-      <c r="M62">
-        <v>62600</v>
-      </c>
-      <c r="N62">
-        <v>15.9</v>
-      </c>
-      <c r="O62">
-        <v>16</v>
-      </c>
       <c r="P62">
-        <v>104600</v>
+        <v>19300</v>
       </c>
     </row>
     <row r="63">
@@ -3164,13 +3164,13 @@
         <v>-</v>
       </c>
       <c r="C63">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="D63">
         <v>0.02</v>
       </c>
       <c r="E63">
-        <v>0.9345794392523364</v>
+        <v>0.9259259259259259</v>
       </c>
       <c r="F63">
         <v>2.16</v>
@@ -3188,13 +3188,13 @@
         <v>0</v>
       </c>
       <c r="K63">
-        <v>122409</v>
+        <v>22202</v>
       </c>
       <c r="L63">
-        <v>265.69162</v>
+        <v>48.1804</v>
       </c>
       <c r="M63">
-        <v>30800</v>
+        <v>2000</v>
       </c>
       <c r="N63">
         <v>2.16</v>
@@ -3203,7 +3203,7 @@
         <v>2.18</v>
       </c>
       <c r="P63">
-        <v>215100</v>
+        <v>94500</v>
       </c>
     </row>
     <row r="64">
@@ -3214,19 +3214,19 @@
         <v>-</v>
       </c>
       <c r="C64">
+        <v>5.65</v>
+      </c>
+      <c r="D64">
+        <v>-0.05</v>
+      </c>
+      <c r="E64">
+        <v>-0.8771929824561403</v>
+      </c>
+      <c r="F64">
         <v>5.7</v>
       </c>
-      <c r="D64">
-        <v>0</v>
-      </c>
-      <c r="E64">
-        <v>0</v>
-      </c>
-      <c r="F64">
-        <v>5.75</v>
-      </c>
       <c r="G64">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="H64">
         <v>5.65</v>
@@ -3238,13 +3238,13 @@
         <v>0</v>
       </c>
       <c r="K64">
-        <v>191700</v>
+        <v>66300</v>
       </c>
       <c r="L64">
-        <v>1088.485</v>
+        <v>375.915</v>
       </c>
       <c r="M64">
-        <v>45400</v>
+        <v>121200</v>
       </c>
       <c r="N64">
         <v>5.65</v>
@@ -3253,7 +3253,7 @@
         <v>5.7</v>
       </c>
       <c r="P64">
-        <v>400</v>
+        <v>56400</v>
       </c>
     </row>
     <row r="65">
@@ -3264,22 +3264,22 @@
         <v>-</v>
       </c>
       <c r="C65">
-        <v>4.64</v>
+        <v>4.62</v>
       </c>
       <c r="D65">
-        <v>0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="E65">
-        <v>0.8695652173913043</v>
+        <v>-0.43103448275862066</v>
       </c>
       <c r="F65">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="G65">
         <v>4.64</v>
       </c>
       <c r="H65">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -3288,22 +3288,22 @@
         <v>0</v>
       </c>
       <c r="K65">
-        <v>2602752</v>
+        <v>1607234</v>
       </c>
       <c r="L65">
-        <v>12004.61808</v>
+        <v>7422.55932</v>
       </c>
       <c r="M65">
-        <v>31200</v>
+        <v>261800</v>
       </c>
       <c r="N65">
+        <v>4.6</v>
+      </c>
+      <c r="O65">
         <v>4.62</v>
       </c>
-      <c r="O65">
-        <v>4.64</v>
-      </c>
       <c r="P65">
-        <v>236500</v>
+        <v>84200</v>
       </c>
     </row>
     <row r="66">
@@ -3323,7 +3323,7 @@
         <v>0</v>
       </c>
       <c r="F66">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="G66">
         <v>5.2</v>
@@ -3338,13 +3338,13 @@
         <v>0</v>
       </c>
       <c r="K66">
-        <v>17700</v>
+        <v>49400</v>
       </c>
       <c r="L66">
-        <v>91.755</v>
+        <v>256.43</v>
       </c>
       <c r="M66">
-        <v>88600</v>
+        <v>108100</v>
       </c>
       <c r="N66">
         <v>5.15</v>
@@ -3353,7 +3353,7 @@
         <v>5.2</v>
       </c>
       <c r="P66">
-        <v>600</v>
+        <v>40700</v>
       </c>
     </row>
     <row r="67">
@@ -3364,19 +3364,19 @@
         <v>-</v>
       </c>
       <c r="C67">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="D67">
-        <v>0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="E67">
-        <v>6.896551724137931</v>
+        <v>-4.838709677419355</v>
       </c>
       <c r="F67">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="G67">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H67">
         <v>0.59</v>
@@ -3388,22 +3388,22 @@
         <v>0</v>
       </c>
       <c r="K67">
-        <v>59064093</v>
+        <v>67046080</v>
       </c>
       <c r="L67">
-        <v>35968.68908</v>
+        <v>41327.21607</v>
       </c>
       <c r="M67">
-        <v>93205100</v>
+        <v>456000</v>
       </c>
       <c r="N67">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="O67">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="P67">
-        <v>9305700</v>
+        <v>1183800</v>
       </c>
     </row>
     <row r="68">
@@ -3414,19 +3414,19 @@
         <v>-</v>
       </c>
       <c r="C68">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="D68">
         <v>-0.2</v>
       </c>
       <c r="E68">
-        <v>-1.0638297872340425</v>
+        <v>-1.075268817204301</v>
       </c>
       <c r="F68">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="G68">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="H68">
         <v>18.4</v>
@@ -3438,22 +3438,22 @@
         <v>0</v>
       </c>
       <c r="K68">
-        <v>1235687</v>
+        <v>2692783</v>
       </c>
       <c r="L68">
-        <v>23003.4544</v>
+        <v>50277.9519</v>
       </c>
       <c r="M68">
-        <v>122700</v>
+        <v>107600</v>
       </c>
       <c r="N68">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="O68">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="P68">
-        <v>20100</v>
+        <v>79800</v>
       </c>
     </row>
     <row r="69">
@@ -3467,43 +3467,43 @@
         <v>11.6</v>
       </c>
       <c r="D69">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E69">
-        <v>-0.8547008547008547</v>
+        <v>0</v>
       </c>
       <c r="F69">
         <v>11.7</v>
       </c>
       <c r="G69">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="H69">
+        <v>11.5</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>2340643</v>
+      </c>
+      <c r="L69">
+        <v>27386.602300000002</v>
+      </c>
+      <c r="M69">
+        <v>14600</v>
+      </c>
+      <c r="N69">
+        <v>11.5</v>
+      </c>
+      <c r="O69">
         <v>11.6</v>
       </c>
-      <c r="I69">
-        <v>0</v>
-      </c>
-      <c r="J69">
-        <v>0</v>
-      </c>
-      <c r="K69">
-        <v>913070</v>
-      </c>
-      <c r="L69">
-        <v>10710.544699999999</v>
-      </c>
-      <c r="M69">
-        <v>112700</v>
-      </c>
-      <c r="N69">
-        <v>11.6</v>
-      </c>
-      <c r="O69">
-        <v>11.7</v>
-      </c>
       <c r="P69">
-        <v>5000</v>
+        <v>431300</v>
       </c>
     </row>
     <row r="70">
@@ -3514,19 +3514,19 @@
         <v>-</v>
       </c>
       <c r="C70">
-        <v>9.95</v>
+        <v>9.9</v>
       </c>
       <c r="D70">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E70">
-        <v>0.5050505050505051</v>
+        <v>-0.5025125628140703</v>
       </c>
       <c r="F70">
         <v>9.9</v>
       </c>
       <c r="G70">
-        <v>10</v>
+        <v>9.95</v>
       </c>
       <c r="H70">
         <v>9.9</v>
@@ -3538,13 +3538,13 @@
         <v>0</v>
       </c>
       <c r="K70">
-        <v>406865</v>
+        <v>527195</v>
       </c>
       <c r="L70">
-        <v>4040.2102999999997</v>
+        <v>5223.926</v>
       </c>
       <c r="M70">
-        <v>128500</v>
+        <v>31300</v>
       </c>
       <c r="N70">
         <v>9.9</v>
@@ -3553,7 +3553,7 @@
         <v>9.95</v>
       </c>
       <c r="P70">
-        <v>78000</v>
+        <v>101700</v>
       </c>
     </row>
     <row r="71">
@@ -3564,13 +3564,13 @@
         <v>-</v>
       </c>
       <c r="C71">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="D71">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="E71">
-        <v>-0.6134969325153374</v>
+        <v>-1.2345679012345678</v>
       </c>
       <c r="F71">
         <v>8.2</v>
@@ -3588,22 +3588,22 @@
         <v>0</v>
       </c>
       <c r="K71">
-        <v>349601</v>
+        <v>395414</v>
       </c>
       <c r="L71">
-        <v>2830.04815</v>
+        <v>3190.77365</v>
       </c>
       <c r="M71">
-        <v>15600</v>
+        <v>191200</v>
       </c>
       <c r="N71">
+        <v>8</v>
+      </c>
+      <c r="O71">
         <v>8.1</v>
       </c>
-      <c r="O71">
-        <v>8.15</v>
-      </c>
       <c r="P71">
-        <v>17800</v>
+        <v>8300</v>
       </c>
     </row>
     <row r="72">
@@ -3614,22 +3614,22 @@
         <v>-</v>
       </c>
       <c r="C72">
+        <v>4.38</v>
+      </c>
+      <c r="D72">
+        <v>-0.14</v>
+      </c>
+      <c r="E72">
+        <v>-3.0973451327433628</v>
+      </c>
+      <c r="F72">
         <v>4.52</v>
       </c>
-      <c r="D72">
-        <v>-0.06</v>
-      </c>
-      <c r="E72">
-        <v>-1.3100436681222707</v>
-      </c>
-      <c r="F72">
-        <v>4.64</v>
-      </c>
       <c r="G72">
-        <v>4.64</v>
+        <v>4.58</v>
       </c>
       <c r="H72">
-        <v>4.5</v>
+        <v>4.38</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -3638,22 +3638,22 @@
         <v>0</v>
       </c>
       <c r="K72">
-        <v>934982</v>
+        <v>1271707</v>
       </c>
       <c r="L72">
-        <v>4270.11116</v>
+        <v>5663.68954</v>
       </c>
       <c r="M72">
-        <v>19100</v>
+        <v>15600</v>
       </c>
       <c r="N72">
-        <v>4.52</v>
+        <v>4.38</v>
       </c>
       <c r="O72">
-        <v>4.54</v>
+        <v>4.44</v>
       </c>
       <c r="P72">
-        <v>32000</v>
+        <v>11100</v>
       </c>
     </row>
     <row r="73">
@@ -3664,19 +3664,19 @@
         <v>-</v>
       </c>
       <c r="C73">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="D73">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="E73">
-        <v>-1.2658227848101267</v>
+        <v>1.2820512820512822</v>
       </c>
       <c r="F73">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="G73">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="H73">
         <v>0.78</v>
@@ -3688,13 +3688,13 @@
         <v>0</v>
       </c>
       <c r="K73">
-        <v>4998544</v>
+        <v>6206695</v>
       </c>
       <c r="L73">
-        <v>3910.43846</v>
+        <v>4889.53128</v>
       </c>
       <c r="M73">
-        <v>5160000</v>
+        <v>4891600</v>
       </c>
       <c r="N73">
         <v>0.78</v>
@@ -3703,7 +3703,7 @@
         <v>0.79</v>
       </c>
       <c r="P73">
-        <v>625100</v>
+        <v>523000</v>
       </c>
     </row>
     <row r="74">
@@ -3717,43 +3717,43 @@
         <v>9.6</v>
       </c>
       <c r="D74">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E74">
-        <v>-1.0309278350515463</v>
+        <v>0</v>
       </c>
       <c r="F74">
-        <v>9.7</v>
+        <v>9.6</v>
       </c>
       <c r="G74">
-        <v>9.7</v>
+        <v>9.65</v>
       </c>
       <c r="H74">
+        <v>9.55</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>44003</v>
+      </c>
+      <c r="L74">
+        <v>421.96395</v>
+      </c>
+      <c r="M74">
+        <v>1800</v>
+      </c>
+      <c r="N74">
+        <v>9.55</v>
+      </c>
+      <c r="O74">
         <v>9.6</v>
       </c>
-      <c r="I74">
-        <v>0</v>
-      </c>
-      <c r="J74">
-        <v>0</v>
-      </c>
-      <c r="K74">
-        <v>70010</v>
-      </c>
-      <c r="L74">
-        <v>673.90645</v>
-      </c>
-      <c r="M74">
-        <v>36300</v>
-      </c>
-      <c r="N74">
-        <v>9.6</v>
-      </c>
-      <c r="O74">
-        <v>9.65</v>
-      </c>
       <c r="P74">
-        <v>1500</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="75">
@@ -3764,22 +3764,22 @@
         <v>-</v>
       </c>
       <c r="C75">
+        <v>4.94</v>
+      </c>
+      <c r="D75">
+        <v>0.1</v>
+      </c>
+      <c r="E75">
+        <v>2.0661157024793386</v>
+      </c>
+      <c r="F75">
         <v>4.84</v>
       </c>
-      <c r="D75">
-        <v>-0.16</v>
-      </c>
-      <c r="E75">
-        <v>-3.2</v>
-      </c>
-      <c r="F75">
-        <v>5</v>
-      </c>
       <c r="G75">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="H75">
-        <v>4.78</v>
+        <v>4.84</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -3788,22 +3788,22 @@
         <v>0</v>
       </c>
       <c r="K75">
-        <v>36472971</v>
+        <v>36635010</v>
       </c>
       <c r="L75">
-        <v>178669.22118</v>
+        <v>182019.72228</v>
       </c>
       <c r="M75">
-        <v>64800</v>
+        <v>275500</v>
       </c>
       <c r="N75">
-        <v>4.84</v>
+        <v>4.94</v>
       </c>
       <c r="O75">
-        <v>4.86</v>
+        <v>4.96</v>
       </c>
       <c r="P75">
-        <v>414500</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="76">
@@ -3814,46 +3814,46 @@
         <v>-</v>
       </c>
       <c r="C76">
+        <v>6.35</v>
+      </c>
+      <c r="D76">
+        <v>-0.1</v>
+      </c>
+      <c r="E76">
+        <v>-1.550387596899225</v>
+      </c>
+      <c r="F76">
         <v>6.45</v>
-      </c>
-      <c r="D76">
-        <v>-0.05</v>
-      </c>
-      <c r="E76">
-        <v>-0.7692307692307693</v>
-      </c>
-      <c r="F76">
-        <v>6.5</v>
       </c>
       <c r="G76">
         <v>6.5</v>
       </c>
       <c r="H76">
+        <v>6.3</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>13085955</v>
+      </c>
+      <c r="L76">
+        <v>83386.8573</v>
+      </c>
+      <c r="M76">
+        <v>443300</v>
+      </c>
+      <c r="N76">
+        <v>6.35</v>
+      </c>
+      <c r="O76">
         <v>6.4</v>
       </c>
-      <c r="I76">
-        <v>0</v>
-      </c>
-      <c r="J76">
-        <v>0</v>
-      </c>
-      <c r="K76">
-        <v>5084039</v>
-      </c>
-      <c r="L76">
-        <v>32840.1161</v>
-      </c>
-      <c r="M76">
-        <v>1176800</v>
-      </c>
-      <c r="N76">
-        <v>6.4</v>
-      </c>
-      <c r="O76">
-        <v>6.45</v>
-      </c>
       <c r="P76">
-        <v>136400</v>
+        <v>515300</v>
       </c>
     </row>
     <row r="77">
@@ -3864,22 +3864,22 @@
         <v>-</v>
       </c>
       <c r="C77">
-        <v>5.65</v>
+        <v>5.6</v>
       </c>
       <c r="D77">
         <v>-0.05</v>
       </c>
       <c r="E77">
-        <v>-0.8771929824561403</v>
+        <v>-0.8849557522123894</v>
       </c>
       <c r="F77">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="G77">
         <v>5.75</v>
       </c>
       <c r="H77">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -3888,22 +3888,22 @@
         <v>0</v>
       </c>
       <c r="K77">
-        <v>4374247</v>
+        <v>2873399</v>
       </c>
       <c r="L77">
-        <v>24894.49825</v>
+        <v>16197.22175</v>
       </c>
       <c r="M77">
-        <v>322000</v>
+        <v>349500</v>
       </c>
       <c r="N77">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="O77">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="P77">
-        <v>10500</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="78">
@@ -3914,22 +3914,22 @@
         <v>-</v>
       </c>
       <c r="C78">
+        <v>5.85</v>
+      </c>
+      <c r="D78">
+        <v>-0.15</v>
+      </c>
+      <c r="E78">
+        <v>-2.5</v>
+      </c>
+      <c r="F78">
         <v>6</v>
       </c>
-      <c r="D78">
-        <v>0</v>
-      </c>
-      <c r="E78">
-        <v>0</v>
-      </c>
-      <c r="F78">
-        <v>6.05</v>
-      </c>
       <c r="G78">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="H78">
-        <v>5.95</v>
+        <v>5.8</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -3938,22 +3938,22 @@
         <v>0</v>
       </c>
       <c r="K78">
-        <v>1057658</v>
+        <v>2109398</v>
       </c>
       <c r="L78">
-        <v>6319.468</v>
+        <v>12391.20655</v>
       </c>
       <c r="M78">
-        <v>25100</v>
+        <v>120400</v>
       </c>
       <c r="N78">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="O78">
-        <v>6.05</v>
+        <v>5.85</v>
       </c>
       <c r="P78">
-        <v>430700</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="79">
@@ -3964,19 +3964,19 @@
         <v>-</v>
       </c>
       <c r="C79">
-        <v>24.9</v>
+        <v>24.6</v>
       </c>
       <c r="D79">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="E79">
-        <v>-0.4</v>
+        <v>-1.2048192771084338</v>
       </c>
       <c r="F79">
-        <v>25.5</v>
+        <v>25</v>
       </c>
       <c r="G79">
-        <v>25.5</v>
+        <v>25</v>
       </c>
       <c r="H79">
         <v>24.5</v>
@@ -3988,22 +3988,22 @@
         <v>0</v>
       </c>
       <c r="K79">
-        <v>1428350</v>
+        <v>996864</v>
       </c>
       <c r="L79">
-        <v>35539.2028</v>
+        <v>24643.779850000003</v>
       </c>
       <c r="M79">
-        <v>22500</v>
+        <v>18900</v>
       </c>
       <c r="N79">
-        <v>24.9</v>
+        <v>24.6</v>
       </c>
       <c r="O79">
-        <v>25</v>
+        <v>24.8</v>
       </c>
       <c r="P79">
-        <v>334100</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="80">
@@ -4014,16 +4014,16 @@
         <v>-</v>
       </c>
       <c r="C80">
+        <v>41.75</v>
+      </c>
+      <c r="D80">
+        <v>0.25</v>
+      </c>
+      <c r="E80">
+        <v>0.6024096385542169</v>
+      </c>
+      <c r="F80">
         <v>41.5</v>
-      </c>
-      <c r="D80">
-        <v>-0.25</v>
-      </c>
-      <c r="E80">
-        <v>-0.5988023952095808</v>
-      </c>
-      <c r="F80">
-        <v>41.75</v>
       </c>
       <c r="G80">
         <v>41.75</v>
@@ -4038,13 +4038,13 @@
         <v>0</v>
       </c>
       <c r="K80">
-        <v>8805</v>
+        <v>28816</v>
       </c>
       <c r="L80">
-        <v>365.83425</v>
+        <v>1202.297</v>
       </c>
       <c r="M80">
-        <v>400</v>
+        <v>7700</v>
       </c>
       <c r="N80">
         <v>41.5</v>
@@ -4053,7 +4053,7 @@
         <v>41.75</v>
       </c>
       <c r="P80">
-        <v>20400</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="81">
@@ -4064,22 +4064,22 @@
         <v>-</v>
       </c>
       <c r="C81">
+        <v>1.08</v>
+      </c>
+      <c r="D81">
+        <v>-0.02</v>
+      </c>
+      <c r="E81">
+        <v>-1.8181818181818181</v>
+      </c>
+      <c r="F81">
         <v>1.1</v>
       </c>
-      <c r="D81">
-        <v>0</v>
-      </c>
-      <c r="E81">
-        <v>0</v>
-      </c>
-      <c r="F81">
-        <v>1.11</v>
-      </c>
       <c r="G81">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="H81">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -4088,22 +4088,22 @@
         <v>0</v>
       </c>
       <c r="K81">
-        <v>4040952</v>
+        <v>26625941</v>
       </c>
       <c r="L81">
-        <v>4453.17992</v>
+        <v>29251.03473</v>
       </c>
       <c r="M81">
-        <v>1842600</v>
+        <v>1100200</v>
       </c>
       <c r="N81">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="O81">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="P81">
-        <v>845200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="82">
@@ -4114,46 +4114,46 @@
         <v>-</v>
       </c>
       <c r="C82">
+        <v>2</v>
+      </c>
+      <c r="D82">
+        <v>-0.06</v>
+      </c>
+      <c r="E82">
+        <v>-2.912621359223301</v>
+      </c>
+      <c r="F82">
         <v>2.06</v>
       </c>
-      <c r="D82">
-        <v>0.02</v>
-      </c>
-      <c r="E82">
-        <v>0.9803921568627451</v>
-      </c>
-      <c r="F82">
+      <c r="G82">
+        <v>2.06</v>
+      </c>
+      <c r="H82">
+        <v>2</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>205400</v>
+      </c>
+      <c r="L82">
+        <v>415.07</v>
+      </c>
+      <c r="M82">
+        <v>126400</v>
+      </c>
+      <c r="N82">
+        <v>2</v>
+      </c>
+      <c r="O82">
         <v>2.04</v>
       </c>
-      <c r="G82">
-        <v>2.08</v>
-      </c>
-      <c r="H82">
-        <v>2.02</v>
-      </c>
-      <c r="I82">
-        <v>0</v>
-      </c>
-      <c r="J82">
-        <v>0</v>
-      </c>
-      <c r="K82">
-        <v>456601</v>
-      </c>
-      <c r="L82">
-        <v>932.6700400000001</v>
-      </c>
-      <c r="M82">
-        <v>34200</v>
-      </c>
-      <c r="N82">
-        <v>2.02</v>
-      </c>
-      <c r="O82">
-        <v>2.06</v>
-      </c>
       <c r="P82">
-        <v>166100</v>
+        <v>129300</v>
       </c>
     </row>
     <row r="83">
@@ -4164,16 +4164,16 @@
         <v>-</v>
       </c>
       <c r="C83">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="D83">
-        <v>0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="E83">
-        <v>1.1363636363636365</v>
+        <v>-0.5617977528089888</v>
       </c>
       <c r="F83">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="G83">
         <v>3.58</v>
@@ -4188,22 +4188,22 @@
         <v>0</v>
       </c>
       <c r="K83">
-        <v>1176916</v>
+        <v>1881824</v>
       </c>
       <c r="L83">
-        <v>4173.16084</v>
+        <v>6675.10318</v>
       </c>
       <c r="M83">
-        <v>93000</v>
+        <v>357800</v>
       </c>
       <c r="N83">
+        <v>3.52</v>
+      </c>
+      <c r="O83">
         <v>3.54</v>
       </c>
-      <c r="O83">
-        <v>3.56</v>
-      </c>
       <c r="P83">
-        <v>156500</v>
+        <v>237500</v>
       </c>
     </row>
     <row r="84">
@@ -4238,13 +4238,13 @@
         <v>0</v>
       </c>
       <c r="K84">
-        <v>9194383</v>
+        <v>19209451</v>
       </c>
       <c r="L84">
-        <v>3950.43152</v>
+        <v>8255.39193</v>
       </c>
       <c r="M84">
-        <v>29158200</v>
+        <v>27460900</v>
       </c>
       <c r="N84">
         <v>0.42</v>
@@ -4253,7 +4253,7 @@
         <v>0.43</v>
       </c>
       <c r="P84">
-        <v>12507400</v>
+        <v>6233400</v>
       </c>
     </row>
     <row r="85">
@@ -4264,22 +4264,22 @@
         <v>-</v>
       </c>
       <c r="C85">
+        <v>3.6</v>
+      </c>
+      <c r="D85">
+        <v>-0.18</v>
+      </c>
+      <c r="E85">
+        <v>-4.761904761904762</v>
+      </c>
+      <c r="F85">
+        <v>3.76</v>
+      </c>
+      <c r="G85">
         <v>3.78</v>
       </c>
-      <c r="D85">
-        <v>0</v>
-      </c>
-      <c r="E85">
-        <v>0</v>
-      </c>
-      <c r="F85">
-        <v>3.82</v>
-      </c>
-      <c r="G85">
-        <v>3.92</v>
-      </c>
       <c r="H85">
-        <v>3.76</v>
+        <v>3.58</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -4288,22 +4288,22 @@
         <v>0</v>
       </c>
       <c r="K85">
-        <v>5181880</v>
+        <v>4796229</v>
       </c>
       <c r="L85">
-        <v>19896.3425</v>
+        <v>17655.696219999998</v>
       </c>
       <c r="M85">
-        <v>215600</v>
+        <v>54900</v>
       </c>
       <c r="N85">
-        <v>3.76</v>
+        <v>3.6</v>
       </c>
       <c r="O85">
-        <v>3.78</v>
+        <v>3.62</v>
       </c>
       <c r="P85">
-        <v>116800</v>
+        <v>61800</v>
       </c>
     </row>
     <row r="86">
@@ -4314,22 +4314,22 @@
         <v>-</v>
       </c>
       <c r="C86">
-        <v>9.3</v>
+        <v>8.8</v>
       </c>
       <c r="D86">
-        <v>-0.15</v>
+        <v>-0.5</v>
       </c>
       <c r="E86">
-        <v>-1.5873015873015872</v>
+        <v>-5.376344086021505</v>
       </c>
       <c r="F86">
-        <v>9.55</v>
+        <v>9.25</v>
       </c>
       <c r="G86">
-        <v>9.6</v>
+        <v>9.25</v>
       </c>
       <c r="H86">
-        <v>9.3</v>
+        <v>8.8</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -4338,22 +4338,22 @@
         <v>0</v>
       </c>
       <c r="K86">
-        <v>6649299</v>
+        <v>10609483</v>
       </c>
       <c r="L86">
-        <v>62934.129049999996</v>
+        <v>95512.82995</v>
       </c>
       <c r="M86">
-        <v>458300</v>
+        <v>388000</v>
       </c>
       <c r="N86">
-        <v>9.25</v>
+        <v>8.8</v>
       </c>
       <c r="O86">
-        <v>9.3</v>
+        <v>8.85</v>
       </c>
       <c r="P86">
-        <v>104000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="87">
@@ -4367,19 +4367,19 @@
         <v>9.65</v>
       </c>
       <c r="D87">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E87">
-        <v>0.5208333333333334</v>
+        <v>0</v>
       </c>
       <c r="F87">
-        <v>9.55</v>
+        <v>9.65</v>
       </c>
       <c r="G87">
         <v>9.7</v>
       </c>
       <c r="H87">
-        <v>9.55</v>
+        <v>9.65</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -4388,13 +4388,13 @@
         <v>0</v>
       </c>
       <c r="K87">
-        <v>24233</v>
+        <v>67256</v>
       </c>
       <c r="L87">
-        <v>232.7922</v>
+        <v>649.65315</v>
       </c>
       <c r="M87">
-        <v>20600</v>
+        <v>6900</v>
       </c>
       <c r="N87">
         <v>9.6</v>
@@ -4403,7 +4403,7 @@
         <v>9.65</v>
       </c>
       <c r="P87">
-        <v>11700</v>
+        <v>24700</v>
       </c>
     </row>
     <row r="88">
@@ -4414,22 +4414,22 @@
         <v>-</v>
       </c>
       <c r="C88">
+        <v>20.5</v>
+      </c>
+      <c r="D88">
+        <v>0.5</v>
+      </c>
+      <c r="E88">
+        <v>2.5</v>
+      </c>
+      <c r="F88">
         <v>20</v>
       </c>
-      <c r="D88">
-        <v>0.1</v>
-      </c>
-      <c r="E88">
-        <v>0.5025125628140703</v>
-      </c>
-      <c r="F88">
-        <v>19.8</v>
-      </c>
       <c r="G88">
-        <v>20.1</v>
+        <v>20.5</v>
       </c>
       <c r="H88">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -4438,22 +4438,22 @@
         <v>0</v>
       </c>
       <c r="K88">
-        <v>1248209</v>
+        <v>2778652</v>
       </c>
       <c r="L88">
-        <v>24861.0687</v>
+        <v>56473.4789</v>
       </c>
       <c r="M88">
-        <v>73000</v>
+        <v>24200</v>
       </c>
       <c r="N88">
-        <v>20</v>
+        <v>20.4</v>
       </c>
       <c r="O88">
-        <v>20.1</v>
+        <v>20.5</v>
       </c>
       <c r="P88">
-        <v>126800</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="89">
@@ -4464,22 +4464,22 @@
         <v>-</v>
       </c>
       <c r="C89">
+        <v>1.58</v>
+      </c>
+      <c r="D89">
+        <v>0.06</v>
+      </c>
+      <c r="E89">
+        <v>3.9473684210526314</v>
+      </c>
+      <c r="F89">
         <v>1.52</v>
       </c>
-      <c r="D89">
-        <v>-0.02</v>
-      </c>
-      <c r="E89">
-        <v>-1.2987012987012987</v>
-      </c>
-      <c r="F89">
-        <v>1.55</v>
-      </c>
       <c r="G89">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="H89">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -4488,22 +4488,22 @@
         <v>0</v>
       </c>
       <c r="K89">
-        <v>3849850</v>
+        <v>13051560</v>
       </c>
       <c r="L89">
-        <v>5894.6715</v>
+        <v>20636.947350000002</v>
       </c>
       <c r="M89">
-        <v>107300</v>
+        <v>183500</v>
       </c>
       <c r="N89">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="O89">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="P89">
-        <v>50000</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="90">
@@ -4517,19 +4517,19 @@
         <v>8</v>
       </c>
       <c r="D90">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E90">
-        <v>1.2658227848101267</v>
+        <v>0</v>
       </c>
       <c r="F90">
-        <v>7.9</v>
+        <v>8.05</v>
       </c>
       <c r="G90">
-        <v>8</v>
+        <v>8.05</v>
       </c>
       <c r="H90">
-        <v>7.85</v>
+        <v>7.8</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -4538,13 +4538,13 @@
         <v>0</v>
       </c>
       <c r="K90">
-        <v>10279852</v>
+        <v>12248999</v>
       </c>
       <c r="L90">
-        <v>81970.08775</v>
+        <v>96951.0574</v>
       </c>
       <c r="M90">
-        <v>437700</v>
+        <v>43300</v>
       </c>
       <c r="N90">
         <v>7.95</v>
@@ -4553,7 +4553,7 @@
         <v>8</v>
       </c>
       <c r="P90">
-        <v>132200</v>
+        <v>672300</v>
       </c>
     </row>
     <row r="91">
@@ -4564,22 +4564,22 @@
         <v>-</v>
       </c>
       <c r="C91">
+        <v>4.34</v>
+      </c>
+      <c r="D91">
+        <v>-0.08</v>
+      </c>
+      <c r="E91">
+        <v>-1.8099547511312217</v>
+      </c>
+      <c r="F91">
+        <v>4.4</v>
+      </c>
+      <c r="G91">
         <v>4.42</v>
       </c>
-      <c r="D91">
-        <v>0</v>
-      </c>
-      <c r="E91">
-        <v>0</v>
-      </c>
-      <c r="F91">
-        <v>4.44</v>
-      </c>
-      <c r="G91">
-        <v>4.46</v>
-      </c>
       <c r="H91">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -4588,22 +4588,22 @@
         <v>0</v>
       </c>
       <c r="K91">
-        <v>334018</v>
+        <v>178101</v>
       </c>
       <c r="L91">
-        <v>1460.69144</v>
+        <v>779.9864</v>
       </c>
       <c r="M91">
-        <v>28000</v>
+        <v>9600</v>
       </c>
       <c r="N91">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="O91">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="P91">
-        <v>53700</v>
+        <v>20900</v>
       </c>
     </row>
     <row r="92">
@@ -4614,46 +4614,46 @@
         <v>-</v>
       </c>
       <c r="C92">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="D92">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="E92">
-        <v>1.7391304347826086</v>
+        <v>-2.5641025641025643</v>
       </c>
       <c r="F92">
+        <v>1.18</v>
+      </c>
+      <c r="G92">
+        <v>1.18</v>
+      </c>
+      <c r="H92">
+        <v>1.13</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>39084239</v>
+      </c>
+      <c r="L92">
+        <v>45109.90783</v>
+      </c>
+      <c r="M92">
+        <v>90000</v>
+      </c>
+      <c r="N92">
+        <v>1.14</v>
+      </c>
+      <c r="O92">
         <v>1.15</v>
       </c>
-      <c r="G92">
-        <v>1.2</v>
-      </c>
-      <c r="H92">
-        <v>1.15</v>
-      </c>
-      <c r="I92">
-        <v>0</v>
-      </c>
-      <c r="J92">
-        <v>0</v>
-      </c>
-      <c r="K92">
-        <v>48974553</v>
-      </c>
-      <c r="L92">
-        <v>57509.14428</v>
-      </c>
-      <c r="M92">
-        <v>1048100</v>
-      </c>
-      <c r="N92">
-        <v>1.17</v>
-      </c>
-      <c r="O92">
-        <v>1.18</v>
-      </c>
       <c r="P92">
-        <v>2874100</v>
+        <v>726900</v>
       </c>
     </row>
     <row r="93">
@@ -4664,46 +4664,46 @@
         <v>-</v>
       </c>
       <c r="C93">
-        <v>31.25</v>
+        <v>31</v>
       </c>
       <c r="D93">
         <v>-0.25</v>
       </c>
       <c r="E93">
-        <v>-0.7936507936507936</v>
+        <v>-0.8</v>
       </c>
       <c r="F93">
-        <v>31.5</v>
+        <v>31.25</v>
       </c>
       <c r="G93">
-        <v>31.5</v>
+        <v>31.25</v>
       </c>
       <c r="H93">
+        <v>30.75</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>181392</v>
+      </c>
+      <c r="L93">
+        <v>5630.0095</v>
+      </c>
+      <c r="M93">
+        <v>32800</v>
+      </c>
+      <c r="N93">
+        <v>30.75</v>
+      </c>
+      <c r="O93">
         <v>31</v>
       </c>
-      <c r="I93">
-        <v>0</v>
-      </c>
-      <c r="J93">
-        <v>0</v>
-      </c>
-      <c r="K93">
-        <v>367902</v>
-      </c>
-      <c r="L93">
-        <v>11501.73625</v>
-      </c>
-      <c r="M93">
-        <v>127300</v>
-      </c>
-      <c r="N93">
-        <v>31</v>
-      </c>
-      <c r="O93">
-        <v>31.5</v>
-      </c>
       <c r="P93">
-        <v>56600</v>
+        <v>500</v>
       </c>
     </row>
     <row r="94">
@@ -4738,13 +4738,13 @@
         <v>0</v>
       </c>
       <c r="K94">
-        <v>3190610</v>
+        <v>2371100</v>
       </c>
       <c r="L94">
-        <v>2389.1915</v>
+        <v>1761.663</v>
       </c>
       <c r="M94">
-        <v>884300</v>
+        <v>426400</v>
       </c>
       <c r="N94">
         <v>0.74</v>
@@ -4753,7 +4753,7 @@
         <v>0.75</v>
       </c>
       <c r="P94">
-        <v>187100</v>
+        <v>1556400</v>
       </c>
     </row>
     <row r="95">
@@ -4764,19 +4764,19 @@
         <v>-</v>
       </c>
       <c r="C95">
+        <v>6.25</v>
+      </c>
+      <c r="D95">
+        <v>0.05</v>
+      </c>
+      <c r="E95">
+        <v>0.8064516129032258</v>
+      </c>
+      <c r="F95">
         <v>6.2</v>
       </c>
-      <c r="D95">
-        <v>-0.15</v>
-      </c>
-      <c r="E95">
-        <v>-2.3622047244094486</v>
-      </c>
-      <c r="F95">
-        <v>6.4</v>
-      </c>
       <c r="G95">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H95">
         <v>6.15</v>
@@ -4788,13 +4788,13 @@
         <v>0</v>
       </c>
       <c r="K95">
-        <v>2363196</v>
+        <v>1672729</v>
       </c>
       <c r="L95">
-        <v>14709.372150000001</v>
+        <v>10420.1811</v>
       </c>
       <c r="M95">
-        <v>76000</v>
+        <v>40100</v>
       </c>
       <c r="N95">
         <v>6.2</v>
@@ -4803,7 +4803,7 @@
         <v>6.25</v>
       </c>
       <c r="P95">
-        <v>83700</v>
+        <v>7600</v>
       </c>
     </row>
     <row r="96">
@@ -4814,19 +4814,19 @@
         <v>-</v>
       </c>
       <c r="C96">
+        <v>6.35</v>
+      </c>
+      <c r="D96">
+        <v>0.05</v>
+      </c>
+      <c r="E96">
+        <v>0.7936507936507936</v>
+      </c>
+      <c r="F96">
         <v>6.3</v>
       </c>
-      <c r="D96">
-        <v>0</v>
-      </c>
-      <c r="E96">
-        <v>0</v>
-      </c>
-      <c r="F96">
+      <c r="G96">
         <v>6.35</v>
-      </c>
-      <c r="G96">
-        <v>6.45</v>
       </c>
       <c r="H96">
         <v>6.3</v>
@@ -4838,13 +4838,13 @@
         <v>0</v>
       </c>
       <c r="K96">
-        <v>1451650</v>
+        <v>373062</v>
       </c>
       <c r="L96">
-        <v>9237.882800000001</v>
+        <v>2359.9132</v>
       </c>
       <c r="M96">
-        <v>51500</v>
+        <v>241200</v>
       </c>
       <c r="N96">
         <v>6.3</v>
@@ -4853,7 +4853,7 @@
         <v>6.35</v>
       </c>
       <c r="P96">
-        <v>40000</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="97">
@@ -4864,22 +4864,22 @@
         <v>-</v>
       </c>
       <c r="C97">
+        <v>18.1</v>
+      </c>
+      <c r="D97">
+        <v>0.8</v>
+      </c>
+      <c r="E97">
+        <v>4.624277456647399</v>
+      </c>
+      <c r="F97">
         <v>17.3</v>
       </c>
-      <c r="D97">
-        <v>-0.2</v>
-      </c>
-      <c r="E97">
-        <v>-1.1428571428571428</v>
-      </c>
-      <c r="F97">
-        <v>17.5</v>
-      </c>
       <c r="G97">
-        <v>17.6</v>
+        <v>18.4</v>
       </c>
       <c r="H97">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -4888,22 +4888,22 @@
         <v>0</v>
       </c>
       <c r="K97">
-        <v>4053447</v>
+        <v>22441062</v>
       </c>
       <c r="L97">
-        <v>70573.511</v>
+        <v>404501.9105</v>
       </c>
       <c r="M97">
-        <v>339300</v>
+        <v>216400</v>
       </c>
       <c r="N97">
-        <v>17.3</v>
+        <v>18</v>
       </c>
       <c r="O97">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="P97">
-        <v>18000</v>
+        <v>330200</v>
       </c>
     </row>
     <row r="98">
@@ -4914,22 +4914,22 @@
         <v>-</v>
       </c>
       <c r="C98">
+        <v>2.02</v>
+      </c>
+      <c r="D98">
+        <v>-0.02</v>
+      </c>
+      <c r="E98">
+        <v>-0.9803921568627451</v>
+      </c>
+      <c r="F98">
         <v>2.04</v>
-      </c>
-      <c r="D98">
-        <v>0.04</v>
-      </c>
-      <c r="E98">
-        <v>2</v>
-      </c>
-      <c r="F98">
-        <v>2.02</v>
       </c>
       <c r="G98">
         <v>2.04</v>
       </c>
       <c r="H98">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -4938,22 +4938,22 @@
         <v>0</v>
       </c>
       <c r="K98">
-        <v>7185045</v>
+        <v>12814282</v>
       </c>
       <c r="L98">
-        <v>14467.114300000001</v>
+        <v>25660.95544</v>
       </c>
       <c r="M98">
-        <v>903500</v>
+        <v>364300</v>
       </c>
       <c r="N98">
         <v>2</v>
       </c>
       <c r="O98">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="P98">
-        <v>531000</v>
+        <v>1194700</v>
       </c>
     </row>
     <row r="99">
@@ -4964,23 +4964,23 @@
         <v>-</v>
       </c>
       <c r="C99">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="D99">
         <v>0.05</v>
       </c>
       <c r="E99">
-        <v>0.9523809523809523</v>
+        <v>0.9433962264150944</v>
       </c>
       <c r="F99">
+        <v>5.35</v>
+      </c>
+      <c r="G99">
+        <v>5.4</v>
+      </c>
+      <c r="H99">
         <v>5.3</v>
       </c>
-      <c r="G99">
-        <v>5.3</v>
-      </c>
-      <c r="H99">
-        <v>5.25</v>
-      </c>
       <c r="I99">
         <v>0</v>
       </c>
@@ -4988,22 +4988,22 @@
         <v>0</v>
       </c>
       <c r="K99">
-        <v>44790</v>
+        <v>232987</v>
       </c>
       <c r="L99">
-        <v>236.87255</v>
+        <v>1252.1511</v>
       </c>
       <c r="M99">
-        <v>63000</v>
+        <v>19100</v>
       </c>
       <c r="N99">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="O99">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="P99">
-        <v>1400</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="100">
@@ -5014,19 +5014,19 @@
         <v>-</v>
       </c>
       <c r="C100">
+        <v>26.25</v>
+      </c>
+      <c r="D100">
+        <v>0.5</v>
+      </c>
+      <c r="E100">
+        <v>1.941747572815534</v>
+      </c>
+      <c r="F100">
         <v>25.75</v>
       </c>
-      <c r="D100">
-        <v>-0.25</v>
-      </c>
-      <c r="E100">
-        <v>-0.9615384615384616</v>
-      </c>
-      <c r="F100">
-        <v>26</v>
-      </c>
       <c r="G100">
-        <v>26.25</v>
+        <v>26.5</v>
       </c>
       <c r="H100">
         <v>25.5</v>
@@ -5038,22 +5038,22 @@
         <v>0</v>
       </c>
       <c r="K100">
-        <v>681003</v>
+        <v>1230305</v>
       </c>
       <c r="L100">
-        <v>17658.303</v>
+        <v>32190.806</v>
       </c>
       <c r="M100">
-        <v>43900</v>
+        <v>16500</v>
       </c>
       <c r="N100">
-        <v>25.75</v>
+        <v>26</v>
       </c>
       <c r="O100">
-        <v>26</v>
+        <v>26.25</v>
       </c>
       <c r="P100">
-        <v>35500</v>
+        <v>188200</v>
       </c>
     </row>
     <row r="101">
@@ -5067,43 +5067,43 @@
         <v>7.05</v>
       </c>
       <c r="D101">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="E101">
-        <v>-2.7586206896551726</v>
+        <v>0</v>
       </c>
       <c r="F101">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="G101">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="H101">
+        <v>7.05</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>1732533</v>
+      </c>
+      <c r="L101">
+        <v>12272.0548</v>
+      </c>
+      <c r="M101">
+        <v>895300</v>
+      </c>
+      <c r="N101">
         <v>7</v>
       </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0</v>
-      </c>
-      <c r="K101">
-        <v>2719032</v>
-      </c>
-      <c r="L101">
-        <v>19312.0583</v>
-      </c>
-      <c r="M101">
-        <v>160900</v>
-      </c>
-      <c r="N101">
+      <c r="O101">
         <v>7.05</v>
       </c>
-      <c r="O101">
-        <v>7.1</v>
-      </c>
       <c r="P101">
-        <v>91000</v>
+        <v>32700</v>
       </c>
     </row>
     <row r="102">
@@ -5114,22 +5114,22 @@
         <v>-</v>
       </c>
       <c r="C102">
+        <v>5.1</v>
+      </c>
+      <c r="D102">
+        <v>-0.5</v>
+      </c>
+      <c r="E102">
+        <v>-8.928571428571429</v>
+      </c>
+      <c r="F102">
         <v>5.6</v>
       </c>
-      <c r="D102">
-        <v>-0.1</v>
-      </c>
-      <c r="E102">
-        <v>-1.7543859649122806</v>
-      </c>
-      <c r="F102">
-        <v>5.85</v>
-      </c>
       <c r="G102">
-        <v>5.85</v>
+        <v>5.6</v>
       </c>
       <c r="H102">
-        <v>5.6</v>
+        <v>5.05</v>
       </c>
       <c r="I102">
         <v>0</v>
@@ -5138,22 +5138,22 @@
         <v>0</v>
       </c>
       <c r="K102">
-        <v>9903903</v>
+        <v>21403547</v>
       </c>
       <c r="L102">
-        <v>56251.202</v>
+        <v>113434.0209</v>
       </c>
       <c r="M102">
-        <v>643900</v>
+        <v>816700</v>
       </c>
       <c r="N102">
-        <v>5.55</v>
+        <v>5.1</v>
       </c>
       <c r="O102">
-        <v>5.6</v>
+        <v>5.15</v>
       </c>
       <c r="P102">
-        <v>1186400</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="103">
@@ -5164,22 +5164,22 @@
         <v>-</v>
       </c>
       <c r="C103">
-        <v>52.5</v>
+        <v>53</v>
       </c>
       <c r="D103">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="E103">
-        <v>6.0606060606060606</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="F103">
-        <v>50</v>
+        <v>52.75</v>
       </c>
       <c r="G103">
-        <v>52.5</v>
+        <v>53</v>
       </c>
       <c r="H103">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I103">
         <v>0</v>
@@ -5188,22 +5188,22 @@
         <v>0</v>
       </c>
       <c r="K103">
-        <v>2552941</v>
+        <v>1154662</v>
       </c>
       <c r="L103">
-        <v>131784.8835</v>
+        <v>59962.5365</v>
       </c>
       <c r="M103">
-        <v>33900</v>
+        <v>800</v>
       </c>
       <c r="N103">
-        <v>51.75</v>
+        <v>52.25</v>
       </c>
       <c r="O103">
-        <v>52.5</v>
+        <v>53</v>
       </c>
       <c r="P103">
-        <v>9300</v>
+        <v>23100</v>
       </c>
     </row>
     <row r="104">
@@ -5214,22 +5214,22 @@
         <v>-</v>
       </c>
       <c r="C104">
+        <v>21.2</v>
+      </c>
+      <c r="D104">
+        <v>-0.3</v>
+      </c>
+      <c r="E104">
+        <v>-1.3953488372093024</v>
+      </c>
+      <c r="F104">
         <v>21.5</v>
       </c>
-      <c r="D104">
-        <v>-0.1</v>
-      </c>
-      <c r="E104">
-        <v>-0.46296296296296297</v>
-      </c>
-      <c r="F104">
+      <c r="G104">
         <v>21.6</v>
       </c>
-      <c r="G104">
-        <v>21.7</v>
-      </c>
       <c r="H104">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="I104">
         <v>0</v>
@@ -5238,22 +5238,22 @@
         <v>0</v>
       </c>
       <c r="K104">
-        <v>438245</v>
+        <v>844079</v>
       </c>
       <c r="L104">
-        <v>9425.7183</v>
+        <v>17973.0022</v>
       </c>
       <c r="M104">
-        <v>129000</v>
+        <v>139400</v>
       </c>
       <c r="N104">
-        <v>21.4</v>
+        <v>21.1</v>
       </c>
       <c r="O104">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
       <c r="P104">
-        <v>400</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="105">
@@ -5264,22 +5264,22 @@
         <v>-</v>
       </c>
       <c r="C105">
-        <v>4.64</v>
+        <v>4.54</v>
       </c>
       <c r="D105">
-        <v>0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="E105">
-        <v>0.8695652173913043</v>
+        <v>-2.1551724137931036</v>
       </c>
       <c r="F105">
-        <v>4.62</v>
+        <v>4.66</v>
       </c>
       <c r="G105">
         <v>4.7</v>
       </c>
       <c r="H105">
-        <v>4.62</v>
+        <v>4.52</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -5288,22 +5288,22 @@
         <v>0</v>
       </c>
       <c r="K105">
-        <v>6508767</v>
+        <v>15341503</v>
       </c>
       <c r="L105">
-        <v>30310.22646</v>
+        <v>70317.48023999999</v>
       </c>
       <c r="M105">
-        <v>228200</v>
+        <v>65100</v>
       </c>
       <c r="N105">
-        <v>4.64</v>
+        <v>4.52</v>
       </c>
       <c r="O105">
-        <v>4.66</v>
+        <v>4.54</v>
       </c>
       <c r="P105">
-        <v>13200</v>
+        <v>281300</v>
       </c>
     </row>
     <row r="106">
@@ -5314,46 +5314,46 @@
         <v>-</v>
       </c>
       <c r="C106">
-        <v>5.85</v>
+        <v>5.8</v>
       </c>
       <c r="D106">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E106">
-        <v>0.8620689655172413</v>
+        <v>-0.8547008547008547</v>
       </c>
       <c r="F106">
         <v>5.85</v>
       </c>
       <c r="G106">
-        <v>5.9</v>
+        <v>5.95</v>
       </c>
       <c r="H106">
+        <v>5.7</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>240200</v>
+      </c>
+      <c r="L106">
+        <v>1392.78</v>
+      </c>
+      <c r="M106">
+        <v>26900</v>
+      </c>
+      <c r="N106">
+        <v>5.7</v>
+      </c>
+      <c r="O106">
         <v>5.8</v>
       </c>
-      <c r="I106">
-        <v>0</v>
-      </c>
-      <c r="J106">
-        <v>0</v>
-      </c>
-      <c r="K106">
-        <v>104600</v>
-      </c>
-      <c r="L106">
-        <v>610.435</v>
-      </c>
-      <c r="M106">
-        <v>1300</v>
-      </c>
-      <c r="N106">
-        <v>5.85</v>
-      </c>
-      <c r="O106">
-        <v>5.9</v>
-      </c>
       <c r="P106">
-        <v>37100</v>
+        <v>19300</v>
       </c>
     </row>
     <row r="107">
@@ -5364,22 +5364,22 @@
         <v>-</v>
       </c>
       <c r="C107">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="D107">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="E107">
-        <v>-0.9900990099009901</v>
+        <v>-1.5</v>
       </c>
       <c r="F107">
-        <v>4.02</v>
+        <v>4.04</v>
       </c>
       <c r="G107">
         <v>4.04</v>
       </c>
       <c r="H107">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="I107">
         <v>0</v>
@@ -5388,22 +5388,22 @@
         <v>0</v>
       </c>
       <c r="K107">
-        <v>499009</v>
+        <v>1719436</v>
       </c>
       <c r="L107">
-        <v>2002.30424</v>
+        <v>6851.28134</v>
       </c>
       <c r="M107">
-        <v>592700</v>
+        <v>168300</v>
       </c>
       <c r="N107">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="O107">
-        <v>4.02</v>
+        <v>3.96</v>
       </c>
       <c r="P107">
-        <v>37300</v>
+        <v>66400</v>
       </c>
     </row>
     <row r="108">
@@ -5414,46 +5414,46 @@
         <v>-</v>
       </c>
       <c r="C108">
+        <v>4.4</v>
+      </c>
+      <c r="D108">
+        <v>-0.04</v>
+      </c>
+      <c r="E108">
+        <v>-0.9009009009009009</v>
+      </c>
+      <c r="F108">
         <v>4.44</v>
       </c>
-      <c r="D108">
-        <v>-0.06</v>
-      </c>
-      <c r="E108">
-        <v>-1.3333333333333333</v>
-      </c>
-      <c r="F108">
-        <v>4.48</v>
-      </c>
       <c r="G108">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="H108">
+        <v>4.38</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108">
+        <v>6314133</v>
+      </c>
+      <c r="L108">
+        <v>27812.07386</v>
+      </c>
+      <c r="M108">
+        <v>181700</v>
+      </c>
+      <c r="N108">
         <v>4.4</v>
       </c>
-      <c r="I108">
-        <v>0</v>
-      </c>
-      <c r="J108">
-        <v>0</v>
-      </c>
-      <c r="K108">
-        <v>8944234</v>
-      </c>
-      <c r="L108">
-        <v>39711.11982</v>
-      </c>
-      <c r="M108">
-        <v>315100</v>
-      </c>
-      <c r="N108">
+      <c r="O108">
         <v>4.42</v>
       </c>
-      <c r="O108">
-        <v>4.44</v>
-      </c>
       <c r="P108">
-        <v>207900</v>
+        <v>351200</v>
       </c>
     </row>
     <row r="109">
@@ -5464,22 +5464,22 @@
         <v>-</v>
       </c>
       <c r="C109">
-        <v>27</v>
+        <v>26.25</v>
       </c>
       <c r="D109">
-        <v>0.25</v>
+        <v>-0.75</v>
       </c>
       <c r="E109">
-        <v>0.9345794392523364</v>
+        <v>-2.7777777777777777</v>
       </c>
       <c r="F109">
-        <v>27</v>
+        <v>27.25</v>
       </c>
       <c r="G109">
-        <v>27</v>
+        <v>27.25</v>
       </c>
       <c r="H109">
-        <v>26.5</v>
+        <v>26</v>
       </c>
       <c r="I109">
         <v>0</v>
@@ -5488,22 +5488,22 @@
         <v>0</v>
       </c>
       <c r="K109">
-        <v>287202</v>
+        <v>744492</v>
       </c>
       <c r="L109">
-        <v>7707.92875</v>
+        <v>19626.482</v>
       </c>
       <c r="M109">
-        <v>48300</v>
+        <v>158600</v>
       </c>
       <c r="N109">
-        <v>26.75</v>
+        <v>26</v>
       </c>
       <c r="O109">
-        <v>27</v>
+        <v>26.25</v>
       </c>
       <c r="P109">
-        <v>82600</v>
+        <v>17000</v>
       </c>
     </row>
     <row r="110">
@@ -5514,22 +5514,22 @@
         <v>-</v>
       </c>
       <c r="C110">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="D110">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="E110">
-        <v>-1.7543859649122806</v>
+        <v>-2.380952380952381</v>
       </c>
       <c r="F110">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="G110">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="H110">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="I110">
         <v>0</v>
@@ -5538,22 +5538,22 @@
         <v>0</v>
       </c>
       <c r="K110">
-        <v>12142101</v>
+        <v>14374566</v>
       </c>
       <c r="L110">
-        <v>20718.8567</v>
+        <v>23749.7131</v>
       </c>
       <c r="M110">
-        <v>1982600</v>
+        <v>1000500</v>
       </c>
       <c r="N110">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="O110">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="P110">
-        <v>11000</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="111">
@@ -5564,46 +5564,46 @@
         <v>-</v>
       </c>
       <c r="C111">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="D111">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E111">
-        <v>0.9433962264150944</v>
+        <v>-0.9345794392523364</v>
       </c>
       <c r="F111">
+        <v>5.4</v>
+      </c>
+      <c r="G111">
+        <v>5.4</v>
+      </c>
+      <c r="H111">
+        <v>5.2</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>672401</v>
+      </c>
+      <c r="L111">
+        <v>3544.2252999999996</v>
+      </c>
+      <c r="M111">
+        <v>106500</v>
+      </c>
+      <c r="N111">
+        <v>5.2</v>
+      </c>
+      <c r="O111">
         <v>5.3</v>
       </c>
-      <c r="G111">
-        <v>5.35</v>
-      </c>
-      <c r="H111">
-        <v>5.25</v>
-      </c>
-      <c r="I111">
-        <v>0</v>
-      </c>
-      <c r="J111">
-        <v>0</v>
-      </c>
-      <c r="K111">
-        <v>149400</v>
-      </c>
-      <c r="L111">
-        <v>794.34</v>
-      </c>
-      <c r="M111">
-        <v>3000</v>
-      </c>
-      <c r="N111">
-        <v>5.35</v>
-      </c>
-      <c r="O111">
-        <v>5.4</v>
-      </c>
       <c r="P111">
-        <v>39300</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="112">
@@ -5614,22 +5614,22 @@
         <v>-</v>
       </c>
       <c r="C112">
+        <v>26.5</v>
+      </c>
+      <c r="D112">
+        <v>0.75</v>
+      </c>
+      <c r="E112">
+        <v>2.912621359223301</v>
+      </c>
+      <c r="F112">
         <v>25.75</v>
       </c>
-      <c r="D112">
-        <v>0.5</v>
-      </c>
-      <c r="E112">
-        <v>1.9801980198019802</v>
-      </c>
-      <c r="F112">
-        <v>25.25</v>
-      </c>
       <c r="G112">
-        <v>26</v>
+        <v>26.5</v>
       </c>
       <c r="H112">
-        <v>24.3</v>
+        <v>24.9</v>
       </c>
       <c r="I112">
         <v>0</v>
@@ -5638,22 +5638,22 @@
         <v>0</v>
       </c>
       <c r="K112">
-        <v>7651251</v>
+        <v>10258192</v>
       </c>
       <c r="L112">
-        <v>192262.764</v>
+        <v>261849.63265</v>
       </c>
       <c r="M112">
-        <v>34800</v>
+        <v>100</v>
       </c>
       <c r="N112">
-        <v>25.5</v>
+        <v>26.25</v>
       </c>
       <c r="O112">
-        <v>25.75</v>
+        <v>26.5</v>
       </c>
       <c r="P112">
-        <v>84100</v>
+        <v>398000</v>
       </c>
     </row>
     <row r="113">
@@ -5664,16 +5664,16 @@
         <v>-</v>
       </c>
       <c r="C113">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="D113">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="E113">
-        <v>0.7575757575757576</v>
+        <v>-0.7518796992481203</v>
       </c>
       <c r="F113">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="G113">
         <v>13.3</v>
@@ -5688,22 +5688,22 @@
         <v>0</v>
       </c>
       <c r="K113">
-        <v>479502</v>
+        <v>880849</v>
       </c>
       <c r="L113">
-        <v>6331.3506</v>
+        <v>11593.788199999999</v>
       </c>
       <c r="M113">
-        <v>131700</v>
+        <v>94700</v>
       </c>
       <c r="N113">
+        <v>13.1</v>
+      </c>
+      <c r="O113">
         <v>13.2</v>
       </c>
-      <c r="O113">
-        <v>13.3</v>
-      </c>
       <c r="P113">
-        <v>112000</v>
+        <v>149400</v>
       </c>
     </row>
     <row r="114">
@@ -5714,46 +5714,46 @@
         <v>-</v>
       </c>
       <c r="C114">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="D114">
-        <v>0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="E114">
-        <v>2.7027027027027026</v>
+        <v>-1.7543859649122806</v>
       </c>
       <c r="F114">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="G114">
         <v>5.85</v>
       </c>
       <c r="H114">
+        <v>5.45</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>10371281</v>
+      </c>
+      <c r="L114">
+        <v>58481.0857</v>
+      </c>
+      <c r="M114">
+        <v>142200</v>
+      </c>
+      <c r="N114">
         <v>5.6</v>
       </c>
-      <c r="I114">
-        <v>0</v>
-      </c>
-      <c r="J114">
-        <v>0</v>
-      </c>
-      <c r="K114">
-        <v>12325066</v>
-      </c>
-      <c r="L114">
-        <v>70888.591</v>
-      </c>
-      <c r="M114">
-        <v>330100</v>
-      </c>
-      <c r="N114">
+      <c r="O114">
         <v>5.7</v>
       </c>
-      <c r="O114">
-        <v>5.75</v>
-      </c>
       <c r="P114">
-        <v>56900</v>
+        <v>92400</v>
       </c>
     </row>
     <row r="115">
@@ -5764,46 +5764,46 @@
         <v>-</v>
       </c>
       <c r="C115">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="D115">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="E115">
-        <v>0.6896551724137931</v>
+        <v>-0.684931506849315</v>
       </c>
       <c r="F115">
         <v>14.6</v>
       </c>
       <c r="G115">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="H115">
+        <v>14.4</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <v>961868</v>
+      </c>
+      <c r="L115">
+        <v>14016.0407</v>
+      </c>
+      <c r="M115">
+        <v>337200</v>
+      </c>
+      <c r="N115">
+        <v>14.4</v>
+      </c>
+      <c r="O115">
         <v>14.5</v>
       </c>
-      <c r="I115">
-        <v>95000</v>
-      </c>
-      <c r="J115">
-        <v>1385.1</v>
-      </c>
-      <c r="K115">
-        <v>373800</v>
-      </c>
-      <c r="L115">
-        <v>5449.58</v>
-      </c>
-      <c r="M115">
-        <v>171300</v>
-      </c>
-      <c r="N115">
-        <v>14.5</v>
-      </c>
-      <c r="O115">
-        <v>14.6</v>
-      </c>
       <c r="P115">
-        <v>142700</v>
+        <v>46700</v>
       </c>
     </row>
     <row r="116">
@@ -5814,16 +5814,16 @@
         <v>-</v>
       </c>
       <c r="C116">
+        <v>9.55</v>
+      </c>
+      <c r="D116">
+        <v>-0.1</v>
+      </c>
+      <c r="E116">
+        <v>-1.0362694300518134</v>
+      </c>
+      <c r="F116">
         <v>9.65</v>
-      </c>
-      <c r="D116">
-        <v>0.1</v>
-      </c>
-      <c r="E116">
-        <v>1.0471204188481675</v>
-      </c>
-      <c r="F116">
-        <v>9.55</v>
       </c>
       <c r="G116">
         <v>9.65</v>
@@ -5838,22 +5838,22 @@
         <v>0</v>
       </c>
       <c r="K116">
-        <v>35604</v>
+        <v>55132</v>
       </c>
       <c r="L116">
-        <v>341.77340000000004</v>
+        <v>527.8371500000001</v>
       </c>
       <c r="M116">
-        <v>30100</v>
+        <v>5200</v>
       </c>
       <c r="N116">
+        <v>9.55</v>
+      </c>
+      <c r="O116">
         <v>9.6</v>
       </c>
-      <c r="O116">
-        <v>9.65</v>
-      </c>
       <c r="P116">
-        <v>35500</v>
+        <v>20400</v>
       </c>
     </row>
     <row r="117">
@@ -5864,22 +5864,22 @@
         <v>-</v>
       </c>
       <c r="C117">
+        <v>14.5</v>
+      </c>
+      <c r="D117">
+        <v>0.1</v>
+      </c>
+      <c r="E117">
+        <v>0.6944444444444444</v>
+      </c>
+      <c r="F117">
         <v>14.4</v>
       </c>
-      <c r="D117">
-        <v>-0.2</v>
-      </c>
-      <c r="E117">
-        <v>-1.36986301369863</v>
-      </c>
-      <c r="F117">
-        <v>14.6</v>
-      </c>
       <c r="G117">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="H117">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="I117">
         <v>0</v>
@@ -5888,13 +5888,13 @@
         <v>0</v>
       </c>
       <c r="K117">
-        <v>983344</v>
+        <v>222222</v>
       </c>
       <c r="L117">
-        <v>14154.1464</v>
+        <v>3206.4883</v>
       </c>
       <c r="M117">
-        <v>44900</v>
+        <v>40900</v>
       </c>
       <c r="N117">
         <v>14.4</v>
@@ -5903,7 +5903,7 @@
         <v>14.5</v>
       </c>
       <c r="P117">
-        <v>24600</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="118">
@@ -5914,13 +5914,13 @@
         <v>-</v>
       </c>
       <c r="C118">
-        <v>9.7</v>
+        <v>9.55</v>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>-1.5463917525773196</v>
       </c>
       <c r="F118">
         <v>9.7</v>
@@ -5929,31 +5929,31 @@
         <v>9.8</v>
       </c>
       <c r="H118">
+        <v>9.55</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>214000</v>
+      </c>
+      <c r="L118">
+        <v>2062.79</v>
+      </c>
+      <c r="M118">
+        <v>26900</v>
+      </c>
+      <c r="N118">
+        <v>9.55</v>
+      </c>
+      <c r="O118">
         <v>9.65</v>
       </c>
-      <c r="I118">
-        <v>0</v>
-      </c>
-      <c r="J118">
-        <v>0</v>
-      </c>
-      <c r="K118">
-        <v>74000</v>
-      </c>
-      <c r="L118">
-        <v>719.175</v>
-      </c>
-      <c r="M118">
-        <v>17600</v>
-      </c>
-      <c r="N118">
-        <v>9.65</v>
-      </c>
-      <c r="O118">
-        <v>9.7</v>
-      </c>
       <c r="P118">
-        <v>400</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="119">
@@ -5964,19 +5964,19 @@
         <v>-</v>
       </c>
       <c r="C119">
-        <v>9.95</v>
+        <v>9.9</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>-0.5025125628140703</v>
       </c>
       <c r="F119">
         <v>9.95</v>
       </c>
       <c r="G119">
-        <v>10</v>
+        <v>9.95</v>
       </c>
       <c r="H119">
         <v>9.9</v>
@@ -5988,22 +5988,22 @@
         <v>0</v>
       </c>
       <c r="K119">
-        <v>1153621</v>
+        <v>928918</v>
       </c>
       <c r="L119">
-        <v>11490.54515</v>
+        <v>9227.94695</v>
       </c>
       <c r="M119">
-        <v>117100</v>
+        <v>376100</v>
       </c>
       <c r="N119">
+        <v>9.9</v>
+      </c>
+      <c r="O119">
         <v>9.95</v>
       </c>
-      <c r="O119">
-        <v>10</v>
-      </c>
       <c r="P119">
-        <v>135900</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="120">
@@ -6014,22 +6014,22 @@
         <v>-</v>
       </c>
       <c r="C120">
+        <v>187.5</v>
+      </c>
+      <c r="D120">
+        <v>-2.5</v>
+      </c>
+      <c r="E120">
+        <v>-1.3157894736842106</v>
+      </c>
+      <c r="F120">
         <v>190</v>
       </c>
-      <c r="D120">
-        <v>2</v>
-      </c>
-      <c r="E120">
-        <v>1.0638297872340425</v>
-      </c>
-      <c r="F120">
-        <v>188</v>
-      </c>
       <c r="G120">
-        <v>190.5</v>
+        <v>190</v>
       </c>
       <c r="H120">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I120">
         <v>0</v>
@@ -6038,22 +6038,22 @@
         <v>0</v>
       </c>
       <c r="K120">
-        <v>41029</v>
+        <v>36100</v>
       </c>
       <c r="L120">
-        <v>7748.941</v>
+        <v>6775.5</v>
       </c>
       <c r="M120">
-        <v>2200</v>
+        <v>500</v>
       </c>
       <c r="N120">
-        <v>189.5</v>
+        <v>187</v>
       </c>
       <c r="O120">
-        <v>190</v>
+        <v>187.5</v>
       </c>
       <c r="P120">
-        <v>700</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="121">
@@ -6064,22 +6064,22 @@
         <v>-</v>
       </c>
       <c r="C121">
+        <v>4.92</v>
+      </c>
+      <c r="D121">
+        <v>-0.18</v>
+      </c>
+      <c r="E121">
+        <v>-3.5294117647058822</v>
+      </c>
+      <c r="F121">
         <v>5.1</v>
       </c>
-      <c r="D121">
-        <v>-0.35</v>
-      </c>
-      <c r="E121">
-        <v>-6.422018348623853</v>
-      </c>
-      <c r="F121">
-        <v>5.5</v>
-      </c>
       <c r="G121">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="H121">
-        <v>5.05</v>
+        <v>4.88</v>
       </c>
       <c r="I121">
         <v>0</v>
@@ -6088,22 +6088,22 @@
         <v>0</v>
       </c>
       <c r="K121">
-        <v>13855772</v>
+        <v>6649345</v>
       </c>
       <c r="L121">
-        <v>72347.81885</v>
+        <v>33157.456399999995</v>
       </c>
       <c r="M121">
-        <v>141000</v>
+        <v>89800</v>
       </c>
       <c r="N121">
-        <v>5.1</v>
+        <v>4.92</v>
       </c>
       <c r="O121">
-        <v>5.15</v>
+        <v>4.94</v>
       </c>
       <c r="P121">
-        <v>197400</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="122">
@@ -6114,46 +6114,46 @@
         <v>-</v>
       </c>
       <c r="C122">
+        <v>4.66</v>
+      </c>
+      <c r="D122">
+        <v>-0.02</v>
+      </c>
+      <c r="E122">
+        <v>-0.42735042735042733</v>
+      </c>
+      <c r="F122">
+        <v>4.7</v>
+      </c>
+      <c r="G122">
+        <v>4.7</v>
+      </c>
+      <c r="H122">
+        <v>4.64</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>484169</v>
+      </c>
+      <c r="L122">
+        <v>2257.37602</v>
+      </c>
+      <c r="M122">
+        <v>72200</v>
+      </c>
+      <c r="N122">
+        <v>4.66</v>
+      </c>
+      <c r="O122">
         <v>4.68</v>
       </c>
-      <c r="D122">
-        <v>0</v>
-      </c>
-      <c r="E122">
-        <v>0</v>
-      </c>
-      <c r="F122">
-        <v>4.68</v>
-      </c>
-      <c r="G122">
-        <v>4.72</v>
-      </c>
-      <c r="H122">
-        <v>4.68</v>
-      </c>
-      <c r="I122">
-        <v>0</v>
-      </c>
-      <c r="J122">
-        <v>0</v>
-      </c>
-      <c r="K122">
-        <v>236390</v>
-      </c>
-      <c r="L122">
-        <v>1111.30126</v>
-      </c>
-      <c r="M122">
-        <v>83200</v>
-      </c>
-      <c r="N122">
-        <v>4.68</v>
-      </c>
-      <c r="O122">
-        <v>4.7</v>
-      </c>
       <c r="P122">
-        <v>11000</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="123">
@@ -6164,46 +6164,46 @@
         <v>-</v>
       </c>
       <c r="C123">
+        <v>3.78</v>
+      </c>
+      <c r="D123">
+        <v>-0.02</v>
+      </c>
+      <c r="E123">
+        <v>-0.5263157894736842</v>
+      </c>
+      <c r="F123">
         <v>3.8</v>
-      </c>
-      <c r="D123">
-        <v>0.02</v>
-      </c>
-      <c r="E123">
-        <v>0.5291005291005291</v>
-      </c>
-      <c r="F123">
-        <v>3.78</v>
       </c>
       <c r="G123">
         <v>3.82</v>
       </c>
       <c r="H123">
+        <v>3.74</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>7208764</v>
+      </c>
+      <c r="L123">
+        <v>27216.180399999997</v>
+      </c>
+      <c r="M123">
+        <v>35100</v>
+      </c>
+      <c r="N123">
+        <v>3.76</v>
+      </c>
+      <c r="O123">
         <v>3.78</v>
       </c>
-      <c r="I123">
-        <v>0</v>
-      </c>
-      <c r="J123">
-        <v>0</v>
-      </c>
-      <c r="K123">
-        <v>3411133</v>
-      </c>
-      <c r="L123">
-        <v>12949.616039999999</v>
-      </c>
-      <c r="M123">
-        <v>600700</v>
-      </c>
-      <c r="N123">
-        <v>3.78</v>
-      </c>
-      <c r="O123">
-        <v>3.8</v>
-      </c>
       <c r="P123">
-        <v>34700</v>
+        <v>83200</v>
       </c>
     </row>
     <row r="124">
@@ -6214,22 +6214,22 @@
         <v>-</v>
       </c>
       <c r="C124">
+        <v>16.3</v>
+      </c>
+      <c r="D124">
+        <v>-0.8</v>
+      </c>
+      <c r="E124">
+        <v>-4.678362573099415</v>
+      </c>
+      <c r="F124">
         <v>17.1</v>
       </c>
-      <c r="D124">
-        <v>0</v>
-      </c>
-      <c r="E124">
-        <v>0</v>
-      </c>
-      <c r="F124">
+      <c r="G124">
         <v>17.2</v>
       </c>
-      <c r="G124">
-        <v>17.6</v>
-      </c>
       <c r="H124">
-        <v>17</v>
+        <v>16.3</v>
       </c>
       <c r="I124">
         <v>0</v>
@@ -6238,22 +6238,22 @@
         <v>0</v>
       </c>
       <c r="K124">
-        <v>6475566</v>
+        <v>3347661</v>
       </c>
       <c r="L124">
-        <v>112298.1049</v>
+        <v>56075.0762</v>
       </c>
       <c r="M124">
-        <v>9600</v>
+        <v>278600</v>
       </c>
       <c r="N124">
-        <v>17.1</v>
+        <v>16.3</v>
       </c>
       <c r="O124">
-        <v>17.2</v>
+        <v>16.4</v>
       </c>
       <c r="P124">
-        <v>203200</v>
+        <v>16100</v>
       </c>
     </row>
     <row r="125">
@@ -6264,22 +6264,22 @@
         <v>-</v>
       </c>
       <c r="C125">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="D125">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E125">
-        <v>-0.819672131147541</v>
+        <v>-1.6528925619834711</v>
       </c>
       <c r="F125">
         <v>12.1</v>
       </c>
       <c r="G125">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="H125">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="I125">
         <v>0</v>
@@ -6288,22 +6288,22 @@
         <v>0</v>
       </c>
       <c r="K125">
-        <v>2355890</v>
+        <v>1009700</v>
       </c>
       <c r="L125">
-        <v>28786.486800000002</v>
+        <v>12074.69</v>
       </c>
       <c r="M125">
-        <v>139400</v>
+        <v>13600</v>
       </c>
       <c r="N125">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="O125">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="P125">
-        <v>93900</v>
+        <v>112400</v>
       </c>
     </row>
     <row r="126">
@@ -6317,10 +6317,10 @@
         <v>10.6</v>
       </c>
       <c r="D126">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E126">
-        <v>0.9523809523809523</v>
+        <v>0</v>
       </c>
       <c r="F126">
         <v>10.5</v>
@@ -6338,22 +6338,22 @@
         <v>0</v>
       </c>
       <c r="K126">
-        <v>212100</v>
+        <v>192061</v>
       </c>
       <c r="L126">
-        <v>2265.44</v>
+        <v>2042.771</v>
       </c>
       <c r="M126">
-        <v>43700</v>
+        <v>100</v>
       </c>
       <c r="N126">
         <v>10.6</v>
       </c>
       <c r="O126">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="P126">
-        <v>10900</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="127">
@@ -6364,46 +6364,46 @@
         <v>-</v>
       </c>
       <c r="C127">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E127">
-        <v>0</v>
+        <v>0.6211180124223602</v>
       </c>
       <c r="F127">
         <v>16.1</v>
       </c>
       <c r="G127">
+        <v>16.6</v>
+      </c>
+      <c r="H127">
+        <v>16</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>11447811</v>
+      </c>
+      <c r="L127">
+        <v>186660.108</v>
+      </c>
+      <c r="M127">
+        <v>233300</v>
+      </c>
+      <c r="N127">
         <v>16.2</v>
       </c>
-      <c r="H127">
-        <v>15.9</v>
-      </c>
-      <c r="I127">
-        <v>0</v>
-      </c>
-      <c r="J127">
-        <v>0</v>
-      </c>
-      <c r="K127">
-        <v>5819119</v>
-      </c>
-      <c r="L127">
-        <v>93254.035</v>
-      </c>
-      <c r="M127">
-        <v>71300</v>
-      </c>
-      <c r="N127">
-        <v>16.1</v>
-      </c>
       <c r="O127">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P127">
-        <v>308200</v>
+        <v>56300</v>
       </c>
     </row>
     <row r="128">
@@ -6414,19 +6414,19 @@
         <v>-</v>
       </c>
       <c r="C128">
-        <v>38.75</v>
+        <v>39.25</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E128">
-        <v>0</v>
+        <v>1.2903225806451613</v>
       </c>
       <c r="F128">
         <v>38.75</v>
       </c>
       <c r="G128">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="H128">
         <v>38.75</v>
@@ -6438,22 +6438,22 @@
         <v>0</v>
       </c>
       <c r="K128">
-        <v>38115</v>
+        <v>99200</v>
       </c>
       <c r="L128">
-        <v>1482.779</v>
+        <v>3887.9</v>
       </c>
       <c r="M128">
-        <v>1700</v>
+        <v>1500</v>
       </c>
       <c r="N128">
-        <v>38.75</v>
+        <v>39.25</v>
       </c>
       <c r="O128">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="P128">
-        <v>12900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="129">
@@ -6464,22 +6464,22 @@
         <v>-</v>
       </c>
       <c r="C129">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="D129">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="E129">
-        <v>-0.9174311926605505</v>
+        <v>-1.8518518518518519</v>
       </c>
       <c r="F129">
+        <v>1.09</v>
+      </c>
+      <c r="G129">
         <v>1.1</v>
       </c>
-      <c r="G129">
-        <v>1.11</v>
-      </c>
       <c r="H129">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="I129">
         <v>0</v>
@@ -6488,22 +6488,22 @@
         <v>0</v>
       </c>
       <c r="K129">
-        <v>7667372</v>
+        <v>3380823</v>
       </c>
       <c r="L129">
-        <v>8363.61527</v>
+        <v>3632.71161</v>
       </c>
       <c r="M129">
-        <v>264500</v>
+        <v>187800</v>
       </c>
       <c r="N129">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="O129">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="P129">
-        <v>65500</v>
+        <v>141500</v>
       </c>
     </row>
     <row r="130">
@@ -6514,19 +6514,19 @@
         <v>-</v>
       </c>
       <c r="C130">
-        <v>9.15</v>
+        <v>9.1</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>-0.546448087431694</v>
       </c>
       <c r="F130">
-        <v>9.25</v>
+        <v>9.2</v>
       </c>
       <c r="G130">
-        <v>9.25</v>
+        <v>9.2</v>
       </c>
       <c r="H130">
         <v>9.1</v>
@@ -6538,22 +6538,22 @@
         <v>0</v>
       </c>
       <c r="K130">
-        <v>303310</v>
+        <v>167443</v>
       </c>
       <c r="L130">
-        <v>2783.03955</v>
+        <v>1532.055</v>
       </c>
       <c r="M130">
-        <v>40000</v>
+        <v>138100</v>
       </c>
       <c r="N130">
-        <v>9.15</v>
+        <v>9.1</v>
       </c>
       <c r="O130">
         <v>9.2</v>
       </c>
       <c r="P130">
-        <v>27900</v>
+        <v>77400</v>
       </c>
     </row>
     <row r="131">
@@ -6564,46 +6564,46 @@
         <v>-</v>
       </c>
       <c r="C131">
+        <v>8.35</v>
+      </c>
+      <c r="D131">
+        <v>-0.1</v>
+      </c>
+      <c r="E131">
+        <v>-1.183431952662722</v>
+      </c>
+      <c r="F131">
         <v>8.45</v>
       </c>
-      <c r="D131">
-        <v>-0.15</v>
-      </c>
-      <c r="E131">
-        <v>-1.744186046511628</v>
-      </c>
-      <c r="F131">
-        <v>8.6</v>
-      </c>
       <c r="G131">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="H131">
+        <v>8.3</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>807688</v>
+      </c>
+      <c r="L131">
+        <v>6758.32425</v>
+      </c>
+      <c r="M131">
+        <v>2000</v>
+      </c>
+      <c r="N131">
+        <v>8.35</v>
+      </c>
+      <c r="O131">
         <v>8.4</v>
       </c>
-      <c r="I131">
-        <v>0</v>
-      </c>
-      <c r="J131">
-        <v>0</v>
-      </c>
-      <c r="K131">
-        <v>1346001</v>
-      </c>
-      <c r="L131">
-        <v>11400.1986</v>
-      </c>
-      <c r="M131">
-        <v>1400</v>
-      </c>
-      <c r="N131">
-        <v>8.45</v>
-      </c>
-      <c r="O131">
-        <v>8.5</v>
-      </c>
       <c r="P131">
-        <v>51200</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="132">
@@ -6614,22 +6614,22 @@
         <v>-</v>
       </c>
       <c r="C132">
-        <v>22.7</v>
+        <v>22.4</v>
       </c>
       <c r="D132">
-        <v>0.5</v>
+        <v>-0.3</v>
       </c>
       <c r="E132">
-        <v>2.2522522522522523</v>
+        <v>-1.3215859030837005</v>
       </c>
       <c r="F132">
-        <v>22.2</v>
+        <v>22.8</v>
       </c>
       <c r="G132">
-        <v>22.9</v>
+        <v>23.2</v>
       </c>
       <c r="H132">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="I132">
         <v>0</v>
@@ -6638,22 +6638,22 @@
         <v>0</v>
       </c>
       <c r="K132">
-        <v>2985565</v>
+        <v>2641636</v>
       </c>
       <c r="L132">
-        <v>67133.51</v>
+        <v>59639.3338</v>
       </c>
       <c r="M132">
-        <v>600</v>
+        <v>8700</v>
       </c>
       <c r="N132">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="O132">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="P132">
-        <v>8000</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="133">
@@ -6664,19 +6664,19 @@
         <v>-</v>
       </c>
       <c r="C133">
+        <v>11.3</v>
+      </c>
+      <c r="D133">
+        <v>-0.3</v>
+      </c>
+      <c r="E133">
+        <v>-2.586206896551724</v>
+      </c>
+      <c r="F133">
         <v>11.6</v>
       </c>
-      <c r="D133">
-        <v>0.2</v>
-      </c>
-      <c r="E133">
-        <v>1.7543859649122806</v>
-      </c>
-      <c r="F133">
-        <v>11.4</v>
-      </c>
       <c r="G133">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="H133">
         <v>11.3</v>
@@ -6688,22 +6688,22 @@
         <v>0</v>
       </c>
       <c r="K133">
-        <v>6892972</v>
+        <v>6985163</v>
       </c>
       <c r="L133">
-        <v>79342.97859999999</v>
+        <v>79887.012</v>
       </c>
       <c r="M133">
-        <v>792500</v>
+        <v>1015800</v>
       </c>
       <c r="N133">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="O133">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="P133">
-        <v>248100</v>
+        <v>242000</v>
       </c>
     </row>
     <row r="134">
@@ -6714,22 +6714,22 @@
         <v>-</v>
       </c>
       <c r="C134">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="D134">
         <v>-0.2</v>
       </c>
       <c r="E134">
-        <v>-1.4705882352941178</v>
+        <v>-1.492537313432836</v>
       </c>
       <c r="F134">
-        <v>13.6</v>
+        <v>13.4</v>
       </c>
       <c r="G134">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="H134">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="I134">
         <v>0</v>
@@ -6738,22 +6738,22 @@
         <v>0</v>
       </c>
       <c r="K134">
-        <v>1934281</v>
+        <v>2950828</v>
       </c>
       <c r="L134">
-        <v>26024.160399999997</v>
+        <v>39079.1244</v>
       </c>
       <c r="M134">
-        <v>275600</v>
+        <v>314800</v>
       </c>
       <c r="N134">
-        <v>13.4</v>
+        <v>13.1</v>
       </c>
       <c r="O134">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="P134">
-        <v>137500</v>
+        <v>182000</v>
       </c>
     </row>
     <row r="135">
@@ -6764,46 +6764,46 @@
         <v>-</v>
       </c>
       <c r="C135">
+        <v>8.1</v>
+      </c>
+      <c r="D135">
+        <v>-0.05</v>
+      </c>
+      <c r="E135">
+        <v>-0.6134969325153374</v>
+      </c>
+      <c r="F135">
         <v>8.15</v>
       </c>
-      <c r="D135">
-        <v>0</v>
-      </c>
-      <c r="E135">
-        <v>0</v>
-      </c>
-      <c r="F135">
-        <v>8.25</v>
-      </c>
       <c r="G135">
-        <v>8.25</v>
+        <v>8.15</v>
       </c>
       <c r="H135">
+        <v>8.05</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>219041</v>
+      </c>
+      <c r="L135">
+        <v>1775.27415</v>
+      </c>
+      <c r="M135">
+        <v>35900</v>
+      </c>
+      <c r="N135">
         <v>8.1</v>
       </c>
-      <c r="I135">
-        <v>0</v>
-      </c>
-      <c r="J135">
-        <v>0</v>
-      </c>
-      <c r="K135">
-        <v>121777</v>
-      </c>
-      <c r="L135">
-        <v>995.21645</v>
-      </c>
-      <c r="M135">
-        <v>12100</v>
-      </c>
-      <c r="N135">
+      <c r="O135">
         <v>8.15</v>
       </c>
-      <c r="O135">
-        <v>8.2</v>
-      </c>
       <c r="P135">
-        <v>28700</v>
+        <v>48900</v>
       </c>
     </row>
     <row r="136">
@@ -6817,10 +6817,10 @@
         <v>9.05</v>
       </c>
       <c r="D136">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="E136">
-        <v>-0.5494505494505495</v>
+        <v>0</v>
       </c>
       <c r="F136">
         <v>9.05</v>
@@ -6829,31 +6829,31 @@
         <v>9.1</v>
       </c>
       <c r="H136">
+        <v>9.05</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>106500</v>
+      </c>
+      <c r="L136">
+        <v>964.465</v>
+      </c>
+      <c r="M136">
+        <v>185200</v>
+      </c>
+      <c r="N136">
         <v>9</v>
       </c>
-      <c r="I136">
-        <v>0</v>
-      </c>
-      <c r="J136">
-        <v>0</v>
-      </c>
-      <c r="K136">
-        <v>91100</v>
-      </c>
-      <c r="L136">
-        <v>824.39</v>
-      </c>
-      <c r="M136">
-        <v>12100</v>
-      </c>
-      <c r="N136">
+      <c r="O136">
         <v>9.05</v>
       </c>
-      <c r="O136">
-        <v>9.1</v>
-      </c>
       <c r="P136">
-        <v>7400</v>
+        <v>100</v>
       </c>
     </row>
     <row r="137">
@@ -6864,23 +6864,23 @@
         <v>-</v>
       </c>
       <c r="C137">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="D137">
         <v>0.02</v>
       </c>
       <c r="E137">
-        <v>0.7874015748031497</v>
+        <v>0.78125</v>
       </c>
       <c r="F137">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G137">
+        <v>2.64</v>
+      </c>
+      <c r="H137">
         <v>2.56</v>
       </c>
-      <c r="H137">
-        <v>2.54</v>
-      </c>
       <c r="I137">
         <v>0</v>
       </c>
@@ -6888,22 +6888,22 @@
         <v>0</v>
       </c>
       <c r="K137">
-        <v>1955738</v>
+        <v>12764393</v>
       </c>
       <c r="L137">
-        <v>4972.2472800000005</v>
+        <v>33242.3026</v>
       </c>
       <c r="M137">
-        <v>325900</v>
+        <v>513200</v>
       </c>
       <c r="N137">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O137">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="P137">
-        <v>974100</v>
+        <v>78400</v>
       </c>
     </row>
     <row r="138">
@@ -6914,46 +6914,46 @@
         <v>-</v>
       </c>
       <c r="C138">
+        <v>1.16</v>
+      </c>
+      <c r="D138">
+        <v>-0.01</v>
+      </c>
+      <c r="E138">
+        <v>-0.8547008547008547</v>
+      </c>
+      <c r="F138">
         <v>1.17</v>
       </c>
-      <c r="D138">
-        <v>0.01</v>
-      </c>
-      <c r="E138">
-        <v>0.8620689655172413</v>
-      </c>
-      <c r="F138">
+      <c r="G138">
+        <v>1.17</v>
+      </c>
+      <c r="H138">
+        <v>1.14</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>5021700</v>
+      </c>
+      <c r="L138">
+        <v>5813.152</v>
+      </c>
+      <c r="M138">
+        <v>674300</v>
+      </c>
+      <c r="N138">
+        <v>1.14</v>
+      </c>
+      <c r="O138">
         <v>1.16</v>
       </c>
-      <c r="G138">
-        <v>1.18</v>
-      </c>
-      <c r="H138">
-        <v>1.15</v>
-      </c>
-      <c r="I138">
-        <v>0</v>
-      </c>
-      <c r="J138">
-        <v>0</v>
-      </c>
-      <c r="K138">
-        <v>2418600</v>
-      </c>
-      <c r="L138">
-        <v>2811.27308</v>
-      </c>
-      <c r="M138">
-        <v>213000</v>
-      </c>
-      <c r="N138">
-        <v>1.16</v>
-      </c>
-      <c r="O138">
-        <v>1.17</v>
-      </c>
       <c r="P138">
-        <v>183700</v>
+        <v>54100</v>
       </c>
     </row>
     <row r="139">
@@ -6964,46 +6964,46 @@
         <v>-</v>
       </c>
       <c r="C139">
+        <v>8</v>
+      </c>
+      <c r="D139">
+        <v>-0.1</v>
+      </c>
+      <c r="E139">
+        <v>-1.2345679012345678</v>
+      </c>
+      <c r="F139">
         <v>8.1</v>
       </c>
-      <c r="D139">
-        <v>0.05</v>
-      </c>
-      <c r="E139">
-        <v>0.6211180124223602</v>
-      </c>
-      <c r="F139">
+      <c r="G139">
+        <v>8.1</v>
+      </c>
+      <c r="H139">
+        <v>7.95</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>4719758</v>
+      </c>
+      <c r="L139">
+        <v>37730.91895000001</v>
+      </c>
+      <c r="M139">
+        <v>5300</v>
+      </c>
+      <c r="N139">
+        <v>8</v>
+      </c>
+      <c r="O139">
         <v>8.05</v>
       </c>
-      <c r="G139">
-        <v>8.15</v>
-      </c>
-      <c r="H139">
-        <v>8</v>
-      </c>
-      <c r="I139">
-        <v>0</v>
-      </c>
-      <c r="J139">
-        <v>0</v>
-      </c>
-      <c r="K139">
-        <v>3759691</v>
-      </c>
-      <c r="L139">
-        <v>30312.5005</v>
-      </c>
-      <c r="M139">
-        <v>178500</v>
-      </c>
-      <c r="N139">
-        <v>8.05</v>
-      </c>
-      <c r="O139">
-        <v>8.1</v>
-      </c>
       <c r="P139">
-        <v>88100</v>
+        <v>86100</v>
       </c>
     </row>
     <row r="140">
@@ -7014,22 +7014,22 @@
         <v>-</v>
       </c>
       <c r="C140">
-        <v>12.7</v>
+        <v>12.3</v>
       </c>
       <c r="D140">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="E140">
-        <v>-0.78125</v>
+        <v>-3.1496062992125986</v>
       </c>
       <c r="F140">
         <v>12.9</v>
       </c>
       <c r="G140">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
       <c r="H140">
-        <v>12.7</v>
+        <v>12.2</v>
       </c>
       <c r="I140">
         <v>0</v>
@@ -7038,22 +7038,22 @@
         <v>0</v>
       </c>
       <c r="K140">
-        <v>374109</v>
+        <v>418570</v>
       </c>
       <c r="L140">
-        <v>4841.7169</v>
+        <v>5225.6003</v>
       </c>
       <c r="M140">
-        <v>47200</v>
+        <v>4200</v>
       </c>
       <c r="N140">
-        <v>12.7</v>
+        <v>12.3</v>
       </c>
       <c r="O140">
-        <v>12.9</v>
+        <v>12.4</v>
       </c>
       <c r="P140">
-        <v>19300</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="141">
@@ -7064,19 +7064,19 @@
         <v>-</v>
       </c>
       <c r="C141">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="D141">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="E141">
-        <v>-1.8518518518518519</v>
+        <v>0.9433962264150944</v>
       </c>
       <c r="F141">
         <v>5.35</v>
       </c>
       <c r="G141">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="H141">
         <v>5.3</v>
@@ -7088,22 +7088,22 @@
         <v>0</v>
       </c>
       <c r="K141">
-        <v>475369</v>
+        <v>1300400</v>
       </c>
       <c r="L141">
-        <v>2521.35165</v>
+        <v>6996.27</v>
       </c>
       <c r="M141">
-        <v>11000</v>
+        <v>36200</v>
       </c>
       <c r="N141">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="O141">
-        <v>5.35</v>
+        <v>5.4</v>
       </c>
       <c r="P141">
-        <v>62700</v>
+        <v>97600</v>
       </c>
     </row>
     <row r="142">
@@ -7114,46 +7114,46 @@
         <v>-</v>
       </c>
       <c r="C142">
-        <v>4.74</v>
+        <v>4.72</v>
       </c>
       <c r="D142">
         <v>-0.02</v>
       </c>
       <c r="E142">
-        <v>-0.42016806722689076</v>
+        <v>-0.4219409282700422</v>
       </c>
       <c r="F142">
+        <v>4.74</v>
+      </c>
+      <c r="G142">
         <v>4.76</v>
       </c>
-      <c r="G142">
-        <v>4.78</v>
-      </c>
       <c r="H142">
+        <v>4.68</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+      <c r="J142">
+        <v>0</v>
+      </c>
+      <c r="K142">
+        <v>312520</v>
+      </c>
+      <c r="L142">
+        <v>1475.8164</v>
+      </c>
+      <c r="M142">
+        <v>14100</v>
+      </c>
+      <c r="N142">
+        <v>4.68</v>
+      </c>
+      <c r="O142">
         <v>4.72</v>
       </c>
-      <c r="I142">
-        <v>0</v>
-      </c>
-      <c r="J142">
-        <v>0</v>
-      </c>
-      <c r="K142">
-        <v>113009</v>
-      </c>
-      <c r="L142">
-        <v>536.1805</v>
-      </c>
-      <c r="M142">
-        <v>44900</v>
-      </c>
-      <c r="N142">
-        <v>4.72</v>
-      </c>
-      <c r="O142">
-        <v>4.74</v>
-      </c>
       <c r="P142">
-        <v>29200</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="143">
@@ -7164,22 +7164,22 @@
         <v>-</v>
       </c>
       <c r="C143">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="D143">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="E143">
-        <v>1.3333333333333333</v>
+        <v>3.9473684210526314</v>
       </c>
       <c r="F143">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="G143">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="H143">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="I143">
         <v>0</v>
@@ -7188,22 +7188,22 @@
         <v>0</v>
       </c>
       <c r="K143">
-        <v>9092247</v>
+        <v>70070759</v>
       </c>
       <c r="L143">
-        <v>13766.77546</v>
+        <v>110143.7982</v>
       </c>
       <c r="M143">
-        <v>56000</v>
+        <v>761400</v>
       </c>
       <c r="N143">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="O143">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="P143">
-        <v>1261600</v>
+        <v>477800</v>
       </c>
     </row>
     <row r="144">
@@ -7214,13 +7214,13 @@
         <v>-</v>
       </c>
       <c r="C144">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="D144">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="E144">
-        <v>0.6451612903225806</v>
+        <v>-0.6410256410256411</v>
       </c>
       <c r="F144">
         <v>15.6</v>
@@ -7229,31 +7229,31 @@
         <v>15.6</v>
       </c>
       <c r="H144">
+        <v>15.4</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+      <c r="J144">
+        <v>0</v>
+      </c>
+      <c r="K144">
+        <v>292715</v>
+      </c>
+      <c r="L144">
+        <v>4538.0253</v>
+      </c>
+      <c r="M144">
+        <v>162200</v>
+      </c>
+      <c r="N144">
+        <v>15.4</v>
+      </c>
+      <c r="O144">
         <v>15.5</v>
       </c>
-      <c r="I144">
-        <v>0</v>
-      </c>
-      <c r="J144">
-        <v>0</v>
-      </c>
-      <c r="K144">
-        <v>230347</v>
-      </c>
-      <c r="L144">
-        <v>3590.2223</v>
-      </c>
-      <c r="M144">
-        <v>170800</v>
-      </c>
-      <c r="N144">
-        <v>15.5</v>
-      </c>
-      <c r="O144">
-        <v>15.6</v>
-      </c>
       <c r="P144">
-        <v>41300</v>
+        <v>14100</v>
       </c>
     </row>
     <row r="145">
@@ -7264,22 +7264,22 @@
         <v>-</v>
       </c>
       <c r="C145">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="D145">
-        <v>-0.02</v>
+        <v>-0.14</v>
       </c>
       <c r="E145">
-        <v>-0.5952380952380952</v>
+        <v>-4.191616766467066</v>
       </c>
       <c r="F145">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="G145">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="H145">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="I145">
         <v>0</v>
@@ -7288,22 +7288,22 @@
         <v>0</v>
       </c>
       <c r="K145">
-        <v>5129884</v>
+        <v>4714316</v>
       </c>
       <c r="L145">
-        <v>17331.42158</v>
+        <v>15424.980800000001</v>
       </c>
       <c r="M145">
-        <v>494300</v>
+        <v>148500</v>
       </c>
       <c r="N145">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="O145">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="P145">
-        <v>73100</v>
+        <v>125200</v>
       </c>
     </row>
     <row r="146">
@@ -7323,14 +7323,14 @@
         <v>0</v>
       </c>
       <c r="F146">
+        <v>7.85</v>
+      </c>
+      <c r="G146">
+        <v>7.9</v>
+      </c>
+      <c r="H146">
         <v>7.8</v>
       </c>
-      <c r="G146">
-        <v>7.85</v>
-      </c>
-      <c r="H146">
-        <v>7.75</v>
-      </c>
       <c r="I146">
         <v>0</v>
       </c>
@@ -7338,13 +7338,13 @@
         <v>0</v>
       </c>
       <c r="K146">
-        <v>267235</v>
+        <v>315710</v>
       </c>
       <c r="L146">
-        <v>2089.61475</v>
+        <v>2477.894</v>
       </c>
       <c r="M146">
-        <v>101600</v>
+        <v>279900</v>
       </c>
       <c r="N146">
         <v>7.8</v>
@@ -7353,7 +7353,7 @@
         <v>7.85</v>
       </c>
       <c r="P146">
-        <v>22000</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="147">
@@ -7364,19 +7364,19 @@
         <v>-</v>
       </c>
       <c r="C147">
-        <v>8.55</v>
+        <v>8.5</v>
       </c>
       <c r="D147">
-        <v>-0.25</v>
+        <v>-0.05</v>
       </c>
       <c r="E147">
-        <v>-2.840909090909091</v>
+        <v>-0.5847953216374269</v>
       </c>
       <c r="F147">
-        <v>8.85</v>
+        <v>8.6</v>
       </c>
       <c r="G147">
-        <v>8.85</v>
+        <v>8.6</v>
       </c>
       <c r="H147">
         <v>8.45</v>
@@ -7388,22 +7388,22 @@
         <v>0</v>
       </c>
       <c r="K147">
-        <v>2876859</v>
+        <v>774630</v>
       </c>
       <c r="L147">
-        <v>24813.46125</v>
+        <v>6613.41365</v>
       </c>
       <c r="M147">
-        <v>10200</v>
+        <v>169900</v>
       </c>
       <c r="N147">
+        <v>8.5</v>
+      </c>
+      <c r="O147">
         <v>8.55</v>
       </c>
-      <c r="O147">
-        <v>8.6</v>
-      </c>
       <c r="P147">
-        <v>37800</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="148">
@@ -7414,22 +7414,22 @@
         <v>-</v>
       </c>
       <c r="C148">
+        <v>5.35</v>
+      </c>
+      <c r="D148">
+        <v>-0.2</v>
+      </c>
+      <c r="E148">
+        <v>-3.6036036036036037</v>
+      </c>
+      <c r="F148">
         <v>5.55</v>
       </c>
-      <c r="D148">
-        <v>-0.05</v>
-      </c>
-      <c r="E148">
-        <v>-0.8928571428571429</v>
-      </c>
-      <c r="F148">
-        <v>5.6</v>
-      </c>
       <c r="G148">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="H148">
-        <v>5.45</v>
+        <v>5.3</v>
       </c>
       <c r="I148">
         <v>0</v>
@@ -7438,22 +7438,22 @@
         <v>0</v>
       </c>
       <c r="K148">
-        <v>746211</v>
+        <v>1626542</v>
       </c>
       <c r="L148">
-        <v>4115.07705</v>
+        <v>8852.3157</v>
       </c>
       <c r="M148">
-        <v>700</v>
+        <v>130700</v>
       </c>
       <c r="N148">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O148">
-        <v>5.55</v>
+        <v>5.35</v>
       </c>
       <c r="P148">
-        <v>79200</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="149">
@@ -7464,46 +7464,46 @@
         <v>-</v>
       </c>
       <c r="C149">
+        <v>4.08</v>
+      </c>
+      <c r="D149">
+        <v>-0.04</v>
+      </c>
+      <c r="E149">
+        <v>-0.970873786407767</v>
+      </c>
+      <c r="F149">
+        <v>4.1</v>
+      </c>
+      <c r="G149">
         <v>4.12</v>
       </c>
-      <c r="D149">
-        <v>0</v>
-      </c>
-      <c r="E149">
-        <v>0</v>
-      </c>
-      <c r="F149">
-        <v>4.12</v>
-      </c>
-      <c r="G149">
-        <v>4.14</v>
-      </c>
       <c r="H149">
+        <v>4.06</v>
+      </c>
+      <c r="I149">
+        <v>0</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+      <c r="K149">
+        <v>2547336</v>
+      </c>
+      <c r="L149">
+        <v>10409.716</v>
+      </c>
+      <c r="M149">
+        <v>941700</v>
+      </c>
+      <c r="N149">
+        <v>4.06</v>
+      </c>
+      <c r="O149">
         <v>4.08</v>
       </c>
-      <c r="I149">
-        <v>0</v>
-      </c>
-      <c r="J149">
-        <v>0</v>
-      </c>
-      <c r="K149">
-        <v>1427266</v>
-      </c>
-      <c r="L149">
-        <v>5862.84376</v>
-      </c>
-      <c r="M149">
-        <v>86100</v>
-      </c>
-      <c r="N149">
-        <v>4.1</v>
-      </c>
-      <c r="O149">
-        <v>4.12</v>
-      </c>
       <c r="P149">
-        <v>9300</v>
+        <v>36700</v>
       </c>
     </row>
     <row r="150">
@@ -7514,22 +7514,22 @@
         <v>-</v>
       </c>
       <c r="C150">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="D150">
         <v>-0.3</v>
       </c>
       <c r="E150">
-        <v>-2.5</v>
+        <v>-2.5641025641025643</v>
       </c>
       <c r="F150">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="G150">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="H150">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="I150">
         <v>0</v>
@@ -7538,22 +7538,22 @@
         <v>0</v>
       </c>
       <c r="K150">
-        <v>6565095</v>
+        <v>5889162</v>
       </c>
       <c r="L150">
-        <v>77325.6161</v>
+        <v>67839.6539</v>
       </c>
       <c r="M150">
-        <v>801500</v>
+        <v>80800</v>
       </c>
       <c r="N150">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="O150">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="P150">
-        <v>357100</v>
+        <v>185700</v>
       </c>
     </row>
     <row r="151">
@@ -7564,46 +7564,46 @@
         <v>-</v>
       </c>
       <c r="C151">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="D151">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E151">
-        <v>0</v>
+        <v>-1.075268817204301</v>
       </c>
       <c r="F151">
         <v>18.6</v>
       </c>
       <c r="G151">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="H151">
+        <v>18.4</v>
+      </c>
+      <c r="I151">
+        <v>0</v>
+      </c>
+      <c r="J151">
+        <v>0</v>
+      </c>
+      <c r="K151">
+        <v>329012</v>
+      </c>
+      <c r="L151">
+        <v>6102.0424</v>
+      </c>
+      <c r="M151">
+        <v>50700</v>
+      </c>
+      <c r="N151">
+        <v>18.4</v>
+      </c>
+      <c r="O151">
         <v>18.5</v>
       </c>
-      <c r="I151">
-        <v>0</v>
-      </c>
-      <c r="J151">
-        <v>0</v>
-      </c>
-      <c r="K151">
-        <v>584418</v>
-      </c>
-      <c r="L151">
-        <v>10880.5927</v>
-      </c>
-      <c r="M151">
-        <v>1000</v>
-      </c>
-      <c r="N151">
-        <v>18.6</v>
-      </c>
-      <c r="O151">
-        <v>18.7</v>
-      </c>
       <c r="P151">
-        <v>92100</v>
+        <v>9800</v>
       </c>
     </row>
     <row r="152">
@@ -7614,22 +7614,22 @@
         <v>-</v>
       </c>
       <c r="C152">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="D152">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="E152">
-        <v>0</v>
+        <v>-2.097902097902098</v>
       </c>
       <c r="F152">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="G152">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="H152">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="I152">
         <v>0</v>
@@ -7638,22 +7638,22 @@
         <v>0</v>
       </c>
       <c r="K152">
-        <v>16048321</v>
+        <v>25496898</v>
       </c>
       <c r="L152">
-        <v>22934.85749</v>
+        <v>36099.40327</v>
       </c>
       <c r="M152">
-        <v>41800</v>
+        <v>5794800</v>
       </c>
       <c r="N152">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="O152">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="P152">
-        <v>1763100</v>
+        <v>123000</v>
       </c>
     </row>
     <row r="153">
@@ -7667,19 +7667,19 @@
         <v>18.3</v>
       </c>
       <c r="D153">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="E153">
-        <v>3.977272727272727</v>
+        <v>0</v>
       </c>
       <c r="F153">
-        <v>17.5</v>
+        <v>18.3</v>
       </c>
       <c r="G153">
         <v>18.4</v>
       </c>
       <c r="H153">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="I153">
         <v>0</v>
@@ -7688,22 +7688,22 @@
         <v>0</v>
       </c>
       <c r="K153">
-        <v>1457528</v>
+        <v>1139365</v>
       </c>
       <c r="L153">
-        <v>26301.2235</v>
+        <v>20800.8516</v>
       </c>
       <c r="M153">
-        <v>5300</v>
+        <v>100</v>
       </c>
       <c r="N153">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="O153">
         <v>18.3</v>
       </c>
       <c r="P153">
-        <v>106500</v>
+        <v>76900</v>
       </c>
     </row>
   </sheetData>
